--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAA0C65-F59D-40AF-B6BE-40E2AB18FD4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE74423-9FCF-4A3C-9AFD-8BC3C4115F09}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="550" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="17385" windowHeight="11595" tabRatio="550" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -33,11 +33,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="450">
   <si>
     <t>CharacterId</t>
   </si>
   <si>
+    <t>Attack</t>
+  </si>
+  <si>
     <t>CHAR_001</t>
   </si>
   <si>
@@ -122,9 +125,15 @@
     <t>EssenceGrade</t>
   </si>
   <si>
+    <t>SKILL_P001</t>
+  </si>
+  <si>
     <t>Passive</t>
   </si>
   <si>
+    <t>IronWill</t>
+  </si>
+  <si>
     <t>Increase defense at battle start</t>
   </si>
   <si>
@@ -134,6 +143,9 @@
     <t>OnBattleStart</t>
   </si>
   <si>
+    <t>SKILL_U001</t>
+  </si>
+  <si>
     <t>Unique</t>
   </si>
   <si>
@@ -146,6 +158,9 @@
     <t>RANGE_001</t>
   </si>
   <si>
+    <t>SKILL_C001</t>
+  </si>
+  <si>
     <t>Common</t>
   </si>
   <si>
@@ -158,6 +173,9 @@
     <t>RANGE_002</t>
   </si>
   <si>
+    <t>SKILL_E001</t>
+  </si>
+  <si>
     <t>Essence</t>
   </si>
   <si>
@@ -1019,9 +1037,6 @@
     <t>PATTERN_AGGRESSIVE</t>
   </si>
   <si>
-    <t>MON_003</t>
-  </si>
-  <si>
     <t>Orc</t>
   </si>
   <si>
@@ -1029,9 +1044,6 @@
   </si>
   <si>
     <t>PATTERN_HEAVY</t>
-  </si>
-  <si>
-    <t>MON_004</t>
   </si>
   <si>
     <t>ForestSpirit</t>
@@ -1311,27 +1323,81 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_P001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_U001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IronWill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Archer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_C001</t>
+    <t>MON_001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_E001</t>
+    <t>MON_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_C002</t>
+  </si>
+  <si>
+    <t>WeakeningShot</t>
+  </si>
+  <si>
+    <t>Reduce enemy defense</t>
+  </si>
+  <si>
+    <t>EFFECT_DEF_DOWN</t>
+  </si>
+  <si>
+    <t>SKILL_U002</t>
+  </si>
+  <si>
+    <t>HealingLight</t>
+  </si>
+  <si>
+    <t>Restore HP to ally</t>
+  </si>
+  <si>
+    <t>RANGE_003</t>
+  </si>
+  <si>
+    <t>EFFECT_HEAL</t>
+  </si>
+  <si>
+    <t>액션 타입</t>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1547,8 +1613,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -1608,11 +1677,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1913,425 +1988,425 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="3">
         <v>100</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4">
+        <v>50</v>
+      </c>
+      <c r="G3" s="4">
+        <v>3</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>650</v>
+      </c>
+      <c r="D4" s="3">
+        <v>80</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="4">
+        <v>120</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>428</v>
+      </c>
+      <c r="C5" s="15">
+        <v>750</v>
+      </c>
+      <c r="D5" s="15">
+        <v>120</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="16">
+        <v>100</v>
+      </c>
+      <c r="G5" s="16">
+        <v>4</v>
+      </c>
+      <c r="H5" s="16">
+        <v>1</v>
+      </c>
+      <c r="I5" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="3">
+        <v>100</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="4">
+        <v>50</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>650</v>
+      </c>
+      <c r="D7" s="3">
+        <v>80</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4">
+        <v>120</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>421</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="C8" s="15">
+        <v>750</v>
+      </c>
+      <c r="D8" s="15">
+        <v>120</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="16">
         <v>100</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3">
-        <v>50</v>
-      </c>
-      <c r="G3" s="3">
-        <v>3</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="G8" s="16">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
-        <v>650</v>
-      </c>
-      <c r="D4" s="2">
-        <v>80</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="3">
-        <v>120</v>
-      </c>
-      <c r="G4" s="3">
-        <v>2</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="19" t="s">
-        <v>423</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>427</v>
-      </c>
-      <c r="C5" s="14">
-        <v>750</v>
-      </c>
-      <c r="D5" s="14">
-        <v>120</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="15">
-        <v>100</v>
-      </c>
-      <c r="G5" s="15">
-        <v>4</v>
-      </c>
-      <c r="H5" s="15">
-        <v>1</v>
-      </c>
-      <c r="I5" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="2">
-        <v>100</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="3">
-        <v>50</v>
-      </c>
-      <c r="G6" s="3">
-        <v>3</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2">
-        <v>650</v>
-      </c>
-      <c r="D7" s="2">
-        <v>80</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="3">
-        <v>120</v>
-      </c>
-      <c r="G7" s="3">
-        <v>2</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="14">
-        <v>750</v>
-      </c>
-      <c r="D8" s="14">
-        <v>120</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="15">
-        <v>100</v>
-      </c>
-      <c r="G8" s="15">
-        <v>4</v>
-      </c>
-      <c r="H8" s="15">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="H8" s="16">
+        <v>1</v>
+      </c>
+      <c r="I8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2359,80 +2434,80 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="J1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="G2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="I2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="J2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E3">
         <v>0.7</v>
@@ -2455,16 +2530,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E4">
         <v>0.3</v>
@@ -2487,16 +2562,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B5" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E5">
         <v>0.6</v>
@@ -2519,16 +2594,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C6" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E6">
         <v>0.2</v>
@@ -2551,16 +2626,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B7" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C7" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E7">
         <v>0.2</v>
@@ -2583,16 +2658,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B8" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C8" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2615,16 +2690,16 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B9" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C9" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -2647,16 +2722,16 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B10" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C10" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -2679,16 +2754,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B11" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C11" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2711,16 +2786,16 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C12" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D12" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E12">
         <v>0.5</v>
@@ -2743,16 +2818,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C13" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2775,16 +2850,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D14" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E14">
         <v>0.5</v>
@@ -2814,236 +2889,330 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="2" max="2" width="9.625" customWidth="1"/>
     <col min="3" max="3" width="12.375" customWidth="1"/>
-    <col min="4" max="4" width="29.25" customWidth="1"/>
-    <col min="5" max="5" width="9.75" customWidth="1"/>
+    <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.25" customWidth="1"/>
     <col min="7" max="7" width="6.75" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="6.75" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34.5" customWidth="1"/>
-    <col min="10" max="11" width="15.375" customWidth="1"/>
-    <col min="12" max="12" width="13.75" customWidth="1"/>
+    <col min="10" max="10" width="35.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I1" t="s">
-        <v>254</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="B1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="G1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="J2" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="K2" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>424</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="M2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="B3" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="C3" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="E3" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="F3" s="18">
+        <v>0</v>
+      </c>
+      <c r="G3" s="18">
+        <v>0</v>
+      </c>
+      <c r="H3" s="18">
+        <v>0</v>
+      </c>
+      <c r="I3" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="J3" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="3">
+      <c r="L3" s="18"/>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="18">
         <v>3</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="18">
         <v>20</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="18">
         <v>120</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="I4" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="18">
+        <v>2</v>
+      </c>
+      <c r="G5" s="18">
+        <v>10</v>
+      </c>
+      <c r="H5" s="18">
+        <v>80</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="18">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18">
+        <v>0</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>15</v>
+      </c>
+      <c r="H7" s="1">
+        <v>60</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3">
-        <v>80</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
-        <v>429</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="1">
-        <v>1</v>
+      <c r="C8" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1">
+        <v>18</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3066,116 +3235,116 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="B5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="4">
         <v>3</v>
       </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="b">
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3205,248 +3374,248 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
-        <v>3</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="J5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="D7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
         <v>5</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="K7" s="2" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -3469,194 +3638,194 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>130</v>
+      <c r="A1" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>58</v>
+      <c r="A2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="A3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="4">
         <v>1.2</v>
       </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.1</v>
       </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="A5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.8</v>
       </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="A6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="A7" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="2">
         <v>0.2</v>
       </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" s="1">
+      <c r="A8" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" s="2">
         <v>0.15</v>
       </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B9" s="1">
+      <c r="A9" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B9" s="2">
         <v>0.08</v>
       </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B10" s="1">
+      <c r="A10" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B10" s="2">
         <v>0.25</v>
       </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B11" s="1">
+      <c r="A11" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B11" s="2">
         <v>50</v>
       </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
+      <c r="A13" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3681,184 +3850,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>136</v>
+      <c r="A1" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>142</v>
+      <c r="A2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="A3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="2">
         <v>999999</v>
       </c>
-      <c r="F3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="b">
+      <c r="F3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="A4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="2">
         <v>99999</v>
       </c>
-      <c r="F4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="b">
+      <c r="F4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="A5" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="2">
         <v>100</v>
       </c>
-      <c r="F5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="b">
+      <c r="F5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="A6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="2">
         <v>9999</v>
       </c>
-      <c r="F6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="b">
+      <c r="F6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="A7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="2">
         <v>99999</v>
       </c>
-      <c r="F7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="b">
+      <c r="F7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3886,132 +4055,132 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" t="s">
         <v>184</v>
       </c>
-      <c r="C4" t="s">
-        <v>178</v>
-      </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F4" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C5" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E5" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F5" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -4044,122 +4213,122 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="J1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="K1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="L1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="M1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="N1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="J2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="K2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="L2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="M2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="N2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="J3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -4168,39 +4337,39 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="J4" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -4209,39 +4378,39 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D5" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -4250,39 +4419,39 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D6" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="G6" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="J6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -4291,39 +4460,39 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D7" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -4332,39 +4501,39 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D8" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="J8" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="K8">
         <v>30</v>
@@ -4373,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4398,142 +4567,142 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>62</v>
+      <c r="F4" s="18" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B5" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C5" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C6" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D6" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D7" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -4559,74 +4728,74 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="H1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="H2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G3">
         <v>100</v>
@@ -4637,22 +4806,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C4" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D4" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E4" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -4663,22 +4832,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" t="s">
         <v>293</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>294</v>
       </c>
-      <c r="D5" t="s">
-        <v>287</v>
-      </c>
-      <c r="E5" t="s">
-        <v>288</v>
-      </c>
       <c r="F5" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="G5">
         <v>20</v>
@@ -4689,22 +4858,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B6" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E6" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F6" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -4715,22 +4884,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B7" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C7" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D7" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -4741,22 +4910,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B8" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C8" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D8" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E8" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G8">
         <v>50</v>
@@ -4767,22 +4936,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B9" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C9" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D9" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F9" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="G9">
         <v>20</v>
@@ -4793,22 +4962,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" t="s">
         <v>308</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
         <v>309</v>
       </c>
-      <c r="C10" t="s">
-        <v>298</v>
-      </c>
-      <c r="D10" t="s">
-        <v>302</v>
-      </c>
-      <c r="E10" t="s">
-        <v>303</v>
-      </c>
       <c r="F10" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -4839,148 +5008,148 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>320</v>
+      <c r="A3" s="21" t="s">
+        <v>429</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>324</v>
+      <c r="A4" s="21" t="s">
+        <v>430</v>
       </c>
       <c r="B4" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D4">
         <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="F4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>328</v>
+      <c r="A5" s="21" t="s">
+        <v>431</v>
       </c>
       <c r="B5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D5">
         <v>300</v>
       </c>
       <c r="E5" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="F5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>332</v>
+      <c r="A6" s="21" t="s">
+        <v>432</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D6">
         <v>400</v>
       </c>
       <c r="E6" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F6" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>336</v>
+      <c r="A7" s="21" t="s">
+        <v>433</v>
       </c>
       <c r="B7" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C7" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D7">
         <v>1000</v>
       </c>
       <c r="E7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5001,77 +5170,77 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H3">
         <v>100</v>
@@ -5079,25 +5248,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E4" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F4">
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H4">
         <v>200</v>
@@ -5105,25 +5274,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C5" t="s">
+        <v>365</v>
+      </c>
+      <c r="D5" t="s">
         <v>359</v>
       </c>
-      <c r="B5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C5" t="s">
-        <v>361</v>
-      </c>
-      <c r="D5" t="s">
-        <v>355</v>
-      </c>
       <c r="E5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H5">
         <v>50</v>
@@ -5131,25 +5300,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B6" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H6">
         <v>150</v>
@@ -5157,25 +5326,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B7" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D7" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E7" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H7">
         <v>30</v>
@@ -5204,59 +5373,59 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="G2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -5273,13 +5442,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -5296,13 +5465,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -5319,13 +5488,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B6" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C6" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -5342,13 +5511,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C7" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D7">
         <v>1</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE74423-9FCF-4A3C-9AFD-8BC3C4115F09}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1F56B5-2FC8-444F-A08B-3BBB53EA0B71}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="17385" windowHeight="11595" tabRatio="550" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="17385" windowHeight="11595" tabRatio="550" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="452">
   <si>
     <t>CharacterId</t>
   </si>
@@ -1398,6 +1398,14 @@
   </si>
   <si>
     <t>ActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EFFECT_BURN;EFFECT_DAMAGE_FIRE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entrance</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3056,8 +3064,8 @@
       <c r="I4" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="18" t="s">
-        <v>263</v>
+      <c r="J4" s="23" t="s">
+        <v>450</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18" t="s">
@@ -4785,8 +4793,8 @@
       <c r="B3" t="s">
         <v>291</v>
       </c>
-      <c r="C3" t="s">
-        <v>292</v>
+      <c r="C3" s="21" t="s">
+        <v>451</v>
       </c>
       <c r="D3" t="s">
         <v>293</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1F56B5-2FC8-444F-A08B-3BBB53EA0B71}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3810B442-E6B8-4FE0-BB71-86B4C1E499E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="30" windowWidth="17385" windowHeight="11595" tabRatio="550" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,21 +19,22 @@
     <sheet name="EventChoice" sheetId="4" r:id="rId4"/>
     <sheet name="Fragment" sheetId="5" r:id="rId5"/>
     <sheet name="Map" sheetId="6" r:id="rId6"/>
-    <sheet name="Monster" sheetId="7" r:id="rId7"/>
-    <sheet name="Quest" sheetId="8" r:id="rId8"/>
-    <sheet name="RewardTable" sheetId="10" r:id="rId9"/>
-    <sheet name="RewardTableEntry" sheetId="11" r:id="rId10"/>
-    <sheet name="SkillMaster" sheetId="13" r:id="rId11"/>
-    <sheet name="SkillRange" sheetId="9" r:id="rId12"/>
-    <sheet name="StatusEffect" sheetId="12" r:id="rId13"/>
-    <sheet name="SkillEffect" sheetId="14" r:id="rId14"/>
+    <sheet name="BattleMap" sheetId="15" r:id="rId7"/>
+    <sheet name="Monster" sheetId="7" r:id="rId8"/>
+    <sheet name="Quest" sheetId="8" r:id="rId9"/>
+    <sheet name="RewardTable" sheetId="10" r:id="rId10"/>
+    <sheet name="RewardTableEntry" sheetId="11" r:id="rId11"/>
+    <sheet name="SkillMaster" sheetId="13" r:id="rId12"/>
+    <sheet name="SkillRange" sheetId="9" r:id="rId13"/>
+    <sheet name="StatusEffect" sheetId="12" r:id="rId14"/>
+    <sheet name="SkillEffect" sheetId="14" r:id="rId15"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="487">
   <si>
     <t>CharacterId</t>
   </si>
@@ -1406,14 +1407,127 @@
   </si>
   <si>
     <t>Entrance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투맵ID</t>
+  </si>
+  <si>
+    <t>이름접미사</t>
+  </si>
+  <si>
+    <t>몬스터ID</t>
+  </si>
+  <si>
+    <t>점유칸1</t>
+  </si>
+  <si>
+    <t>점유칸2</t>
+  </si>
+  <si>
+    <t>점유칸3</t>
+  </si>
+  <si>
+    <t>점유칸4</t>
+  </si>
+  <si>
+    <t>BATTLEMAP_001</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>슬라임 2마리 맵</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>BATTLEMAP_002</t>
+  </si>
+  <si>
+    <t>가시늑대 2마리와 슬라임 1마리</t>
+  </si>
+  <si>
+    <t>BATTLEMAP_003</t>
+  </si>
+  <si>
+    <t>MON_006</t>
+  </si>
+  <si>
+    <t>망령검사 1마리와 화약벌레 2마리</t>
+  </si>
+  <si>
+    <t>MON_008</t>
+  </si>
+  <si>
+    <t>BATTLEMAP_004</t>
+  </si>
+  <si>
+    <t>MON_007</t>
+  </si>
+  <si>
+    <t>골렘 1마리와 정령A 1마리와 정령B 1마리</t>
+  </si>
+  <si>
+    <t>MON_003</t>
+  </si>
+  <si>
+    <t>MON_004</t>
+  </si>
+  <si>
+    <t>BATTLEMAP_005</t>
+  </si>
+  <si>
+    <t>MON_009</t>
+  </si>
+  <si>
+    <t>까마귀 2마리, 슬라임 1마리, 화약벌레 1마리</t>
+  </si>
+  <si>
+    <t>BattleMapId</t>
+  </si>
+  <si>
+    <t>NameSuffix</t>
+  </si>
+  <si>
+    <t>MonsterId</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cell1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cell2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cell3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cell4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투맵ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EventId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1457,16 +1571,43 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1609,8 +1750,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1620,8 +1776,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1697,14 +1856,252 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF94A5DF"/>
+          <bgColor rgb="FF94A5DF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color rgb="FF6182D6"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF6182D6"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border>
+        <top style="thin">
+          <color rgb="FF6182D6"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF6182D6"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <border>
+        <left/>
+        <right/>
+        <top style="medium">
+          <color rgb="FF6182D6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF6182D6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thick">
+          <color rgb="FFFFFFFF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thick">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD7DFF4"/>
+          <bgColor rgb="FFD7DFF4"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFFFFFFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFFFFFFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFFFFFFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFFFFFFF"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFFFFFFF"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="12"/>
+      <tableStyleElement type="totalRow" dxfId="11"/>
+      <tableStyleElement type="firstColumn" dxfId="10"/>
+      <tableStyleElement type="lastColumn" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+    </tableStyle>
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFF7CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2424,6 +2821,188 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.25" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="21.25" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C5" t="s">
+        <v>390</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6" t="s">
+        <v>393</v>
+      </c>
+      <c r="C6" t="s">
+        <v>304</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2895,7 +3474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3230,7 +3809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3363,7 +3942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3633,7 +4212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4722,19 +5301,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="4" max="4" width="16.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12.125" customWidth="1"/>
     <col min="7" max="7" width="13.625" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="10" max="10" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -4744,23 +5324,29 @@
       <c r="C1" t="s">
         <v>276</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>485</v>
+      </c>
+      <c r="F1" t="s">
         <v>277</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>278</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>279</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>280</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>282</v>
       </c>
@@ -4770,23 +5356,29 @@
       <c r="C2" t="s">
         <v>284</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="32" t="s">
+        <v>477</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="F2" t="s">
         <v>285</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>286</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>287</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>288</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>290</v>
       </c>
@@ -4796,23 +5388,29 @@
       <c r="C3" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
         <v>293</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>294</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>42</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>100</v>
       </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>295</v>
       </c>
@@ -4822,23 +5420,29 @@
       <c r="C4" t="s">
         <v>297</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>293</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>294</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>42</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>50</v>
       </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>298</v>
       </c>
@@ -4848,23 +5452,29 @@
       <c r="C5" t="s">
         <v>300</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
         <v>293</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>294</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>301</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>20</v>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>302</v>
       </c>
@@ -4874,23 +5484,29 @@
       <c r="C6" t="s">
         <v>304</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
         <v>293</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>294</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>305</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>10</v>
       </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>306</v>
       </c>
@@ -4900,23 +5516,29 @@
       <c r="C7" t="s">
         <v>292</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
         <v>308</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>309</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>42</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>100</v>
       </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>310</v>
       </c>
@@ -4926,23 +5548,29 @@
       <c r="C8" t="s">
         <v>297</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
         <v>308</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>309</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>42</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>50</v>
       </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>312</v>
       </c>
@@ -4952,23 +5580,29 @@
       <c r="C9" t="s">
         <v>300</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
         <v>308</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>309</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>301</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>20</v>
       </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>314</v>
       </c>
@@ -4978,19 +5612,25 @@
       <c r="C10" t="s">
         <v>304</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
         <v>308</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>309</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>305</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>10</v>
       </c>
-      <c r="H10" t="b">
+      <c r="J10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5002,6 +5642,550 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D571884F-4B2F-4650-81A7-3EAB94FD7E74}">
+  <dimension ref="A1:Q23"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="41.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
+        <v>452</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>453</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>454</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>455</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>456</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>457</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+    </row>
+    <row r="2" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>477</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>478</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>480</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>481</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>483</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="3" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
+        <v>459</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>460</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" s="27">
+        <v>27</v>
+      </c>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+    </row>
+    <row r="4" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="28" t="s">
+        <v>459</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>462</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="D4" s="27">
+        <v>29</v>
+      </c>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="29"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+    </row>
+    <row r="5" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="D5" s="27">
+        <v>23</v>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="29" t="s">
+        <v>464</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+    </row>
+    <row r="6" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>460</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="27">
+        <v>26</v>
+      </c>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="29"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>462</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="D7" s="27">
+        <v>34</v>
+      </c>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="29"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27" t="s">
+        <v>466</v>
+      </c>
+      <c r="D8" s="27">
+        <v>28</v>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="29" t="s">
+        <v>467</v>
+      </c>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>460</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>468</v>
+      </c>
+      <c r="D9" s="27">
+        <v>31</v>
+      </c>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="29"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>468</v>
+      </c>
+      <c r="D10" s="27">
+        <v>35</v>
+      </c>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="29"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27" t="s">
+        <v>470</v>
+      </c>
+      <c r="D11" s="27">
+        <v>28</v>
+      </c>
+      <c r="E11" s="27">
+        <v>29</v>
+      </c>
+      <c r="F11" s="27">
+        <v>33</v>
+      </c>
+      <c r="G11" s="27">
+        <v>34</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>471</v>
+      </c>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27" t="s">
+        <v>472</v>
+      </c>
+      <c r="D12" s="27">
+        <v>25</v>
+      </c>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="29"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="D13" s="27">
+        <v>26</v>
+      </c>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="29"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>460</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="D14" s="27">
+        <v>21</v>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>462</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="D15" s="27">
+        <v>30</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="29"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="D16" s="27">
+        <v>33</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="29"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27" t="s">
+        <v>468</v>
+      </c>
+      <c r="D17" s="27">
+        <v>32</v>
+      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="29"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L1:N1"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5161,7 +6345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5363,186 +6547,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.25" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
-    <col min="4" max="4" width="21.25" customWidth="1"/>
-    <col min="5" max="5" width="21.5" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E1" t="s">
-        <v>379</v>
-      </c>
-      <c r="F1" t="s">
-        <v>380</v>
-      </c>
-      <c r="G1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F2" t="s">
-        <v>387</v>
-      </c>
-      <c r="G2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C3" t="s">
-        <v>390</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B4" t="s">
-        <v>391</v>
-      </c>
-      <c r="C4" t="s">
-        <v>390</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B5" t="s">
-        <v>392</v>
-      </c>
-      <c r="C5" t="s">
-        <v>390</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B6" t="s">
-        <v>393</v>
-      </c>
-      <c r="C6" t="s">
-        <v>304</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>188</v>
-      </c>
-      <c r="B7" t="s">
-        <v>394</v>
-      </c>
-      <c r="C7" t="s">
-        <v>297</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
 </file>
--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9E1868-79FB-49B9-A8B0-57380DFE8570}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D2AFE2-4540-443B-BA94-265AA6DF98B4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="17385" windowHeight="11595" tabRatio="550" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="17385" windowHeight="11595" tabRatio="550" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2938" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2938" uniqueCount="1103">
   <si>
     <t>Attack</t>
   </si>
@@ -1907,62 +1907,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>Strike</t>
-  </si>
-  <si>
-    <t>Pierce</t>
-  </si>
-  <si>
-    <t>Thorns</t>
-  </si>
-  <si>
-    <t>Weaken</t>
-  </si>
-  <si>
-    <t>Multi</t>
-  </si>
-  <si>
-    <t>Vulnerable</t>
-  </si>
-  <si>
-    <t>Haste</t>
-  </si>
-  <si>
-    <t>Strength</t>
-  </si>
-  <si>
     <t>Move</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Armor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strike</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pierce</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weaken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Poison</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Heal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strength</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3658,6 +3607,34 @@
   </si>
   <si>
     <t>S_Ability_12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player Party</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy Party</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_Recharge;E_Cleanse</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4559,7 +4536,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="14" t="s">
-        <v>1079</v>
+        <v>1064</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>568</v>
@@ -4593,7 +4570,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="14" t="s">
-        <v>1080</v>
+        <v>1065</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>570</v>
@@ -4627,7 +4604,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="14" t="s">
-        <v>1081</v>
+        <v>1066</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>572</v>
@@ -4869,206 +4846,206 @@
         <v>14</v>
       </c>
       <c r="C1" s="22" t="s">
+        <v>688</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>689</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>690</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>691</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>692</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>693</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>694</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>695</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>696</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>698</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>699</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>700</v>
+      </c>
+      <c r="P1" s="22" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q1" s="22" t="s">
+        <v>702</v>
+      </c>
+      <c r="R1" s="22" t="s">
         <v>703</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="S1" s="22" t="s">
         <v>704</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="T1" s="22" t="s">
         <v>705</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="U1" s="22" t="s">
         <v>706</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="V1" s="22" t="s">
         <v>707</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="W1" s="22" t="s">
         <v>708</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="X1" s="22" t="s">
         <v>709</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="Y1" s="22" t="s">
         <v>710</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>711</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="AA1" s="22" t="s">
         <v>712</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="AB1" s="22" t="s">
         <v>713</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="AC1" s="22" t="s">
         <v>714</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="AD1" s="22" t="s">
         <v>715</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="AE1" s="22" t="s">
         <v>716</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="AF1" s="22" t="s">
         <v>717</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="AG1" s="22" t="s">
         <v>718</v>
-      </c>
-      <c r="S1" s="22" t="s">
-        <v>719</v>
-      </c>
-      <c r="T1" s="22" t="s">
-        <v>720</v>
-      </c>
-      <c r="U1" s="22" t="s">
-        <v>721</v>
-      </c>
-      <c r="V1" s="22" t="s">
-        <v>722</v>
-      </c>
-      <c r="W1" s="22" t="s">
-        <v>723</v>
-      </c>
-      <c r="X1" s="22" t="s">
-        <v>724</v>
-      </c>
-      <c r="Y1" s="22" t="s">
-        <v>725</v>
-      </c>
-      <c r="Z1" s="22" t="s">
-        <v>726</v>
-      </c>
-      <c r="AA1" s="22" t="s">
-        <v>727</v>
-      </c>
-      <c r="AB1" s="22" t="s">
-        <v>728</v>
-      </c>
-      <c r="AC1" s="22" t="s">
-        <v>729</v>
-      </c>
-      <c r="AD1" s="22" t="s">
-        <v>730</v>
-      </c>
-      <c r="AE1" s="22" t="s">
-        <v>731</v>
-      </c>
-      <c r="AF1" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="AG1" s="22" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="2" spans="1:33">
       <c r="A2" s="23" t="s">
+        <v>719</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>721</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>722</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>723</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>725</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>727</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>728</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>729</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>730</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>731</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>732</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>733</v>
+      </c>
+      <c r="P2" s="23" t="s">
         <v>734</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="Q2" s="23" t="s">
         <v>735</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="R2" s="23" t="s">
         <v>736</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="S2" s="23" t="s">
         <v>737</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="T2" s="23" t="s">
         <v>738</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="U2" s="23" t="s">
         <v>739</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="V2" s="23" t="s">
         <v>740</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="W2" s="23" t="s">
         <v>741</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="X2" s="23" t="s">
         <v>742</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="Y2" s="23" t="s">
         <v>743</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="Z2" s="23" t="s">
         <v>744</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="AA2" s="23" t="s">
         <v>745</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="AB2" s="23" t="s">
         <v>746</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="AC2" s="23" t="s">
         <v>747</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="AD2" s="23" t="s">
         <v>748</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="AE2" s="23" t="s">
         <v>749</v>
       </c>
-      <c r="Q2" s="23" t="s">
+      <c r="AF2" s="23" t="s">
         <v>750</v>
       </c>
-      <c r="R2" s="23" t="s">
+      <c r="AG2" s="23" t="s">
         <v>751</v>
-      </c>
-      <c r="S2" s="23" t="s">
-        <v>752</v>
-      </c>
-      <c r="T2" s="23" t="s">
-        <v>753</v>
-      </c>
-      <c r="U2" s="23" t="s">
-        <v>754</v>
-      </c>
-      <c r="V2" s="23" t="s">
-        <v>755</v>
-      </c>
-      <c r="W2" s="23" t="s">
-        <v>756</v>
-      </c>
-      <c r="X2" s="23" t="s">
-        <v>757</v>
-      </c>
-      <c r="Y2" s="23" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z2" s="23" t="s">
-        <v>759</v>
-      </c>
-      <c r="AA2" s="23" t="s">
-        <v>760</v>
-      </c>
-      <c r="AB2" s="23" t="s">
-        <v>761</v>
-      </c>
-      <c r="AC2" s="23" t="s">
-        <v>762</v>
-      </c>
-      <c r="AD2" s="23" t="s">
-        <v>763</v>
-      </c>
-      <c r="AE2" s="23" t="s">
-        <v>764</v>
-      </c>
-      <c r="AF2" s="23" t="s">
-        <v>765</v>
-      </c>
-      <c r="AG2" s="23" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="3" spans="1:33">
       <c r="A3" s="12" t="s">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>768</v>
+        <v>753</v>
       </c>
       <c r="C3" s="13">
         <v>1</v>
@@ -5166,10 +5143,10 @@
     </row>
     <row r="4" spans="1:33">
       <c r="A4" s="12" t="s">
-        <v>769</v>
+        <v>754</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="C4" s="13">
         <v>0</v>
@@ -5181,10 +5158,10 @@
         <v>415</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="H4" s="13">
         <v>0</v>
@@ -5267,10 +5244,10 @@
     </row>
     <row r="5" spans="1:33">
       <c r="A5" s="12" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>774</v>
+        <v>759</v>
       </c>
       <c r="C5" s="13">
         <v>1</v>
@@ -5282,10 +5259,10 @@
         <v>415</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="H5" s="13">
         <v>0</v>
@@ -5368,10 +5345,10 @@
     </row>
     <row r="6" spans="1:33">
       <c r="A6" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="C6" s="13">
         <v>0</v>
@@ -5383,22 +5360,22 @@
         <v>415</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="J6" s="34" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="K6" s="34" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="L6" s="13">
         <v>0</v>
@@ -5469,10 +5446,10 @@
     </row>
     <row r="7" spans="1:33">
       <c r="A7" s="12" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="C7" s="13">
         <v>1</v>
@@ -5484,22 +5461,22 @@
         <v>415</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="J7" s="34" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="K7" s="34" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="L7" s="13">
         <v>0</v>
@@ -5570,10 +5547,10 @@
     </row>
     <row r="8" spans="1:33">
       <c r="A8" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="C8" s="13">
         <v>0</v>
@@ -5585,34 +5562,34 @@
         <v>415</v>
       </c>
       <c r="F8" s="34" t="s">
+        <v>756</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>757</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>762</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>763</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>764</v>
+      </c>
+      <c r="K8" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="L8" s="34" t="s">
+        <v>770</v>
+      </c>
+      <c r="M8" s="34" t="s">
         <v>771</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="N8" s="34" t="s">
         <v>772</v>
       </c>
-      <c r="H8" s="34" t="s">
-        <v>777</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>778</v>
-      </c>
-      <c r="J8" s="34" t="s">
-        <v>779</v>
-      </c>
-      <c r="K8" s="34" t="s">
-        <v>780</v>
-      </c>
-      <c r="L8" s="34" t="s">
-        <v>785</v>
-      </c>
-      <c r="M8" s="34" t="s">
-        <v>786</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>787</v>
-      </c>
       <c r="O8" s="34" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="P8" s="13">
         <v>0</v>
@@ -5671,10 +5648,10 @@
     </row>
     <row r="9" spans="1:33">
       <c r="A9" s="12" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="C9" s="13">
         <v>1</v>
@@ -5686,34 +5663,34 @@
         <v>415</v>
       </c>
       <c r="F9" s="34" t="s">
+        <v>756</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>757</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>762</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>763</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>764</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>770</v>
+      </c>
+      <c r="M9" s="34" t="s">
         <v>771</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="N9" s="34" t="s">
         <v>772</v>
       </c>
-      <c r="H9" s="34" t="s">
-        <v>777</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>778</v>
-      </c>
-      <c r="J9" s="34" t="s">
-        <v>779</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>780</v>
-      </c>
-      <c r="L9" s="34" t="s">
-        <v>785</v>
-      </c>
-      <c r="M9" s="34" t="s">
-        <v>786</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>787</v>
-      </c>
       <c r="O9" s="34" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="P9" s="13">
         <v>0</v>
@@ -5772,10 +5749,10 @@
     </row>
     <row r="10" spans="1:33">
       <c r="A10" s="12" t="s">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="C10" s="13">
         <v>0</v>
@@ -5787,22 +5764,22 @@
         <v>415</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="L10" s="13">
         <v>0</v>
@@ -5873,10 +5850,10 @@
     </row>
     <row r="11" spans="1:33">
       <c r="A11" s="12" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="C11" s="13">
         <v>1</v>
@@ -5888,22 +5865,22 @@
         <v>415</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="K11" s="34" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="L11" s="13">
         <v>0</v>
@@ -5974,46 +5951,46 @@
     </row>
     <row r="12" spans="1:33">
       <c r="A12" s="12" t="s">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
       <c r="C12" s="13">
         <v>0</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="F12" s="34" t="s">
+        <v>764</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>788</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>789</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>790</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>778</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>756</v>
+      </c>
+      <c r="L12" s="34" t="s">
         <v>779</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>803</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>804</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>805</v>
-      </c>
-      <c r="J12" s="34" t="s">
-        <v>793</v>
-      </c>
-      <c r="K12" s="34" t="s">
-        <v>771</v>
-      </c>
-      <c r="L12" s="34" t="s">
-        <v>794</v>
       </c>
       <c r="M12" s="34" t="s">
         <v>392</v>
       </c>
       <c r="N12" s="34" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="O12" s="34" t="s">
         <v>415</v>
@@ -6022,37 +5999,37 @@
         <v>412</v>
       </c>
       <c r="Q12" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="R12" s="34" t="s">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="S12" s="34" t="s">
+        <v>781</v>
+      </c>
+      <c r="T12" s="34" t="s">
+        <v>757</v>
+      </c>
+      <c r="U12" s="34" t="s">
+        <v>780</v>
+      </c>
+      <c r="V12" s="34" t="s">
+        <v>792</v>
+      </c>
+      <c r="W12" s="34" t="s">
+        <v>793</v>
+      </c>
+      <c r="X12" s="34" t="s">
+        <v>794</v>
+      </c>
+      <c r="Y12" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="Z12" s="34" t="s">
+        <v>795</v>
+      </c>
+      <c r="AA12" s="34" t="s">
         <v>796</v>
-      </c>
-      <c r="T12" s="34" t="s">
-        <v>772</v>
-      </c>
-      <c r="U12" s="34" t="s">
-        <v>795</v>
-      </c>
-      <c r="V12" s="34" t="s">
-        <v>807</v>
-      </c>
-      <c r="W12" s="34" t="s">
-        <v>808</v>
-      </c>
-      <c r="X12" s="34" t="s">
-        <v>809</v>
-      </c>
-      <c r="Y12" s="34" t="s">
-        <v>780</v>
-      </c>
-      <c r="Z12" s="34" t="s">
-        <v>810</v>
-      </c>
-      <c r="AA12" s="34" t="s">
-        <v>811</v>
       </c>
       <c r="AB12" s="12">
         <v>0</v>
@@ -6075,46 +6052,46 @@
     </row>
     <row r="13" spans="1:33">
       <c r="A13" s="12" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="C13" s="13">
         <v>1</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="F13" s="34" t="s">
+        <v>764</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>788</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>789</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>790</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>778</v>
+      </c>
+      <c r="K13" s="34" t="s">
+        <v>756</v>
+      </c>
+      <c r="L13" s="34" t="s">
         <v>779</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>803</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>804</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>805</v>
-      </c>
-      <c r="J13" s="34" t="s">
-        <v>793</v>
-      </c>
-      <c r="K13" s="34" t="s">
-        <v>771</v>
-      </c>
-      <c r="L13" s="34" t="s">
-        <v>794</v>
       </c>
       <c r="M13" s="34" t="s">
         <v>392</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="O13" s="34" t="s">
         <v>415</v>
@@ -6123,37 +6100,37 @@
         <v>412</v>
       </c>
       <c r="Q13" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="R13" s="34" t="s">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="S13" s="34" t="s">
+        <v>781</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>757</v>
+      </c>
+      <c r="U13" s="34" t="s">
+        <v>780</v>
+      </c>
+      <c r="V13" s="34" t="s">
+        <v>792</v>
+      </c>
+      <c r="W13" s="34" t="s">
+        <v>793</v>
+      </c>
+      <c r="X13" s="34" t="s">
+        <v>794</v>
+      </c>
+      <c r="Y13" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="Z13" s="34" t="s">
+        <v>795</v>
+      </c>
+      <c r="AA13" s="34" t="s">
         <v>796</v>
-      </c>
-      <c r="T13" s="34" t="s">
-        <v>772</v>
-      </c>
-      <c r="U13" s="34" t="s">
-        <v>795</v>
-      </c>
-      <c r="V13" s="34" t="s">
-        <v>807</v>
-      </c>
-      <c r="W13" s="34" t="s">
-        <v>808</v>
-      </c>
-      <c r="X13" s="34" t="s">
-        <v>809</v>
-      </c>
-      <c r="Y13" s="34" t="s">
-        <v>780</v>
-      </c>
-      <c r="Z13" s="34" t="s">
-        <v>810</v>
-      </c>
-      <c r="AA13" s="34" t="s">
-        <v>811</v>
       </c>
       <c r="AB13" s="12">
         <v>0</v>
@@ -6176,10 +6153,10 @@
     </row>
     <row r="14" spans="1:33">
       <c r="A14" s="12" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="C14" s="13">
         <v>0</v>
@@ -6191,34 +6168,34 @@
         <v>415</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="J14" s="34" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="M14" s="34" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="N14" s="34" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="O14" s="34" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="P14" s="13">
         <v>0</v>
@@ -6277,10 +6254,10 @@
     </row>
     <row r="15" spans="1:33">
       <c r="A15" s="12" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="C15" s="13">
         <v>1</v>
@@ -6292,34 +6269,34 @@
         <v>415</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="J15" s="34" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="K15" s="34" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="L15" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="M15" s="34" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="N15" s="34" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="O15" s="34" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="P15" s="13">
         <v>0</v>
@@ -6378,28 +6355,28 @@
     </row>
     <row r="16" spans="1:33">
       <c r="A16" s="12" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="C16" s="13">
         <v>0</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="I16" s="34" t="s">
         <v>415</v>
@@ -6408,19 +6385,19 @@
         <v>412</v>
       </c>
       <c r="K16" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="L16" s="34" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="M16" s="34" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="N16" s="34" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="O16" s="34" t="s">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="P16" s="13">
         <v>0</v>
@@ -6479,10 +6456,10 @@
     </row>
     <row r="17" spans="1:33">
       <c r="A17" s="12" t="s">
-        <v>826</v>
+        <v>811</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C17" s="13">
         <v>0</v>
@@ -6580,10 +6557,10 @@
     </row>
     <row r="18" spans="1:33">
       <c r="A18" s="12" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>829</v>
+        <v>814</v>
       </c>
       <c r="C18" s="13">
         <v>0</v>
@@ -6592,7 +6569,7 @@
         <v>412</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="F18" s="13">
         <v>0</v>
@@ -6681,10 +6658,10 @@
     </row>
     <row r="19" spans="1:33">
       <c r="A19" s="12" t="s">
-        <v>830</v>
+        <v>815</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C19" s="13">
         <v>0</v>
@@ -6693,10 +6670,10 @@
         <v>412</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="G19" s="13">
         <v>0</v>
@@ -6782,25 +6759,25 @@
     </row>
     <row r="20" spans="1:33">
       <c r="A20" s="12" t="s">
-        <v>832</v>
+        <v>817</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>833</v>
+        <v>818</v>
       </c>
       <c r="C20" s="13">
         <v>0</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="E20" s="34" t="s">
         <v>412</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="H20" s="13">
         <v>0</v>
@@ -6883,40 +6860,40 @@
     </row>
     <row r="21" spans="1:33">
       <c r="A21" s="12" t="s">
-        <v>834</v>
+        <v>819</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>835</v>
+        <v>820</v>
       </c>
       <c r="C21" s="13">
         <v>0</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="E21" s="34" t="s">
         <v>392</v>
       </c>
       <c r="F21" s="34" t="s">
-        <v>836</v>
+        <v>821</v>
       </c>
       <c r="G21" s="34" t="s">
         <v>412</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="I21" s="34" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="J21" s="34" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="K21" s="34" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="L21" s="34" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="M21" s="13">
         <v>0</v>
@@ -6984,28 +6961,28 @@
     </row>
     <row r="22" spans="1:33">
       <c r="A22" s="12" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
       <c r="C22" s="13">
         <v>0</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="F22" s="34" t="s">
         <v>412</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="I22" s="13">
         <v>0</v>
@@ -7085,40 +7062,40 @@
     </row>
     <row r="23" spans="1:33">
       <c r="A23" s="12" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>841</v>
+        <v>826</v>
       </c>
       <c r="C23" s="13">
         <v>0</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>805</v>
+        <v>790</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="I23" s="34" t="s">
         <v>392</v>
       </c>
       <c r="J23" s="34" t="s">
-        <v>836</v>
+        <v>821</v>
       </c>
       <c r="K23" s="34" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="L23" s="34" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="M23" s="34" t="s">
         <v>415</v>
@@ -7127,31 +7104,31 @@
         <v>412</v>
       </c>
       <c r="O23" s="34" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="P23" s="34" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="Q23" s="34" t="s">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="R23" s="34" t="s">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="S23" s="34" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="T23" s="19" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="U23" s="19" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="V23" s="19" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="W23" s="19" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="X23" s="12">
         <v>0</v>
@@ -7206,16 +7183,16 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="15" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>847</v>
+        <v>832</v>
       </c>
       <c r="E1" s="16" t="s">
         <v>467</v>
@@ -7230,77 +7207,77 @@
         <v>466</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="K1" s="16" t="s">
         <v>328</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>850</v>
+        <v>835</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="36" t="s">
-        <v>851</v>
+        <v>836</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="D2" s="36" t="s">
         <v>545</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>463</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>1076</v>
+        <v>1061</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>464</v>
       </c>
       <c r="I2" s="36" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="J2" s="36" t="s">
-        <v>854</v>
+        <v>839</v>
       </c>
       <c r="K2" s="36" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="L2" s="36" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="38" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>857</v>
+        <v>842</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F3" s="12">
         <v>1</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H3" s="12">
         <v>1</v>
@@ -7320,25 +7297,25 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="38" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F4" s="12">
         <v>2</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H4" s="12">
         <v>1</v>
@@ -7358,25 +7335,25 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="38" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F5" s="12">
         <v>-1</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H5" s="12">
         <v>1</v>
@@ -7396,25 +7373,25 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="38" t="s">
-        <v>864</v>
+        <v>849</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>865</v>
+        <v>850</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F6" s="12">
         <v>-2</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H6" s="12">
         <v>1</v>
@@ -7434,25 +7411,25 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="38" t="s">
-        <v>866</v>
+        <v>851</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>535</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F7" s="12">
         <v>2</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H7" s="12">
         <v>1</v>
@@ -7472,25 +7449,25 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="38" t="s">
-        <v>869</v>
+        <v>854</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>870</v>
+        <v>855</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>506</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F8" s="12">
         <v>1</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H8" s="12">
         <v>1</v>
@@ -7510,25 +7487,25 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="38" t="s">
-        <v>872</v>
+        <v>857</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>873</v>
+        <v>858</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="D9" s="39" t="s">
         <v>507</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F9" s="12">
         <v>1</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H9" s="12">
         <v>1</v>
@@ -7548,25 +7525,25 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="38" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="D10" s="24" t="s">
         <v>512</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F10" s="12">
         <v>1</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H10" s="12">
         <v>1</v>
@@ -7586,25 +7563,25 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="38" t="s">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>878</v>
+        <v>863</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="D11" s="25" t="s">
         <v>515</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F11" s="12">
         <v>1</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H11" s="12">
         <v>1</v>
@@ -7624,25 +7601,25 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="38" t="s">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="D12" s="25" t="s">
         <v>402</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F12" s="12">
         <v>1</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H12" s="12">
         <v>1</v>
@@ -7662,25 +7639,25 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="38" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>882</v>
+        <v>867</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="D13" s="25" t="s">
         <v>528</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="F13" s="12">
         <v>0</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H13" s="12">
         <v>1</v>
@@ -7700,25 +7677,25 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="38" t="s">
-        <v>883</v>
+        <v>868</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="D14" s="25" t="s">
         <v>531</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="F14" s="12">
         <v>0</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H14" s="12">
         <v>1</v>
@@ -7738,25 +7715,25 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="38" t="s">
-        <v>885</v>
+        <v>870</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="D15" s="38" t="s">
         <v>510</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F15" s="12">
         <v>1</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H15" s="12">
         <v>1</v>
@@ -7776,25 +7753,25 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="38" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F16" s="12">
         <v>-1</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H16" s="12">
         <v>1</v>
@@ -7806,33 +7783,33 @@
         <v>0</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>834</v>
+        <v>819</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="38" t="s">
-        <v>891</v>
+        <v>876</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>892</v>
+        <v>877</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="F17" s="12">
         <v>0</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H17" s="12">
         <v>1</v>
@@ -7844,33 +7821,33 @@
         <v>0</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="38" t="s">
-        <v>893</v>
+        <v>878</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="D18" s="25" t="s">
         <v>395</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F18" s="12">
         <v>1</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H18" s="12">
         <v>1</v>
@@ -7890,25 +7867,25 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="38" t="s">
-        <v>895</v>
+        <v>880</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>896</v>
+        <v>881</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="D19" s="25" t="s">
         <v>362</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="F19" s="12">
         <v>1</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H19" s="12">
         <v>1</v>
@@ -7928,25 +7905,25 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="38" t="s">
-        <v>897</v>
+        <v>882</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="D20" s="26" t="s">
         <v>524</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="F20" s="12">
         <v>0</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H20" s="12">
         <v>1</v>
@@ -7966,25 +7943,25 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="38" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="D21" s="25" t="s">
         <v>526</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="F21" s="12">
         <v>0</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H21" s="12">
         <v>1</v>
@@ -8004,25 +7981,25 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="38" t="s">
-        <v>901</v>
+        <v>886</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>902</v>
+        <v>887</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="D22" s="26" t="s">
         <v>333</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="F22" s="12">
         <v>0</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="H22" s="12">
         <v>1</v>
@@ -9733,7 +9710,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="14" t="s">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>581</v>
@@ -9874,7 +9851,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="14" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>584</v>
@@ -10409,13 +10386,13 @@
         <v>445</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="I2" s="16" t="s">
         <v>463</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>1076</v>
+        <v>1061</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>464</v>
@@ -10487,12 +10464,12 @@
       </c>
       <c r="R3" s="12"/>
       <c r="S3" s="14" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="14" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>335</v>
@@ -10582,7 +10559,7 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="14" t="s">
-        <v>1084</v>
+        <v>1069</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>337</v>
@@ -10627,7 +10604,7 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="14" t="s">
-        <v>1089</v>
+        <v>1074</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>339</v>
@@ -10672,7 +10649,7 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="14" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>341</v>
@@ -10717,7 +10694,7 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="14" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>343</v>
@@ -10762,7 +10739,7 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="14" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>345</v>
@@ -10807,7 +10784,7 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="14" t="s">
-        <v>1093</v>
+        <v>1078</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>347</v>
@@ -10852,7 +10829,7 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="14" t="s">
-        <v>1085</v>
+        <v>1070</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>348</v>
@@ -10863,8 +10840,8 @@
       <c r="D12" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="E12" t="s">
-        <v>433</v>
+      <c r="E12" s="5" t="s">
+        <v>1097</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>8</v>
@@ -10898,14 +10875,14 @@
       </c>
       <c r="R12" s="12"/>
       <c r="S12" s="14" t="s">
-        <v>603</v>
+        <v>1099</v>
       </c>
       <c r="U12" s="20"/>
       <c r="V12" s="20"/>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="14" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>350</v>
@@ -10916,11 +10893,11 @@
       <c r="D13" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="E13" t="s">
-        <v>434</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>0</v>
+      <c r="E13" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>1096</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>351</v>
@@ -10932,10 +10909,10 @@
         <v>473</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
@@ -10951,14 +10928,14 @@
       </c>
       <c r="R13" s="12"/>
       <c r="S13" s="14" t="s">
-        <v>604</v>
+        <v>472</v>
       </c>
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="14" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>354</v>
@@ -10985,10 +10962,10 @@
         <v>474</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>1063</v>
+        <v>1048</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
@@ -11003,15 +10980,15 @@
         <v>352</v>
       </c>
       <c r="R14" s="12"/>
-      <c r="S14" s="12" t="s">
-        <v>594</v>
+      <c r="S14" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U14" s="13"/>
       <c r="V14" s="13"/>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="14" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>356</v>
@@ -11057,14 +11034,14 @@
       </c>
       <c r="R15" s="12"/>
       <c r="S15" s="14" t="s">
-        <v>605</v>
+        <v>472</v>
       </c>
       <c r="U15" s="13"/>
       <c r="V15" s="13"/>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="14" t="s">
-        <v>1105</v>
+        <v>1090</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>358</v>
@@ -11109,15 +11086,15 @@
         <v>334</v>
       </c>
       <c r="R16" s="12"/>
-      <c r="S16" s="12" t="s">
-        <v>596</v>
+      <c r="S16" s="14" t="s">
+        <v>1100</v>
       </c>
       <c r="U16" s="13"/>
       <c r="V16" s="13"/>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="14" t="s">
-        <v>1106</v>
+        <v>1091</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>361</v>
@@ -11163,14 +11140,14 @@
       </c>
       <c r="R17" s="12"/>
       <c r="S17" s="14" t="s">
-        <v>606</v>
+        <v>1101</v>
       </c>
       <c r="U17" s="13"/>
       <c r="V17" s="13"/>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="14" t="s">
-        <v>1086</v>
+        <v>1071</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>365</v>
@@ -11179,7 +11156,7 @@
         <v>437</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>1083</v>
+        <v>1068</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -11215,15 +11192,15 @@
         <v>334</v>
       </c>
       <c r="R18" s="12"/>
-      <c r="S18" s="12" t="s">
-        <v>593</v>
+      <c r="S18" s="14" t="s">
+        <v>1099</v>
       </c>
       <c r="U18" s="13"/>
       <c r="V18" s="13"/>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="14" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>367</v>
@@ -11268,15 +11245,15 @@
         <v>352</v>
       </c>
       <c r="R19" s="12"/>
-      <c r="S19" s="12" t="s">
-        <v>594</v>
+      <c r="S19" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U19" s="13"/>
       <c r="V19" s="13"/>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="14" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>370</v>
@@ -11321,15 +11298,15 @@
         <v>352</v>
       </c>
       <c r="R20" s="12"/>
-      <c r="S20" s="12" t="s">
-        <v>594</v>
+      <c r="S20" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U20" s="13"/>
       <c r="V20" s="13"/>
     </row>
     <row r="21" spans="1:22">
       <c r="A21" s="14" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>372</v>
@@ -11356,10 +11333,10 @@
         <v>374</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
@@ -11374,15 +11351,15 @@
         <v>334</v>
       </c>
       <c r="R21" s="12"/>
-      <c r="S21" s="12" t="s">
-        <v>598</v>
+      <c r="S21" s="14" t="s">
+        <v>1100</v>
       </c>
       <c r="U21" s="17"/>
       <c r="V21" s="17"/>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" s="14" t="s">
-        <v>1101</v>
+        <v>1086</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>376</v>
@@ -11427,15 +11404,15 @@
         <v>352</v>
       </c>
       <c r="R22" s="12"/>
-      <c r="S22" s="12" t="s">
-        <v>595</v>
+      <c r="S22" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U22" s="18"/>
       <c r="V22" s="18"/>
     </row>
     <row r="23" spans="1:22">
       <c r="A23" s="14" t="s">
-        <v>1102</v>
+        <v>1087</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>378</v>
@@ -11462,10 +11439,10 @@
         <v>475</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
@@ -11480,15 +11457,15 @@
         <v>352</v>
       </c>
       <c r="R23" s="12"/>
-      <c r="S23" s="12" t="s">
-        <v>594</v>
+      <c r="S23" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U23" s="18"/>
       <c r="V23" s="18"/>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" s="14" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>380</v>
@@ -11533,15 +11510,15 @@
         <v>352</v>
       </c>
       <c r="R24" s="12"/>
-      <c r="S24" s="12" t="s">
-        <v>594</v>
+      <c r="S24" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U24" s="18"/>
       <c r="V24" s="18"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="14" t="s">
-        <v>1104</v>
+        <v>1089</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>382</v>
@@ -11568,10 +11545,10 @@
         <v>384</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
@@ -11586,15 +11563,15 @@
         <v>334</v>
       </c>
       <c r="R25" s="12"/>
-      <c r="S25" s="12" t="s">
-        <v>598</v>
+      <c r="S25" s="14" t="s">
+        <v>1100</v>
       </c>
       <c r="U25" s="17"/>
       <c r="V25" s="17"/>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="14" t="s">
-        <v>1107</v>
+        <v>1092</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>386</v>
@@ -11621,10 +11598,10 @@
         <v>474</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
@@ -11639,15 +11616,15 @@
         <v>352</v>
       </c>
       <c r="R26" s="12"/>
-      <c r="S26" s="12" t="s">
-        <v>594</v>
+      <c r="S26" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U26" s="18"/>
       <c r="V26" s="18"/>
     </row>
     <row r="27" spans="1:22">
       <c r="A27" s="14" t="s">
-        <v>1108</v>
+        <v>1093</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>388</v>
@@ -11692,15 +11669,15 @@
         <v>334</v>
       </c>
       <c r="R27" s="12"/>
-      <c r="S27" s="12" t="s">
-        <v>594</v>
+      <c r="S27" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U27" s="13"/>
       <c r="V27" s="13"/>
     </row>
     <row r="28" spans="1:22">
       <c r="A28" s="14" t="s">
-        <v>1109</v>
+        <v>1094</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>390</v>
@@ -11727,10 +11704,10 @@
         <v>392</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
@@ -11745,15 +11722,15 @@
         <v>334</v>
       </c>
       <c r="R28" s="12"/>
-      <c r="S28" s="12" t="s">
-        <v>598</v>
+      <c r="S28" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U28" s="13"/>
       <c r="V28" s="13"/>
     </row>
     <row r="29" spans="1:22">
       <c r="A29" s="14" t="s">
-        <v>1110</v>
+        <v>1095</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>394</v>
@@ -11798,8 +11775,8 @@
         <v>352</v>
       </c>
       <c r="R29" s="12"/>
-      <c r="S29" s="12" t="s">
-        <v>599</v>
+      <c r="S29" s="14" t="s">
+        <v>1101</v>
       </c>
       <c r="U29" s="18"/>
       <c r="V29" s="18"/>
@@ -11823,8 +11800,8 @@
       <c r="F30" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G30" s="12" t="s">
-        <v>399</v>
+      <c r="G30" s="14" t="s">
+        <v>1102</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>469</v>
@@ -11833,10 +11810,10 @@
         <v>476</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
@@ -11851,8 +11828,8 @@
         <v>352</v>
       </c>
       <c r="R30" s="12"/>
-      <c r="S30" s="12" t="s">
-        <v>598</v>
+      <c r="S30" s="14" t="s">
+        <v>1100</v>
       </c>
       <c r="U30" s="17"/>
       <c r="V30" s="17"/>
@@ -11905,7 +11882,7 @@
       </c>
       <c r="R31" s="12"/>
       <c r="S31" s="14" t="s">
-        <v>607</v>
+        <v>1101</v>
       </c>
       <c r="U31" s="18"/>
       <c r="V31" s="18"/>
@@ -11957,15 +11934,15 @@
         <v>334</v>
       </c>
       <c r="R32" s="12"/>
-      <c r="S32" s="12" t="s">
-        <v>600</v>
+      <c r="S32" s="14" t="s">
+        <v>1100</v>
       </c>
       <c r="U32" s="18"/>
       <c r="V32" s="18"/>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="14" t="s">
-        <v>1087</v>
+        <v>1072</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>408</v>
@@ -12010,8 +11987,8 @@
         <v>352</v>
       </c>
       <c r="R33" s="12"/>
-      <c r="S33" s="12" t="s">
-        <v>594</v>
+      <c r="S33" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U33" s="18"/>
       <c r="V33" s="18"/>
@@ -12045,10 +12022,10 @@
         <v>475</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
@@ -12065,8 +12042,8 @@
         <v>352</v>
       </c>
       <c r="R34" s="12"/>
-      <c r="S34" s="12" t="s">
-        <v>594</v>
+      <c r="S34" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U34" s="13"/>
       <c r="V34" s="13"/>
@@ -12100,10 +12077,10 @@
         <v>475</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L35" s="19"/>
       <c r="M35" s="11"/>
@@ -12120,8 +12097,8 @@
         <v>352</v>
       </c>
       <c r="R35" s="12"/>
-      <c r="S35" s="12" t="s">
-        <v>594</v>
+      <c r="S35" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U35" s="18"/>
       <c r="V35" s="18"/>
@@ -12155,10 +12132,10 @@
         <v>477</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="L36" s="11"/>
       <c r="M36" s="11"/>
@@ -12173,8 +12150,8 @@
         <v>352</v>
       </c>
       <c r="R36" s="12"/>
-      <c r="S36" s="12" t="s">
-        <v>594</v>
+      <c r="S36" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
@@ -12226,8 +12203,8 @@
         <v>352</v>
       </c>
       <c r="R37" s="12"/>
-      <c r="S37" s="12" t="s">
-        <v>595</v>
+      <c r="S37" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U37" s="18"/>
       <c r="V37" s="18"/>
@@ -12279,8 +12256,8 @@
         <v>352</v>
       </c>
       <c r="R38" s="12"/>
-      <c r="S38" s="12" t="s">
-        <v>595</v>
+      <c r="S38" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="U38" s="18"/>
       <c r="V38" s="18"/>
@@ -12333,7 +12310,7 @@
       </c>
       <c r="R39" s="12"/>
       <c r="S39" s="14" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="U39" s="17"/>
       <c r="V39" s="17"/>
@@ -12386,7 +12363,7 @@
       </c>
       <c r="R40" s="12"/>
       <c r="S40" s="14" t="s">
-        <v>609</v>
+        <v>1100</v>
       </c>
       <c r="U40" s="18"/>
       <c r="V40" s="18"/>
@@ -12438,8 +12415,8 @@
         <v>352</v>
       </c>
       <c r="R41" s="12"/>
-      <c r="S41" s="12" t="s">
-        <v>599</v>
+      <c r="S41" s="14" t="s">
+        <v>1101</v>
       </c>
       <c r="U41" s="17"/>
       <c r="V41" s="17"/>
@@ -12491,8 +12468,8 @@
         <v>352</v>
       </c>
       <c r="R42" s="12"/>
-      <c r="S42" s="12" t="s">
-        <v>597</v>
+      <c r="S42" s="14" t="s">
+        <v>1101</v>
       </c>
       <c r="U42" s="18"/>
       <c r="V42" s="18"/>
@@ -12544,8 +12521,8 @@
         <v>334</v>
       </c>
       <c r="R43" s="12"/>
-      <c r="S43" s="12" t="s">
-        <v>601</v>
+      <c r="S43" s="14" t="s">
+        <v>1100</v>
       </c>
       <c r="U43" s="18"/>
       <c r="V43" s="18"/>
@@ -12597,8 +12574,8 @@
         <v>352</v>
       </c>
       <c r="R44" s="12"/>
-      <c r="S44" s="12" t="s">
-        <v>599</v>
+      <c r="S44" s="14" t="s">
+        <v>1101</v>
       </c>
       <c r="U44" s="18"/>
       <c r="V44" s="18"/>
@@ -12650,8 +12627,8 @@
         <v>352</v>
       </c>
       <c r="R45" s="12"/>
-      <c r="S45" s="12" t="s">
-        <v>597</v>
+      <c r="S45" s="14" t="s">
+        <v>1101</v>
       </c>
       <c r="U45" s="18"/>
       <c r="V45" s="18"/>
@@ -13616,6 +13593,7 @@
     <col min="9" max="9" width="14.25" customWidth="1"/>
     <col min="10" max="10" width="14.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -13623,7 +13601,7 @@
         <v>14</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>223</v>
@@ -13635,7 +13613,7 @@
         <v>122</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>847</v>
+        <v>832</v>
       </c>
       <c r="G1" s="16" t="s">
         <v>467</v>
@@ -13650,7 +13628,7 @@
         <v>466</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>904</v>
+        <v>889</v>
       </c>
       <c r="L1" s="35" t="s">
         <v>327</v>
@@ -13667,10 +13645,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>905</v>
+        <v>890</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="D2" s="36" t="s">
         <v>331</v>
@@ -13679,48 +13657,48 @@
         <v>123</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1078</v>
+        <v>1063</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>463</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>1076</v>
+        <v>1061</v>
       </c>
       <c r="J2" s="16" t="s">
         <v>464</v>
       </c>
       <c r="K2" s="36" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="M2" s="36" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="N2" s="36" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="25" t="s">
-        <v>908</v>
+        <v>893</v>
       </c>
       <c r="B3" s="13">
         <v>2</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>338</v>
@@ -13744,27 +13722,27 @@
         <v>0</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>767</v>
+        <v>752</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="25" t="s">
-        <v>908</v>
+        <v>893</v>
       </c>
       <c r="B4" s="13">
         <v>3</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>338</v>
@@ -13788,27 +13766,27 @@
         <v>0</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>767</v>
+        <v>752</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="25" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="B5" s="13">
         <v>2</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>368</v>
@@ -13832,27 +13810,27 @@
         <v>0</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="25" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="B6" s="13">
         <v>3</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>368</v>
@@ -13876,27 +13854,27 @@
         <v>0</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="25" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="B7" s="13">
         <v>2</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>368</v>
@@ -13920,27 +13898,27 @@
         <v>0</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="25" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="B8" s="13">
         <v>3</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>368</v>
@@ -13964,42 +13942,42 @@
         <v>0</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N8" s="40" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="25" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="B9" s="13">
         <v>2</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>373</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>374</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K9" s="12">
         <v>35</v>
@@ -14008,42 +13986,42 @@
         <v>0</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N9" s="40" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="25" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="B10" s="13">
         <v>3</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>373</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>374</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K10" s="40">
         <v>32</v>
@@ -14052,30 +14030,30 @@
         <v>0</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="25" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="B11" s="13">
         <v>2</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>450</v>
@@ -14096,27 +14074,27 @@
         <v>0</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N11" s="40" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="25" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="B12" s="13">
         <v>3</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>357</v>
@@ -14140,42 +14118,42 @@
         <v>0</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="25" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="B13" s="13">
         <v>2</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>355</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H13" s="40" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J13" s="14" t="s">
         <v>1052</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>1065</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>1067</v>
       </c>
       <c r="K13" s="12">
         <v>30</v>
@@ -14184,42 +14162,42 @@
         <v>0</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="25" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="B14" s="13">
         <v>3</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>355</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H14" s="40" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K14" s="40">
         <v>28</v>
@@ -14228,27 +14206,27 @@
         <v>0</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="25" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="B15" s="13">
         <v>2</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>368</v>
@@ -14272,27 +14250,27 @@
         <v>0</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N15" s="40" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="25" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="B16" s="13">
         <v>3</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>368</v>
@@ -14316,42 +14294,42 @@
         <v>0</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="25" t="s">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="B17" s="13">
         <v>2</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>383</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>384</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K17" s="12">
         <v>25</v>
@@ -14360,42 +14338,42 @@
         <v>0</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N17" s="40" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="25" t="s">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="B18" s="13">
         <v>3</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>383</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>384</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K18" s="12">
         <v>25</v>
@@ -14404,42 +14382,42 @@
         <v>0</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="25" t="s">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="B19" s="13">
         <v>2</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>355</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H19" s="40" t="s">
-        <v>1054</v>
+        <v>1039</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>1068</v>
+        <v>1053</v>
       </c>
       <c r="K19" s="12">
         <v>35</v>
@@ -14448,42 +14426,42 @@
         <v>0</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="25" t="s">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="B20" s="13">
         <v>3</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>355</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>1055</v>
+        <v>1040</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>1068</v>
+        <v>1053</v>
       </c>
       <c r="K20" s="40">
         <v>31</v>
@@ -14492,27 +14470,27 @@
         <v>0</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="25" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="B21" s="13">
         <v>2</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>368</v>
@@ -14536,27 +14514,27 @@
         <v>0</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="25" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="B22" s="13">
         <v>3</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>368</v>
@@ -14580,42 +14558,42 @@
         <v>0</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="25" t="s">
-        <v>928</v>
+        <v>913</v>
       </c>
       <c r="B23" s="13">
         <v>2</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>391</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>1056</v>
+        <v>1041</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K23" s="12">
         <v>35</v>
@@ -14624,42 +14602,42 @@
         <v>0</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="25" t="s">
-        <v>928</v>
+        <v>913</v>
       </c>
       <c r="B24" s="13">
         <v>3</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>391</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>929</v>
+        <v>914</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K24" s="12">
         <v>35</v>
@@ -14668,27 +14646,27 @@
         <v>0</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="25" t="s">
-        <v>930</v>
+        <v>915</v>
       </c>
       <c r="B25" s="13">
         <v>2</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>395</v>
@@ -14712,27 +14690,27 @@
         <v>0</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="25" t="s">
-        <v>930</v>
+        <v>915</v>
       </c>
       <c r="B26" s="13">
         <v>3</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>395</v>
@@ -14756,42 +14734,42 @@
         <v>0</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N26" s="40" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="25" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="B27" s="13">
         <v>2</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>399</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>1057</v>
+        <v>1042</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K27" s="40">
         <v>26</v>
@@ -14800,42 +14778,42 @@
         <v>0</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="25" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="B28" s="13">
         <v>3</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>399</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K28" s="12">
         <v>30</v>
@@ -14844,27 +14822,27 @@
         <v>0</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="25" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
       <c r="B29" s="13">
         <v>2</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>402</v>
@@ -14888,27 +14866,27 @@
         <v>0</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N29" s="40" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="25" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
       <c r="B30" s="13">
         <v>3</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>402</v>
@@ -14932,27 +14910,27 @@
         <v>0</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N30" s="40" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="25" t="s">
-        <v>934</v>
+        <v>919</v>
       </c>
       <c r="B31" s="13">
         <v>2</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>406</v>
@@ -14976,27 +14954,27 @@
         <v>0</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="25" t="s">
-        <v>934</v>
+        <v>919</v>
       </c>
       <c r="B32" s="13">
         <v>3</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>406</v>
@@ -15020,27 +14998,27 @@
         <v>0</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="25" t="s">
-        <v>935</v>
+        <v>920</v>
       </c>
       <c r="B33" s="13">
         <v>2</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>368</v>
@@ -15064,27 +15042,27 @@
         <v>0</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="25" t="s">
-        <v>935</v>
+        <v>920</v>
       </c>
       <c r="B34" s="13">
         <v>3</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>368</v>
@@ -15108,42 +15086,42 @@
         <v>0</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N34" s="40" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="25" t="s">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="B35" s="13">
         <v>2</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>411</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K35" s="40">
         <v>22</v>
@@ -15152,42 +15130,42 @@
         <v>1</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="25" t="s">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="B36" s="13">
         <v>3</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>411</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K36" s="12">
         <v>25</v>
@@ -15196,42 +15174,42 @@
         <v>2</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="25" t="s">
-        <v>937</v>
+        <v>922</v>
       </c>
       <c r="B37" s="13">
         <v>2</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>411</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>1060</v>
+        <v>1045</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K37" s="12">
         <v>25</v>
@@ -15240,42 +15218,42 @@
         <v>-1</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N37" s="40" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="25" t="s">
-        <v>937</v>
+        <v>922</v>
       </c>
       <c r="B38" s="13">
         <v>3</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>411</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H38" s="40" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J38" s="14" t="s">
         <v>1052</v>
-      </c>
-      <c r="I38" s="14" t="s">
-        <v>1065</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>1067</v>
       </c>
       <c r="K38" s="12">
         <v>25</v>
@@ -15284,42 +15262,42 @@
         <v>-1</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="25" t="s">
-        <v>938</v>
+        <v>923</v>
       </c>
       <c r="B39" s="13">
         <v>2</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>355</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H39" s="14" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J39" s="40" t="s">
         <v>1054</v>
-      </c>
-      <c r="I39" s="14" t="s">
-        <v>1065</v>
-      </c>
-      <c r="J39" s="40" t="s">
-        <v>1069</v>
       </c>
       <c r="K39" s="12">
         <v>30</v>
@@ -15328,42 +15306,42 @@
         <v>0</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="25" t="s">
-        <v>938</v>
+        <v>923</v>
       </c>
       <c r="B40" s="13">
         <v>3</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>355</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>1061</v>
+        <v>1046</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>1069</v>
+        <v>1054</v>
       </c>
       <c r="K40" s="12">
         <v>30</v>
@@ -15372,27 +15350,27 @@
         <v>0</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="25" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
       <c r="B41" s="13">
         <v>2</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>357</v>
@@ -15416,27 +15394,27 @@
         <v>0</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="25" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
       <c r="B42" s="13">
         <v>3</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>357</v>
@@ -15460,27 +15438,27 @@
         <v>0</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="25" t="s">
-        <v>940</v>
+        <v>925</v>
       </c>
       <c r="B43" s="13">
         <v>2</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>357</v>
@@ -15504,27 +15482,27 @@
         <v>0</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N43" s="40" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="25" t="s">
-        <v>940</v>
+        <v>925</v>
       </c>
       <c r="B44" s="13">
         <v>3</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>357</v>
@@ -15548,27 +15526,27 @@
         <v>0</v>
       </c>
       <c r="M44" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="25" t="s">
-        <v>941</v>
+        <v>926</v>
       </c>
       <c r="B45" s="13">
         <v>2</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>424</v>
@@ -15592,27 +15570,27 @@
         <v>0</v>
       </c>
       <c r="M45" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N45" s="12" t="s">
-        <v>942</v>
+        <v>927</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="25" t="s">
-        <v>941</v>
+        <v>926</v>
       </c>
       <c r="B46" s="13">
         <v>3</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>424</v>
@@ -15636,27 +15614,27 @@
         <v>0</v>
       </c>
       <c r="M46" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N46" s="40" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="25" t="s">
-        <v>943</v>
+        <v>928</v>
       </c>
       <c r="B47" s="13">
         <v>2</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>340</v>
@@ -15680,27 +15658,27 @@
         <v>0</v>
       </c>
       <c r="M47" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N47" s="12" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="25" t="s">
-        <v>943</v>
+        <v>928</v>
       </c>
       <c r="B48" s="13">
         <v>3</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>340</v>
@@ -15724,27 +15702,27 @@
         <v>0</v>
       </c>
       <c r="M48" s="12" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="N48" s="40" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="25" t="s">
-        <v>944</v>
+        <v>929</v>
       </c>
       <c r="B49" s="13">
         <v>2</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>395</v>
@@ -15768,27 +15746,27 @@
         <v>0</v>
       </c>
       <c r="M49" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N49" s="40" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="25" t="s">
-        <v>944</v>
+        <v>929</v>
       </c>
       <c r="B50" s="13">
         <v>3</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>395</v>
@@ -15812,27 +15790,27 @@
         <v>0</v>
       </c>
       <c r="M50" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N50" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="25" t="s">
-        <v>945</v>
+        <v>930</v>
       </c>
       <c r="B51" s="13">
         <v>2</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>362</v>
@@ -15856,27 +15834,27 @@
         <v>0</v>
       </c>
       <c r="M51" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N51" s="40" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="25" t="s">
-        <v>945</v>
+        <v>930</v>
       </c>
       <c r="B52" s="13">
         <v>3</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>362</v>
@@ -15900,10 +15878,10 @@
         <v>0</v>
       </c>
       <c r="M52" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="N52" s="12" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>
@@ -15934,7 +15912,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="15" t="s">
-        <v>946</v>
+        <v>931</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>14</v>
@@ -15943,7 +15921,7 @@
         <v>18</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>847</v>
+        <v>832</v>
       </c>
       <c r="E1" s="16" t="s">
         <v>467</v>
@@ -15972,40 +15950,40 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="36" t="s">
-        <v>947</v>
+        <v>932</v>
       </c>
       <c r="B2" s="36" t="s">
         <v>560</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>948</v>
+        <v>933</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1078</v>
+        <v>1063</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>463</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>1076</v>
+        <v>1061</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>464</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>854</v>
+        <v>839</v>
       </c>
       <c r="J2" s="36" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="K2" s="36" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -16013,16 +15991,16 @@
         <v>236</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>950</v>
+        <v>935</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F3" s="25">
         <v>0</v>
@@ -16037,13 +16015,13 @@
         <v>0</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L3" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -16051,10 +16029,10 @@
         <v>237</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>368</v>
@@ -16075,13 +16053,13 @@
         <v>0</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -16089,10 +16067,10 @@
         <v>238</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>955</v>
+        <v>940</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>368</v>
@@ -16113,13 +16091,13 @@
         <v>0</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -16127,16 +16105,16 @@
         <v>241</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>956</v>
+        <v>941</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D6" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F6" s="25">
         <v>0</v>
@@ -16151,13 +16129,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -16165,10 +16143,10 @@
         <v>242</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>957</v>
+        <v>942</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D7" s="25" t="s">
         <v>368</v>
@@ -16189,13 +16167,13 @@
         <v>0</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -16203,16 +16181,16 @@
         <v>245</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>958</v>
+        <v>943</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D8" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F8" s="25">
         <v>0</v>
@@ -16227,13 +16205,13 @@
         <v>0</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -16241,10 +16219,10 @@
         <v>246</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>959</v>
+        <v>944</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>340</v>
@@ -16265,13 +16243,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="K9" s="25">
         <v>0</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -16279,10 +16257,10 @@
         <v>247</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>962</v>
+        <v>947</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>338</v>
@@ -16303,13 +16281,13 @@
         <v>0</v>
       </c>
       <c r="J10" s="25" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="K10" s="25">
         <v>0</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -16317,10 +16295,10 @@
         <v>249</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>395</v>
@@ -16341,13 +16319,13 @@
         <v>0</v>
       </c>
       <c r="J11" s="25" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="K11" s="25">
         <v>0</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -16355,10 +16333,10 @@
         <v>250</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>362</v>
@@ -16379,13 +16357,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="K12" s="25">
         <v>0</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -16393,16 +16371,16 @@
         <v>253</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>968</v>
+        <v>953</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D13" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F13" s="25">
         <v>0</v>
@@ -16417,13 +16395,13 @@
         <v>0</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K13" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L13" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -16431,10 +16409,10 @@
         <v>254</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>969</v>
+        <v>954</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D14" s="25" t="s">
         <v>368</v>
@@ -16455,13 +16433,13 @@
         <v>0</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -16469,10 +16447,10 @@
         <v>255</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>970</v>
+        <v>955</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D15" s="25" t="s">
         <v>368</v>
@@ -16493,13 +16471,13 @@
         <v>6</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -16507,16 +16485,16 @@
         <v>258</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>971</v>
+        <v>956</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D16" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F16" s="25">
         <v>0</v>
@@ -16531,13 +16509,13 @@
         <v>0</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K16" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L16" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -16545,10 +16523,10 @@
         <v>259</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>972</v>
+        <v>957</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D17" s="25" t="s">
         <v>368</v>
@@ -16569,13 +16547,13 @@
         <v>0</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -16583,10 +16561,10 @@
         <v>260</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>973</v>
+        <v>958</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D18" s="25" t="s">
         <v>368</v>
@@ -16607,13 +16585,13 @@
         <v>0</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -16621,16 +16599,16 @@
         <v>263</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>340</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F19" s="25">
         <v>0</v>
@@ -16645,13 +16623,13 @@
         <v>0</v>
       </c>
       <c r="J19" s="25" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="K19" s="12">
         <v>0</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -16659,16 +16637,16 @@
         <v>264</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>975</v>
+        <v>960</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="D20" s="26" t="s">
         <v>338</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F20" s="25">
         <v>0</v>
@@ -16683,13 +16661,13 @@
         <v>0</v>
       </c>
       <c r="J20" s="25" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="K20" s="25">
         <v>0</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -16697,10 +16675,10 @@
         <v>265</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>976</v>
+        <v>961</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D21" s="25" t="s">
         <v>368</v>
@@ -16721,13 +16699,13 @@
         <v>0</v>
       </c>
       <c r="J21" s="25" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="K21" s="25">
         <v>0</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -16735,10 +16713,10 @@
         <v>266</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D22" s="25" t="s">
         <v>368</v>
@@ -16759,13 +16737,13 @@
         <v>0</v>
       </c>
       <c r="J22" s="25" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="K22" s="25">
         <v>0</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -16773,16 +16751,16 @@
         <v>269</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D23" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F23" s="25">
         <v>0</v>
@@ -16797,13 +16775,13 @@
         <v>0</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K23" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -16811,10 +16789,10 @@
         <v>270</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D24" s="25" t="s">
         <v>357</v>
@@ -16835,13 +16813,13 @@
         <v>0</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -16849,16 +16827,16 @@
         <v>273</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>981</v>
+        <v>966</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D25" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F25" s="25">
         <v>0</v>
@@ -16873,13 +16851,13 @@
         <v>0</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K25" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -16887,10 +16865,10 @@
         <v>274</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D26" s="25" t="s">
         <v>515</v>
@@ -16911,13 +16889,13 @@
         <v>0</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -16925,10 +16903,10 @@
         <v>275</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D27" s="25" t="s">
         <v>368</v>
@@ -16949,13 +16927,13 @@
         <v>0</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -16963,16 +16941,16 @@
         <v>278</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D28" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F28" s="25">
         <v>0</v>
@@ -16987,13 +16965,13 @@
         <v>0</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K28" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -17001,10 +16979,10 @@
         <v>279</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>985</v>
+        <v>970</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="D29" s="25" t="s">
         <v>359</v>
@@ -17025,13 +17003,13 @@
         <v>0</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="K29" s="25">
         <v>0</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -17039,10 +17017,10 @@
         <v>280</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>986</v>
+        <v>971</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D30" s="25" t="s">
         <v>368</v>
@@ -17063,13 +17041,13 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -17077,10 +17055,10 @@
         <v>281</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>987</v>
+        <v>972</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D31" s="25" t="s">
         <v>368</v>
@@ -17101,13 +17079,13 @@
         <v>0</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -17115,10 +17093,10 @@
         <v>282</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>988</v>
+        <v>973</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D32" s="25" t="s">
         <v>368</v>
@@ -17139,13 +17117,13 @@
         <v>0</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -17153,16 +17131,16 @@
         <v>285</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>989</v>
+        <v>974</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D33" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F33" s="25">
         <v>0</v>
@@ -17177,13 +17155,13 @@
         <v>0</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K33" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L33" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -17191,10 +17169,10 @@
         <v>286</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>990</v>
+        <v>975</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D34" s="25" t="s">
         <v>402</v>
@@ -17215,13 +17193,13 @@
         <v>0</v>
       </c>
       <c r="J34" s="25" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="K34" s="25">
         <v>0</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -17229,10 +17207,10 @@
         <v>287</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>991</v>
+        <v>976</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D35" s="25" t="s">
         <v>368</v>
@@ -17253,13 +17231,13 @@
         <v>0</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -17267,10 +17245,10 @@
         <v>288</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>992</v>
+        <v>977</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D36" s="25" t="s">
         <v>368</v>
@@ -17291,13 +17269,13 @@
         <v>0</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -17305,10 +17283,10 @@
         <v>289</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>993</v>
+        <v>978</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D37" s="25" t="s">
         <v>368</v>
@@ -17329,13 +17307,13 @@
         <v>0</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -17343,16 +17321,16 @@
         <v>292</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>994</v>
+        <v>979</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D38" s="25" t="s">
         <v>333</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F38" s="25">
         <v>0</v>
@@ -17367,13 +17345,13 @@
         <v>0</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K38" s="25" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="L38" s="25" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -17381,10 +17359,10 @@
         <v>293</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="D39" s="25" t="s">
         <v>338</v>
@@ -17405,13 +17383,13 @@
         <v>0</v>
       </c>
       <c r="J39" s="25" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="K39" s="25">
         <v>0</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -17419,10 +17397,10 @@
         <v>294</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>996</v>
+        <v>981</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="D40" s="25" t="s">
         <v>424</v>
@@ -17443,13 +17421,13 @@
         <v>0</v>
       </c>
       <c r="J40" s="25" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="K40" s="25">
         <v>0</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -17457,10 +17435,10 @@
         <v>295</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>997</v>
+        <v>982</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D41" s="25" t="s">
         <v>362</v>
@@ -17481,13 +17459,13 @@
         <v>0</v>
       </c>
       <c r="J41" s="25" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="K41" s="25">
         <v>0</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -17495,16 +17473,16 @@
         <v>296</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>998</v>
+        <v>983</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D42" s="25" t="s">
         <v>522</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="F42" s="25">
         <v>0</v>
@@ -17519,13 +17497,13 @@
         <v>0</v>
       </c>
       <c r="J42" s="25" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="K42" s="25">
         <v>0</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -17533,10 +17511,10 @@
         <v>297</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>999</v>
+        <v>984</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D43" s="25" t="s">
         <v>368</v>
@@ -17557,13 +17535,13 @@
         <v>0</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -17571,10 +17549,10 @@
         <v>298</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D44" s="25" t="s">
         <v>368</v>
@@ -17595,13 +17573,13 @@
         <v>0</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -17609,10 +17587,10 @@
         <v>299</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>1001</v>
+        <v>986</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D45" s="25" t="s">
         <v>368</v>
@@ -17633,13 +17611,13 @@
         <v>0</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K45" s="12" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="L45" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -17647,10 +17625,10 @@
         <v>300</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D46" s="25" t="s">
         <v>357</v>
@@ -17671,13 +17649,13 @@
         <v>0</v>
       </c>
       <c r="J46" s="25" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="K46" s="25">
         <v>0</v>
       </c>
       <c r="L46" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -17685,10 +17663,10 @@
         <v>301</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>1003</v>
+        <v>988</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="D47" s="25" t="s">
         <v>357</v>
@@ -17709,13 +17687,13 @@
         <v>0</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="K47" s="25">
         <v>0</v>
       </c>
       <c r="L47" s="12" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -17745,16 +17723,16 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="22" t="s">
-        <v>1004</v>
+        <v>989</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>1005</v>
+        <v>990</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>1006</v>
+        <v>991</v>
       </c>
       <c r="E1" s="22" t="s">
         <v>478</v>
@@ -17772,74 +17750,74 @@
         <v>466</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>1007</v>
+        <v>992</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>850</v>
+        <v>835</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="36" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>1077</v>
+        <v>1062</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="G2" s="16" t="s">
         <v>463</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>1076</v>
+        <v>1061</v>
       </c>
       <c r="I2" s="16" t="s">
         <v>464</v>
       </c>
       <c r="J2" s="36" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="K2" s="36" t="s">
-        <v>905</v>
+        <v>890</v>
       </c>
       <c r="L2" s="36" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="M2" s="36" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="11" t="s">
-        <v>1012</v>
+        <v>997</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>1013</v>
+        <v>998</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="D3" s="12">
         <v>0</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>455</v>
@@ -17868,19 +17846,19 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="11" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>1017</v>
+        <v>1002</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="D4" s="12">
         <v>0</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="F4" s="14" t="s">
         <v>455</v>
@@ -17909,13 +17887,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="11" t="s">
-        <v>1018</v>
+        <v>1003</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>1019</v>
+        <v>1004</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="D5" s="12">
         <v>0</v>
@@ -17950,13 +17928,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="11" t="s">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>1021</v>
+        <v>1006</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="D6" s="12">
         <v>0</v>
@@ -17991,13 +17969,13 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="11" t="s">
-        <v>1022</v>
+        <v>1007</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1023</v>
+        <v>1008</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="D7" s="12">
         <v>0</v>
@@ -18032,13 +18010,13 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="11" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="D8" s="12">
         <v>0</v>
@@ -18073,13 +18051,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="11" t="s">
-        <v>1026</v>
+        <v>1011</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="D9" s="12">
         <v>0</v>
@@ -18114,13 +18092,13 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="11" t="s">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>1029</v>
+        <v>1014</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="D10" s="12">
         <v>0</v>
@@ -18155,10 +18133,10 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="11" t="s">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>1031</v>
+        <v>1016</v>
       </c>
       <c r="C11" s="12">
         <v>1</v>
@@ -18196,10 +18174,10 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="11" t="s">
-        <v>1032</v>
+        <v>1017</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="C12" s="11">
         <v>1</v>
@@ -18211,7 +18189,7 @@
         <v>539</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G12" s="12">
         <v>0</v>
@@ -18237,10 +18215,10 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="11" t="s">
-        <v>1034</v>
+        <v>1019</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>1035</v>
+        <v>1020</v>
       </c>
       <c r="C13" s="12">
         <v>1</v>
@@ -18252,7 +18230,7 @@
         <v>537</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G13" s="12">
         <v>0</v>
@@ -18270,18 +18248,18 @@
         <v>0</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="11" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="C14" s="12">
         <v>1</v>
@@ -18293,7 +18271,7 @@
         <v>502</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G14" s="12">
         <v>0</v>
@@ -18319,10 +18297,10 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="11" t="s">
-        <v>1040</v>
+        <v>1025</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
       <c r="C15" s="12">
         <v>1</v>
@@ -18334,7 +18312,7 @@
         <v>539</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G15" s="12">
         <v>0</v>
@@ -18360,10 +18338,10 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="11" t="s">
-        <v>1042</v>
+        <v>1027</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>1031</v>
+        <v>1016</v>
       </c>
       <c r="C16" s="44">
         <v>2</v>
@@ -18401,10 +18379,10 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="11" t="s">
-        <v>1043</v>
+        <v>1028</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="C17" s="44">
         <v>2</v>
@@ -18416,7 +18394,7 @@
         <v>539</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
@@ -18442,10 +18420,10 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="11" t="s">
-        <v>1044</v>
+        <v>1029</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>1035</v>
+        <v>1020</v>
       </c>
       <c r="C18" s="44">
         <v>2</v>
@@ -18457,7 +18435,7 @@
         <v>537</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G18" s="12">
         <v>0</v>
@@ -18475,18 +18453,18 @@
         <v>0</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="11" t="s">
-        <v>1045</v>
+        <v>1030</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="C19" s="44">
         <v>2</v>
@@ -18498,7 +18476,7 @@
         <v>502</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G19" s="12">
         <v>0</v>
@@ -18524,10 +18502,10 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="11" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
       <c r="C20" s="44">
         <v>2</v>
@@ -18539,7 +18517,7 @@
         <v>539</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G20" s="12">
         <v>0</v>
@@ -18565,10 +18543,10 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="11" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>1031</v>
+        <v>1016</v>
       </c>
       <c r="C21" s="44">
         <v>3</v>
@@ -18606,10 +18584,10 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="11" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="C22" s="44">
         <v>3</v>
@@ -18621,7 +18599,7 @@
         <v>539</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
@@ -18647,10 +18625,10 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="11" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>1035</v>
+        <v>1020</v>
       </c>
       <c r="C23" s="44">
         <v>3</v>
@@ -18662,7 +18640,7 @@
         <v>537</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G23" s="12">
         <v>0</v>
@@ -18680,18 +18658,18 @@
         <v>0</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="11" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="C24" s="44">
         <v>3</v>
@@ -18703,7 +18681,7 @@
         <v>502</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G24" s="12">
         <v>0</v>
@@ -18729,10 +18707,10 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="11" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
       <c r="C25" s="44">
         <v>3</v>
@@ -18744,7 +18722,7 @@
         <v>539</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="G25" s="12">
         <v>0</v>
@@ -20184,7 +20162,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="22" t="s">
-        <v>610</v>
+        <v>595</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>14</v>
@@ -20196,95 +20174,95 @@
         <v>222</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>611</v>
+        <v>596</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>612</v>
+        <v>597</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>613</v>
+        <v>598</v>
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="30" t="s">
-        <v>614</v>
+        <v>599</v>
       </c>
       <c r="B2" s="30" t="s">
         <v>560</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>615</v>
+        <v>600</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>685</v>
+        <v>670</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>1072</v>
+        <v>1057</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="13" t="s">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="E3" s="13">
         <v>0</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H3" s="13">
         <v>1</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="13" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>627</v>
+        <v>612</v>
       </c>
       <c r="C4" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="E4" s="13">
         <v>0</v>
@@ -20293,7 +20271,7 @@
         <v>128</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H4" s="13">
         <v>1</v>
@@ -20304,16 +20282,16 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="13" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="E5" s="13">
         <v>0</v>
@@ -20322,7 +20300,7 @@
         <v>128</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H5" s="13">
         <v>1</v>
@@ -20333,16 +20311,16 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="13" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="C6" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="E6" s="13">
         <v>0</v>
@@ -20351,7 +20329,7 @@
         <v>128</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H6" s="13">
         <v>1</v>
@@ -20362,16 +20340,16 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="13" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>634</v>
+        <v>619</v>
       </c>
       <c r="C7" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
@@ -20380,7 +20358,7 @@
         <v>128</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H7" s="12">
         <v>1</v>
@@ -20391,16 +20369,16 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="13" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
@@ -20409,7 +20387,7 @@
         <v>128</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H8" s="12">
         <v>1</v>
@@ -20420,16 +20398,16 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="13" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>639</v>
+        <v>624</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
@@ -20438,7 +20416,7 @@
         <v>128</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H9" s="12">
         <v>1</v>
@@ -20449,16 +20427,16 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="13" t="s">
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>641</v>
+        <v>626</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
@@ -20467,7 +20445,7 @@
         <v>128</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H10" s="12">
         <v>1</v>
@@ -20478,16 +20456,16 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="13" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>645</v>
+        <v>630</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>131</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="E11" s="12">
         <v>0</v>
@@ -20496,7 +20474,7 @@
         <v>128</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H11" s="12">
         <v>1</v>
@@ -20507,16 +20485,16 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="13" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>647</v>
+        <v>632</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>648</v>
+        <v>633</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>649</v>
+        <v>634</v>
       </c>
       <c r="E12" s="12">
         <v>0</v>
@@ -20525,65 +20503,65 @@
         <v>128</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H12" s="12">
         <v>1</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="13" t="s">
-        <v>651</v>
+        <v>636</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>652</v>
+        <v>637</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>653</v>
+        <v>638</v>
       </c>
       <c r="D13" s="12">
         <v>0</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>654</v>
+        <v>639</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H13" s="12">
         <v>1</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="13" t="s">
-        <v>656</v>
+        <v>641</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>653</v>
+        <v>638</v>
       </c>
       <c r="D14" s="12">
         <v>0</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>654</v>
+        <v>639</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H14" s="12">
         <v>1</v>
@@ -20594,25 +20572,25 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="13" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="D15" s="12">
         <v>0</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H15" s="12">
         <v>1</v>
@@ -20623,25 +20601,25 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="13" t="s">
-        <v>661</v>
+        <v>646</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>662</v>
+        <v>647</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>662</v>
+        <v>647</v>
       </c>
       <c r="D16" s="12">
         <v>0</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H16" s="12">
         <v>1</v>
@@ -20652,25 +20630,25 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="13" t="s">
-        <v>664</v>
+        <v>649</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="D17" s="12">
         <v>0</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H17" s="12">
         <v>1</v>
@@ -20681,25 +20659,25 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="13" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="D18" s="12">
         <v>0</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H18" s="12">
         <v>1</v>
@@ -20710,25 +20688,25 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="13" t="s">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="D19" s="12">
         <v>0</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H19" s="12">
         <v>1</v>
@@ -20739,25 +20717,25 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="13" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="D20" s="12">
         <v>0</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H20" s="12">
         <v>1</v>
@@ -20768,25 +20746,25 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="13" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="D21" s="12">
         <v>0</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H21" s="12">
         <v>1</v>
@@ -20797,25 +20775,25 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="13" t="s">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>681</v>
+        <v>666</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="D22" s="12">
         <v>0</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>682</v>
+        <v>667</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>128</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="H22" s="12">
         <v>1</v>
@@ -21096,22 +21074,22 @@
     </row>
     <row r="2" spans="1:16" ht="33" customHeight="1">
       <c r="A2" s="23" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>576</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>689</v>
+        <v>674</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>691</v>
+        <v>676</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>7</v>
@@ -21127,10 +21105,10 @@
     </row>
     <row r="3" spans="1:16" ht="33" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="C3" s="12">
         <v>27</v>
@@ -21158,10 +21136,10 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="C4" s="12">
         <v>29</v>
@@ -21187,10 +21165,10 @@
     </row>
     <row r="5" spans="1:16" ht="33" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="C5" s="12">
         <v>23</v>
@@ -21218,10 +21196,10 @@
     </row>
     <row r="6" spans="1:16" ht="33" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="C6" s="12">
         <v>26</v>
@@ -21247,10 +21225,10 @@
     </row>
     <row r="7" spans="1:16" ht="33" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="C7" s="12">
         <v>34</v>
@@ -21276,10 +21254,10 @@
     </row>
     <row r="8" spans="1:16" ht="33" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="C8" s="12">
         <v>28</v>
@@ -21307,10 +21285,10 @@
     </row>
     <row r="9" spans="1:16" ht="33" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="C9" s="12">
         <v>31</v>
@@ -21336,10 +21314,10 @@
     </row>
     <row r="10" spans="1:16" ht="33" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="C10" s="12">
         <v>35</v>
@@ -21365,10 +21343,10 @@
     </row>
     <row r="11" spans="1:16" ht="33" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>698</v>
+        <v>683</v>
       </c>
       <c r="C11" s="12">
         <v>28</v>
@@ -21396,10 +21374,10 @@
     </row>
     <row r="12" spans="1:16" ht="33" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="C12" s="12">
         <v>25</v>
@@ -21425,10 +21403,10 @@
     </row>
     <row r="13" spans="1:16" ht="33" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="C13" s="12">
         <v>26</v>
@@ -21454,10 +21432,10 @@
     </row>
     <row r="14" spans="1:16" ht="33" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="C14" s="12">
         <v>21</v>
@@ -21485,10 +21463,10 @@
     </row>
     <row r="15" spans="1:16" ht="33" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="C15" s="12">
         <v>30</v>
@@ -21514,10 +21492,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="12" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="C16" s="12">
         <v>33</v>
@@ -21543,10 +21521,10 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="12" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="C17" s="12">
         <v>32</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16860" tabRatio="550" activeTab="2"/>
+    <workbookView windowHeight="17580" tabRatio="550" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -3127,7 +3127,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3174,12 +3174,6 @@
       <name val="맑은 고딕"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
     </font>
     <font>
       <b/>
@@ -3711,28 +3705,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3741,128 +3738,125 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3971,31 +3965,25 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4255,7 +4243,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{DFCD992E-9DA2-45AC-A6EE-77C02303A8DB}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{372E29BF-875D-4DA2-817B-0EC0661D44EE}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -4264,7 +4252,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{0F161735-A194-4DC0-9AF7-3393BDD2938D}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{777630CB-AB2A-40EA-BBBC-166156D71CAF}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -4581,7 +4569,7 @@
       <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="45" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="19" t="s">
@@ -4596,43 +4584,43 @@
       <c r="J1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="51" t="s">
+      <c r="S1" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="51" t="s">
+      <c r="T1" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="51" t="s">
+      <c r="U1" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="51" t="s">
+      <c r="V1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="W1" s="49" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4667,43 +4655,43 @@
       <c r="J2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="M2" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="N2" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="51" t="s">
+      <c r="O2" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="51" t="s">
+      <c r="S2" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="51" t="s">
+      <c r="T2" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="51" t="s">
+      <c r="U2" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="51" t="s">
+      <c r="V2" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="51" t="s">
+      <c r="W2" s="49" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4738,46 +4726,46 @@
       <c r="J3" s="7">
         <v>1</v>
       </c>
-      <c r="K3" s="52" t="s">
+      <c r="K3" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="52" t="s">
+      <c r="L3" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="52" t="s">
+      <c r="M3" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="52" t="s">
+      <c r="N3" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="52" t="s">
+      <c r="O3" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="P3" s="52" t="s">
+      <c r="P3" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="Q3" s="52" t="s">
+      <c r="Q3" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="R3" s="52" t="s">
+      <c r="R3" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="52" t="s">
+      <c r="S3" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="52" t="s">
+      <c r="T3" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="U3" s="52" t="s">
+      <c r="U3" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="V3" s="52" t="s">
+      <c r="V3" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="W3" s="52" t="s">
+      <c r="W3" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="X3" s="52"/>
+      <c r="X3" s="50"/>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="8" t="s">
@@ -4810,46 +4798,46 @@
       <c r="J4" s="7">
         <v>1</v>
       </c>
-      <c r="K4" s="52" t="s">
+      <c r="K4" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="52" t="s">
+      <c r="L4" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="M4" s="52" t="s">
+      <c r="M4" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="N4" s="52" t="s">
+      <c r="N4" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="O4" s="52" t="s">
+      <c r="O4" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="P4" s="52" t="s">
+      <c r="P4" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="Q4" s="52" t="s">
+      <c r="Q4" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="R4" s="52" t="s">
+      <c r="R4" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="S4" s="52" t="s">
+      <c r="S4" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="T4" s="52" t="s">
+      <c r="T4" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="U4" s="52" t="s">
+      <c r="U4" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="V4" s="52" t="s">
+      <c r="V4" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="W4" s="52" t="s">
+      <c r="W4" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="X4" s="52"/>
+      <c r="X4" s="50"/>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="8" t="s">
@@ -4882,229 +4870,229 @@
       <c r="J5" s="7">
         <v>1</v>
       </c>
-      <c r="K5" s="52" t="s">
+      <c r="K5" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="L5" s="52" t="s">
+      <c r="L5" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="M5" s="52" t="s">
+      <c r="M5" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="N5" s="52" t="s">
+      <c r="N5" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="O5" s="52" t="s">
+      <c r="O5" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="P5" s="52" t="s">
+      <c r="P5" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="Q5" s="52" t="s">
+      <c r="Q5" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="R5" s="52" t="s">
+      <c r="R5" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="S5" s="52" t="s">
+      <c r="S5" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="T5" s="52" t="s">
+      <c r="T5" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="U5" s="52" t="s">
+      <c r="U5" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="V5" s="52" t="s">
+      <c r="V5" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="W5" s="52" t="s">
+      <c r="W5" s="50" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="48"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="50"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
+      <c r="A7" s="48"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
+      <c r="A8" s="46"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
       <c r="K8" s="25"/>
       <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
+      <c r="A9" s="46"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
       <c r="K9" s="25"/>
       <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
+      <c r="A10" s="46"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
       <c r="K10" s="25"/>
       <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
+      <c r="A11" s="46"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="48"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
+      <c r="A12" s="46"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
       <c r="K12" s="25"/>
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
+      <c r="A14" s="46"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
       <c r="K14" s="25"/>
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="48"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
       <c r="K15" s="25"/>
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="48"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
+      <c r="A16" s="46"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="48"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
+      <c r="A17" s="46"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
       <c r="K17" s="25"/>
       <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9743,10 +9731,10 @@
       <c r="A3" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D3" s="7">
@@ -9790,10 +9778,10 @@
       <c r="A4" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D4" s="7">
@@ -9837,10 +9825,10 @@
       <c r="A5" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D5" s="7">
@@ -9884,10 +9872,10 @@
       <c r="A6" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D6" s="7">
@@ -9931,10 +9919,10 @@
       <c r="A7" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D7" s="7">
@@ -9978,10 +9966,10 @@
       <c r="A8" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D8" s="7">
@@ -10025,10 +10013,10 @@
       <c r="A9" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D9" s="7">
@@ -10072,10 +10060,10 @@
       <c r="A10" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D10" s="7">
@@ -10119,10 +10107,10 @@
       <c r="A11" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D11" s="7">
@@ -10166,10 +10154,10 @@
       <c r="A12" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="44" t="s">
         <v>177</v>
       </c>
       <c r="D12" s="7">
@@ -10213,10 +10201,10 @@
       <c r="A13" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="44" t="s">
         <v>177</v>
       </c>
       <c r="D13" s="7">
@@ -10260,10 +10248,10 @@
       <c r="A14" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="44" t="s">
         <v>194</v>
       </c>
       <c r="D14" s="7">
@@ -10486,25 +10474,25 @@
       <c r="K3" s="29">
         <v>1</v>
       </c>
-      <c r="L3" s="42">
-        <v>0</v>
-      </c>
-      <c r="M3" s="42">
-        <v>0</v>
-      </c>
-      <c r="N3" s="42">
-        <v>0</v>
-      </c>
-      <c r="O3" s="42">
-        <v>0</v>
-      </c>
-      <c r="P3" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="43" t="s">
+      <c r="L3" s="40">
+        <v>0</v>
+      </c>
+      <c r="M3" s="40">
+        <v>0</v>
+      </c>
+      <c r="N3" s="40">
+        <v>0</v>
+      </c>
+      <c r="O3" s="40">
+        <v>0</v>
+      </c>
+      <c r="P3" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="R3" s="43" t="s">
+      <c r="R3" s="41" t="s">
         <v>251</v>
       </c>
       <c r="S3" s="8" t="s">
@@ -10543,25 +10531,25 @@
       <c r="K4" s="29">
         <v>1</v>
       </c>
-      <c r="L4" s="42">
-        <v>0</v>
-      </c>
-      <c r="M4" s="42">
-        <v>0</v>
-      </c>
-      <c r="N4" s="42">
-        <v>0</v>
-      </c>
-      <c r="O4" s="42">
-        <v>0</v>
-      </c>
-      <c r="P4" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="43" t="s">
+      <c r="L4" s="40">
+        <v>0</v>
+      </c>
+      <c r="M4" s="40">
+        <v>0</v>
+      </c>
+      <c r="N4" s="40">
+        <v>0</v>
+      </c>
+      <c r="O4" s="40">
+        <v>0</v>
+      </c>
+      <c r="P4" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="R4" s="43" t="s">
+      <c r="R4" s="41" t="s">
         <v>251</v>
       </c>
       <c r="S4" s="7" t="s">
@@ -10600,25 +10588,25 @@
       <c r="K5" s="29">
         <v>1</v>
       </c>
-      <c r="L5" s="42">
-        <v>0</v>
-      </c>
-      <c r="M5" s="42">
-        <v>0</v>
-      </c>
-      <c r="N5" s="42">
-        <v>0</v>
-      </c>
-      <c r="O5" s="42">
-        <v>0</v>
-      </c>
-      <c r="P5" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="43" t="s">
+      <c r="L5" s="40">
+        <v>0</v>
+      </c>
+      <c r="M5" s="40">
+        <v>0</v>
+      </c>
+      <c r="N5" s="40">
+        <v>0</v>
+      </c>
+      <c r="O5" s="40">
+        <v>0</v>
+      </c>
+      <c r="P5" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="R5" s="43" t="s">
+      <c r="R5" s="41" t="s">
         <v>251</v>
       </c>
       <c r="S5" s="7" t="s">
@@ -10663,22 +10651,22 @@
       <c r="M6" s="29">
         <v>1</v>
       </c>
-      <c r="N6" s="42">
-        <v>0</v>
-      </c>
-      <c r="O6" s="42">
-        <v>0</v>
-      </c>
-      <c r="P6" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="43">
-        <v>0</v>
-      </c>
-      <c r="R6" s="43" t="s">
+      <c r="N6" s="40">
+        <v>0</v>
+      </c>
+      <c r="O6" s="40">
+        <v>0</v>
+      </c>
+      <c r="P6" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="41">
+        <v>0</v>
+      </c>
+      <c r="R6" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="41">
         <v>0</v>
       </c>
     </row>
@@ -10720,22 +10708,22 @@
       <c r="M7" s="29">
         <v>2</v>
       </c>
-      <c r="N7" s="42">
-        <v>0</v>
-      </c>
-      <c r="O7" s="42">
-        <v>0</v>
-      </c>
-      <c r="P7" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="43">
-        <v>0</v>
-      </c>
-      <c r="R7" s="43" t="s">
+      <c r="N7" s="40">
+        <v>0</v>
+      </c>
+      <c r="O7" s="40">
+        <v>0</v>
+      </c>
+      <c r="P7" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="41">
+        <v>0</v>
+      </c>
+      <c r="R7" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="S7" s="43">
+      <c r="S7" s="41">
         <v>0</v>
       </c>
     </row>
@@ -10777,22 +10765,22 @@
       <c r="M8" s="29">
         <v>2</v>
       </c>
-      <c r="N8" s="42">
-        <v>0</v>
-      </c>
-      <c r="O8" s="42">
-        <v>0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="43">
-        <v>0</v>
-      </c>
-      <c r="R8" s="43" t="s">
+      <c r="N8" s="40">
+        <v>0</v>
+      </c>
+      <c r="O8" s="40">
+        <v>0</v>
+      </c>
+      <c r="P8" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="41">
+        <v>0</v>
+      </c>
+      <c r="R8" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="S8" s="43">
+      <c r="S8" s="41">
         <v>0</v>
       </c>
     </row>
@@ -10834,22 +10822,22 @@
       <c r="M9" s="29">
         <v>3</v>
       </c>
-      <c r="N9" s="42">
-        <v>0</v>
-      </c>
-      <c r="O9" s="42">
-        <v>0</v>
-      </c>
-      <c r="P9" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="43">
-        <v>0</v>
-      </c>
-      <c r="R9" s="43" t="s">
+      <c r="N9" s="40">
+        <v>0</v>
+      </c>
+      <c r="O9" s="40">
+        <v>0</v>
+      </c>
+      <c r="P9" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="41">
+        <v>0</v>
+      </c>
+      <c r="R9" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="S9" s="43">
+      <c r="S9" s="41">
         <v>0</v>
       </c>
     </row>
@@ -10891,22 +10879,22 @@
       <c r="M10" s="29">
         <v>2</v>
       </c>
-      <c r="N10" s="42">
-        <v>0</v>
-      </c>
-      <c r="O10" s="42">
-        <v>0</v>
-      </c>
-      <c r="P10" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="43">
-        <v>0</v>
-      </c>
-      <c r="R10" s="43" t="s">
+      <c r="N10" s="40">
+        <v>0</v>
+      </c>
+      <c r="O10" s="40">
+        <v>0</v>
+      </c>
+      <c r="P10" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="41">
+        <v>0</v>
+      </c>
+      <c r="R10" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="S10" s="43">
+      <c r="S10" s="41">
         <v>0</v>
       </c>
     </row>
@@ -10948,22 +10936,22 @@
       <c r="M11" s="29">
         <v>3</v>
       </c>
-      <c r="N11" s="42">
-        <v>0</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="43">
-        <v>0</v>
-      </c>
-      <c r="R11" s="43" t="s">
+      <c r="N11" s="40">
+        <v>0</v>
+      </c>
+      <c r="O11" s="40">
+        <v>0</v>
+      </c>
+      <c r="P11" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="41">
+        <v>0</v>
+      </c>
+      <c r="R11" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="S11" s="43">
+      <c r="S11" s="41">
         <v>0</v>
       </c>
     </row>
@@ -11001,10 +10989,10 @@
       <c r="K12" s="29">
         <v>1</v>
       </c>
-      <c r="L12" s="42">
-        <v>0</v>
-      </c>
-      <c r="M12" s="42">
+      <c r="L12" s="40">
+        <v>0</v>
+      </c>
+      <c r="M12" s="40">
         <v>0</v>
       </c>
       <c r="N12" s="8" t="s">
@@ -11013,13 +11001,13 @@
       <c r="O12" s="29">
         <v>2</v>
       </c>
-      <c r="P12" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="44" t="s">
+      <c r="P12" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R12" s="43" t="s">
+      <c r="R12" s="41" t="s">
         <v>279</v>
       </c>
       <c r="S12" s="8" t="s">
@@ -11062,10 +11050,10 @@
       <c r="K13" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L13" s="42">
-        <v>0</v>
-      </c>
-      <c r="M13" s="42">
+      <c r="L13" s="40">
+        <v>0</v>
+      </c>
+      <c r="M13" s="40">
         <v>0</v>
       </c>
       <c r="N13" s="8" t="s">
@@ -11074,13 +11062,13 @@
       <c r="O13" s="29">
         <v>2</v>
       </c>
-      <c r="P13" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="44" t="s">
+      <c r="P13" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R13" s="43" t="s">
+      <c r="R13" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S13" s="8" t="s">
@@ -11123,10 +11111,10 @@
       <c r="K14" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L14" s="42">
-        <v>0</v>
-      </c>
-      <c r="M14" s="42">
+      <c r="L14" s="40">
+        <v>0</v>
+      </c>
+      <c r="M14" s="40">
         <v>0</v>
       </c>
       <c r="N14" s="8" t="s">
@@ -11135,13 +11123,13 @@
       <c r="O14" s="29">
         <v>3</v>
       </c>
-      <c r="P14" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="44" t="s">
+      <c r="P14" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R14" s="43" t="s">
+      <c r="R14" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S14" s="8" t="s">
@@ -11184,10 +11172,10 @@
       <c r="K15" s="29">
         <v>1</v>
       </c>
-      <c r="L15" s="42">
-        <v>0</v>
-      </c>
-      <c r="M15" s="42">
+      <c r="L15" s="40">
+        <v>0</v>
+      </c>
+      <c r="M15" s="40">
         <v>0</v>
       </c>
       <c r="N15" s="8" t="s">
@@ -11196,13 +11184,13 @@
       <c r="O15" s="29">
         <v>3</v>
       </c>
-      <c r="P15" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="44" t="s">
+      <c r="P15" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R15" s="43" t="s">
+      <c r="R15" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S15" s="8" t="s">
@@ -11245,10 +11233,10 @@
       <c r="K16" s="7">
         <v>1</v>
       </c>
-      <c r="L16" s="42">
-        <v>0</v>
-      </c>
-      <c r="M16" s="42">
+      <c r="L16" s="40">
+        <v>0</v>
+      </c>
+      <c r="M16" s="40">
         <v>0</v>
       </c>
       <c r="N16" s="8" t="s">
@@ -11257,13 +11245,13 @@
       <c r="O16" s="29">
         <v>2</v>
       </c>
-      <c r="P16" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="44" t="s">
+      <c r="P16" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R16" s="43" t="s">
+      <c r="R16" s="41" t="s">
         <v>279</v>
       </c>
       <c r="S16" s="8" t="s">
@@ -11306,10 +11294,10 @@
       <c r="K17" s="7">
         <v>1</v>
       </c>
-      <c r="L17" s="42">
-        <v>0</v>
-      </c>
-      <c r="M17" s="42">
+      <c r="L17" s="40">
+        <v>0</v>
+      </c>
+      <c r="M17" s="40">
         <v>0</v>
       </c>
       <c r="N17" s="8" t="s">
@@ -11318,13 +11306,13 @@
       <c r="O17" s="29">
         <v>2</v>
       </c>
-      <c r="P17" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="44" t="s">
+      <c r="P17" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R17" s="43" t="s">
+      <c r="R17" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S17" s="8" t="s">
@@ -11367,10 +11355,10 @@
       <c r="K18" s="7">
         <v>1</v>
       </c>
-      <c r="L18" s="42">
-        <v>0</v>
-      </c>
-      <c r="M18" s="42">
+      <c r="L18" s="40">
+        <v>0</v>
+      </c>
+      <c r="M18" s="40">
         <v>0</v>
       </c>
       <c r="N18" s="7" t="s">
@@ -11379,13 +11367,13 @@
       <c r="O18" s="7">
         <v>25</v>
       </c>
-      <c r="P18" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="44" t="s">
+      <c r="P18" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R18" s="43" t="s">
+      <c r="R18" s="41" t="s">
         <v>261</v>
       </c>
       <c r="S18" s="8" t="s">
@@ -11428,10 +11416,10 @@
       <c r="K19" s="7">
         <v>1</v>
       </c>
-      <c r="L19" s="42">
-        <v>0</v>
-      </c>
-      <c r="M19" s="42">
+      <c r="L19" s="40">
+        <v>0</v>
+      </c>
+      <c r="M19" s="40">
         <v>0</v>
       </c>
       <c r="N19" s="7" t="s">
@@ -11440,13 +11428,13 @@
       <c r="O19" s="7">
         <v>30</v>
       </c>
-      <c r="P19" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="44" t="s">
+      <c r="P19" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R19" s="43" t="s">
+      <c r="R19" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S19" s="8" t="s">
@@ -11489,10 +11477,10 @@
       <c r="K20" s="7">
         <v>1</v>
       </c>
-      <c r="L20" s="42">
-        <v>0</v>
-      </c>
-      <c r="M20" s="42">
+      <c r="L20" s="40">
+        <v>0</v>
+      </c>
+      <c r="M20" s="40">
         <v>0</v>
       </c>
       <c r="N20" s="7" t="s">
@@ -11501,13 +11489,13 @@
       <c r="O20" s="7">
         <v>25</v>
       </c>
-      <c r="P20" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="44" t="s">
+      <c r="P20" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R20" s="43" t="s">
+      <c r="R20" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S20" s="8" t="s">
@@ -11550,10 +11538,10 @@
       <c r="K21" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L21" s="42">
-        <v>0</v>
-      </c>
-      <c r="M21" s="42">
+      <c r="L21" s="40">
+        <v>0</v>
+      </c>
+      <c r="M21" s="40">
         <v>0</v>
       </c>
       <c r="N21" s="7" t="s">
@@ -11562,13 +11550,13 @@
       <c r="O21" s="7">
         <v>35</v>
       </c>
-      <c r="P21" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="44" t="s">
+      <c r="P21" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R21" s="43" t="s">
+      <c r="R21" s="41" t="s">
         <v>279</v>
       </c>
       <c r="S21" s="8" t="s">
@@ -11611,10 +11599,10 @@
       <c r="K22" s="7">
         <v>1</v>
       </c>
-      <c r="L22" s="42">
-        <v>0</v>
-      </c>
-      <c r="M22" s="42">
+      <c r="L22" s="40">
+        <v>0</v>
+      </c>
+      <c r="M22" s="40">
         <v>0</v>
       </c>
       <c r="N22" s="7" t="s">
@@ -11623,20 +11611,20 @@
       <c r="O22" s="7">
         <v>40</v>
       </c>
-      <c r="P22" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="44" t="s">
+      <c r="P22" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R22" s="43" t="s">
+      <c r="R22" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S22" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="U22" s="45"/>
-      <c r="V22" s="45"/>
+      <c r="U22" s="43"/>
+      <c r="V22" s="43"/>
     </row>
     <row r="23" spans="1:22">
       <c r="A23" s="8" t="s">
@@ -11672,10 +11660,10 @@
       <c r="K23" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L23" s="42">
-        <v>0</v>
-      </c>
-      <c r="M23" s="42">
+      <c r="L23" s="40">
+        <v>0</v>
+      </c>
+      <c r="M23" s="40">
         <v>0</v>
       </c>
       <c r="N23" s="7" t="s">
@@ -11684,20 +11672,20 @@
       <c r="O23" s="7">
         <v>30</v>
       </c>
-      <c r="P23" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="44" t="s">
+      <c r="P23" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R23" s="43" t="s">
+      <c r="R23" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S23" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="U23" s="45"/>
-      <c r="V23" s="45"/>
+      <c r="U23" s="43"/>
+      <c r="V23" s="43"/>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" s="8" t="s">
@@ -11733,10 +11721,10 @@
       <c r="K24" s="7">
         <v>1</v>
       </c>
-      <c r="L24" s="42">
-        <v>0</v>
-      </c>
-      <c r="M24" s="42">
+      <c r="L24" s="40">
+        <v>0</v>
+      </c>
+      <c r="M24" s="40">
         <v>0</v>
       </c>
       <c r="N24" s="7" t="s">
@@ -11745,20 +11733,20 @@
       <c r="O24" s="7">
         <v>30</v>
       </c>
-      <c r="P24" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="44" t="s">
+      <c r="P24" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R24" s="43" t="s">
+      <c r="R24" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S24" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="U24" s="45"/>
-      <c r="V24" s="45"/>
+      <c r="U24" s="43"/>
+      <c r="V24" s="43"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="8" t="s">
@@ -11794,10 +11782,10 @@
       <c r="K25" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L25" s="42">
-        <v>0</v>
-      </c>
-      <c r="M25" s="42">
+      <c r="L25" s="40">
+        <v>0</v>
+      </c>
+      <c r="M25" s="40">
         <v>0</v>
       </c>
       <c r="N25" s="7" t="s">
@@ -11806,13 +11794,13 @@
       <c r="O25" s="7">
         <v>25</v>
       </c>
-      <c r="P25" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="44" t="s">
+      <c r="P25" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R25" s="43" t="s">
+      <c r="R25" s="41" t="s">
         <v>261</v>
       </c>
       <c r="S25" s="8" t="s">
@@ -11855,10 +11843,10 @@
       <c r="K26" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L26" s="42">
-        <v>0</v>
-      </c>
-      <c r="M26" s="42">
+      <c r="L26" s="40">
+        <v>0</v>
+      </c>
+      <c r="M26" s="40">
         <v>0</v>
       </c>
       <c r="N26" s="7" t="s">
@@ -11867,20 +11855,20 @@
       <c r="O26" s="7">
         <v>35</v>
       </c>
-      <c r="P26" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="44" t="s">
+      <c r="P26" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R26" s="43" t="s">
+      <c r="R26" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S26" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="U26" s="45"/>
-      <c r="V26" s="45"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
     </row>
     <row r="27" spans="1:22">
       <c r="A27" s="8" t="s">
@@ -11916,10 +11904,10 @@
       <c r="K27" s="7">
         <v>1</v>
       </c>
-      <c r="L27" s="42">
-        <v>0</v>
-      </c>
-      <c r="M27" s="42">
+      <c r="L27" s="40">
+        <v>0</v>
+      </c>
+      <c r="M27" s="40">
         <v>0</v>
       </c>
       <c r="N27" s="7" t="s">
@@ -11928,13 +11916,13 @@
       <c r="O27" s="7">
         <v>40</v>
       </c>
-      <c r="P27" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="44" t="s">
+      <c r="P27" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R27" s="43" t="s">
+      <c r="R27" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S27" s="8" t="s">
@@ -11977,10 +11965,10 @@
       <c r="K28" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L28" s="42">
-        <v>0</v>
-      </c>
-      <c r="M28" s="42">
+      <c r="L28" s="40">
+        <v>0</v>
+      </c>
+      <c r="M28" s="40">
         <v>0</v>
       </c>
       <c r="N28" s="7" t="s">
@@ -11989,13 +11977,13 @@
       <c r="O28" s="7">
         <v>35</v>
       </c>
-      <c r="P28" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="44" t="s">
+      <c r="P28" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R28" s="43" t="s">
+      <c r="R28" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S28" s="8" t="s">
@@ -12038,10 +12026,10 @@
       <c r="K29" s="7">
         <v>1</v>
       </c>
-      <c r="L29" s="42">
-        <v>0</v>
-      </c>
-      <c r="M29" s="42">
+      <c r="L29" s="40">
+        <v>0</v>
+      </c>
+      <c r="M29" s="40">
         <v>0</v>
       </c>
       <c r="N29" s="7" t="s">
@@ -12050,20 +12038,20 @@
       <c r="O29" s="7">
         <v>25</v>
       </c>
-      <c r="P29" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="44" t="s">
+      <c r="P29" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R29" s="43" t="s">
+      <c r="R29" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S29" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="U29" s="45"/>
-      <c r="V29" s="45"/>
+      <c r="U29" s="43"/>
+      <c r="V29" s="43"/>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="29" t="s">
@@ -12099,10 +12087,10 @@
       <c r="K30" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L30" s="42">
-        <v>0</v>
-      </c>
-      <c r="M30" s="42">
+      <c r="L30" s="40">
+        <v>0</v>
+      </c>
+      <c r="M30" s="40">
         <v>0</v>
       </c>
       <c r="N30" s="7" t="s">
@@ -12111,13 +12099,13 @@
       <c r="O30" s="7">
         <v>30</v>
       </c>
-      <c r="P30" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="44" t="s">
+      <c r="P30" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R30" s="43" t="s">
+      <c r="R30" s="41" t="s">
         <v>279</v>
       </c>
       <c r="S30" s="8" t="s">
@@ -12160,10 +12148,10 @@
       <c r="K31" s="7">
         <v>1</v>
       </c>
-      <c r="L31" s="42">
-        <v>0</v>
-      </c>
-      <c r="M31" s="42">
+      <c r="L31" s="40">
+        <v>0</v>
+      </c>
+      <c r="M31" s="40">
         <v>0</v>
       </c>
       <c r="N31" s="7" t="s">
@@ -12172,20 +12160,20 @@
       <c r="O31" s="7">
         <v>30</v>
       </c>
-      <c r="P31" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="44" t="s">
+      <c r="P31" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R31" s="43" t="s">
+      <c r="R31" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S31" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="U31" s="45"/>
-      <c r="V31" s="45"/>
+      <c r="U31" s="43"/>
+      <c r="V31" s="43"/>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="29" t="s">
@@ -12221,10 +12209,10 @@
       <c r="K32" s="7">
         <v>1</v>
       </c>
-      <c r="L32" s="42">
-        <v>0</v>
-      </c>
-      <c r="M32" s="42">
+      <c r="L32" s="40">
+        <v>0</v>
+      </c>
+      <c r="M32" s="40">
         <v>0</v>
       </c>
       <c r="N32" s="7" t="s">
@@ -12233,20 +12221,20 @@
       <c r="O32" s="7">
         <v>40</v>
       </c>
-      <c r="P32" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="44" t="s">
+      <c r="P32" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R32" s="43" t="s">
+      <c r="R32" s="41" t="s">
         <v>279</v>
       </c>
       <c r="S32" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="U32" s="45"/>
-      <c r="V32" s="45"/>
+      <c r="U32" s="43"/>
+      <c r="V32" s="43"/>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="8" t="s">
@@ -12282,10 +12270,10 @@
       <c r="K33" s="7">
         <v>1</v>
       </c>
-      <c r="L33" s="42">
-        <v>0</v>
-      </c>
-      <c r="M33" s="42">
+      <c r="L33" s="40">
+        <v>0</v>
+      </c>
+      <c r="M33" s="40">
         <v>0</v>
       </c>
       <c r="N33" s="7" t="s">
@@ -12294,20 +12282,20 @@
       <c r="O33" s="7">
         <v>20</v>
       </c>
-      <c r="P33" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="44" t="s">
+      <c r="P33" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R33" s="43" t="s">
+      <c r="R33" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S33" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="U33" s="45"/>
-      <c r="V33" s="45"/>
+      <c r="U33" s="43"/>
+      <c r="V33" s="43"/>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="29" t="s">
@@ -12343,10 +12331,10 @@
       <c r="K34" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L34" s="42">
-        <v>0</v>
-      </c>
-      <c r="M34" s="42">
+      <c r="L34" s="40">
+        <v>0</v>
+      </c>
+      <c r="M34" s="40">
         <v>0</v>
       </c>
       <c r="N34" s="7" t="s">
@@ -12355,13 +12343,13 @@
       <c r="O34" s="7">
         <v>25</v>
       </c>
-      <c r="P34" s="42">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="44" t="s">
+      <c r="P34" s="40">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R34" s="43" t="s">
+      <c r="R34" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S34" s="8" t="s">
@@ -12404,10 +12392,10 @@
       <c r="K35" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L35" s="42">
-        <v>0</v>
-      </c>
-      <c r="M35" s="42">
+      <c r="L35" s="40">
+        <v>0</v>
+      </c>
+      <c r="M35" s="40">
         <v>0</v>
       </c>
       <c r="N35" s="7" t="s">
@@ -12416,20 +12404,20 @@
       <c r="O35" s="7">
         <v>25</v>
       </c>
-      <c r="P35" s="42">
+      <c r="P35" s="40">
         <v>-1</v>
       </c>
-      <c r="Q35" s="44" t="s">
+      <c r="Q35" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R35" s="43" t="s">
+      <c r="R35" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S35" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="U35" s="45"/>
-      <c r="V35" s="45"/>
+      <c r="U35" s="43"/>
+      <c r="V35" s="43"/>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="29" t="s">
@@ -12465,10 +12453,10 @@
       <c r="K36" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L36" s="42">
-        <v>0</v>
-      </c>
-      <c r="M36" s="42">
+      <c r="L36" s="40">
+        <v>0</v>
+      </c>
+      <c r="M36" s="40">
         <v>0</v>
       </c>
       <c r="N36" s="7" t="s">
@@ -12477,20 +12465,20 @@
       <c r="O36" s="7">
         <v>30</v>
       </c>
-      <c r="P36" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="44" t="s">
+      <c r="P36" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R36" s="43" t="s">
+      <c r="R36" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S36" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="U36" s="45"/>
-      <c r="V36" s="45"/>
+      <c r="U36" s="43"/>
+      <c r="V36" s="43"/>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" s="29" t="s">
@@ -12526,10 +12514,10 @@
       <c r="K37" s="7">
         <v>1</v>
       </c>
-      <c r="L37" s="42">
-        <v>0</v>
-      </c>
-      <c r="M37" s="42">
+      <c r="L37" s="40">
+        <v>0</v>
+      </c>
+      <c r="M37" s="40">
         <v>0</v>
       </c>
       <c r="N37" s="7" t="s">
@@ -12538,20 +12526,20 @@
       <c r="O37" s="7">
         <v>25</v>
       </c>
-      <c r="P37" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="44" t="s">
+      <c r="P37" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R37" s="43" t="s">
+      <c r="R37" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S37" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="U37" s="45"/>
-      <c r="V37" s="45"/>
+      <c r="U37" s="43"/>
+      <c r="V37" s="43"/>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="29" t="s">
@@ -12587,10 +12575,10 @@
       <c r="K38" s="7">
         <v>1</v>
       </c>
-      <c r="L38" s="42">
-        <v>0</v>
-      </c>
-      <c r="M38" s="42">
+      <c r="L38" s="40">
+        <v>0</v>
+      </c>
+      <c r="M38" s="40">
         <v>0</v>
       </c>
       <c r="N38" s="7" t="s">
@@ -12599,20 +12587,20 @@
       <c r="O38" s="7">
         <v>30</v>
       </c>
-      <c r="P38" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="44" t="s">
+      <c r="P38" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R38" s="43" t="s">
+      <c r="R38" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S38" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="U38" s="45"/>
-      <c r="V38" s="45"/>
+      <c r="U38" s="43"/>
+      <c r="V38" s="43"/>
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="29" t="s">
@@ -12648,10 +12636,10 @@
       <c r="K39" s="7">
         <v>1</v>
       </c>
-      <c r="L39" s="42">
-        <v>0</v>
-      </c>
-      <c r="M39" s="42">
+      <c r="L39" s="40">
+        <v>0</v>
+      </c>
+      <c r="M39" s="40">
         <v>0</v>
       </c>
       <c r="N39" s="7" t="s">
@@ -12660,13 +12648,13 @@
       <c r="O39" s="7">
         <v>25</v>
       </c>
-      <c r="P39" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="44" t="s">
+      <c r="P39" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R39" s="43" t="s">
+      <c r="R39" s="41" t="s">
         <v>261</v>
       </c>
       <c r="S39" s="8" t="s">
@@ -12709,10 +12697,10 @@
       <c r="K40" s="7">
         <v>1</v>
       </c>
-      <c r="L40" s="42">
-        <v>0</v>
-      </c>
-      <c r="M40" s="42">
+      <c r="L40" s="40">
+        <v>0</v>
+      </c>
+      <c r="M40" s="40">
         <v>0</v>
       </c>
       <c r="N40" s="7" t="s">
@@ -12721,20 +12709,20 @@
       <c r="O40" s="7">
         <v>20</v>
       </c>
-      <c r="P40" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="44" t="s">
+      <c r="P40" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R40" s="43" t="s">
+      <c r="R40" s="41" t="s">
         <v>279</v>
       </c>
       <c r="S40" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="U40" s="45"/>
-      <c r="V40" s="45"/>
+      <c r="U40" s="43"/>
+      <c r="V40" s="43"/>
     </row>
     <row r="41" spans="1:22">
       <c r="A41" s="29" t="s">
@@ -12770,10 +12758,10 @@
       <c r="K41" s="7">
         <v>1</v>
       </c>
-      <c r="L41" s="42">
-        <v>0</v>
-      </c>
-      <c r="M41" s="42">
+      <c r="L41" s="40">
+        <v>0</v>
+      </c>
+      <c r="M41" s="40">
         <v>0</v>
       </c>
       <c r="N41" s="7" t="s">
@@ -12782,13 +12770,13 @@
       <c r="O41" s="7">
         <v>25</v>
       </c>
-      <c r="P41" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="44" t="s">
+      <c r="P41" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R41" s="43" t="s">
+      <c r="R41" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S41" s="8" t="s">
@@ -12831,10 +12819,10 @@
       <c r="K42" s="7">
         <v>1</v>
       </c>
-      <c r="L42" s="42">
-        <v>0</v>
-      </c>
-      <c r="M42" s="42">
+      <c r="L42" s="40">
+        <v>0</v>
+      </c>
+      <c r="M42" s="40">
         <v>0</v>
       </c>
       <c r="N42" s="7" t="s">
@@ -12843,20 +12831,20 @@
       <c r="O42" s="7">
         <v>25</v>
       </c>
-      <c r="P42" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="44" t="s">
+      <c r="P42" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="R42" s="43" t="s">
+      <c r="R42" s="41" t="s">
         <v>289</v>
       </c>
       <c r="S42" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="U42" s="45"/>
-      <c r="V42" s="45"/>
+      <c r="U42" s="43"/>
+      <c r="V42" s="43"/>
     </row>
     <row r="43" spans="1:22">
       <c r="A43" s="29"/>
@@ -12878,8 +12866,8 @@
       <c r="Q43" s="7"/>
       <c r="R43" s="7"/>
       <c r="S43" s="8"/>
-      <c r="U43" s="45"/>
-      <c r="V43" s="45"/>
+      <c r="U43" s="43"/>
+      <c r="V43" s="43"/>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="29"/>
@@ -12901,8 +12889,8 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="7"/>
       <c r="S44" s="8"/>
-      <c r="U44" s="45"/>
-      <c r="V44" s="45"/>
+      <c r="U44" s="43"/>
+      <c r="V44" s="43"/>
     </row>
     <row r="45" spans="1:22">
       <c r="A45" s="29"/>
@@ -12924,8 +12912,8 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="8"/>
-      <c r="U45" s="45"/>
-      <c r="V45" s="45"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="43"/>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="29"/>
@@ -12946,8 +12934,8 @@
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
-      <c r="U46" s="45"/>
-      <c r="V46" s="45"/>
+      <c r="U46" s="43"/>
+      <c r="V46" s="43"/>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" s="3"/>
@@ -12969,8 +12957,8 @@
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
       <c r="S47" s="2"/>
-      <c r="U47" s="45"/>
-      <c r="V47" s="45"/>
+      <c r="U47" s="43"/>
+      <c r="V47" s="43"/>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" s="3"/>
@@ -13036,8 +13024,8 @@
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
-      <c r="U50" s="45"/>
-      <c r="V50" s="45"/>
+      <c r="U50" s="43"/>
+      <c r="V50" s="43"/>
     </row>
     <row r="51" spans="1:22">
       <c r="A51" s="29"/>
@@ -13058,8 +13046,8 @@
       <c r="Q51" s="7"/>
       <c r="R51" s="7"/>
       <c r="S51" s="7"/>
-      <c r="U51" s="45"/>
-      <c r="V51" s="45"/>
+      <c r="U51" s="43"/>
+      <c r="V51" s="43"/>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" s="29"/>
@@ -13102,8 +13090,8 @@
       <c r="Q53" s="7"/>
       <c r="R53" s="7"/>
       <c r="S53" s="7"/>
-      <c r="U53" s="45"/>
-      <c r="V53" s="45"/>
+      <c r="U53" s="43"/>
+      <c r="V53" s="43"/>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="29"/>
@@ -13124,8 +13112,8 @@
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
       <c r="S54" s="7"/>
-      <c r="U54" s="45"/>
-      <c r="V54" s="45"/>
+      <c r="U54" s="43"/>
+      <c r="V54" s="43"/>
     </row>
     <row r="55" spans="1:19">
       <c r="A55" s="29"/>
@@ -14001,7 +13989,7 @@
       <c r="G3" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="H3" s="38">
+      <c r="H3" s="36">
         <v>8</v>
       </c>
       <c r="I3" s="29" t="s">
@@ -14013,7 +14001,7 @@
       <c r="K3" s="7">
         <v>25</v>
       </c>
-      <c r="L3" s="40">
+      <c r="L3" s="38">
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
@@ -14033,7 +14021,7 @@
       <c r="C4" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="36" t="s">
         <v>275</v>
       </c>
       <c r="E4" s="29" t="s">
@@ -14057,7 +14045,7 @@
       <c r="K4" s="7">
         <v>25</v>
       </c>
-      <c r="L4" s="41">
+      <c r="L4" s="39">
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
@@ -14089,7 +14077,7 @@
       <c r="G5" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="H5" s="38">
+      <c r="H5" s="36">
         <v>7</v>
       </c>
       <c r="I5" s="29" t="s">
@@ -14101,7 +14089,7 @@
       <c r="K5" s="7">
         <v>30</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="38">
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
@@ -14142,10 +14130,10 @@
       <c r="J6" s="7">
         <v>1</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="36">
         <v>26</v>
       </c>
-      <c r="L6" s="41">
+      <c r="L6" s="39">
         <v>0</v>
       </c>
       <c r="M6" s="7" t="s">
@@ -14186,10 +14174,10 @@
       <c r="J7" s="7">
         <v>1</v>
       </c>
-      <c r="K7" s="38">
+      <c r="K7" s="36">
         <v>22</v>
       </c>
-      <c r="L7" s="40">
+      <c r="L7" s="38">
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
@@ -14233,13 +14221,13 @@
       <c r="K8" s="7">
         <v>25</v>
       </c>
-      <c r="L8" s="41">
+      <c r="L8" s="39">
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N8" s="38" t="s">
+      <c r="N8" s="36" t="s">
         <v>374</v>
       </c>
     </row>
@@ -14277,13 +14265,13 @@
       <c r="K9" s="7">
         <v>35</v>
       </c>
-      <c r="L9" s="40">
+      <c r="L9" s="38">
         <v>0</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="N9" s="38" t="s">
+      <c r="N9" s="36" t="s">
         <v>376</v>
       </c>
     </row>
@@ -14318,10 +14306,10 @@
       <c r="J10" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="36">
         <v>32</v>
       </c>
-      <c r="L10" s="41">
+      <c r="L10" s="39">
         <v>0</v>
       </c>
       <c r="M10" s="7" t="s">
@@ -14365,13 +14353,13 @@
       <c r="K11" s="7">
         <v>40</v>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="38">
         <v>0</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N11" s="38" t="s">
+      <c r="N11" s="36" t="s">
         <v>374</v>
       </c>
     </row>
@@ -14397,7 +14385,7 @@
       <c r="G12" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="36">
         <v>7</v>
       </c>
       <c r="I12" s="29" t="s">
@@ -14409,7 +14397,7 @@
       <c r="K12" s="7">
         <v>40</v>
       </c>
-      <c r="L12" s="41">
+      <c r="L12" s="39">
         <v>0</v>
       </c>
       <c r="M12" s="7" t="s">
@@ -14441,7 +14429,7 @@
       <c r="G13" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="H13" s="38" t="s">
+      <c r="H13" s="36" t="s">
         <v>379</v>
       </c>
       <c r="I13" s="8" t="s">
@@ -14453,7 +14441,7 @@
       <c r="K13" s="7">
         <v>30</v>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="38">
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
@@ -14485,7 +14473,7 @@
       <c r="G14" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="36" t="s">
         <v>380</v>
       </c>
       <c r="I14" s="8" t="s">
@@ -14494,10 +14482,10 @@
       <c r="J14" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14" s="36">
         <v>28</v>
       </c>
-      <c r="L14" s="41">
+      <c r="L14" s="39">
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
@@ -14541,13 +14529,13 @@
       <c r="K15" s="7">
         <v>30</v>
       </c>
-      <c r="L15" s="40">
+      <c r="L15" s="38">
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N15" s="38" t="s">
+      <c r="N15" s="36" t="s">
         <v>374</v>
       </c>
     </row>
@@ -14573,7 +14561,7 @@
       <c r="G16" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="36">
         <v>3</v>
       </c>
       <c r="I16" s="29" t="s">
@@ -14585,7 +14573,7 @@
       <c r="K16" s="7">
         <v>30</v>
       </c>
-      <c r="L16" s="41">
+      <c r="L16" s="39">
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
@@ -14629,13 +14617,13 @@
       <c r="K17" s="7">
         <v>25</v>
       </c>
-      <c r="L17" s="40">
+      <c r="L17" s="38">
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="N17" s="38" t="s">
+      <c r="N17" s="36" t="s">
         <v>251</v>
       </c>
     </row>
@@ -14649,7 +14637,7 @@
       <c r="C18" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="36" t="s">
         <v>275</v>
       </c>
       <c r="E18" s="29" t="s">
@@ -14673,7 +14661,7 @@
       <c r="K18" s="7">
         <v>25</v>
       </c>
-      <c r="L18" s="41">
+      <c r="L18" s="39">
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
@@ -14705,7 +14693,7 @@
       <c r="G19" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="H19" s="38" t="s">
+      <c r="H19" s="36" t="s">
         <v>347</v>
       </c>
       <c r="I19" s="8" t="s">
@@ -14717,7 +14705,7 @@
       <c r="K19" s="7">
         <v>35</v>
       </c>
-      <c r="L19" s="40">
+      <c r="L19" s="38">
         <v>0</v>
       </c>
       <c r="M19" s="7" t="s">
@@ -14758,10 +14746,10 @@
       <c r="J20" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="K20" s="38">
+      <c r="K20" s="36">
         <v>31</v>
       </c>
-      <c r="L20" s="41">
+      <c r="L20" s="39">
         <v>0</v>
       </c>
       <c r="M20" s="7" t="s">
@@ -14802,10 +14790,10 @@
       <c r="J21" s="7">
         <v>3</v>
       </c>
-      <c r="K21" s="38">
+      <c r="K21" s="36">
         <v>37</v>
       </c>
-      <c r="L21" s="40">
+      <c r="L21" s="38">
         <v>0</v>
       </c>
       <c r="M21" s="7" t="s">
@@ -14843,13 +14831,13 @@
       <c r="I22" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="36">
         <v>4</v>
       </c>
       <c r="K22" s="7">
         <v>40</v>
       </c>
-      <c r="L22" s="41">
+      <c r="L22" s="39">
         <v>0</v>
       </c>
       <c r="M22" s="7" t="s">
@@ -14893,7 +14881,7 @@
       <c r="K23" s="7">
         <v>35</v>
       </c>
-      <c r="L23" s="40">
+      <c r="L23" s="38">
         <v>0</v>
       </c>
       <c r="M23" s="7" t="s">
@@ -14937,7 +14925,7 @@
       <c r="K24" s="7">
         <v>35</v>
       </c>
-      <c r="L24" s="41">
+      <c r="L24" s="39">
         <v>0</v>
       </c>
       <c r="M24" s="7" t="s">
@@ -14978,10 +14966,10 @@
       <c r="J25" s="7">
         <v>1</v>
       </c>
-      <c r="K25" s="38">
+      <c r="K25" s="36">
         <v>23</v>
       </c>
-      <c r="L25" s="40">
+      <c r="L25" s="38">
         <v>0</v>
       </c>
       <c r="M25" s="7" t="s">
@@ -15025,13 +15013,13 @@
       <c r="K26" s="7">
         <v>25</v>
       </c>
-      <c r="L26" s="41">
+      <c r="L26" s="39">
         <v>0</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N26" s="38" t="s">
+      <c r="N26" s="36" t="s">
         <v>374</v>
       </c>
     </row>
@@ -15066,10 +15054,10 @@
       <c r="J27" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="K27" s="38">
+      <c r="K27" s="36">
         <v>26</v>
       </c>
-      <c r="L27" s="40">
+      <c r="L27" s="38">
         <v>0</v>
       </c>
       <c r="M27" s="7" t="s">
@@ -15101,7 +15089,7 @@
       <c r="G28" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="H28" s="38" t="s">
+      <c r="H28" s="36" t="s">
         <v>390</v>
       </c>
       <c r="I28" s="8" t="s">
@@ -15113,7 +15101,7 @@
       <c r="K28" s="7">
         <v>30</v>
       </c>
-      <c r="L28" s="41">
+      <c r="L28" s="39">
         <v>0</v>
       </c>
       <c r="M28" s="7" t="s">
@@ -15157,13 +15145,13 @@
       <c r="K29" s="7">
         <v>30</v>
       </c>
-      <c r="L29" s="40">
+      <c r="L29" s="38">
         <v>0</v>
       </c>
       <c r="M29" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N29" s="38" t="s">
+      <c r="N29" s="36" t="s">
         <v>392</v>
       </c>
     </row>
@@ -15201,13 +15189,13 @@
       <c r="K30" s="7">
         <v>30</v>
       </c>
-      <c r="L30" s="41">
+      <c r="L30" s="39">
         <v>0</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N30" s="38" t="s">
+      <c r="N30" s="36" t="s">
         <v>376</v>
       </c>
     </row>
@@ -15242,10 +15230,10 @@
       <c r="J31" s="7">
         <v>1</v>
       </c>
-      <c r="K31" s="38">
+      <c r="K31" s="36">
         <v>37</v>
       </c>
-      <c r="L31" s="40">
+      <c r="L31" s="38">
         <v>0</v>
       </c>
       <c r="M31" s="7" t="s">
@@ -15286,10 +15274,10 @@
       <c r="J32" s="7">
         <v>1</v>
       </c>
-      <c r="K32" s="38">
+      <c r="K32" s="36">
         <v>34</v>
       </c>
-      <c r="L32" s="41">
+      <c r="L32" s="39">
         <v>0</v>
       </c>
       <c r="M32" s="7" t="s">
@@ -15321,7 +15309,7 @@
       <c r="G33" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="H33" s="38">
+      <c r="H33" s="36">
         <v>7</v>
       </c>
       <c r="I33" s="29" t="s">
@@ -15333,7 +15321,7 @@
       <c r="K33" s="7">
         <v>20</v>
       </c>
-      <c r="L33" s="40">
+      <c r="L33" s="38">
         <v>0</v>
       </c>
       <c r="M33" s="7" t="s">
@@ -15377,13 +15365,13 @@
       <c r="K34" s="7">
         <v>20</v>
       </c>
-      <c r="L34" s="41">
+      <c r="L34" s="39">
         <v>0</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N34" s="38" t="s">
+      <c r="N34" s="36" t="s">
         <v>374</v>
       </c>
     </row>
@@ -15409,7 +15397,7 @@
       <c r="G35" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="H35" s="38" t="s">
+      <c r="H35" s="36" t="s">
         <v>396</v>
       </c>
       <c r="I35" s="8" t="s">
@@ -15418,7 +15406,7 @@
       <c r="J35" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="K35" s="38">
+      <c r="K35" s="36">
         <v>22</v>
       </c>
       <c r="L35" s="7">
@@ -15465,7 +15453,7 @@
       <c r="K36" s="7">
         <v>25</v>
       </c>
-      <c r="L36" s="38">
+      <c r="L36" s="36">
         <v>2</v>
       </c>
       <c r="M36" s="7" t="s">
@@ -15515,7 +15503,7 @@
       <c r="M37" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N37" s="38" t="s">
+      <c r="N37" s="36" t="s">
         <v>374</v>
       </c>
     </row>
@@ -15541,7 +15529,7 @@
       <c r="G38" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="H38" s="38" t="s">
+      <c r="H38" s="36" t="s">
         <v>379</v>
       </c>
       <c r="I38" s="8" t="s">
@@ -15591,13 +15579,13 @@
       <c r="I39" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="J39" s="38" t="s">
+      <c r="J39" s="36" t="s">
         <v>399</v>
       </c>
       <c r="K39" s="7">
         <v>30</v>
       </c>
-      <c r="L39" s="40">
+      <c r="L39" s="38">
         <v>0</v>
       </c>
       <c r="M39" s="7" t="s">
@@ -15629,7 +15617,7 @@
       <c r="G40" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="H40" s="38" t="s">
+      <c r="H40" s="36" t="s">
         <v>286</v>
       </c>
       <c r="I40" s="8" t="s">
@@ -15641,7 +15629,7 @@
       <c r="K40" s="7">
         <v>30</v>
       </c>
-      <c r="L40" s="41">
+      <c r="L40" s="39">
         <v>0</v>
       </c>
       <c r="M40" s="7" t="s">
@@ -15682,10 +15670,10 @@
       <c r="J41" s="7">
         <v>1</v>
       </c>
-      <c r="K41" s="38">
+      <c r="K41" s="36">
         <v>22</v>
       </c>
-      <c r="L41" s="40">
+      <c r="L41" s="38">
         <v>0</v>
       </c>
       <c r="M41" s="7" t="s">
@@ -15723,13 +15711,13 @@
       <c r="I42" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="J42" s="38">
+      <c r="J42" s="36">
         <v>2</v>
       </c>
       <c r="K42" s="7">
         <v>25</v>
       </c>
-      <c r="L42" s="41">
+      <c r="L42" s="39">
         <v>0</v>
       </c>
       <c r="M42" s="7" t="s">
@@ -15773,13 +15761,13 @@
       <c r="K43" s="7">
         <v>30</v>
       </c>
-      <c r="L43" s="40">
+      <c r="L43" s="38">
         <v>0</v>
       </c>
       <c r="M43" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N43" s="38" t="s">
+      <c r="N43" s="36" t="s">
         <v>374</v>
       </c>
     </row>
@@ -15805,7 +15793,7 @@
       <c r="G44" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="H44" s="38">
+      <c r="H44" s="36">
         <v>8</v>
       </c>
       <c r="I44" s="29" t="s">
@@ -15814,10 +15802,10 @@
       <c r="J44" s="7">
         <v>1</v>
       </c>
-      <c r="K44" s="38">
+      <c r="K44" s="36">
         <v>28</v>
       </c>
-      <c r="L44" s="41">
+      <c r="L44" s="39">
         <v>0</v>
       </c>
       <c r="M44" s="7" t="s">
@@ -15837,7 +15825,7 @@
       <c r="C45" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="D45" s="39" t="s">
+      <c r="D45" s="37" t="s">
         <v>275</v>
       </c>
       <c r="E45" s="29" t="s">
@@ -15861,7 +15849,7 @@
       <c r="K45" s="7">
         <v>25</v>
       </c>
-      <c r="L45" s="40">
+      <c r="L45" s="38">
         <v>0</v>
       </c>
       <c r="M45" s="7" t="s">
@@ -15905,13 +15893,13 @@
       <c r="K46" s="7">
         <v>25</v>
       </c>
-      <c r="L46" s="41">
+      <c r="L46" s="39">
         <v>0</v>
       </c>
       <c r="M46" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="N46" s="38" t="s">
+      <c r="N46" s="36" t="s">
         <v>251</v>
       </c>
     </row>
@@ -15946,10 +15934,10 @@
       <c r="J47" s="7">
         <v>1</v>
       </c>
-      <c r="K47" s="38">
+      <c r="K47" s="36">
         <v>17</v>
       </c>
-      <c r="L47" s="40">
+      <c r="L47" s="38">
         <v>0</v>
       </c>
       <c r="M47" s="7" t="s">
@@ -15993,13 +15981,13 @@
       <c r="K48" s="7">
         <v>20</v>
       </c>
-      <c r="L48" s="41">
+      <c r="L48" s="39">
         <v>0</v>
       </c>
       <c r="M48" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="N48" s="38" t="s">
+      <c r="N48" s="36" t="s">
         <v>376</v>
       </c>
     </row>
@@ -16037,13 +16025,13 @@
       <c r="K49" s="7">
         <v>25</v>
       </c>
-      <c r="L49" s="40">
+      <c r="L49" s="38">
         <v>0</v>
       </c>
       <c r="M49" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N49" s="38" t="s">
+      <c r="N49" s="36" t="s">
         <v>374</v>
       </c>
     </row>
@@ -16078,10 +16066,10 @@
       <c r="J50" s="7">
         <v>1</v>
       </c>
-      <c r="K50" s="38">
+      <c r="K50" s="36">
         <v>23</v>
       </c>
-      <c r="L50" s="41">
+      <c r="L50" s="39">
         <v>0</v>
       </c>
       <c r="M50" s="7" t="s">
@@ -16125,13 +16113,13 @@
       <c r="K51" s="7">
         <v>25</v>
       </c>
-      <c r="L51" s="40">
+      <c r="L51" s="38">
         <v>0</v>
       </c>
       <c r="M51" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="N51" s="38" t="s">
+      <c r="N51" s="36" t="s">
         <v>374</v>
       </c>
     </row>
@@ -16166,10 +16154,10 @@
       <c r="J52" s="7">
         <v>1</v>
       </c>
-      <c r="K52" s="38">
+      <c r="K52" s="36">
         <v>22</v>
       </c>
-      <c r="L52" s="41">
+      <c r="L52" s="39">
         <v>0</v>
       </c>
       <c r="M52" s="7" t="s">
@@ -16316,7 +16304,7 @@
       <c r="K3" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -16354,7 +16342,7 @@
       <c r="K4" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L4" s="37" t="s">
+      <c r="L4" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -16392,7 +16380,7 @@
       <c r="K5" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -16430,7 +16418,7 @@
       <c r="K6" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L6" s="36" t="s">
+      <c r="L6" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -16468,7 +16456,7 @@
       <c r="K7" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -16506,7 +16494,7 @@
       <c r="K8" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L8" s="36" t="s">
+      <c r="L8" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -16544,7 +16532,7 @@
       <c r="K9" s="6">
         <v>0</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="8" t="s">
         <v>299</v>
       </c>
     </row>
@@ -16582,7 +16570,7 @@
       <c r="K10" s="6">
         <v>0</v>
       </c>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="8" t="s">
         <v>355</v>
       </c>
     </row>
@@ -16620,7 +16608,7 @@
       <c r="K11" s="6">
         <v>0</v>
       </c>
-      <c r="L11" s="37" t="s">
+      <c r="L11" s="8" t="s">
         <v>303</v>
       </c>
     </row>
@@ -16658,7 +16646,7 @@
       <c r="K12" s="6">
         <v>0</v>
       </c>
-      <c r="L12" s="37" t="s">
+      <c r="L12" s="8" t="s">
         <v>303</v>
       </c>
     </row>
@@ -16696,7 +16684,7 @@
       <c r="K13" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L13" s="36" t="s">
+      <c r="L13" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -16734,7 +16722,7 @@
       <c r="K14" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -16772,7 +16760,7 @@
       <c r="K15" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -16810,7 +16798,7 @@
       <c r="K16" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L16" s="36" t="s">
+      <c r="L16" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -16848,7 +16836,7 @@
       <c r="K17" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L17" s="37" t="s">
+      <c r="L17" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -16886,7 +16874,7 @@
       <c r="K18" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L18" s="37" t="s">
+      <c r="L18" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -16924,7 +16912,7 @@
       <c r="K19" s="7">
         <v>0</v>
       </c>
-      <c r="L19" s="37" t="s">
+      <c r="L19" s="8" t="s">
         <v>299</v>
       </c>
     </row>
@@ -16962,7 +16950,7 @@
       <c r="K20" s="6">
         <v>0</v>
       </c>
-      <c r="L20" s="37" t="s">
+      <c r="L20" s="8" t="s">
         <v>355</v>
       </c>
     </row>
@@ -17000,7 +16988,7 @@
       <c r="K21" s="6">
         <v>0</v>
       </c>
-      <c r="L21" s="37" t="s">
+      <c r="L21" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17038,7 +17026,7 @@
       <c r="K22" s="6">
         <v>0</v>
       </c>
-      <c r="L22" s="37" t="s">
+      <c r="L22" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17076,7 +17064,7 @@
       <c r="K23" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L23" s="36" t="s">
+      <c r="L23" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -17114,7 +17102,7 @@
       <c r="K24" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L24" s="37" t="s">
+      <c r="L24" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17152,7 +17140,7 @@
       <c r="K25" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L25" s="36" t="s">
+      <c r="L25" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -17190,7 +17178,7 @@
       <c r="K26" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L26" s="37" t="s">
+      <c r="L26" s="8" t="s">
         <v>303</v>
       </c>
     </row>
@@ -17228,7 +17216,7 @@
       <c r="K27" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L27" s="37" t="s">
+      <c r="L27" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17266,7 +17254,7 @@
       <c r="K28" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L28" s="36" t="s">
+      <c r="L28" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -17304,7 +17292,7 @@
       <c r="K29" s="6">
         <v>0</v>
       </c>
-      <c r="L29" s="37" t="s">
+      <c r="L29" s="8" t="s">
         <v>299</v>
       </c>
     </row>
@@ -17342,7 +17330,7 @@
       <c r="K30" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L30" s="37" t="s">
+      <c r="L30" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17380,7 +17368,7 @@
       <c r="K31" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L31" s="37" t="s">
+      <c r="L31" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17418,7 +17406,7 @@
       <c r="K32" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L32" s="37" t="s">
+      <c r="L32" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17456,7 +17444,7 @@
       <c r="K33" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L33" s="36" t="s">
+      <c r="L33" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -17494,7 +17482,7 @@
       <c r="K34" s="6">
         <v>0</v>
       </c>
-      <c r="L34" s="37" t="s">
+      <c r="L34" s="8" t="s">
         <v>303</v>
       </c>
     </row>
@@ -17532,7 +17520,7 @@
       <c r="K35" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L35" s="37" t="s">
+      <c r="L35" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17570,7 +17558,7 @@
       <c r="K36" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L36" s="37" t="s">
+      <c r="L36" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17608,7 +17596,7 @@
       <c r="K37" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L37" s="37" t="s">
+      <c r="L37" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17646,7 +17634,7 @@
       <c r="K38" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="L38" s="36" t="s">
+      <c r="L38" s="33" t="s">
         <v>244</v>
       </c>
     </row>
@@ -17684,7 +17672,7 @@
       <c r="K39" s="6">
         <v>0</v>
       </c>
-      <c r="L39" s="37" t="s">
+      <c r="L39" s="8" t="s">
         <v>355</v>
       </c>
     </row>
@@ -17722,7 +17710,7 @@
       <c r="K40" s="6">
         <v>0</v>
       </c>
-      <c r="L40" s="37" t="s">
+      <c r="L40" s="8" t="s">
         <v>355</v>
       </c>
     </row>
@@ -17760,7 +17748,7 @@
       <c r="K41" s="6">
         <v>0</v>
       </c>
-      <c r="L41" s="37" t="s">
+      <c r="L41" s="8" t="s">
         <v>303</v>
       </c>
     </row>
@@ -17798,7 +17786,7 @@
       <c r="K42" s="6">
         <v>0</v>
       </c>
-      <c r="L42" s="37" t="s">
+      <c r="L42" s="8" t="s">
         <v>303</v>
       </c>
     </row>
@@ -17836,7 +17824,7 @@
       <c r="K43" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L43" s="37" t="s">
+      <c r="L43" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17874,7 +17862,7 @@
       <c r="K44" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L44" s="37" t="s">
+      <c r="L44" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17912,7 +17900,7 @@
       <c r="K45" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="L45" s="37" t="s">
+      <c r="L45" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17950,7 +17938,7 @@
       <c r="K46" s="6">
         <v>0</v>
       </c>
-      <c r="L46" s="37" t="s">
+      <c r="L46" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -17988,7 +17976,7 @@
       <c r="K47" s="6">
         <v>0</v>
       </c>
-      <c r="L47" s="37" t="s">
+      <c r="L47" s="8" t="s">
         <v>283</v>
       </c>
     </row>
@@ -21413,13 +21401,13 @@
         <v>26</v>
       </c>
       <c r="D3" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E3" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F3" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G3" s="22" t="s">
         <v>639</v>
@@ -21444,13 +21432,13 @@
         <v>28</v>
       </c>
       <c r="D4" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E4" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F4" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G4" s="22"/>
       <c r="I4" s="26"/>
@@ -21473,13 +21461,13 @@
         <v>22</v>
       </c>
       <c r="D5" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E5" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F5" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G5" s="22" t="s">
         <v>640</v>
@@ -21504,13 +21492,13 @@
         <v>25</v>
       </c>
       <c r="D6" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E6" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F6" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G6" s="22"/>
       <c r="I6" s="26"/>
@@ -21533,13 +21521,13 @@
         <v>33</v>
       </c>
       <c r="D7" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E7" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F7" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G7" s="22"/>
       <c r="I7" s="26"/>
@@ -21562,13 +21550,13 @@
         <v>27</v>
       </c>
       <c r="D8" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E8" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F8" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>641</v>
@@ -21593,13 +21581,13 @@
         <v>30</v>
       </c>
       <c r="D9" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E9" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F9" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G9" s="22"/>
       <c r="I9" s="26"/>
@@ -21622,13 +21610,13 @@
         <v>34</v>
       </c>
       <c r="D10" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E10" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F10" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G10" s="22"/>
       <c r="I10" s="26"/>
@@ -21682,13 +21670,13 @@
         <v>24</v>
       </c>
       <c r="D12" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E12" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F12" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G12" s="22"/>
       <c r="I12" s="26"/>
@@ -21711,13 +21699,13 @@
         <v>25</v>
       </c>
       <c r="D13" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E13" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F13" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G13" s="22"/>
       <c r="I13" s="26"/>
@@ -21740,13 +21728,13 @@
         <v>20</v>
       </c>
       <c r="D14" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E14" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F14" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>643</v>
@@ -21771,13 +21759,13 @@
         <v>29</v>
       </c>
       <c r="D15" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E15" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F15" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G15" s="22"/>
       <c r="I15" s="26"/>
@@ -21800,13 +21788,13 @@
         <v>32</v>
       </c>
       <c r="D16" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E16" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F16" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G16" s="22"/>
       <c r="I16" s="26"/>
@@ -21829,13 +21817,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E17" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F17" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G17" s="22"/>
       <c r="I17" s="26"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16860" tabRatio="550" firstSheet="3" activeTab="2"/>
+    <workbookView windowHeight="16860" tabRatio="550" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="1025">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -2463,16 +2463,10 @@
     <t>유물 ID</t>
   </si>
   <si>
-    <t>횟수계산타입</t>
-  </si>
-  <si>
     <t>효과설명</t>
   </si>
   <si>
     <t>FragmentId</t>
-  </si>
-  <si>
-    <t>CountCalcTypes</t>
   </si>
   <si>
     <t>EffectDesc</t>
@@ -3208,7 +3202,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3263,13 +3257,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -3282,13 +3269,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="돋움"/>
@@ -3298,12 +3278,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
       <charset val="129"/>
     </font>
     <font>
@@ -4028,19 +4002,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4049,137 +4035,125 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4288,16 +4262,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
@@ -4306,7 +4274,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4324,16 +4292,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4360,16 +4325,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4403,9 +4368,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4641,7 +4603,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{BDCF795A-A338-4067-8659-51805AA9E7B5}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{5610F9F3-3424-44D6-A293-88F298CE25F4}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -4650,7 +4612,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{4CA1867F-8BA9-4EBA-BD23-E5199DCC6629}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{6D211BC7-6A0F-44E2-880C-245759715191}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -4967,7 +4929,7 @@
       <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="64" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="24" t="s">
@@ -4982,43 +4944,43 @@
       <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="73" t="s">
+      <c r="K1" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="73" t="s">
+      <c r="L1" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="73" t="s">
+      <c r="M1" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="73" t="s">
+      <c r="N1" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="73" t="s">
+      <c r="O1" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="73" t="s">
+      <c r="P1" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="73" t="s">
+      <c r="Q1" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="73" t="s">
+      <c r="R1" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="73" t="s">
+      <c r="S1" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="73" t="s">
+      <c r="T1" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="73" t="s">
+      <c r="U1" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="73" t="s">
+      <c r="V1" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="73" t="s">
+      <c r="W1" s="70" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5053,43 +5015,43 @@
       <c r="J2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="73" t="s">
+      <c r="K2" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="L2" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="M2" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="73" t="s">
+      <c r="O2" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="73" t="s">
+      <c r="P2" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="73" t="s">
+      <c r="Q2" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="73" t="s">
+      <c r="R2" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="73" t="s">
+      <c r="U2" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="73" t="s">
+      <c r="V2" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="73" t="s">
+      <c r="W2" s="70" t="s">
         <v>45</v>
       </c>
     </row>
@@ -5100,10 +5062,10 @@
       <c r="B3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="68">
+      <c r="C3" s="65">
         <v>114</v>
       </c>
-      <c r="D3" s="68">
+      <c r="D3" s="65">
         <v>8</v>
       </c>
       <c r="E3" s="7">
@@ -5124,46 +5086,46 @@
       <c r="J3" s="7">
         <v>1</v>
       </c>
-      <c r="K3" s="74" t="s">
+      <c r="K3" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="74" t="s">
+      <c r="L3" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="74" t="s">
+      <c r="M3" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="74" t="s">
+      <c r="N3" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="74" t="s">
+      <c r="O3" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="P3" s="74" t="s">
+      <c r="P3" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="Q3" s="75" t="s">
+      <c r="Q3" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="R3" s="75" t="s">
+      <c r="R3" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="74" t="s">
+      <c r="T3" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="U3" s="74" t="s">
+      <c r="U3" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="V3" s="74" t="s">
+      <c r="V3" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="W3" s="74" t="s">
+      <c r="W3" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="X3" s="74"/>
+      <c r="X3" s="71"/>
     </row>
     <row r="4" ht="17.25" spans="1:24">
       <c r="A4" s="8" t="s">
@@ -5172,10 +5134,10 @@
       <c r="B4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="69">
+      <c r="C4" s="66">
         <v>100</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="66">
         <v>10</v>
       </c>
       <c r="E4" s="7">
@@ -5196,46 +5158,46 @@
       <c r="J4" s="7">
         <v>1</v>
       </c>
-      <c r="K4" s="74" t="s">
+      <c r="K4" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="74" t="s">
+      <c r="L4" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="M4" s="74" t="s">
+      <c r="M4" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="N4" s="74" t="s">
+      <c r="N4" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="O4" s="74" t="s">
+      <c r="O4" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="P4" s="74" t="s">
+      <c r="P4" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="Q4" s="75" t="s">
+      <c r="Q4" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="R4" s="75" t="s">
+      <c r="R4" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="S4" s="74" t="s">
+      <c r="S4" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="T4" s="74" t="s">
+      <c r="T4" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="U4" s="74" t="s">
+      <c r="U4" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="V4" s="74" t="s">
+      <c r="V4" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="W4" s="74" t="s">
+      <c r="W4" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="X4" s="74"/>
+      <c r="X4" s="71"/>
     </row>
     <row r="5" ht="17.25" spans="1:23">
       <c r="A5" s="8" t="s">
@@ -5244,10 +5206,10 @@
       <c r="B5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="66">
         <v>86</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="66">
         <v>12</v>
       </c>
       <c r="E5" s="7">
@@ -5268,229 +5230,229 @@
       <c r="J5" s="7">
         <v>1</v>
       </c>
-      <c r="K5" s="74" t="s">
+      <c r="K5" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="L5" s="74" t="s">
+      <c r="L5" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="M5" s="74" t="s">
+      <c r="M5" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="N5" s="74" t="s">
+      <c r="N5" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="O5" s="74" t="s">
+      <c r="O5" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="P5" s="74" t="s">
+      <c r="P5" s="71" t="s">
         <v>86</v>
       </c>
-      <c r="Q5" s="75" t="s">
+      <c r="Q5" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="R5" s="75" t="s">
+      <c r="R5" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="S5" s="74" t="s">
+      <c r="S5" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="T5" s="74" t="s">
+      <c r="T5" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="U5" s="74" t="s">
+      <c r="U5" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="V5" s="74" t="s">
+      <c r="V5" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="W5" s="74" t="s">
+      <c r="W5" s="71" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="70"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
+      <c r="A6" s="67"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
       <c r="K6" s="30"/>
       <c r="L6" s="30"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="72"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
+      <c r="A7" s="69"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="70"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
       <c r="K8" s="30"/>
       <c r="L8" s="30"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="70"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="70"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
       <c r="K10" s="30"/>
       <c r="L10" s="30"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="70"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
       <c r="K11" s="30"/>
       <c r="L11" s="30"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="70"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="68"/>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="70"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="70"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
+      <c r="A14" s="67"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="70"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
+      <c r="A15" s="67"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
       <c r="K15" s="30"/>
       <c r="L15" s="30"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="70"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
+      <c r="A16" s="67"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="68"/>
       <c r="K16" s="30"/>
       <c r="L16" s="30"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="70"/>
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
       <c r="K17" s="30"/>
       <c r="L17" s="30"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="70"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="70"/>
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5502,18 +5464,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.5833333333333" customWidth="1"/>
     <col min="2" max="2" width="22.8333333333333" customWidth="1"/>
     <col min="3" max="4" width="19.5" customWidth="1"/>
-    <col min="5" max="6" width="20.0833333333333" customWidth="1"/>
-    <col min="7" max="7" width="41" customWidth="1"/>
-    <col min="8" max="8" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="20.0833333333333" customWidth="1"/>
+    <col min="6" max="6" width="41" customWidth="1"/>
+    <col min="7" max="7" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>781</v>
       </c>
@@ -5530,18 +5492,15 @@
         <v>214</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>783</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
-        <v>784</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>24</v>
@@ -5556,21 +5515,18 @@
         <v>231</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>786</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
-        <v>787</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>788</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>511</v>
@@ -5581,22 +5537,19 @@
       <c r="E3" s="7">
         <v>1</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G3" s="7">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="F3" s="7">
+        <v>1</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>788</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="5" t="s">
-        <v>789</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>790</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>511</v>
@@ -5607,22 +5560,19 @@
       <c r="E4" s="7">
         <v>2</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G4" s="7">
-        <v>1</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="F4" s="7">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>511</v>
@@ -5633,22 +5583,19 @@
       <c r="E5" s="7">
         <v>-1</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G5" s="7">
-        <v>1</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>511</v>
@@ -5659,25 +5606,22 @@
       <c r="E6" s="7">
         <v>-2</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>795</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>796</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>797</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>247</v>
@@ -5685,22 +5629,19 @@
       <c r="E7" s="7">
         <v>2</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="5" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>297</v>
@@ -5711,25 +5652,22 @@
       <c r="E8" s="7">
         <v>1</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G8" s="7">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="F8" s="7">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>800</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>802</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>247</v>
@@ -5737,22 +5675,19 @@
       <c r="E9" s="7">
         <v>1</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G9" s="7">
-        <v>1</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>344</v>
@@ -5763,22 +5698,19 @@
       <c r="E10" s="7">
         <v>1</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="F10" s="7">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>464</v>
@@ -5789,22 +5721,19 @@
       <c r="E11" s="7">
         <v>1</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G11" s="7">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="F11" s="7">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="5" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>473</v>
@@ -5815,25 +5744,22 @@
       <c r="E12" s="7">
         <v>1</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G12" s="7">
-        <v>1</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>809</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>810</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>811</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>246</v>
@@ -5841,25 +5767,22 @@
       <c r="E13" s="7">
         <v>0</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G13" s="7">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="F13" s="7">
+        <v>1</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>812</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>814</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>246</v>
@@ -5867,22 +5790,19 @@
       <c r="E14" s="7">
         <v>0</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G14" s="7">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="F14" s="7">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="5" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>391</v>
@@ -5893,22 +5813,19 @@
       <c r="E15" s="7">
         <v>1</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G15" s="7">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="F15" s="7">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>514</v>
@@ -5919,22 +5836,19 @@
       <c r="E16" s="7">
         <v>-1</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G16" s="7">
-        <v>1</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="F16" s="7">
+        <v>1</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="5" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>514</v>
@@ -5945,22 +5859,19 @@
       <c r="E17" s="7">
         <v>0</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G17" s="7">
-        <v>1</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>308</v>
@@ -5971,22 +5882,19 @@
       <c r="E18" s="7">
         <v>1</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G18" s="7">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="F18" s="7">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="5" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>366</v>
@@ -5997,22 +5905,19 @@
       <c r="E19" s="7">
         <v>1</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G19" s="7">
-        <v>1</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="F19" s="7">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="5" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>586</v>
@@ -6023,22 +5928,19 @@
       <c r="E20" s="7">
         <v>0</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G20" s="7">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="F20" s="7">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="5" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>589</v>
@@ -6049,22 +5951,19 @@
       <c r="E21" s="7">
         <v>0</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G21" s="7">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="F21" s="7">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>245</v>
@@ -6075,14 +5974,11 @@
       <c r="E22" s="7">
         <v>0</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G22" s="7">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>788</v>
+      <c r="F22" s="7">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -6110,33 +6006,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>835</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
@@ -6145,33 +6041,33 @@
         <v>224</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>845</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>846</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>847</v>
       </c>
       <c r="E3" s="1">
         <v>999999</v>
@@ -6188,16 +6084,16 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>849</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>851</v>
       </c>
       <c r="E4" s="1">
         <v>99999</v>
@@ -6214,16 +6110,16 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>853</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>855</v>
       </c>
       <c r="E5" s="1">
         <v>100</v>
@@ -6240,16 +6136,16 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>857</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>859</v>
       </c>
       <c r="E6" s="1">
         <v>9999</v>
@@ -6266,16 +6162,16 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>863</v>
       </c>
       <c r="E7" s="1">
         <v>99999</v>
@@ -6315,28 +6211,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B1" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1" t="s">
         <v>864</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>865</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>866</v>
-      </c>
-      <c r="D1" t="s">
-        <v>867</v>
-      </c>
-      <c r="E1" t="s">
-        <v>868</v>
       </c>
       <c r="F1" t="s">
         <v>670</v>
       </c>
       <c r="G1" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="H1" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6344,103 +6240,103 @@
         <v>602</v>
       </c>
       <c r="B2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C2" t="s">
+        <v>870</v>
+      </c>
+      <c r="D2" t="s">
         <v>871</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>872</v>
-      </c>
-      <c r="D2" t="s">
-        <v>873</v>
-      </c>
-      <c r="E2" t="s">
-        <v>874</v>
       </c>
       <c r="F2" t="s">
         <v>675</v>
       </c>
       <c r="G2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="H2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
+        <v>875</v>
+      </c>
+      <c r="B3" t="s">
+        <v>876</v>
+      </c>
+      <c r="C3" t="s">
         <v>877</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>878</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>879</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>880</v>
-      </c>
-      <c r="E3" t="s">
-        <v>881</v>
-      </c>
-      <c r="F3" t="s">
-        <v>882</v>
       </c>
       <c r="G3" t="s">
         <v>246</v>
       </c>
       <c r="H3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
+        <v>882</v>
+      </c>
+      <c r="B4" t="s">
+        <v>883</v>
+      </c>
+      <c r="C4" t="s">
+        <v>877</v>
+      </c>
+      <c r="D4" t="s">
+        <v>878</v>
+      </c>
+      <c r="E4" t="s">
         <v>884</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>885</v>
       </c>
-      <c r="C4" t="s">
-        <v>879</v>
-      </c>
-      <c r="D4" t="s">
-        <v>880</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>886</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>887</v>
-      </c>
-      <c r="G4" t="s">
-        <v>888</v>
-      </c>
-      <c r="H4" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
+        <v>888</v>
+      </c>
+      <c r="B5" t="s">
+        <v>889</v>
+      </c>
+      <c r="C5" t="s">
+        <v>877</v>
+      </c>
+      <c r="D5" t="s">
         <v>890</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>891</v>
       </c>
-      <c r="C5" t="s">
-        <v>879</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>892</v>
-      </c>
-      <c r="E5" t="s">
-        <v>893</v>
-      </c>
-      <c r="F5" t="s">
-        <v>894</v>
       </c>
       <c r="G5" t="s">
         <v>246</v>
       </c>
       <c r="H5" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -6474,46 +6370,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B1" t="s">
+        <v>894</v>
+      </c>
+      <c r="C1" t="s">
+        <v>895</v>
+      </c>
+      <c r="D1" t="s">
         <v>896</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>897</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>898</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>899</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>900</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>901</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>902</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>903</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>904</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>905</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>906</v>
-      </c>
-      <c r="M1" t="s">
-        <v>907</v>
-      </c>
-      <c r="N1" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -6521,57 +6417,57 @@
         <v>602</v>
       </c>
       <c r="B2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C2" t="s">
+        <v>908</v>
+      </c>
+      <c r="D2" t="s">
         <v>909</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>910</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>911</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>912</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>913</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>914</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>915</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>916</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>917</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>918</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>919</v>
-      </c>
-      <c r="M2" t="s">
-        <v>920</v>
-      </c>
-      <c r="N2" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="E3" t="s">
         <v>246</v>
@@ -6586,10 +6482,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="J3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -6603,16 +6499,16 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D4" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="E4" t="s">
         <v>246</v>
@@ -6627,10 +6523,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="J4" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -6639,21 +6535,21 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D5" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="E5" t="s">
         <v>246</v>
@@ -6685,34 +6581,34 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D6" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E6" t="s">
         <v>246</v>
       </c>
       <c r="F6" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="G6" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="J6" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -6726,16 +6622,16 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D7" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="E7" t="s">
         <v>246</v>
@@ -6767,13 +6663,13 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D8" t="s">
         <v>445</v>
@@ -6831,7 +6727,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -6840,24 +6736,24 @@
         <v>670</v>
       </c>
       <c r="D1" t="s">
+        <v>933</v>
+      </c>
+      <c r="E1" t="s">
+        <v>934</v>
+      </c>
+      <c r="F1" t="s">
         <v>935</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>936</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>937</v>
-      </c>
-      <c r="G1" t="s">
-        <v>938</v>
-      </c>
-      <c r="H1" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -6866,42 +6762,42 @@
         <v>675</v>
       </c>
       <c r="D2" t="s">
+        <v>939</v>
+      </c>
+      <c r="E2" t="s">
+        <v>940</v>
+      </c>
+      <c r="F2" t="s">
         <v>941</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>942</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>943</v>
-      </c>
-      <c r="G2" t="s">
-        <v>944</v>
-      </c>
-      <c r="H2" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B3" t="s">
+        <v>945</v>
+      </c>
+      <c r="C3" t="s">
         <v>946</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>947</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>948</v>
-      </c>
-      <c r="D3" t="s">
-        <v>949</v>
-      </c>
-      <c r="E3" t="s">
-        <v>950</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H3">
         <v>100</v>
@@ -6909,25 +6805,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4" t="s">
+        <v>950</v>
+      </c>
+      <c r="C4" t="s">
         <v>951</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>947</v>
+      </c>
+      <c r="E4" t="s">
         <v>952</v>
-      </c>
-      <c r="C4" t="s">
-        <v>953</v>
-      </c>
-      <c r="D4" t="s">
-        <v>949</v>
-      </c>
-      <c r="E4" t="s">
-        <v>954</v>
       </c>
       <c r="F4">
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H4">
         <v>200</v>
@@ -6935,25 +6831,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
+        <v>953</v>
+      </c>
+      <c r="B5" t="s">
+        <v>954</v>
+      </c>
+      <c r="C5" t="s">
         <v>955</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>947</v>
+      </c>
+      <c r="E5" t="s">
         <v>956</v>
       </c>
-      <c r="C5" t="s">
-        <v>957</v>
-      </c>
-      <c r="D5" t="s">
-        <v>949</v>
-      </c>
-      <c r="E5" t="s">
-        <v>958</v>
-      </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="H5">
         <v>50</v>
@@ -6961,25 +6857,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>957</v>
+      </c>
+      <c r="B6" t="s">
+        <v>958</v>
+      </c>
+      <c r="C6" t="s">
         <v>959</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>960</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>961</v>
-      </c>
-      <c r="D6" t="s">
-        <v>962</v>
-      </c>
-      <c r="E6" t="s">
-        <v>963</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H6">
         <v>150</v>
@@ -6987,25 +6883,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>962</v>
+      </c>
+      <c r="B7" t="s">
+        <v>963</v>
+      </c>
+      <c r="C7" t="s">
         <v>964</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>965</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>966</v>
       </c>
-      <c r="D7" t="s">
-        <v>967</v>
-      </c>
-      <c r="E7" t="s">
-        <v>968</v>
-      </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="H7">
         <v>30</v>
@@ -7035,59 +6931,59 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B1" t="s">
+        <v>968</v>
+      </c>
+      <c r="C1" t="s">
         <v>969</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>970</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>971</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>972</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>973</v>
-      </c>
-      <c r="F1" t="s">
-        <v>974</v>
-      </c>
-      <c r="G1" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B2" t="s">
+        <v>975</v>
+      </c>
+      <c r="C2" t="s">
         <v>976</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>977</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>978</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>979</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>980</v>
-      </c>
-      <c r="F2" t="s">
-        <v>981</v>
-      </c>
-      <c r="G2" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>981</v>
+      </c>
+      <c r="B3" t="s">
+        <v>982</v>
+      </c>
+      <c r="C3" t="s">
         <v>983</v>
-      </c>
-      <c r="B3" t="s">
-        <v>984</v>
-      </c>
-      <c r="C3" t="s">
-        <v>985</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7104,13 +7000,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C4" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7127,13 +7023,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B5" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -7150,10 +7046,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B6" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C6" t="s">
         <v>194</v>
@@ -7173,13 +7069,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B7" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C7" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7221,80 +7117,80 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B1" t="s">
+        <v>967</v>
+      </c>
+      <c r="C1" t="s">
+        <v>936</v>
+      </c>
+      <c r="D1" t="s">
+        <v>993</v>
+      </c>
+      <c r="E1" t="s">
         <v>994</v>
       </c>
-      <c r="B1" t="s">
-        <v>969</v>
-      </c>
-      <c r="C1" t="s">
-        <v>938</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>995</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>996</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>997</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>998</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>999</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>974</v>
+      </c>
+      <c r="C2" t="s">
+        <v>942</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E2" t="s">
         <v>1002</v>
       </c>
-      <c r="B2" t="s">
-        <v>976</v>
-      </c>
-      <c r="C2" t="s">
-        <v>944</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>1003</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>1004</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>1005</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>1006</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>1007</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E3">
         <v>0.7</v>
@@ -7317,16 +7213,16 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B4" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C4" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D4" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E4">
         <v>0.3</v>
@@ -7349,16 +7245,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B5" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C5" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E5">
         <v>0.6</v>
@@ -7381,16 +7277,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B6" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C6" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D6" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E6">
         <v>0.2</v>
@@ -7413,16 +7309,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B7" t="s">
+        <v>984</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D7" t="s">
         <v>1014</v>
-      </c>
-      <c r="B7" t="s">
-        <v>986</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1016</v>
       </c>
       <c r="E7">
         <v>0.2</v>
@@ -7445,16 +7341,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B8" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C8" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D8" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -7477,16 +7373,16 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B9" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C9" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D9" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -7509,16 +7405,16 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B10" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C10" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D10" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -7541,16 +7437,16 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B11" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C11" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D11" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -7573,16 +7469,16 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B12" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C12" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D12" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="E12">
         <v>0.5</v>
@@ -7605,16 +7501,16 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B13" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C13" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D13" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -7637,16 +7533,16 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B14" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C14" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D14" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E14">
         <v>0.5</v>
@@ -7787,10 +7683,10 @@
       <c r="A3" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="63" t="s">
         <v>124</v>
       </c>
       <c r="D3" s="7">
@@ -7834,10 +7730,10 @@
       <c r="A4" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="63" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="63" t="s">
         <v>124</v>
       </c>
       <c r="D4" s="7">
@@ -7881,10 +7777,10 @@
       <c r="A5" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="63" t="s">
         <v>124</v>
       </c>
       <c r="D5" s="7">
@@ -7928,10 +7824,10 @@
       <c r="A6" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="66" t="s">
+      <c r="C6" s="63" t="s">
         <v>124</v>
       </c>
       <c r="D6" s="7">
@@ -7975,10 +7871,10 @@
       <c r="A7" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="63" t="s">
         <v>124</v>
       </c>
       <c r="D7" s="7">
@@ -8022,10 +7918,10 @@
       <c r="A8" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="63" t="s">
         <v>124</v>
       </c>
       <c r="D8" s="7">
@@ -8069,10 +7965,10 @@
       <c r="A9" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="63" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="63" t="s">
         <v>124</v>
       </c>
       <c r="D9" s="7">
@@ -8116,10 +8012,10 @@
       <c r="A10" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="63" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="63" t="s">
         <v>124</v>
       </c>
       <c r="D10" s="7">
@@ -8163,10 +8059,10 @@
       <c r="A11" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="63" t="s">
         <v>170</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C11" s="63" t="s">
         <v>124</v>
       </c>
       <c r="D11" s="7">
@@ -8210,10 +8106,10 @@
       <c r="A12" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="63" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="63" t="s">
         <v>177</v>
       </c>
       <c r="D12" s="7">
@@ -8257,10 +8153,10 @@
       <c r="A13" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="63" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="63" t="s">
         <v>177</v>
       </c>
       <c r="D13" s="7">
@@ -8304,10 +8200,10 @@
       <c r="A14" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="63" t="s">
         <v>194</v>
       </c>
       <c r="D14" s="7">
@@ -8396,7 +8292,7 @@
       <c r="E1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F1" s="48" t="s">
+      <c r="F1" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -8420,7 +8316,7 @@
       <c r="M1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="N1" s="48" t="s">
+      <c r="N1" s="3" t="s">
         <v>218</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -8432,7 +8328,7 @@
       <c r="Q1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="R1" s="61" t="s">
+      <c r="R1" s="58" t="s">
         <v>222</v>
       </c>
     </row>
@@ -8452,7 +8348,7 @@
       <c r="E2" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="46" t="s">
         <v>227</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -8485,3342 +8381,3342 @@
       <c r="P2" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="Q2" s="48" t="s">
+      <c r="Q2" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="R2" s="61" t="s">
+      <c r="R2" s="58" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:18">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="47" t="s">
         <v>242</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="49" t="s">
         <v>243</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="F3" s="53">
-        <v>1</v>
-      </c>
-      <c r="G3" s="50">
-        <v>0</v>
-      </c>
-      <c r="H3" s="54" t="s">
+      <c r="F3" s="50">
+        <v>1</v>
+      </c>
+      <c r="G3" s="47">
+        <v>0</v>
+      </c>
+      <c r="H3" s="51" t="s">
         <v>245</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="55" t="s">
         <v>246</v>
       </c>
-      <c r="J3" s="58">
-        <v>0</v>
-      </c>
-      <c r="K3" s="58">
-        <v>1</v>
-      </c>
-      <c r="L3" s="50">
-        <v>0</v>
-      </c>
-      <c r="M3" s="59" t="s">
+      <c r="J3" s="55">
+        <v>0</v>
+      </c>
+      <c r="K3" s="55">
+        <v>1</v>
+      </c>
+      <c r="L3" s="47">
+        <v>0</v>
+      </c>
+      <c r="M3" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N3" s="58">
-        <v>1</v>
-      </c>
-      <c r="O3" s="58">
-        <v>0</v>
-      </c>
-      <c r="P3" s="58" t="s">
+      <c r="N3" s="55">
+        <v>1</v>
+      </c>
+      <c r="O3" s="55">
+        <v>0</v>
+      </c>
+      <c r="P3" s="55" t="s">
         <v>248</v>
       </c>
-      <c r="Q3" s="52" t="s">
+      <c r="Q3" s="49" t="s">
         <v>249</v>
       </c>
-      <c r="R3" s="62" t="s">
+      <c r="R3" s="59" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:18">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="50" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="50" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="50" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="49" t="s">
         <v>243</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="53">
+      <c r="F4" s="50">
         <v>2</v>
       </c>
-      <c r="G4" s="53">
-        <v>0</v>
-      </c>
-      <c r="H4" s="55" t="s">
+      <c r="G4" s="50">
+        <v>0</v>
+      </c>
+      <c r="H4" s="52" t="s">
         <v>245</v>
       </c>
-      <c r="I4" s="59" t="s">
+      <c r="I4" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="J4" s="59">
-        <v>0</v>
-      </c>
-      <c r="K4" s="59">
-        <v>1</v>
-      </c>
-      <c r="L4" s="53">
-        <v>0</v>
-      </c>
-      <c r="M4" s="59" t="s">
+      <c r="J4" s="56">
+        <v>0</v>
+      </c>
+      <c r="K4" s="56">
+        <v>1</v>
+      </c>
+      <c r="L4" s="50">
+        <v>0</v>
+      </c>
+      <c r="M4" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N4" s="59">
-        <v>1</v>
-      </c>
-      <c r="O4" s="59">
-        <v>0</v>
-      </c>
-      <c r="P4" s="59" t="s">
+      <c r="N4" s="56">
+        <v>1</v>
+      </c>
+      <c r="O4" s="56">
+        <v>0</v>
+      </c>
+      <c r="P4" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="Q4" s="52" t="s">
+      <c r="Q4" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="R4" s="62" t="s">
+      <c r="R4" s="59" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:18">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="F5" s="53">
-        <v>0</v>
-      </c>
-      <c r="G5" s="53">
-        <v>0</v>
-      </c>
-      <c r="H5" s="55" t="s">
+      <c r="F5" s="50">
+        <v>0</v>
+      </c>
+      <c r="G5" s="50">
+        <v>0</v>
+      </c>
+      <c r="H5" s="52" t="s">
         <v>257</v>
       </c>
-      <c r="I5" s="59" t="s">
+      <c r="I5" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J5" s="59">
-        <v>1</v>
-      </c>
-      <c r="K5" s="59">
-        <v>1</v>
-      </c>
-      <c r="L5" s="53" t="s">
+      <c r="J5" s="56">
+        <v>1</v>
+      </c>
+      <c r="K5" s="56">
+        <v>1</v>
+      </c>
+      <c r="L5" s="50" t="s">
         <v>258</v>
       </c>
-      <c r="M5" s="59">
-        <v>0</v>
-      </c>
-      <c r="N5" s="59">
-        <v>0</v>
-      </c>
-      <c r="O5" s="59">
-        <v>0</v>
-      </c>
-      <c r="P5" s="59">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="59">
-        <v>0</v>
-      </c>
-      <c r="R5" s="62" t="s">
+      <c r="M5" s="56">
+        <v>0</v>
+      </c>
+      <c r="N5" s="56">
+        <v>0</v>
+      </c>
+      <c r="O5" s="56">
+        <v>0</v>
+      </c>
+      <c r="P5" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="56">
+        <v>0</v>
+      </c>
+      <c r="R5" s="59" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:18">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="F6" s="53">
-        <v>0</v>
-      </c>
-      <c r="G6" s="53">
-        <v>0</v>
-      </c>
-      <c r="H6" s="55" t="s">
+      <c r="F6" s="50">
+        <v>0</v>
+      </c>
+      <c r="G6" s="50">
+        <v>0</v>
+      </c>
+      <c r="H6" s="52" t="s">
         <v>261</v>
       </c>
-      <c r="I6" s="59" t="s">
+      <c r="I6" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="56">
         <v>2</v>
       </c>
-      <c r="K6" s="59">
-        <v>1</v>
-      </c>
-      <c r="L6" s="53" t="s">
+      <c r="K6" s="56">
+        <v>1</v>
+      </c>
+      <c r="L6" s="50" t="s">
         <v>262</v>
       </c>
-      <c r="M6" s="59">
-        <v>0</v>
-      </c>
-      <c r="N6" s="59">
-        <v>0</v>
-      </c>
-      <c r="O6" s="59">
-        <v>0</v>
-      </c>
-      <c r="P6" s="59">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="59">
-        <v>0</v>
-      </c>
-      <c r="R6" s="62" t="s">
+      <c r="M6" s="56">
+        <v>0</v>
+      </c>
+      <c r="N6" s="56">
+        <v>0</v>
+      </c>
+      <c r="O6" s="56">
+        <v>0</v>
+      </c>
+      <c r="P6" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="56">
+        <v>0</v>
+      </c>
+      <c r="R6" s="59" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:18">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="50" t="s">
         <v>264</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="F7" s="53">
-        <v>0</v>
-      </c>
-      <c r="G7" s="53">
-        <v>0</v>
-      </c>
-      <c r="H7" s="55" t="s">
+      <c r="F7" s="50">
+        <v>0</v>
+      </c>
+      <c r="G7" s="50">
+        <v>0</v>
+      </c>
+      <c r="H7" s="52" t="s">
         <v>265</v>
       </c>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="J7" s="59">
-        <v>0</v>
-      </c>
-      <c r="K7" s="59">
-        <v>1</v>
-      </c>
-      <c r="L7" s="53" t="s">
+      <c r="J7" s="56">
+        <v>0</v>
+      </c>
+      <c r="K7" s="56">
+        <v>1</v>
+      </c>
+      <c r="L7" s="50" t="s">
         <v>266</v>
       </c>
-      <c r="M7" s="59">
-        <v>0</v>
-      </c>
-      <c r="N7" s="59">
-        <v>0</v>
-      </c>
-      <c r="O7" s="59">
-        <v>0</v>
-      </c>
-      <c r="P7" s="59">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="59">
-        <v>0</v>
-      </c>
-      <c r="R7" s="62" t="s">
+      <c r="M7" s="56">
+        <v>0</v>
+      </c>
+      <c r="N7" s="56">
+        <v>0</v>
+      </c>
+      <c r="O7" s="56">
+        <v>0</v>
+      </c>
+      <c r="P7" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="56">
+        <v>0</v>
+      </c>
+      <c r="R7" s="59" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:18">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="50" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="F8" s="53">
-        <v>0</v>
-      </c>
-      <c r="G8" s="53">
-        <v>0</v>
-      </c>
-      <c r="H8" s="55" t="s">
+      <c r="F8" s="50">
+        <v>0</v>
+      </c>
+      <c r="G8" s="50">
+        <v>0</v>
+      </c>
+      <c r="H8" s="52" t="s">
         <v>269</v>
       </c>
-      <c r="I8" s="59" t="s">
+      <c r="I8" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="J8" s="59">
-        <v>0</v>
-      </c>
-      <c r="K8" s="59">
-        <v>1</v>
-      </c>
-      <c r="L8" s="53" t="s">
+      <c r="J8" s="56">
+        <v>0</v>
+      </c>
+      <c r="K8" s="56">
+        <v>1</v>
+      </c>
+      <c r="L8" s="50" t="s">
         <v>266</v>
       </c>
-      <c r="M8" s="59">
-        <v>0</v>
-      </c>
-      <c r="N8" s="59">
-        <v>0</v>
-      </c>
-      <c r="O8" s="59">
-        <v>0</v>
-      </c>
-      <c r="P8" s="59">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="59">
-        <v>0</v>
-      </c>
-      <c r="R8" s="62" t="s">
+      <c r="M8" s="56">
+        <v>0</v>
+      </c>
+      <c r="N8" s="56">
+        <v>0</v>
+      </c>
+      <c r="O8" s="56">
+        <v>0</v>
+      </c>
+      <c r="P8" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="56">
+        <v>0</v>
+      </c>
+      <c r="R8" s="59" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:18">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="50" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="F9" s="53">
-        <v>0</v>
-      </c>
-      <c r="G9" s="53">
-        <v>0</v>
-      </c>
-      <c r="H9" s="55" t="s">
+      <c r="F9" s="50">
+        <v>0</v>
+      </c>
+      <c r="G9" s="50">
+        <v>0</v>
+      </c>
+      <c r="H9" s="52" t="s">
         <v>272</v>
       </c>
-      <c r="I9" s="59" t="s">
+      <c r="I9" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="J9" s="59">
-        <v>0</v>
-      </c>
-      <c r="K9" s="59">
-        <v>1</v>
-      </c>
-      <c r="L9" s="53" t="s">
+      <c r="J9" s="56">
+        <v>0</v>
+      </c>
+      <c r="K9" s="56">
+        <v>1</v>
+      </c>
+      <c r="L9" s="50" t="s">
         <v>273</v>
       </c>
-      <c r="M9" s="59">
-        <v>0</v>
-      </c>
-      <c r="N9" s="59">
-        <v>0</v>
-      </c>
-      <c r="O9" s="59">
-        <v>0</v>
-      </c>
-      <c r="P9" s="59">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="59">
-        <v>0</v>
-      </c>
-      <c r="R9" s="62" t="s">
+      <c r="M9" s="56">
+        <v>0</v>
+      </c>
+      <c r="N9" s="56">
+        <v>0</v>
+      </c>
+      <c r="O9" s="56">
+        <v>0</v>
+      </c>
+      <c r="P9" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="56">
+        <v>0</v>
+      </c>
+      <c r="R9" s="59" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:18">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="50" t="s">
         <v>275</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="D10" s="55" t="s">
+      <c r="D10" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="F10" s="53">
-        <v>0</v>
-      </c>
-      <c r="G10" s="53">
-        <v>0</v>
-      </c>
-      <c r="H10" s="55" t="s">
+      <c r="F10" s="50">
+        <v>0</v>
+      </c>
+      <c r="G10" s="50">
+        <v>0</v>
+      </c>
+      <c r="H10" s="52" t="s">
         <v>276</v>
       </c>
-      <c r="I10" s="59" t="s">
+      <c r="I10" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="J10" s="59">
-        <v>0</v>
-      </c>
-      <c r="K10" s="59">
-        <v>1</v>
-      </c>
-      <c r="L10" s="53" t="s">
+      <c r="J10" s="56">
+        <v>0</v>
+      </c>
+      <c r="K10" s="56">
+        <v>1</v>
+      </c>
+      <c r="L10" s="50" t="s">
         <v>277</v>
       </c>
-      <c r="M10" s="59">
-        <v>0</v>
-      </c>
-      <c r="N10" s="59">
-        <v>0</v>
-      </c>
-      <c r="O10" s="59">
-        <v>0</v>
-      </c>
-      <c r="P10" s="59">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="59">
-        <v>0</v>
-      </c>
-      <c r="R10" s="62" t="s">
+      <c r="M10" s="56">
+        <v>0</v>
+      </c>
+      <c r="N10" s="56">
+        <v>0</v>
+      </c>
+      <c r="O10" s="56">
+        <v>0</v>
+      </c>
+      <c r="P10" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="56">
+        <v>0</v>
+      </c>
+      <c r="R10" s="59" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:18">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="50" t="s">
         <v>279</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F11" s="53">
-        <v>0</v>
-      </c>
-      <c r="G11" s="53" t="s">
+      <c r="F11" s="50">
+        <v>0</v>
+      </c>
+      <c r="G11" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H11" s="55" t="s">
+      <c r="H11" s="52" t="s">
         <v>257</v>
       </c>
-      <c r="I11" s="59" t="s">
+      <c r="I11" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J11" s="59">
+      <c r="J11" s="56">
         <v>3</v>
       </c>
-      <c r="K11" s="59">
-        <v>1</v>
-      </c>
-      <c r="L11" s="53">
-        <v>0</v>
-      </c>
-      <c r="M11" s="59" t="s">
+      <c r="K11" s="56">
+        <v>1</v>
+      </c>
+      <c r="L11" s="50">
+        <v>0</v>
+      </c>
+      <c r="M11" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="N11" s="59">
+      <c r="N11" s="56">
         <v>2</v>
       </c>
-      <c r="O11" s="59">
-        <v>0</v>
-      </c>
-      <c r="P11" s="59" t="s">
+      <c r="O11" s="56">
+        <v>0</v>
+      </c>
+      <c r="P11" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q11" s="52" t="s">
+      <c r="Q11" s="49" t="s">
         <v>285</v>
       </c>
-      <c r="R11" s="62" t="s">
+      <c r="R11" s="59" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:21">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="50" t="s">
         <v>287</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F12" s="53">
-        <v>0</v>
-      </c>
-      <c r="G12" s="53" t="s">
+      <c r="F12" s="50">
+        <v>0</v>
+      </c>
+      <c r="G12" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H12" s="55" t="s">
+      <c r="H12" s="52" t="s">
         <v>290</v>
       </c>
-      <c r="I12" s="59" t="s">
+      <c r="I12" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="J12" s="59" t="s">
+      <c r="J12" s="56" t="s">
         <v>292</v>
       </c>
-      <c r="K12" s="59" t="s">
+      <c r="K12" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="L12" s="53">
-        <v>0</v>
-      </c>
-      <c r="M12" s="59" t="s">
+      <c r="L12" s="50">
+        <v>0</v>
+      </c>
+      <c r="M12" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="N12" s="59">
+      <c r="N12" s="56">
         <v>2</v>
       </c>
-      <c r="O12" s="59">
-        <v>0</v>
-      </c>
-      <c r="P12" s="59" t="s">
+      <c r="O12" s="56">
+        <v>0</v>
+      </c>
+      <c r="P12" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q12" s="52" t="s">
+      <c r="Q12" s="49" t="s">
         <v>294</v>
       </c>
-      <c r="R12" s="62" t="s">
+      <c r="R12" s="59" t="s">
         <v>295</v>
       </c>
       <c r="T12" s="33"/>
       <c r="U12" s="33"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:21">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="50" t="s">
         <v>296</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E13" s="53" t="s">
+      <c r="E13" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F13" s="53">
-        <v>0</v>
-      </c>
-      <c r="G13" s="53" t="s">
+      <c r="F13" s="50">
+        <v>0</v>
+      </c>
+      <c r="G13" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H13" s="55" t="s">
+      <c r="H13" s="52" t="s">
         <v>297</v>
       </c>
-      <c r="I13" s="59" t="s">
+      <c r="I13" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J13" s="59">
+      <c r="J13" s="56">
         <v>2</v>
       </c>
-      <c r="K13" s="59">
-        <v>1</v>
-      </c>
-      <c r="L13" s="53">
-        <v>0</v>
-      </c>
-      <c r="M13" s="59" t="s">
+      <c r="K13" s="56">
+        <v>1</v>
+      </c>
+      <c r="L13" s="50">
+        <v>0</v>
+      </c>
+      <c r="M13" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="N13" s="59">
+      <c r="N13" s="56">
         <v>3</v>
       </c>
-      <c r="O13" s="59">
-        <v>0</v>
-      </c>
-      <c r="P13" s="59" t="s">
+      <c r="O13" s="56">
+        <v>0</v>
+      </c>
+      <c r="P13" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q13" s="52" t="s">
+      <c r="Q13" s="49" t="s">
         <v>298</v>
       </c>
-      <c r="R13" s="62" t="s">
+      <c r="R13" s="59" t="s">
         <v>299</v>
       </c>
       <c r="T13" s="18"/>
       <c r="U13" s="18"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:21">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="50" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="D14" s="55" t="s">
+      <c r="D14" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E14" s="53" t="s">
+      <c r="E14" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F14" s="53">
-        <v>0</v>
-      </c>
-      <c r="G14" s="53" t="s">
+      <c r="F14" s="50">
+        <v>0</v>
+      </c>
+      <c r="G14" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H14" s="55" t="s">
+      <c r="H14" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="I14" s="59" t="s">
+      <c r="I14" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="J14" s="59" t="s">
+      <c r="J14" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="K14" s="59" t="s">
+      <c r="K14" s="56" t="s">
         <v>303</v>
       </c>
-      <c r="L14" s="53">
-        <v>0</v>
-      </c>
-      <c r="M14" s="59" t="s">
+      <c r="L14" s="50">
+        <v>0</v>
+      </c>
+      <c r="M14" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="N14" s="59">
+      <c r="N14" s="56">
         <v>3</v>
       </c>
-      <c r="O14" s="59">
-        <v>0</v>
-      </c>
-      <c r="P14" s="59" t="s">
+      <c r="O14" s="56">
+        <v>0</v>
+      </c>
+      <c r="P14" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q14" s="52" t="s">
+      <c r="Q14" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="R14" s="62" t="s">
+      <c r="R14" s="59" t="s">
         <v>305</v>
       </c>
       <c r="T14" s="18"/>
       <c r="U14" s="18"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:21">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="50" t="s">
         <v>306</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F15" s="53">
-        <v>0</v>
-      </c>
-      <c r="G15" s="53" t="s">
+      <c r="F15" s="50">
+        <v>0</v>
+      </c>
+      <c r="G15" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H15" s="55" t="s">
+      <c r="H15" s="52" t="s">
         <v>308</v>
       </c>
-      <c r="I15" s="59" t="s">
+      <c r="I15" s="56" t="s">
         <v>309</v>
       </c>
-      <c r="J15" s="59">
-        <v>1</v>
-      </c>
-      <c r="K15" s="59">
-        <v>1</v>
-      </c>
-      <c r="L15" s="53">
-        <v>0</v>
-      </c>
-      <c r="M15" s="59" t="s">
+      <c r="J15" s="56">
+        <v>1</v>
+      </c>
+      <c r="K15" s="56">
+        <v>1</v>
+      </c>
+      <c r="L15" s="50">
+        <v>0</v>
+      </c>
+      <c r="M15" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="N15" s="59">
+      <c r="N15" s="56">
         <v>2</v>
       </c>
-      <c r="O15" s="59">
-        <v>0</v>
-      </c>
-      <c r="P15" s="59" t="s">
+      <c r="O15" s="56">
+        <v>0</v>
+      </c>
+      <c r="P15" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q15" s="52" t="s">
+      <c r="Q15" s="49" t="s">
         <v>310</v>
       </c>
-      <c r="R15" s="62" t="s">
+      <c r="R15" s="59" t="s">
         <v>311</v>
       </c>
       <c r="T15" s="18"/>
       <c r="U15" s="18"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:21">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="50" t="s">
         <v>312</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D16" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="E16" s="53" t="s">
+      <c r="E16" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F16" s="53">
-        <v>0</v>
-      </c>
-      <c r="G16" s="53" t="s">
+      <c r="F16" s="50">
+        <v>0</v>
+      </c>
+      <c r="G16" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H16" s="55" t="s">
+      <c r="H16" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I16" s="59" t="s">
+      <c r="I16" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J16" s="59">
-        <v>1</v>
-      </c>
-      <c r="K16" s="59">
-        <v>1</v>
-      </c>
-      <c r="L16" s="53">
-        <v>0</v>
-      </c>
-      <c r="M16" s="59" t="s">
+      <c r="J16" s="56">
+        <v>1</v>
+      </c>
+      <c r="K16" s="56">
+        <v>1</v>
+      </c>
+      <c r="L16" s="50">
+        <v>0</v>
+      </c>
+      <c r="M16" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="N16" s="59">
+      <c r="N16" s="56">
         <v>2</v>
       </c>
-      <c r="O16" s="59">
-        <v>0</v>
-      </c>
-      <c r="P16" s="59" t="s">
+      <c r="O16" s="56">
+        <v>0</v>
+      </c>
+      <c r="P16" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q16" s="52" t="s">
+      <c r="Q16" s="49" t="s">
         <v>314</v>
       </c>
-      <c r="R16" s="62" t="s">
+      <c r="R16" s="59" t="s">
         <v>315</v>
       </c>
       <c r="T16" s="18"/>
       <c r="U16" s="18"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:21">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="50" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D17" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E17" s="53" t="s">
+      <c r="E17" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F17" s="53">
-        <v>1</v>
-      </c>
-      <c r="G17" s="53" t="s">
+      <c r="F17" s="50">
+        <v>1</v>
+      </c>
+      <c r="G17" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H17" s="55" t="s">
+      <c r="H17" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I17" s="59" t="s">
+      <c r="I17" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J17" s="59">
+      <c r="J17" s="56">
         <v>6</v>
       </c>
-      <c r="K17" s="59">
-        <v>1</v>
-      </c>
-      <c r="L17" s="53">
-        <v>0</v>
-      </c>
-      <c r="M17" s="59" t="s">
+      <c r="K17" s="56">
+        <v>1</v>
+      </c>
+      <c r="L17" s="50">
+        <v>0</v>
+      </c>
+      <c r="M17" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N17" s="59">
+      <c r="N17" s="56">
         <v>2</v>
       </c>
-      <c r="O17" s="59">
-        <v>0</v>
-      </c>
-      <c r="P17" s="59" t="s">
+      <c r="O17" s="56">
+        <v>0</v>
+      </c>
+      <c r="P17" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q17" s="52" t="s">
+      <c r="Q17" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="R17" s="63" t="s">
+      <c r="R17" s="60" t="s">
         <v>319</v>
       </c>
       <c r="T17" s="18"/>
       <c r="U17" s="18"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:21">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="50" t="s">
         <v>320</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="50">
         <v>2</v>
       </c>
-      <c r="G18" s="53" t="s">
+      <c r="G18" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H18" s="55" t="s">
+      <c r="H18" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I18" s="59" t="s">
+      <c r="I18" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J18" s="59">
+      <c r="J18" s="56">
         <v>8</v>
       </c>
-      <c r="K18" s="59">
-        <v>1</v>
-      </c>
-      <c r="L18" s="53">
-        <v>0</v>
-      </c>
-      <c r="M18" s="59" t="s">
+      <c r="K18" s="56">
+        <v>1</v>
+      </c>
+      <c r="L18" s="50">
+        <v>0</v>
+      </c>
+      <c r="M18" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N18" s="59">
+      <c r="N18" s="56">
         <v>2</v>
       </c>
-      <c r="O18" s="59">
-        <v>0</v>
-      </c>
-      <c r="P18" s="59" t="s">
+      <c r="O18" s="56">
+        <v>0</v>
+      </c>
+      <c r="P18" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q18" s="52" t="s">
+      <c r="Q18" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="R18" s="62" t="s">
+      <c r="R18" s="59" t="s">
         <v>321</v>
       </c>
       <c r="T18" s="18"/>
       <c r="U18" s="18"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:21">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="50" t="s">
         <v>322</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="50" t="s">
         <v>323</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E19" s="53" t="s">
+      <c r="E19" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F19" s="53">
-        <v>1</v>
-      </c>
-      <c r="G19" s="53" t="s">
+      <c r="F19" s="50">
+        <v>1</v>
+      </c>
+      <c r="G19" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H19" s="55" t="s">
+      <c r="H19" s="52" t="s">
         <v>290</v>
       </c>
-      <c r="I19" s="59" t="s">
+      <c r="I19" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="J19" s="59">
+      <c r="J19" s="56">
         <v>5</v>
       </c>
-      <c r="K19" s="59" t="s">
+      <c r="K19" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="L19" s="53">
-        <v>0</v>
-      </c>
-      <c r="M19" s="59" t="s">
+      <c r="L19" s="50">
+        <v>0</v>
+      </c>
+      <c r="M19" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N19" s="59">
+      <c r="N19" s="56">
         <v>3</v>
       </c>
-      <c r="O19" s="59">
-        <v>0</v>
-      </c>
-      <c r="P19" s="59" t="s">
+      <c r="O19" s="56">
+        <v>0</v>
+      </c>
+      <c r="P19" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q19" s="52" t="s">
+      <c r="Q19" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="R19" s="62" t="s">
+      <c r="R19" s="59" t="s">
         <v>325</v>
       </c>
       <c r="T19" s="18"/>
       <c r="U19" s="18"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:21">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="50" t="s">
         <v>326</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="50" t="s">
         <v>327</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="E20" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="50">
         <v>2</v>
       </c>
-      <c r="G20" s="53" t="s">
+      <c r="G20" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H20" s="55" t="s">
+      <c r="H20" s="52" t="s">
         <v>290</v>
       </c>
-      <c r="I20" s="59" t="s">
+      <c r="I20" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="J20" s="59">
+      <c r="J20" s="56">
         <v>7</v>
       </c>
-      <c r="K20" s="59" t="s">
+      <c r="K20" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="L20" s="53">
-        <v>0</v>
-      </c>
-      <c r="M20" s="59" t="s">
+      <c r="L20" s="50">
+        <v>0</v>
+      </c>
+      <c r="M20" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N20" s="59">
+      <c r="N20" s="56">
         <v>3</v>
       </c>
-      <c r="O20" s="59">
-        <v>0</v>
-      </c>
-      <c r="P20" s="59" t="s">
+      <c r="O20" s="56">
+        <v>0</v>
+      </c>
+      <c r="P20" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q20" s="52" t="s">
+      <c r="Q20" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="R20" s="62" t="s">
+      <c r="R20" s="59" t="s">
         <v>325</v>
       </c>
       <c r="T20" s="18"/>
       <c r="U20" s="18"/>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:21">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="50" t="s">
         <v>328</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E21" s="53" t="s">
+      <c r="E21" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F21" s="53">
-        <v>1</v>
-      </c>
-      <c r="G21" s="53" t="s">
+      <c r="F21" s="50">
+        <v>1</v>
+      </c>
+      <c r="G21" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H21" s="55" t="s">
+      <c r="H21" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="I21" s="59" t="s">
+      <c r="I21" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="J21" s="59">
+      <c r="J21" s="56">
         <v>7</v>
       </c>
-      <c r="K21" s="59" t="s">
+      <c r="K21" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="L21" s="53">
-        <v>0</v>
-      </c>
-      <c r="M21" s="59" t="s">
+      <c r="L21" s="50">
+        <v>0</v>
+      </c>
+      <c r="M21" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N21" s="59">
+      <c r="N21" s="56">
         <v>2</v>
       </c>
-      <c r="O21" s="59">
-        <v>0</v>
-      </c>
-      <c r="P21" s="59" t="s">
+      <c r="O21" s="56">
+        <v>0</v>
+      </c>
+      <c r="P21" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q21" s="52" t="s">
+      <c r="Q21" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="R21" s="62" t="s">
+      <c r="R21" s="59" t="s">
         <v>330</v>
       </c>
-      <c r="T21" s="43"/>
-      <c r="U21" s="43"/>
+      <c r="T21" s="41"/>
+      <c r="U21" s="41"/>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:21">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="53" t="s">
+      <c r="B22" s="50" t="s">
         <v>331</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E22" s="53" t="s">
+      <c r="E22" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F22" s="53">
+      <c r="F22" s="50">
         <v>2</v>
       </c>
-      <c r="G22" s="53" t="s">
+      <c r="G22" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H22" s="55" t="s">
+      <c r="H22" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="I22" s="59" t="s">
+      <c r="I22" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="J22" s="59">
+      <c r="J22" s="56">
         <v>9</v>
       </c>
-      <c r="K22" s="59" t="s">
+      <c r="K22" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="L22" s="53">
-        <v>0</v>
-      </c>
-      <c r="M22" s="59" t="s">
+      <c r="L22" s="50">
+        <v>0</v>
+      </c>
+      <c r="M22" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N22" s="59">
+      <c r="N22" s="56">
         <v>2</v>
       </c>
-      <c r="O22" s="59">
-        <v>0</v>
-      </c>
-      <c r="P22" s="59" t="s">
+      <c r="O22" s="56">
+        <v>0</v>
+      </c>
+      <c r="P22" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q22" s="52" t="s">
+      <c r="Q22" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="R22" s="62" t="s">
+      <c r="R22" s="59" t="s">
         <v>330</v>
       </c>
-      <c r="T22" s="64"/>
-      <c r="U22" s="64"/>
+      <c r="T22" s="61"/>
+      <c r="U22" s="61"/>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:21">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="50" t="s">
         <v>332</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="50" t="s">
         <v>333</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D23" s="55" t="s">
+      <c r="D23" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E23" s="53" t="s">
+      <c r="E23" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F23" s="53">
-        <v>1</v>
-      </c>
-      <c r="G23" s="53" t="s">
+      <c r="F23" s="50">
+        <v>1</v>
+      </c>
+      <c r="G23" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H23" s="55" t="s">
+      <c r="H23" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I23" s="59" t="s">
+      <c r="I23" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="J23" s="59">
+      <c r="J23" s="56">
         <v>6</v>
       </c>
-      <c r="K23" s="59">
-        <v>1</v>
-      </c>
-      <c r="L23" s="53">
-        <v>0</v>
-      </c>
-      <c r="M23" s="59" t="s">
+      <c r="K23" s="56">
+        <v>1</v>
+      </c>
+      <c r="L23" s="50">
+        <v>0</v>
+      </c>
+      <c r="M23" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N23" s="59">
+      <c r="N23" s="56">
         <v>3</v>
       </c>
-      <c r="O23" s="59">
-        <v>0</v>
-      </c>
-      <c r="P23" s="59" t="s">
+      <c r="O23" s="56">
+        <v>0</v>
+      </c>
+      <c r="P23" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q23" s="52" t="s">
+      <c r="Q23" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="R23" s="62" t="s">
+      <c r="R23" s="59" t="s">
         <v>321</v>
       </c>
-      <c r="T23" s="64"/>
-      <c r="U23" s="64"/>
+      <c r="T23" s="61"/>
+      <c r="U23" s="61"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:21">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="50" t="s">
         <v>334</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="50" t="s">
         <v>335</v>
       </c>
-      <c r="C24" s="53" t="s">
+      <c r="C24" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D24" s="55" t="s">
+      <c r="D24" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E24" s="53" t="s">
+      <c r="E24" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F24" s="53">
+      <c r="F24" s="50">
         <v>2</v>
       </c>
-      <c r="G24" s="53" t="s">
+      <c r="G24" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H24" s="55" t="s">
+      <c r="H24" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I24" s="59" t="s">
+      <c r="I24" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="J24" s="59">
+      <c r="J24" s="56">
         <v>8</v>
       </c>
-      <c r="K24" s="59">
-        <v>1</v>
-      </c>
-      <c r="L24" s="53">
-        <v>0</v>
-      </c>
-      <c r="M24" s="59" t="s">
+      <c r="K24" s="56">
+        <v>1</v>
+      </c>
+      <c r="L24" s="50">
+        <v>0</v>
+      </c>
+      <c r="M24" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N24" s="59">
+      <c r="N24" s="56">
         <v>3</v>
       </c>
-      <c r="O24" s="59">
-        <v>0</v>
-      </c>
-      <c r="P24" s="59" t="s">
+      <c r="O24" s="56">
+        <v>0</v>
+      </c>
+      <c r="P24" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q24" s="52" t="s">
+      <c r="Q24" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="R24" s="62" t="s">
+      <c r="R24" s="59" t="s">
         <v>321</v>
       </c>
-      <c r="T24" s="64"/>
-      <c r="U24" s="64"/>
+      <c r="T24" s="61"/>
+      <c r="U24" s="61"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:21">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="53" t="s">
+      <c r="B25" s="50" t="s">
         <v>336</v>
       </c>
-      <c r="C25" s="53" t="s">
+      <c r="C25" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E25" s="53" t="s">
+      <c r="E25" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F25" s="53">
-        <v>1</v>
-      </c>
-      <c r="G25" s="53" t="s">
+      <c r="F25" s="50">
+        <v>1</v>
+      </c>
+      <c r="G25" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H25" s="56" t="s">
+      <c r="H25" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="I25" s="59" t="s">
+      <c r="I25" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J25" s="59">
+      <c r="J25" s="56">
         <v>4</v>
       </c>
-      <c r="K25" s="59">
-        <v>1</v>
-      </c>
-      <c r="L25" s="55">
-        <v>0</v>
-      </c>
-      <c r="M25" s="59" t="s">
+      <c r="K25" s="56">
+        <v>1</v>
+      </c>
+      <c r="L25" s="52">
+        <v>0</v>
+      </c>
+      <c r="M25" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N25" s="59">
+      <c r="N25" s="56">
         <v>2</v>
       </c>
-      <c r="O25" s="59">
-        <v>0</v>
-      </c>
-      <c r="P25" s="59" t="s">
+      <c r="O25" s="56">
+        <v>0</v>
+      </c>
+      <c r="P25" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q25" s="52" t="s">
+      <c r="Q25" s="49" t="s">
         <v>338</v>
       </c>
-      <c r="R25" s="62" t="s">
+      <c r="R25" s="59" t="s">
         <v>339</v>
       </c>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:21">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="50" t="s">
         <v>340</v>
       </c>
-      <c r="C26" s="53" t="s">
+      <c r="C26" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E26" s="53" t="s">
+      <c r="E26" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F26" s="53">
+      <c r="F26" s="50">
         <v>2</v>
       </c>
-      <c r="G26" s="53" t="s">
+      <c r="G26" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H26" s="57" t="s">
+      <c r="H26" s="54" t="s">
         <v>337</v>
       </c>
-      <c r="I26" s="59" t="s">
+      <c r="I26" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J26" s="59">
+      <c r="J26" s="56">
         <v>4</v>
       </c>
-      <c r="K26" s="59">
-        <v>1</v>
-      </c>
-      <c r="L26" s="53">
-        <v>0</v>
-      </c>
-      <c r="M26" s="59" t="s">
+      <c r="K26" s="56">
+        <v>1</v>
+      </c>
+      <c r="L26" s="50">
+        <v>0</v>
+      </c>
+      <c r="M26" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N26" s="59">
+      <c r="N26" s="56">
         <v>2</v>
       </c>
-      <c r="O26" s="59">
-        <v>0</v>
-      </c>
-      <c r="P26" s="59" t="s">
+      <c r="O26" s="56">
+        <v>0</v>
+      </c>
+      <c r="P26" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q26" s="52" t="s">
+      <c r="Q26" s="49" t="s">
         <v>341</v>
       </c>
-      <c r="R26" s="62" t="s">
+      <c r="R26" s="59" t="s">
         <v>339</v>
       </c>
-      <c r="T26" s="64"/>
-      <c r="U26" s="64"/>
+      <c r="T26" s="61"/>
+      <c r="U26" s="61"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:21">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="50" t="s">
         <v>342</v>
       </c>
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="50" t="s">
         <v>343</v>
       </c>
-      <c r="C27" s="53" t="s">
+      <c r="C27" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E27" s="53" t="s">
+      <c r="E27" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F27" s="53">
-        <v>1</v>
-      </c>
-      <c r="G27" s="53" t="s">
+      <c r="F27" s="50">
+        <v>1</v>
+      </c>
+      <c r="G27" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H27" s="55" t="s">
+      <c r="H27" s="52" t="s">
         <v>344</v>
       </c>
-      <c r="I27" s="59" t="s">
+      <c r="I27" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J27" s="59">
+      <c r="J27" s="56">
         <v>2</v>
       </c>
-      <c r="K27" s="59">
-        <v>1</v>
-      </c>
-      <c r="L27" s="53">
-        <v>0</v>
-      </c>
-      <c r="M27" s="59" t="s">
+      <c r="K27" s="56">
+        <v>1</v>
+      </c>
+      <c r="L27" s="50">
+        <v>0</v>
+      </c>
+      <c r="M27" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N27" s="59">
+      <c r="N27" s="56">
         <v>3</v>
       </c>
-      <c r="O27" s="59">
-        <v>0</v>
-      </c>
-      <c r="P27" s="59" t="s">
+      <c r="O27" s="56">
+        <v>0</v>
+      </c>
+      <c r="P27" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q27" s="52" t="s">
+      <c r="Q27" s="49" t="s">
         <v>345</v>
       </c>
-      <c r="R27" s="62" t="s">
+      <c r="R27" s="59" t="s">
         <v>346</v>
       </c>
       <c r="T27" s="18"/>
       <c r="U27" s="18"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:21">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="50" t="s">
         <v>347</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="50" t="s">
         <v>348</v>
       </c>
-      <c r="C28" s="53" t="s">
+      <c r="C28" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="D28" s="55" t="s">
+      <c r="D28" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E28" s="53" t="s">
+      <c r="E28" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F28" s="53">
+      <c r="F28" s="50">
         <v>2</v>
       </c>
-      <c r="G28" s="53" t="s">
+      <c r="G28" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H28" s="55" t="s">
+      <c r="H28" s="52" t="s">
         <v>344</v>
       </c>
-      <c r="I28" s="59" t="s">
+      <c r="I28" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J28" s="59">
+      <c r="J28" s="56">
         <v>2</v>
       </c>
-      <c r="K28" s="59">
-        <v>1</v>
-      </c>
-      <c r="L28" s="53">
-        <v>0</v>
-      </c>
-      <c r="M28" s="59" t="s">
+      <c r="K28" s="56">
+        <v>1</v>
+      </c>
+      <c r="L28" s="50">
+        <v>0</v>
+      </c>
+      <c r="M28" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N28" s="59">
+      <c r="N28" s="56">
         <v>3</v>
       </c>
-      <c r="O28" s="59">
-        <v>0</v>
-      </c>
-      <c r="P28" s="59" t="s">
+      <c r="O28" s="56">
+        <v>0</v>
+      </c>
+      <c r="P28" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q28" s="52" t="s">
+      <c r="Q28" s="49" t="s">
         <v>338</v>
       </c>
-      <c r="R28" s="62" t="s">
+      <c r="R28" s="59" t="s">
         <v>346</v>
       </c>
       <c r="T28" s="18"/>
       <c r="U28" s="18"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:21">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="50" t="s">
         <v>349</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E29" s="53" t="s">
+      <c r="E29" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F29" s="53">
-        <v>1</v>
-      </c>
-      <c r="G29" s="53" t="s">
+      <c r="F29" s="50">
+        <v>1</v>
+      </c>
+      <c r="G29" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H29" s="55" t="s">
+      <c r="H29" s="52" t="s">
         <v>257</v>
       </c>
-      <c r="I29" s="59" t="s">
+      <c r="I29" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J29" s="59">
+      <c r="J29" s="56">
         <v>6</v>
       </c>
-      <c r="K29" s="59">
-        <v>1</v>
-      </c>
-      <c r="L29" s="53">
-        <v>0</v>
-      </c>
-      <c r="M29" s="59" t="s">
+      <c r="K29" s="56">
+        <v>1</v>
+      </c>
+      <c r="L29" s="50">
+        <v>0</v>
+      </c>
+      <c r="M29" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N29" s="59">
-        <v>1</v>
-      </c>
-      <c r="O29" s="59">
-        <v>0</v>
-      </c>
-      <c r="P29" s="59" t="s">
+      <c r="N29" s="56">
+        <v>1</v>
+      </c>
+      <c r="O29" s="56">
+        <v>0</v>
+      </c>
+      <c r="P29" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q29" s="52" t="s">
+      <c r="Q29" s="49" t="s">
         <v>249</v>
       </c>
-      <c r="R29" s="62" t="s">
+      <c r="R29" s="59" t="s">
         <v>351</v>
       </c>
-      <c r="T29" s="64"/>
-      <c r="U29" s="64"/>
+      <c r="T29" s="61"/>
+      <c r="U29" s="61"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:21">
-      <c r="A30" s="53" t="s">
+      <c r="A30" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="50" t="s">
         <v>352</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D30" s="55" t="s">
+      <c r="D30" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E30" s="53" t="s">
+      <c r="E30" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F30" s="53">
+      <c r="F30" s="50">
         <v>2</v>
       </c>
-      <c r="G30" s="53" t="s">
+      <c r="G30" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H30" s="55" t="s">
+      <c r="H30" s="52" t="s">
         <v>257</v>
       </c>
-      <c r="I30" s="59" t="s">
+      <c r="I30" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J30" s="60"/>
-      <c r="K30" s="59">
-        <v>1</v>
-      </c>
-      <c r="L30" s="53">
-        <v>0</v>
-      </c>
-      <c r="M30" s="59" t="s">
+      <c r="J30" s="57"/>
+      <c r="K30" s="56">
+        <v>1</v>
+      </c>
+      <c r="L30" s="50">
+        <v>0</v>
+      </c>
+      <c r="M30" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N30" s="59">
-        <v>1</v>
-      </c>
-      <c r="O30" s="59">
-        <v>0</v>
-      </c>
-      <c r="P30" s="59" t="s">
+      <c r="N30" s="56">
+        <v>1</v>
+      </c>
+      <c r="O30" s="56">
+        <v>0</v>
+      </c>
+      <c r="P30" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q30" s="52" t="s">
+      <c r="Q30" s="49" t="s">
         <v>249</v>
       </c>
-      <c r="R30" s="62" t="s">
+      <c r="R30" s="59" t="s">
         <v>351</v>
       </c>
-      <c r="T30" s="43"/>
-      <c r="U30" s="43"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:21">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="53" t="s">
+      <c r="B31" s="50" t="s">
         <v>353</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="C31" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="D31" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F31" s="53">
-        <v>1</v>
-      </c>
-      <c r="G31" s="53" t="s">
+      <c r="F31" s="50">
+        <v>1</v>
+      </c>
+      <c r="G31" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H31" s="55" t="s">
+      <c r="H31" s="52" t="s">
         <v>261</v>
       </c>
-      <c r="I31" s="59" t="s">
+      <c r="I31" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J31" s="59">
-        <v>1</v>
-      </c>
-      <c r="K31" s="59">
-        <v>1</v>
-      </c>
-      <c r="L31" s="53">
-        <v>0</v>
-      </c>
-      <c r="M31" s="59" t="s">
+      <c r="J31" s="56">
+        <v>1</v>
+      </c>
+      <c r="K31" s="56">
+        <v>1</v>
+      </c>
+      <c r="L31" s="50">
+        <v>0</v>
+      </c>
+      <c r="M31" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N31" s="59">
-        <v>1</v>
-      </c>
-      <c r="O31" s="59">
-        <v>0</v>
-      </c>
-      <c r="P31" s="59" t="s">
+      <c r="N31" s="56">
+        <v>1</v>
+      </c>
+      <c r="O31" s="56">
+        <v>0</v>
+      </c>
+      <c r="P31" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q31" s="52" t="s">
+      <c r="Q31" s="49" t="s">
         <v>285</v>
       </c>
-      <c r="R31" s="62" t="s">
+      <c r="R31" s="59" t="s">
         <v>354</v>
       </c>
-      <c r="T31" s="64"/>
-      <c r="U31" s="64"/>
+      <c r="T31" s="61"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:21">
-      <c r="A32" s="53" t="s">
+      <c r="A32" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="50" t="s">
         <v>355</v>
       </c>
-      <c r="C32" s="53" t="s">
+      <c r="C32" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D32" s="52" t="s">
+      <c r="D32" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="53" t="s">
+      <c r="E32" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F32" s="53">
+      <c r="F32" s="50">
         <v>2</v>
       </c>
-      <c r="G32" s="53" t="s">
+      <c r="G32" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H32" s="55" t="s">
+      <c r="H32" s="52" t="s">
         <v>261</v>
       </c>
-      <c r="I32" s="59" t="s">
+      <c r="I32" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J32" s="59">
+      <c r="J32" s="56">
         <v>2</v>
       </c>
-      <c r="K32" s="59">
-        <v>1</v>
-      </c>
-      <c r="L32" s="53">
-        <v>0</v>
-      </c>
-      <c r="M32" s="59" t="s">
+      <c r="K32" s="56">
+        <v>1</v>
+      </c>
+      <c r="L32" s="50">
+        <v>0</v>
+      </c>
+      <c r="M32" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N32" s="59">
-        <v>1</v>
-      </c>
-      <c r="O32" s="59">
-        <v>0</v>
-      </c>
-      <c r="P32" s="59" t="s">
+      <c r="N32" s="56">
+        <v>1</v>
+      </c>
+      <c r="O32" s="56">
+        <v>0</v>
+      </c>
+      <c r="P32" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q32" s="52" t="s">
+      <c r="Q32" s="49" t="s">
         <v>285</v>
       </c>
-      <c r="R32" s="62" t="s">
+      <c r="R32" s="59" t="s">
         <v>354</v>
       </c>
-      <c r="T32" s="64"/>
-      <c r="U32" s="64"/>
+      <c r="T32" s="61"/>
+      <c r="U32" s="61"/>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:21">
-      <c r="A33" s="53" t="s">
+      <c r="A33" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="53" t="s">
+      <c r="B33" s="50" t="s">
         <v>356</v>
       </c>
-      <c r="C33" s="53" t="s">
+      <c r="C33" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D33" s="55" t="s">
+      <c r="D33" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F33" s="53">
-        <v>1</v>
-      </c>
-      <c r="G33" s="53" t="s">
+      <c r="F33" s="50">
+        <v>1</v>
+      </c>
+      <c r="G33" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H33" s="55" t="s">
+      <c r="H33" s="52" t="s">
         <v>261</v>
       </c>
-      <c r="I33" s="59" t="s">
+      <c r="I33" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J33" s="59">
-        <v>1</v>
-      </c>
-      <c r="K33" s="59">
-        <v>1</v>
-      </c>
-      <c r="L33" s="53">
-        <v>0</v>
-      </c>
-      <c r="M33" s="59" t="s">
+      <c r="J33" s="56">
+        <v>1</v>
+      </c>
+      <c r="K33" s="56">
+        <v>1</v>
+      </c>
+      <c r="L33" s="50">
+        <v>0</v>
+      </c>
+      <c r="M33" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N33" s="59">
-        <v>1</v>
-      </c>
-      <c r="O33" s="59">
-        <v>0</v>
-      </c>
-      <c r="P33" s="59" t="s">
+      <c r="N33" s="56">
+        <v>1</v>
+      </c>
+      <c r="O33" s="56">
+        <v>0</v>
+      </c>
+      <c r="P33" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q33" s="52" t="s">
+      <c r="Q33" s="49" t="s">
         <v>285</v>
       </c>
-      <c r="R33" s="62" t="s">
+      <c r="R33" s="59" t="s">
         <v>354</v>
       </c>
-      <c r="T33" s="64"/>
-      <c r="U33" s="64"/>
+      <c r="T33" s="61"/>
+      <c r="U33" s="61"/>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:21">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="53" t="s">
+      <c r="B34" s="50" t="s">
         <v>357</v>
       </c>
-      <c r="C34" s="53" t="s">
+      <c r="C34" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D34" s="55" t="s">
+      <c r="D34" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="53" t="s">
+      <c r="E34" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F34" s="53">
+      <c r="F34" s="50">
         <v>2</v>
       </c>
-      <c r="G34" s="53" t="s">
+      <c r="G34" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H34" s="55" t="s">
+      <c r="H34" s="52" t="s">
         <v>261</v>
       </c>
-      <c r="I34" s="59" t="s">
+      <c r="I34" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J34" s="59">
+      <c r="J34" s="56">
         <v>2</v>
       </c>
-      <c r="K34" s="59">
-        <v>1</v>
-      </c>
-      <c r="L34" s="53">
-        <v>0</v>
-      </c>
-      <c r="M34" s="59" t="s">
+      <c r="K34" s="56">
+        <v>1</v>
+      </c>
+      <c r="L34" s="50">
+        <v>0</v>
+      </c>
+      <c r="M34" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N34" s="59">
-        <v>1</v>
-      </c>
-      <c r="O34" s="59">
-        <v>0</v>
-      </c>
-      <c r="P34" s="59" t="s">
+      <c r="N34" s="56">
+        <v>1</v>
+      </c>
+      <c r="O34" s="56">
+        <v>0</v>
+      </c>
+      <c r="P34" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q34" s="52" t="s">
+      <c r="Q34" s="49" t="s">
         <v>285</v>
       </c>
-      <c r="R34" s="62" t="s">
+      <c r="R34" s="59" t="s">
         <v>354</v>
       </c>
       <c r="T34" s="18"/>
       <c r="U34" s="18"/>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:21">
-      <c r="A35" s="53" t="s">
+      <c r="A35" s="50" t="s">
         <v>358</v>
       </c>
-      <c r="B35" s="53" t="s">
+      <c r="B35" s="50" t="s">
         <v>359</v>
       </c>
-      <c r="C35" s="53" t="s">
+      <c r="C35" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D35" s="55" t="s">
+      <c r="D35" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E35" s="53" t="s">
+      <c r="E35" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F35" s="53">
-        <v>1</v>
-      </c>
-      <c r="G35" s="53" t="s">
+      <c r="F35" s="50">
+        <v>1</v>
+      </c>
+      <c r="G35" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H35" s="55" t="s">
+      <c r="H35" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I35" s="59" t="s">
+      <c r="I35" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J35" s="59">
+      <c r="J35" s="56">
         <v>2</v>
       </c>
-      <c r="K35" s="59">
+      <c r="K35" s="56">
         <v>3</v>
       </c>
-      <c r="L35" s="53">
-        <v>0</v>
-      </c>
-      <c r="M35" s="59" t="s">
+      <c r="L35" s="50">
+        <v>0</v>
+      </c>
+      <c r="M35" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N35" s="59">
+      <c r="N35" s="56">
         <v>3</v>
       </c>
-      <c r="O35" s="59">
-        <v>0</v>
-      </c>
-      <c r="P35" s="59" t="s">
+      <c r="O35" s="56">
+        <v>0</v>
+      </c>
+      <c r="P35" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q35" s="52" t="s">
+      <c r="Q35" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="R35" s="62" t="s">
+      <c r="R35" s="59" t="s">
         <v>361</v>
       </c>
-      <c r="T35" s="64"/>
-      <c r="U35" s="64"/>
+      <c r="T35" s="61"/>
+      <c r="U35" s="61"/>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:21">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="50" t="s">
         <v>362</v>
       </c>
-      <c r="B36" s="53" t="s">
+      <c r="B36" s="50" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="53" t="s">
+      <c r="C36" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D36" s="55" t="s">
+      <c r="D36" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E36" s="53" t="s">
+      <c r="E36" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F36" s="53">
+      <c r="F36" s="50">
         <v>2</v>
       </c>
-      <c r="G36" s="53" t="s">
+      <c r="G36" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H36" s="55" t="s">
+      <c r="H36" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I36" s="59" t="s">
+      <c r="I36" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J36" s="59">
+      <c r="J36" s="56">
         <v>3</v>
       </c>
-      <c r="K36" s="59">
+      <c r="K36" s="56">
         <v>3</v>
       </c>
-      <c r="L36" s="53">
-        <v>0</v>
-      </c>
-      <c r="M36" s="59" t="s">
+      <c r="L36" s="50">
+        <v>0</v>
+      </c>
+      <c r="M36" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N36" s="59">
+      <c r="N36" s="56">
         <v>3</v>
       </c>
-      <c r="O36" s="59">
-        <v>0</v>
-      </c>
-      <c r="P36" s="59" t="s">
+      <c r="O36" s="56">
+        <v>0</v>
+      </c>
+      <c r="P36" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q36" s="52" t="s">
+      <c r="Q36" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="R36" s="62" t="s">
+      <c r="R36" s="59" t="s">
         <v>361</v>
       </c>
-      <c r="T36" s="64"/>
-      <c r="U36" s="64"/>
+      <c r="T36" s="61"/>
+      <c r="U36" s="61"/>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:21">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="B37" s="53" t="s">
+      <c r="B37" s="50" t="s">
         <v>365</v>
       </c>
-      <c r="C37" s="53" t="s">
+      <c r="C37" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D37" s="55" t="s">
+      <c r="D37" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E37" s="53" t="s">
+      <c r="E37" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F37" s="53">
-        <v>1</v>
-      </c>
-      <c r="G37" s="53" t="s">
+      <c r="F37" s="50">
+        <v>1</v>
+      </c>
+      <c r="G37" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H37" s="55" t="s">
+      <c r="H37" s="52" t="s">
         <v>366</v>
       </c>
-      <c r="I37" s="59" t="s">
+      <c r="I37" s="56" t="s">
         <v>309</v>
       </c>
-      <c r="J37" s="59">
-        <v>1</v>
-      </c>
-      <c r="K37" s="59">
-        <v>1</v>
-      </c>
-      <c r="L37" s="53">
-        <v>0</v>
-      </c>
-      <c r="M37" s="59" t="s">
+      <c r="J37" s="56">
+        <v>1</v>
+      </c>
+      <c r="K37" s="56">
+        <v>1</v>
+      </c>
+      <c r="L37" s="50">
+        <v>0</v>
+      </c>
+      <c r="M37" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N37" s="59">
+      <c r="N37" s="56">
         <v>3</v>
       </c>
-      <c r="O37" s="59">
-        <v>0</v>
-      </c>
-      <c r="P37" s="59" t="s">
+      <c r="O37" s="56">
+        <v>0</v>
+      </c>
+      <c r="P37" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q37" s="52" t="s">
+      <c r="Q37" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="R37" s="62" t="s">
+      <c r="R37" s="59" t="s">
         <v>367</v>
       </c>
-      <c r="T37" s="64"/>
-      <c r="U37" s="64"/>
+      <c r="T37" s="61"/>
+      <c r="U37" s="61"/>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:21">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="50" t="s">
         <v>368</v>
       </c>
-      <c r="B38" s="53" t="s">
+      <c r="B38" s="50" t="s">
         <v>369</v>
       </c>
-      <c r="C38" s="53" t="s">
+      <c r="C38" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D38" s="55" t="s">
+      <c r="D38" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E38" s="53" t="s">
+      <c r="E38" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F38" s="53">
+      <c r="F38" s="50">
         <v>2</v>
       </c>
-      <c r="G38" s="53" t="s">
+      <c r="G38" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H38" s="55" t="s">
+      <c r="H38" s="52" t="s">
         <v>366</v>
       </c>
-      <c r="I38" s="59" t="s">
+      <c r="I38" s="56" t="s">
         <v>309</v>
       </c>
-      <c r="J38" s="59">
-        <v>1</v>
-      </c>
-      <c r="K38" s="59">
-        <v>1</v>
-      </c>
-      <c r="L38" s="53">
-        <v>0</v>
-      </c>
-      <c r="M38" s="59" t="s">
+      <c r="J38" s="56">
+        <v>1</v>
+      </c>
+      <c r="K38" s="56">
+        <v>1</v>
+      </c>
+      <c r="L38" s="50">
+        <v>0</v>
+      </c>
+      <c r="M38" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N38" s="59">
+      <c r="N38" s="56">
         <v>3</v>
       </c>
-      <c r="O38" s="59">
-        <v>0</v>
-      </c>
-      <c r="P38" s="59" t="s">
+      <c r="O38" s="56">
+        <v>0</v>
+      </c>
+      <c r="P38" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q38" s="52" t="s">
+      <c r="Q38" s="49" t="s">
         <v>370</v>
       </c>
-      <c r="R38" s="62" t="s">
+      <c r="R38" s="59" t="s">
         <v>367</v>
       </c>
-      <c r="T38" s="64"/>
-      <c r="U38" s="64"/>
+      <c r="T38" s="61"/>
+      <c r="U38" s="61"/>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:21">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="50" t="s">
         <v>371</v>
       </c>
-      <c r="B39" s="53" t="s">
+      <c r="B39" s="50" t="s">
         <v>372</v>
       </c>
-      <c r="C39" s="53" t="s">
+      <c r="C39" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D39" s="55" t="s">
+      <c r="D39" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E39" s="53" t="s">
+      <c r="E39" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F39" s="53">
-        <v>1</v>
-      </c>
-      <c r="G39" s="53" t="s">
+      <c r="F39" s="50">
+        <v>1</v>
+      </c>
+      <c r="G39" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H39" s="55" t="s">
+      <c r="H39" s="52" t="s">
         <v>373</v>
       </c>
-      <c r="I39" s="59" t="s">
+      <c r="I39" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J39" s="59">
+      <c r="J39" s="56">
         <v>3</v>
       </c>
-      <c r="K39" s="59">
-        <v>1</v>
-      </c>
-      <c r="L39" s="53">
-        <v>0</v>
-      </c>
-      <c r="M39" s="59" t="s">
+      <c r="K39" s="56">
+        <v>1</v>
+      </c>
+      <c r="L39" s="50">
+        <v>0</v>
+      </c>
+      <c r="M39" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N39" s="59">
+      <c r="N39" s="56">
         <v>3</v>
       </c>
-      <c r="O39" s="59">
-        <v>0</v>
-      </c>
-      <c r="P39" s="59" t="s">
+      <c r="O39" s="56">
+        <v>0</v>
+      </c>
+      <c r="P39" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q39" s="52" t="s">
+      <c r="Q39" s="49" t="s">
         <v>310</v>
       </c>
-      <c r="R39" s="62" t="s">
+      <c r="R39" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="T39" s="43"/>
-      <c r="U39" s="43"/>
+      <c r="T39" s="41"/>
+      <c r="U39" s="41"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:21">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="50" t="s">
         <v>375</v>
       </c>
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="50" t="s">
         <v>376</v>
       </c>
-      <c r="C40" s="53" t="s">
+      <c r="C40" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="D40" s="55" t="s">
+      <c r="D40" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E40" s="53" t="s">
+      <c r="E40" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F40" s="53">
+      <c r="F40" s="50">
         <v>2</v>
       </c>
-      <c r="G40" s="53" t="s">
+      <c r="G40" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H40" s="55" t="s">
+      <c r="H40" s="52" t="s">
         <v>373</v>
       </c>
-      <c r="I40" s="59" t="s">
+      <c r="I40" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J40" s="59">
+      <c r="J40" s="56">
         <v>3</v>
       </c>
-      <c r="K40" s="59">
-        <v>1</v>
-      </c>
-      <c r="L40" s="53">
-        <v>0</v>
-      </c>
-      <c r="M40" s="59" t="s">
+      <c r="K40" s="56">
+        <v>1</v>
+      </c>
+      <c r="L40" s="50">
+        <v>0</v>
+      </c>
+      <c r="M40" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N40" s="59">
+      <c r="N40" s="56">
         <v>3</v>
       </c>
-      <c r="O40" s="59">
-        <v>0</v>
-      </c>
-      <c r="P40" s="59" t="s">
+      <c r="O40" s="56">
+        <v>0</v>
+      </c>
+      <c r="P40" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q40" s="52" t="s">
+      <c r="Q40" s="49" t="s">
         <v>298</v>
       </c>
-      <c r="R40" s="62" t="s">
+      <c r="R40" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="T40" s="64"/>
-      <c r="U40" s="64"/>
+      <c r="T40" s="61"/>
+      <c r="U40" s="61"/>
     </row>
     <row r="41" ht="18" customHeight="1" spans="1:21">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="50" t="s">
         <v>377</v>
       </c>
-      <c r="B41" s="53" t="s">
+      <c r="B41" s="50" t="s">
         <v>378</v>
       </c>
-      <c r="C41" s="53" t="s">
+      <c r="C41" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D41" s="52" t="s">
+      <c r="D41" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="E41" s="53" t="s">
+      <c r="E41" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F41" s="53">
-        <v>1</v>
-      </c>
-      <c r="G41" s="53" t="s">
+      <c r="F41" s="50">
+        <v>1</v>
+      </c>
+      <c r="G41" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H41" s="56" t="s">
+      <c r="H41" s="53" t="s">
         <v>380</v>
       </c>
-      <c r="I41" s="59" t="s">
+      <c r="I41" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="J41" s="59">
-        <v>1</v>
-      </c>
-      <c r="K41" s="59">
-        <v>1</v>
-      </c>
-      <c r="L41" s="53">
-        <v>0</v>
-      </c>
-      <c r="M41" s="59" t="s">
+      <c r="J41" s="56">
+        <v>1</v>
+      </c>
+      <c r="K41" s="56">
+        <v>1</v>
+      </c>
+      <c r="L41" s="50">
+        <v>0</v>
+      </c>
+      <c r="M41" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N41" s="59">
+      <c r="N41" s="56">
         <v>2</v>
       </c>
-      <c r="O41" s="59">
-        <v>0</v>
-      </c>
-      <c r="P41" s="59" t="s">
+      <c r="O41" s="56">
+        <v>0</v>
+      </c>
+      <c r="P41" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q41" s="52" t="s">
+      <c r="Q41" s="49" t="s">
         <v>381</v>
       </c>
-      <c r="R41" s="62" t="s">
+      <c r="R41" s="59" t="s">
         <v>382</v>
       </c>
-      <c r="T41" s="43"/>
-      <c r="U41" s="43"/>
+      <c r="T41" s="41"/>
+      <c r="U41" s="41"/>
     </row>
     <row r="42" ht="18" customHeight="1" spans="1:21">
-      <c r="A42" s="53" t="s">
+      <c r="A42" s="50" t="s">
         <v>383</v>
       </c>
-      <c r="B42" s="53" t="s">
+      <c r="B42" s="50" t="s">
         <v>384</v>
       </c>
-      <c r="C42" s="53" t="s">
+      <c r="C42" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D42" s="52" t="s">
+      <c r="D42" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="E42" s="53" t="s">
+      <c r="E42" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F42" s="53">
+      <c r="F42" s="50">
         <v>2</v>
       </c>
-      <c r="G42" s="53" t="s">
+      <c r="G42" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H42" s="57" t="s">
+      <c r="H42" s="54" t="s">
         <v>380</v>
       </c>
-      <c r="I42" s="59" t="s">
+      <c r="I42" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="J42" s="59">
-        <v>1</v>
-      </c>
-      <c r="K42" s="59">
-        <v>1</v>
-      </c>
-      <c r="L42" s="53">
-        <v>0</v>
-      </c>
-      <c r="M42" s="59" t="s">
+      <c r="J42" s="56">
+        <v>1</v>
+      </c>
+      <c r="K42" s="56">
+        <v>1</v>
+      </c>
+      <c r="L42" s="50">
+        <v>0</v>
+      </c>
+      <c r="M42" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N42" s="59">
+      <c r="N42" s="56">
         <v>2</v>
       </c>
-      <c r="O42" s="59">
-        <v>0</v>
-      </c>
-      <c r="P42" s="59" t="s">
+      <c r="O42" s="56">
+        <v>0</v>
+      </c>
+      <c r="P42" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q42" s="52" t="s">
+      <c r="Q42" s="49" t="s">
         <v>381</v>
       </c>
-      <c r="R42" s="62" t="s">
+      <c r="R42" s="59" t="s">
         <v>382</v>
       </c>
-      <c r="T42" s="64"/>
-      <c r="U42" s="64"/>
+      <c r="T42" s="61"/>
+      <c r="U42" s="61"/>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:21">
-      <c r="A43" s="53" t="s">
+      <c r="A43" s="50" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="53" t="s">
+      <c r="B43" s="50" t="s">
         <v>386</v>
       </c>
-      <c r="C43" s="53" t="s">
+      <c r="C43" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D43" s="55" t="s">
+      <c r="D43" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E43" s="53" t="s">
+      <c r="E43" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F43" s="53">
-        <v>1</v>
-      </c>
-      <c r="G43" s="53" t="s">
+      <c r="F43" s="50">
+        <v>1</v>
+      </c>
+      <c r="G43" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H43" s="55" t="s">
+      <c r="H43" s="52" t="s">
         <v>261</v>
       </c>
-      <c r="I43" s="59" t="s">
+      <c r="I43" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J43" s="59">
-        <v>1</v>
-      </c>
-      <c r="K43" s="59">
-        <v>1</v>
-      </c>
-      <c r="L43" s="53">
-        <v>0</v>
-      </c>
-      <c r="M43" s="59" t="s">
+      <c r="J43" s="56">
+        <v>1</v>
+      </c>
+      <c r="K43" s="56">
+        <v>1</v>
+      </c>
+      <c r="L43" s="50">
+        <v>0</v>
+      </c>
+      <c r="M43" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N43" s="59">
-        <v>1</v>
-      </c>
-      <c r="O43" s="59">
-        <v>0</v>
-      </c>
-      <c r="P43" s="59" t="s">
+      <c r="N43" s="56">
+        <v>1</v>
+      </c>
+      <c r="O43" s="56">
+        <v>0</v>
+      </c>
+      <c r="P43" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q43" s="52" t="s">
+      <c r="Q43" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="R43" s="62" t="s">
+      <c r="R43" s="59" t="s">
         <v>354</v>
       </c>
-      <c r="T43" s="64"/>
-      <c r="U43" s="64"/>
+      <c r="T43" s="61"/>
+      <c r="U43" s="61"/>
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:21">
-      <c r="A44" s="53" t="s">
+      <c r="A44" s="50" t="s">
         <v>387</v>
       </c>
-      <c r="B44" s="53" t="s">
+      <c r="B44" s="50" t="s">
         <v>388</v>
       </c>
-      <c r="C44" s="53" t="s">
+      <c r="C44" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D44" s="55" t="s">
+      <c r="D44" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E44" s="53" t="s">
+      <c r="E44" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F44" s="53">
+      <c r="F44" s="50">
         <v>2</v>
       </c>
-      <c r="G44" s="53" t="s">
+      <c r="G44" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H44" s="55" t="s">
+      <c r="H44" s="52" t="s">
         <v>261</v>
       </c>
-      <c r="I44" s="59" t="s">
+      <c r="I44" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J44" s="59">
-        <v>1</v>
-      </c>
-      <c r="K44" s="59">
-        <v>1</v>
-      </c>
-      <c r="L44" s="53">
-        <v>0</v>
-      </c>
-      <c r="M44" s="59" t="s">
+      <c r="J44" s="56">
+        <v>1</v>
+      </c>
+      <c r="K44" s="56">
+        <v>1</v>
+      </c>
+      <c r="L44" s="50">
+        <v>0</v>
+      </c>
+      <c r="M44" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N44" s="59">
-        <v>1</v>
-      </c>
-      <c r="O44" s="59">
-        <v>0</v>
-      </c>
-      <c r="P44" s="59" t="s">
+      <c r="N44" s="56">
+        <v>1</v>
+      </c>
+      <c r="O44" s="56">
+        <v>0</v>
+      </c>
+      <c r="P44" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q44" s="52" t="s">
+      <c r="Q44" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="R44" s="62" t="s">
+      <c r="R44" s="59" t="s">
         <v>354</v>
       </c>
-      <c r="T44" s="64"/>
-      <c r="U44" s="64"/>
+      <c r="T44" s="61"/>
+      <c r="U44" s="61"/>
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:21">
-      <c r="A45" s="53" t="s">
+      <c r="A45" s="50" t="s">
         <v>389</v>
       </c>
-      <c r="B45" s="53" t="s">
+      <c r="B45" s="50" t="s">
         <v>390</v>
       </c>
-      <c r="C45" s="53" t="s">
+      <c r="C45" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D45" s="52" t="s">
+      <c r="D45" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="E45" s="53" t="s">
+      <c r="E45" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F45" s="53">
-        <v>1</v>
-      </c>
-      <c r="G45" s="53" t="s">
+      <c r="F45" s="50">
+        <v>1</v>
+      </c>
+      <c r="G45" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H45" s="55" t="s">
+      <c r="H45" s="52" t="s">
         <v>391</v>
       </c>
-      <c r="I45" s="59" t="s">
+      <c r="I45" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J45" s="59">
+      <c r="J45" s="56">
         <v>3</v>
       </c>
-      <c r="K45" s="59">
-        <v>1</v>
-      </c>
-      <c r="L45" s="53">
-        <v>0</v>
-      </c>
-      <c r="M45" s="59" t="s">
+      <c r="K45" s="56">
+        <v>1</v>
+      </c>
+      <c r="L45" s="50">
+        <v>0</v>
+      </c>
+      <c r="M45" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N45" s="59">
+      <c r="N45" s="56">
         <v>2</v>
       </c>
-      <c r="O45" s="59">
-        <v>0</v>
-      </c>
-      <c r="P45" s="59" t="s">
+      <c r="O45" s="56">
+        <v>0</v>
+      </c>
+      <c r="P45" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q45" s="52" t="s">
+      <c r="Q45" s="49" t="s">
         <v>381</v>
       </c>
-      <c r="R45" s="62" t="s">
+      <c r="R45" s="59" t="s">
         <v>392</v>
       </c>
-      <c r="T45" s="64"/>
-      <c r="U45" s="64"/>
+      <c r="T45" s="61"/>
+      <c r="U45" s="61"/>
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:21">
-      <c r="A46" s="53" t="s">
+      <c r="A46" s="50" t="s">
         <v>393</v>
       </c>
-      <c r="B46" s="53" t="s">
+      <c r="B46" s="50" t="s">
         <v>394</v>
       </c>
-      <c r="C46" s="53" t="s">
+      <c r="C46" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D46" s="52" t="s">
+      <c r="D46" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="E46" s="53" t="s">
+      <c r="E46" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="F46" s="53">
+      <c r="F46" s="50">
         <v>2</v>
       </c>
-      <c r="G46" s="53" t="s">
+      <c r="G46" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="H46" s="55" t="s">
+      <c r="H46" s="52" t="s">
         <v>391</v>
       </c>
-      <c r="I46" s="59" t="s">
+      <c r="I46" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J46" s="59">
+      <c r="J46" s="56">
         <v>4</v>
       </c>
-      <c r="K46" s="59">
-        <v>1</v>
-      </c>
-      <c r="L46" s="53">
-        <v>0</v>
-      </c>
-      <c r="M46" s="59" t="s">
+      <c r="K46" s="56">
+        <v>1</v>
+      </c>
+      <c r="L46" s="50">
+        <v>0</v>
+      </c>
+      <c r="M46" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N46" s="59">
+      <c r="N46" s="56">
         <v>2</v>
       </c>
-      <c r="O46" s="59">
-        <v>0</v>
-      </c>
-      <c r="P46" s="59" t="s">
+      <c r="O46" s="56">
+        <v>0</v>
+      </c>
+      <c r="P46" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q46" s="52" t="s">
+      <c r="Q46" s="49" t="s">
         <v>381</v>
       </c>
-      <c r="R46" s="62" t="s">
+      <c r="R46" s="59" t="s">
         <v>392</v>
       </c>
-      <c r="T46" s="64"/>
-      <c r="U46" s="64"/>
+      <c r="T46" s="61"/>
+      <c r="U46" s="61"/>
     </row>
     <row r="47" ht="18" customHeight="1" spans="1:21">
-      <c r="A47" s="53" t="s">
+      <c r="A47" s="50" t="s">
         <v>395</v>
       </c>
-      <c r="B47" s="53" t="s">
+      <c r="B47" s="50" t="s">
         <v>396</v>
       </c>
-      <c r="C47" s="53" t="s">
+      <c r="C47" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D47" s="55" t="s">
+      <c r="D47" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E47" s="53" t="s">
+      <c r="E47" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F47" s="53">
-        <v>1</v>
-      </c>
-      <c r="G47" s="53" t="s">
+      <c r="F47" s="50">
+        <v>1</v>
+      </c>
+      <c r="G47" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H47" s="55" t="s">
+      <c r="H47" s="52" t="s">
         <v>308</v>
       </c>
-      <c r="I47" s="59" t="s">
+      <c r="I47" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J47" s="59">
-        <v>1</v>
-      </c>
-      <c r="K47" s="59">
-        <v>1</v>
-      </c>
-      <c r="L47" s="53">
-        <v>0</v>
-      </c>
-      <c r="M47" s="59" t="s">
+      <c r="J47" s="56">
+        <v>1</v>
+      </c>
+      <c r="K47" s="56">
+        <v>1</v>
+      </c>
+      <c r="L47" s="50">
+        <v>0</v>
+      </c>
+      <c r="M47" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N47" s="59">
+      <c r="N47" s="56">
         <v>3</v>
       </c>
-      <c r="O47" s="59">
-        <v>0</v>
-      </c>
-      <c r="P47" s="59" t="s">
+      <c r="O47" s="56">
+        <v>0</v>
+      </c>
+      <c r="P47" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q47" s="52" t="s">
+      <c r="Q47" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="R47" s="62" t="s">
+      <c r="R47" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="T47" s="64"/>
-      <c r="U47" s="64"/>
+      <c r="T47" s="61"/>
+      <c r="U47" s="61"/>
     </row>
     <row r="48" ht="18" customHeight="1" spans="1:21">
-      <c r="A48" s="53" t="s">
+      <c r="A48" s="50" t="s">
         <v>398</v>
       </c>
-      <c r="B48" s="53" t="s">
+      <c r="B48" s="50" t="s">
         <v>399</v>
       </c>
-      <c r="C48" s="53" t="s">
+      <c r="C48" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D48" s="55" t="s">
+      <c r="D48" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E48" s="53" t="s">
+      <c r="E48" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F48" s="53">
+      <c r="F48" s="50">
         <v>2</v>
       </c>
-      <c r="G48" s="53" t="s">
+      <c r="G48" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H48" s="55" t="s">
+      <c r="H48" s="52" t="s">
         <v>308</v>
       </c>
-      <c r="I48" s="59" t="s">
+      <c r="I48" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J48" s="59">
-        <v>1</v>
-      </c>
-      <c r="K48" s="59">
-        <v>1</v>
-      </c>
-      <c r="L48" s="53">
-        <v>0</v>
-      </c>
-      <c r="M48" s="59" t="s">
+      <c r="J48" s="56">
+        <v>1</v>
+      </c>
+      <c r="K48" s="56">
+        <v>1</v>
+      </c>
+      <c r="L48" s="50">
+        <v>0</v>
+      </c>
+      <c r="M48" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N48" s="59">
+      <c r="N48" s="56">
         <v>3</v>
       </c>
-      <c r="O48" s="59">
-        <v>0</v>
-      </c>
-      <c r="P48" s="59" t="s">
+      <c r="O48" s="56">
+        <v>0</v>
+      </c>
+      <c r="P48" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q48" s="52" t="s">
+      <c r="Q48" s="49" t="s">
         <v>370</v>
       </c>
-      <c r="R48" s="62" t="s">
+      <c r="R48" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="T48" s="43"/>
-      <c r="U48" s="43"/>
+      <c r="T48" s="41"/>
+      <c r="U48" s="41"/>
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:21">
-      <c r="A49" s="53" t="s">
+      <c r="A49" s="50" t="s">
         <v>400</v>
       </c>
-      <c r="B49" s="53" t="s">
+      <c r="B49" s="50" t="s">
         <v>401</v>
       </c>
-      <c r="C49" s="53" t="s">
+      <c r="C49" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D49" s="55" t="s">
+      <c r="D49" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E49" s="53" t="s">
+      <c r="E49" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F49" s="53">
-        <v>1</v>
-      </c>
-      <c r="G49" s="53" t="s">
+      <c r="F49" s="50">
+        <v>1</v>
+      </c>
+      <c r="G49" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H49" s="55" t="s">
+      <c r="H49" s="52" t="s">
         <v>366</v>
       </c>
-      <c r="I49" s="59" t="s">
+      <c r="I49" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J49" s="59">
-        <v>1</v>
-      </c>
-      <c r="K49" s="59">
-        <v>1</v>
-      </c>
-      <c r="L49" s="53">
-        <v>0</v>
-      </c>
-      <c r="M49" s="59" t="s">
+      <c r="J49" s="56">
+        <v>1</v>
+      </c>
+      <c r="K49" s="56">
+        <v>1</v>
+      </c>
+      <c r="L49" s="50">
+        <v>0</v>
+      </c>
+      <c r="M49" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N49" s="59">
+      <c r="N49" s="56">
         <v>3</v>
       </c>
-      <c r="O49" s="59">
-        <v>0</v>
-      </c>
-      <c r="P49" s="59" t="s">
+      <c r="O49" s="56">
+        <v>0</v>
+      </c>
+      <c r="P49" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q49" s="52" t="s">
+      <c r="Q49" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="R49" s="62" t="s">
+      <c r="R49" s="59" t="s">
         <v>367</v>
       </c>
-      <c r="T49" s="43"/>
-      <c r="U49" s="43"/>
+      <c r="T49" s="41"/>
+      <c r="U49" s="41"/>
     </row>
     <row r="50" ht="18" customHeight="1" spans="1:21">
-      <c r="A50" s="53" t="s">
+      <c r="A50" s="50" t="s">
         <v>402</v>
       </c>
-      <c r="B50" s="53" t="s">
+      <c r="B50" s="50" t="s">
         <v>403</v>
       </c>
-      <c r="C50" s="53" t="s">
+      <c r="C50" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D50" s="55" t="s">
+      <c r="D50" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E50" s="53" t="s">
+      <c r="E50" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F50" s="53">
+      <c r="F50" s="50">
         <v>2</v>
       </c>
-      <c r="G50" s="53" t="s">
+      <c r="G50" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H50" s="55" t="s">
+      <c r="H50" s="52" t="s">
         <v>366</v>
       </c>
-      <c r="I50" s="59" t="s">
+      <c r="I50" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J50" s="59">
-        <v>1</v>
-      </c>
-      <c r="K50" s="59">
-        <v>1</v>
-      </c>
-      <c r="L50" s="53">
-        <v>0</v>
-      </c>
-      <c r="M50" s="59" t="s">
+      <c r="J50" s="56">
+        <v>1</v>
+      </c>
+      <c r="K50" s="56">
+        <v>1</v>
+      </c>
+      <c r="L50" s="50">
+        <v>0</v>
+      </c>
+      <c r="M50" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N50" s="59">
+      <c r="N50" s="56">
         <v>3</v>
       </c>
-      <c r="O50" s="59">
-        <v>0</v>
-      </c>
-      <c r="P50" s="59" t="s">
+      <c r="O50" s="56">
+        <v>0</v>
+      </c>
+      <c r="P50" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q50" s="52" t="s">
+      <c r="Q50" s="49" t="s">
         <v>370</v>
       </c>
-      <c r="R50" s="62" t="s">
+      <c r="R50" s="59" t="s">
         <v>367</v>
       </c>
-      <c r="T50" s="64"/>
-      <c r="U50" s="64"/>
+      <c r="T50" s="61"/>
+      <c r="U50" s="61"/>
     </row>
     <row r="51" ht="18" customHeight="1" spans="1:21">
-      <c r="A51" s="53" t="s">
+      <c r="A51" s="50" t="s">
         <v>404</v>
       </c>
-      <c r="B51" s="53" t="s">
+      <c r="B51" s="50" t="s">
         <v>405</v>
       </c>
-      <c r="C51" s="53" t="s">
+      <c r="C51" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D51" s="55" t="s">
+      <c r="D51" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E51" s="53" t="s">
+      <c r="E51" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F51" s="53">
-        <v>1</v>
-      </c>
-      <c r="G51" s="53" t="s">
+      <c r="F51" s="50">
+        <v>1</v>
+      </c>
+      <c r="G51" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H51" s="56" t="s">
+      <c r="H51" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="I51" s="59" t="s">
+      <c r="I51" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J51" s="59">
+      <c r="J51" s="56">
         <v>3</v>
       </c>
-      <c r="K51" s="59">
-        <v>1</v>
-      </c>
-      <c r="L51" s="53">
-        <v>0</v>
-      </c>
-      <c r="M51" s="59" t="s">
+      <c r="K51" s="56">
+        <v>1</v>
+      </c>
+      <c r="L51" s="50">
+        <v>0</v>
+      </c>
+      <c r="M51" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N51" s="59">
+      <c r="N51" s="56">
         <v>3</v>
       </c>
-      <c r="O51" s="59">
-        <v>0</v>
-      </c>
-      <c r="P51" s="59" t="s">
+      <c r="O51" s="56">
+        <v>0</v>
+      </c>
+      <c r="P51" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q51" s="52" t="s">
+      <c r="Q51" s="49" t="s">
         <v>310</v>
       </c>
-      <c r="R51" s="62" t="s">
+      <c r="R51" s="59" t="s">
         <v>339</v>
       </c>
-      <c r="T51" s="64"/>
-      <c r="U51" s="64"/>
+      <c r="T51" s="61"/>
+      <c r="U51" s="61"/>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:21">
-      <c r="A52" s="53" t="s">
+      <c r="A52" s="50" t="s">
         <v>406</v>
       </c>
-      <c r="B52" s="53" t="s">
+      <c r="B52" s="50" t="s">
         <v>407</v>
       </c>
-      <c r="C52" s="53" t="s">
+      <c r="C52" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D52" s="55" t="s">
+      <c r="D52" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E52" s="53" t="s">
+      <c r="E52" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F52" s="53">
+      <c r="F52" s="50">
         <v>2</v>
       </c>
-      <c r="G52" s="53" t="s">
+      <c r="G52" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="H52" s="57" t="s">
+      <c r="H52" s="54" t="s">
         <v>337</v>
       </c>
-      <c r="I52" s="59" t="s">
+      <c r="I52" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J52" s="59">
+      <c r="J52" s="56">
         <v>3</v>
       </c>
-      <c r="K52" s="59">
-        <v>1</v>
-      </c>
-      <c r="L52" s="53">
-        <v>0</v>
-      </c>
-      <c r="M52" s="59" t="s">
+      <c r="K52" s="56">
+        <v>1</v>
+      </c>
+      <c r="L52" s="50">
+        <v>0</v>
+      </c>
+      <c r="M52" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N52" s="59">
+      <c r="N52" s="56">
         <v>3</v>
       </c>
-      <c r="O52" s="59">
-        <v>0</v>
-      </c>
-      <c r="P52" s="59" t="s">
+      <c r="O52" s="56">
+        <v>0</v>
+      </c>
+      <c r="P52" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q52" s="52" t="s">
+      <c r="Q52" s="49" t="s">
         <v>298</v>
       </c>
-      <c r="R52" s="62" t="s">
+      <c r="R52" s="59" t="s">
         <v>339</v>
       </c>
-      <c r="T52" s="43"/>
-      <c r="U52" s="43"/>
+      <c r="T52" s="41"/>
+      <c r="U52" s="41"/>
     </row>
     <row r="53" ht="18" customHeight="1" spans="1:21">
-      <c r="A53" s="53" t="s">
+      <c r="A53" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="B53" s="53" t="s">
+      <c r="B53" s="50" t="s">
         <v>409</v>
       </c>
-      <c r="C53" s="53" t="s">
+      <c r="C53" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D53" s="52" t="s">
+      <c r="D53" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="E53" s="53" t="s">
+      <c r="E53" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F53" s="53">
-        <v>1</v>
-      </c>
-      <c r="G53" s="53" t="s">
+      <c r="F53" s="50">
+        <v>1</v>
+      </c>
+      <c r="G53" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H53" s="55" t="s">
+      <c r="H53" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I53" s="59" t="s">
+      <c r="I53" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J53" s="59">
+      <c r="J53" s="56">
         <v>8</v>
       </c>
-      <c r="K53" s="59">
-        <v>1</v>
-      </c>
-      <c r="L53" s="53">
-        <v>0</v>
-      </c>
-      <c r="M53" s="59" t="s">
+      <c r="K53" s="56">
+        <v>1</v>
+      </c>
+      <c r="L53" s="50">
+        <v>0</v>
+      </c>
+      <c r="M53" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N53" s="59">
+      <c r="N53" s="56">
         <v>3</v>
       </c>
-      <c r="O53" s="59">
-        <v>1</v>
-      </c>
-      <c r="P53" s="59" t="s">
+      <c r="O53" s="56">
+        <v>1</v>
+      </c>
+      <c r="P53" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q53" s="52" t="s">
+      <c r="Q53" s="49" t="s">
         <v>410</v>
       </c>
-      <c r="R53" s="62" t="s">
+      <c r="R53" s="59" t="s">
         <v>411</v>
       </c>
-      <c r="T53" s="64"/>
-      <c r="U53" s="64"/>
+      <c r="T53" s="61"/>
+      <c r="U53" s="61"/>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:21">
-      <c r="A54" s="53" t="s">
+      <c r="A54" s="50" t="s">
         <v>412</v>
       </c>
-      <c r="B54" s="53" t="s">
+      <c r="B54" s="50" t="s">
         <v>413</v>
       </c>
-      <c r="C54" s="53" t="s">
+      <c r="C54" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D54" s="52" t="s">
+      <c r="D54" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="E54" s="53" t="s">
+      <c r="E54" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F54" s="53">
+      <c r="F54" s="50">
         <v>2</v>
       </c>
-      <c r="G54" s="53" t="s">
+      <c r="G54" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H54" s="55" t="s">
+      <c r="H54" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I54" s="59" t="s">
+      <c r="I54" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J54" s="59">
+      <c r="J54" s="56">
         <v>10</v>
       </c>
-      <c r="K54" s="59">
-        <v>1</v>
-      </c>
-      <c r="L54" s="53">
-        <v>0</v>
-      </c>
-      <c r="M54" s="59" t="s">
+      <c r="K54" s="56">
+        <v>1</v>
+      </c>
+      <c r="L54" s="50">
+        <v>0</v>
+      </c>
+      <c r="M54" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N54" s="59">
+      <c r="N54" s="56">
         <v>3</v>
       </c>
-      <c r="O54" s="59">
-        <v>1</v>
-      </c>
-      <c r="P54" s="59" t="s">
+      <c r="O54" s="56">
+        <v>1</v>
+      </c>
+      <c r="P54" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q54" s="52" t="s">
+      <c r="Q54" s="49" t="s">
         <v>410</v>
       </c>
-      <c r="R54" s="62" t="s">
+      <c r="R54" s="59" t="s">
         <v>411</v>
       </c>
-      <c r="T54" s="64"/>
-      <c r="U54" s="64"/>
+      <c r="T54" s="61"/>
+      <c r="U54" s="61"/>
     </row>
     <row r="55" ht="18" customHeight="1" spans="1:18">
-      <c r="A55" s="53" t="s">
+      <c r="A55" s="50" t="s">
         <v>414</v>
       </c>
-      <c r="B55" s="53" t="s">
+      <c r="B55" s="50" t="s">
         <v>415</v>
       </c>
-      <c r="C55" s="53" t="s">
+      <c r="C55" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D55" s="55" t="s">
+      <c r="D55" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E55" s="53" t="s">
+      <c r="E55" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F55" s="53">
-        <v>1</v>
-      </c>
-      <c r="G55" s="53" t="s">
+      <c r="F55" s="50">
+        <v>1</v>
+      </c>
+      <c r="G55" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H55" s="55" t="s">
+      <c r="H55" s="52" t="s">
         <v>297</v>
       </c>
-      <c r="I55" s="59" t="s">
+      <c r="I55" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J55" s="59">
+      <c r="J55" s="56">
         <v>7</v>
       </c>
-      <c r="K55" s="59">
-        <v>1</v>
-      </c>
-      <c r="L55" s="53">
-        <v>0</v>
-      </c>
-      <c r="M55" s="59" t="s">
+      <c r="K55" s="56">
+        <v>1</v>
+      </c>
+      <c r="L55" s="50">
+        <v>0</v>
+      </c>
+      <c r="M55" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N55" s="59">
+      <c r="N55" s="56">
         <v>3</v>
       </c>
-      <c r="O55" s="59">
-        <v>0</v>
-      </c>
-      <c r="P55" s="59" t="s">
+      <c r="O55" s="56">
+        <v>0</v>
+      </c>
+      <c r="P55" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q55" s="52" t="s">
+      <c r="Q55" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="R55" s="62" t="s">
+      <c r="R55" s="59" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" spans="1:18">
-      <c r="A56" s="53" t="s">
+      <c r="A56" s="50" t="s">
         <v>417</v>
       </c>
-      <c r="B56" s="53" t="s">
+      <c r="B56" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="C56" s="53" t="s">
+      <c r="C56" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D56" s="55" t="s">
+      <c r="D56" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E56" s="53" t="s">
+      <c r="E56" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F56" s="53">
+      <c r="F56" s="50">
         <v>2</v>
       </c>
-      <c r="G56" s="53" t="s">
+      <c r="G56" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H56" s="55" t="s">
+      <c r="H56" s="52" t="s">
         <v>297</v>
       </c>
-      <c r="I56" s="59" t="s">
+      <c r="I56" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J56" s="59">
+      <c r="J56" s="56">
         <v>9</v>
       </c>
-      <c r="K56" s="59">
-        <v>1</v>
-      </c>
-      <c r="L56" s="53">
-        <v>0</v>
-      </c>
-      <c r="M56" s="59" t="s">
+      <c r="K56" s="56">
+        <v>1</v>
+      </c>
+      <c r="L56" s="50">
+        <v>0</v>
+      </c>
+      <c r="M56" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N56" s="59">
+      <c r="N56" s="56">
         <v>3</v>
       </c>
-      <c r="O56" s="59">
-        <v>0</v>
-      </c>
-      <c r="P56" s="59" t="s">
+      <c r="O56" s="56">
+        <v>0</v>
+      </c>
+      <c r="P56" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q56" s="52" t="s">
+      <c r="Q56" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="R56" s="62" t="s">
+      <c r="R56" s="59" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" spans="1:18">
-      <c r="A57" s="53" t="s">
+      <c r="A57" s="50" t="s">
         <v>419</v>
       </c>
-      <c r="B57" s="53" t="s">
+      <c r="B57" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C57" s="53" t="s">
+      <c r="C57" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D57" s="55" t="s">
+      <c r="D57" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E57" s="53" t="s">
+      <c r="E57" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F57" s="53">
-        <v>1</v>
-      </c>
-      <c r="G57" s="53" t="s">
+      <c r="F57" s="50">
+        <v>1</v>
+      </c>
+      <c r="G57" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H57" s="55" t="s">
+      <c r="H57" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I57" s="59" t="s">
+      <c r="I57" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J57" s="59">
+      <c r="J57" s="56">
         <v>4</v>
       </c>
-      <c r="K57" s="59">
+      <c r="K57" s="56">
         <v>2</v>
       </c>
-      <c r="L57" s="53">
-        <v>0</v>
-      </c>
-      <c r="M57" s="59" t="s">
+      <c r="L57" s="50">
+        <v>0</v>
+      </c>
+      <c r="M57" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N57" s="59">
+      <c r="N57" s="56">
         <v>3</v>
       </c>
-      <c r="O57" s="59">
-        <v>0</v>
-      </c>
-      <c r="P57" s="59" t="s">
+      <c r="O57" s="56">
+        <v>0</v>
+      </c>
+      <c r="P57" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q57" s="52" t="s">
+      <c r="Q57" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="R57" s="62" t="s">
+      <c r="R57" s="59" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" spans="1:18">
-      <c r="A58" s="53" t="s">
+      <c r="A58" s="50" t="s">
         <v>422</v>
       </c>
-      <c r="B58" s="53" t="s">
+      <c r="B58" s="50" t="s">
         <v>423</v>
       </c>
-      <c r="C58" s="53" t="s">
+      <c r="C58" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D58" s="55" t="s">
+      <c r="D58" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E58" s="53" t="s">
+      <c r="E58" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F58" s="53">
+      <c r="F58" s="50">
         <v>2</v>
       </c>
-      <c r="G58" s="53" t="s">
+      <c r="G58" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H58" s="55" t="s">
+      <c r="H58" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I58" s="59" t="s">
+      <c r="I58" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J58" s="59">
+      <c r="J58" s="56">
         <v>5</v>
       </c>
-      <c r="K58" s="59">
+      <c r="K58" s="56">
         <v>2</v>
       </c>
-      <c r="L58" s="53">
-        <v>0</v>
-      </c>
-      <c r="M58" s="59" t="s">
+      <c r="L58" s="50">
+        <v>0</v>
+      </c>
+      <c r="M58" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N58" s="59">
+      <c r="N58" s="56">
         <v>3</v>
       </c>
-      <c r="O58" s="59">
-        <v>0</v>
-      </c>
-      <c r="P58" s="59" t="s">
+      <c r="O58" s="56">
+        <v>0</v>
+      </c>
+      <c r="P58" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q58" s="52" t="s">
+      <c r="Q58" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="R58" s="62" t="s">
+      <c r="R58" s="59" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" spans="1:18">
-      <c r="A59" s="53" t="s">
+      <c r="A59" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="B59" s="53" t="s">
+      <c r="B59" s="50" t="s">
         <v>425</v>
       </c>
-      <c r="C59" s="53" t="s">
+      <c r="C59" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D59" s="55" t="s">
+      <c r="D59" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E59" s="53" t="s">
+      <c r="E59" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F59" s="53">
-        <v>1</v>
-      </c>
-      <c r="G59" s="53" t="s">
+      <c r="F59" s="50">
+        <v>1</v>
+      </c>
+      <c r="G59" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H59" s="55" t="s">
+      <c r="H59" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I59" s="59" t="s">
+      <c r="I59" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J59" s="59">
+      <c r="J59" s="56">
         <v>12</v>
       </c>
-      <c r="K59" s="59">
-        <v>1</v>
-      </c>
-      <c r="L59" s="53">
-        <v>0</v>
-      </c>
-      <c r="M59" s="59" t="s">
+      <c r="K59" s="56">
+        <v>1</v>
+      </c>
+      <c r="L59" s="50">
+        <v>0</v>
+      </c>
+      <c r="M59" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N59" s="59">
+      <c r="N59" s="56">
         <v>3</v>
       </c>
-      <c r="O59" s="59">
-        <v>0</v>
-      </c>
-      <c r="P59" s="59" t="s">
+      <c r="O59" s="56">
+        <v>0</v>
+      </c>
+      <c r="P59" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q59" s="52" t="s">
+      <c r="Q59" s="49" t="s">
         <v>410</v>
       </c>
-      <c r="R59" s="62" t="s">
+      <c r="R59" s="59" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" spans="1:18">
-      <c r="A60" s="53" t="s">
+      <c r="A60" s="50" t="s">
         <v>426</v>
       </c>
-      <c r="B60" s="53" t="s">
+      <c r="B60" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="C60" s="53" t="s">
+      <c r="C60" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="D60" s="55" t="s">
+      <c r="D60" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E60" s="53" t="s">
+      <c r="E60" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F60" s="53">
+      <c r="F60" s="50">
         <v>2</v>
       </c>
-      <c r="G60" s="53" t="s">
+      <c r="G60" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="H60" s="55" t="s">
+      <c r="H60" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I60" s="59" t="s">
+      <c r="I60" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="J60" s="59">
+      <c r="J60" s="56">
         <v>15</v>
       </c>
-      <c r="K60" s="59">
-        <v>1</v>
-      </c>
-      <c r="L60" s="53">
-        <v>0</v>
-      </c>
-      <c r="M60" s="59" t="s">
+      <c r="K60" s="56">
+        <v>1</v>
+      </c>
+      <c r="L60" s="50">
+        <v>0</v>
+      </c>
+      <c r="M60" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N60" s="59">
+      <c r="N60" s="56">
         <v>3</v>
       </c>
-      <c r="O60" s="59">
-        <v>0</v>
-      </c>
-      <c r="P60" s="59" t="s">
+      <c r="O60" s="56">
+        <v>0</v>
+      </c>
+      <c r="P60" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="Q60" s="52" t="s">
+      <c r="Q60" s="49" t="s">
         <v>410</v>
       </c>
-      <c r="R60" s="62" t="s">
+      <c r="R60" s="59" t="s">
         <v>321</v>
       </c>
     </row>
@@ -12198,7 +12094,7 @@
       <c r="M81" s="34"/>
       <c r="N81" s="7"/>
       <c r="O81" s="7"/>
-      <c r="P81" s="65"/>
+      <c r="P81" s="62"/>
       <c r="Q81" s="7"/>
       <c r="R81" s="7"/>
     </row>
@@ -12429,7 +12325,7 @@
       <c r="G1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="43" t="s">
         <v>219</v>
       </c>
       <c r="I1" s="3" t="s">
@@ -12464,7 +12360,7 @@
       <c r="G2" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="H2" s="46" t="s">
+      <c r="H2" s="44" t="s">
         <v>236</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -12490,7 +12386,7 @@
       <c r="D3" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F3" s="6">
@@ -12508,7 +12404,7 @@
       <c r="J3" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -12595,7 +12491,7 @@
       <c r="D6" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F6" s="6">
@@ -12613,7 +12509,7 @@
       <c r="J6" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -12665,7 +12561,7 @@
       <c r="D8" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F8" s="6">
@@ -12683,7 +12579,7 @@
       <c r="J8" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K8" s="47" t="s">
+      <c r="K8" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -12840,7 +12736,7 @@
       <c r="D13" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="E13" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F13" s="6">
@@ -12858,7 +12754,7 @@
       <c r="J13" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K13" s="47" t="s">
+      <c r="K13" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -12945,7 +12841,7 @@
       <c r="D16" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="E16" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F16" s="6">
@@ -12963,7 +12859,7 @@
       <c r="J16" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K16" s="47" t="s">
+      <c r="K16" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -13050,7 +12946,7 @@
       <c r="D19" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="E19" s="47" t="s">
+      <c r="E19" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F19" s="6">
@@ -13085,7 +12981,7 @@
       <c r="D20" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="E20" s="47" t="s">
+      <c r="E20" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F20" s="6">
@@ -13190,7 +13086,7 @@
       <c r="D23" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F23" s="6">
@@ -13208,7 +13104,7 @@
       <c r="J23" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K23" s="47" t="s">
+      <c r="K23" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -13260,7 +13156,7 @@
       <c r="D25" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E25" s="47" t="s">
+      <c r="E25" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F25" s="6">
@@ -13278,7 +13174,7 @@
       <c r="J25" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K25" s="47" t="s">
+      <c r="K25" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -13365,7 +13261,7 @@
       <c r="D28" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E28" s="47" t="s">
+      <c r="E28" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F28" s="6">
@@ -13383,7 +13279,7 @@
       <c r="J28" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K28" s="47" t="s">
+      <c r="K28" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -13540,7 +13436,7 @@
       <c r="D33" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E33" s="47" t="s">
+      <c r="E33" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F33" s="6">
@@ -13558,7 +13454,7 @@
       <c r="J33" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K33" s="47" t="s">
+      <c r="K33" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -13715,7 +13611,7 @@
       <c r="D38" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E38" s="47" t="s">
+      <c r="E38" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F38" s="6">
@@ -13733,7 +13629,7 @@
       <c r="J38" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K38" s="47" t="s">
+      <c r="K38" s="45" t="s">
         <v>242</v>
       </c>
     </row>
@@ -13855,7 +13751,7 @@
       <c r="D42" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="E42" s="47" t="s">
+      <c r="E42" s="45" t="s">
         <v>246</v>
       </c>
       <c r="F42" s="6">
@@ -15060,13 +14956,13 @@
       <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="12" t="s">
         <v>222</v>
       </c>
       <c r="F1" s="12"/>
@@ -15084,13 +14980,13 @@
       <c r="B2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="13" t="s">
         <v>534</v>
       </c>
       <c r="F2" s="13"/>
@@ -15102,19 +14998,19 @@
       <c r="L2" s="13"/>
     </row>
     <row r="3" ht="17.25" spans="1:12">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="36" t="s">
         <v>499</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="36" t="s">
         <v>535</v>
       </c>
-      <c r="C3" s="39">
-        <v>1</v>
-      </c>
-      <c r="D3" s="39">
-        <v>0</v>
-      </c>
-      <c r="E3" s="40" t="s">
+      <c r="C3" s="37">
+        <v>1</v>
+      </c>
+      <c r="D3" s="37">
+        <v>0</v>
+      </c>
+      <c r="E3" s="38" t="s">
         <v>536</v>
       </c>
       <c r="F3" s="18"/>
@@ -15126,19 +15022,19 @@
       <c r="L3" s="18"/>
     </row>
     <row r="4" ht="28.5" spans="1:12">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="36" t="s">
         <v>537</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="36" t="s">
         <v>538</v>
       </c>
-      <c r="C4" s="39">
-        <v>1</v>
-      </c>
-      <c r="D4" s="39">
-        <v>0</v>
-      </c>
-      <c r="E4" s="40" t="s">
+      <c r="C4" s="37">
+        <v>1</v>
+      </c>
+      <c r="D4" s="37">
+        <v>0</v>
+      </c>
+      <c r="E4" s="38" t="s">
         <v>539</v>
       </c>
       <c r="F4" s="18"/>
@@ -15150,19 +15046,19 @@
       <c r="L4" s="18"/>
     </row>
     <row r="5" ht="17.25" spans="1:12">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="36" t="s">
         <v>508</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="36" t="s">
         <v>540</v>
       </c>
-      <c r="C5" s="39">
-        <v>1</v>
-      </c>
-      <c r="D5" s="39">
-        <v>0</v>
-      </c>
-      <c r="E5" s="40" t="s">
+      <c r="C5" s="37">
+        <v>1</v>
+      </c>
+      <c r="D5" s="37">
+        <v>0</v>
+      </c>
+      <c r="E5" s="38" t="s">
         <v>541</v>
       </c>
       <c r="F5" s="18"/>
@@ -15174,19 +15070,19 @@
       <c r="L5" s="18"/>
     </row>
     <row r="6" ht="17.25" spans="1:12">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="36" t="s">
         <v>313</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="36" t="s">
         <v>542</v>
       </c>
-      <c r="C6" s="39">
-        <v>1</v>
-      </c>
-      <c r="D6" s="39">
-        <v>0</v>
-      </c>
-      <c r="E6" s="40" t="s">
+      <c r="C6" s="37">
+        <v>1</v>
+      </c>
+      <c r="D6" s="37">
+        <v>0</v>
+      </c>
+      <c r="E6" s="38" t="s">
         <v>543</v>
       </c>
       <c r="F6" s="18"/>
@@ -15198,19 +15094,19 @@
       <c r="L6" s="18"/>
     </row>
     <row r="7" ht="17.25" spans="1:12">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="36" t="s">
         <v>297</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="36" t="s">
         <v>544</v>
       </c>
-      <c r="C7" s="39">
-        <v>1</v>
-      </c>
-      <c r="D7" s="39">
-        <v>0</v>
-      </c>
-      <c r="E7" s="40" t="s">
+      <c r="C7" s="37">
+        <v>1</v>
+      </c>
+      <c r="D7" s="37">
+        <v>0</v>
+      </c>
+      <c r="E7" s="38" t="s">
         <v>545</v>
       </c>
       <c r="F7" s="18"/>
@@ -15222,19 +15118,19 @@
       <c r="L7" s="18"/>
     </row>
     <row r="8" ht="17.25" spans="1:12">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="36" t="s">
         <v>546</v>
       </c>
-      <c r="C8" s="39">
-        <v>1</v>
-      </c>
-      <c r="D8" s="41" t="s">
+      <c r="C8" s="37">
+        <v>1</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="38" t="s">
         <v>548</v>
       </c>
       <c r="F8" s="18"/>
@@ -15246,19 +15142,19 @@
       <c r="L8" s="18"/>
     </row>
     <row r="9" ht="17.25" spans="1:12">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="36" t="s">
         <v>549</v>
       </c>
-      <c r="C9" s="39">
-        <v>1</v>
-      </c>
-      <c r="D9" s="41" t="s">
+      <c r="C9" s="37">
+        <v>1</v>
+      </c>
+      <c r="D9" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="38" t="s">
         <v>550</v>
       </c>
       <c r="F9" s="18"/>
@@ -15270,19 +15166,19 @@
       <c r="L9" s="18"/>
     </row>
     <row r="10" ht="17.25" spans="1:12">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="36" t="s">
         <v>337</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="36" t="s">
         <v>551</v>
       </c>
-      <c r="C10" s="39">
-        <v>1</v>
-      </c>
-      <c r="D10" s="41" t="s">
+      <c r="C10" s="37">
+        <v>1</v>
+      </c>
+      <c r="D10" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="38" t="s">
         <v>552</v>
       </c>
       <c r="F10" s="18"/>
@@ -15294,19 +15190,19 @@
       <c r="L10" s="18"/>
     </row>
     <row r="11" ht="17.25" spans="1:12">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="36" t="s">
         <v>261</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="36" t="s">
         <v>553</v>
       </c>
-      <c r="C11" s="39">
-        <v>1</v>
-      </c>
-      <c r="D11" s="41" t="s">
+      <c r="C11" s="37">
+        <v>1</v>
+      </c>
+      <c r="D11" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="38" t="s">
         <v>554</v>
       </c>
       <c r="F11" s="18"/>
@@ -15318,19 +15214,19 @@
       <c r="L11" s="18"/>
     </row>
     <row r="12" ht="17.25" spans="1:12">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="36" t="s">
         <v>555</v>
       </c>
-      <c r="C12" s="39">
-        <v>1</v>
-      </c>
-      <c r="D12" s="41" t="s">
+      <c r="C12" s="37">
+        <v>1</v>
+      </c>
+      <c r="D12" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="38" t="s">
         <v>556</v>
       </c>
       <c r="F12" s="18"/>
@@ -15342,19 +15238,19 @@
       <c r="L12" s="18"/>
     </row>
     <row r="13" ht="17.25" spans="1:12">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="36" t="s">
         <v>557</v>
       </c>
-      <c r="C13" s="41">
-        <v>0</v>
-      </c>
-      <c r="D13" s="41" t="s">
+      <c r="C13" s="39">
+        <v>0</v>
+      </c>
+      <c r="D13" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="38" t="s">
         <v>558</v>
       </c>
       <c r="F13" s="18"/>
@@ -15366,19 +15262,19 @@
       <c r="L13" s="18"/>
     </row>
     <row r="14" ht="17.25" spans="1:12">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="36" t="s">
         <v>559</v>
       </c>
-      <c r="C14" s="41">
-        <v>0</v>
-      </c>
-      <c r="D14" s="41" t="s">
+      <c r="C14" s="39">
+        <v>0</v>
+      </c>
+      <c r="D14" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="38" t="s">
         <v>560</v>
       </c>
       <c r="F14" s="18"/>
@@ -15390,19 +15286,19 @@
       <c r="L14" s="18"/>
     </row>
     <row r="15" ht="17.25" spans="1:12">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="36" t="s">
         <v>561</v>
       </c>
-      <c r="C15" s="41">
-        <v>0</v>
-      </c>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="39">
+        <v>0</v>
+      </c>
+      <c r="D15" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="38" t="s">
         <v>562</v>
       </c>
       <c r="F15" s="18"/>
@@ -15414,19 +15310,19 @@
       <c r="L15" s="18"/>
     </row>
     <row r="16" ht="17.25" spans="1:12">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="36" t="s">
         <v>563</v>
       </c>
-      <c r="C16" s="41">
-        <v>0</v>
-      </c>
-      <c r="D16" s="41" t="s">
+      <c r="C16" s="39">
+        <v>0</v>
+      </c>
+      <c r="D16" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E16" s="40" t="s">
+      <c r="E16" s="38" t="s">
         <v>564</v>
       </c>
       <c r="F16" s="18"/>
@@ -15438,19 +15334,19 @@
       <c r="L16" s="18"/>
     </row>
     <row r="17" ht="17.25" spans="1:12">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="36" t="s">
         <v>565</v>
       </c>
-      <c r="C17" s="41">
-        <v>0</v>
-      </c>
-      <c r="D17" s="41" t="s">
+      <c r="C17" s="39">
+        <v>0</v>
+      </c>
+      <c r="D17" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="38" t="s">
         <v>566</v>
       </c>
       <c r="F17" s="18"/>
@@ -15462,19 +15358,19 @@
       <c r="L17" s="18"/>
     </row>
     <row r="18" ht="17.25" spans="1:12">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="C18" s="39">
-        <v>1</v>
-      </c>
-      <c r="D18" s="42" t="s">
+      <c r="C18" s="37">
+        <v>1</v>
+      </c>
+      <c r="D18" s="40" t="s">
         <v>568</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="38" t="s">
         <v>569</v>
       </c>
       <c r="F18" s="18"/>
@@ -15486,19 +15382,19 @@
       <c r="L18" s="18"/>
     </row>
     <row r="19" ht="17.25" spans="1:12">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="36" t="s">
         <v>366</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="36" t="s">
         <v>570</v>
       </c>
-      <c r="C19" s="39">
-        <v>1</v>
-      </c>
-      <c r="D19" s="42" t="s">
+      <c r="C19" s="37">
+        <v>1</v>
+      </c>
+      <c r="D19" s="40" t="s">
         <v>568</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="38" t="s">
         <v>571</v>
       </c>
       <c r="F19" s="18"/>
@@ -15510,19 +15406,19 @@
       <c r="L19" s="18"/>
     </row>
     <row r="20" ht="17.25" spans="1:12">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="36" t="s">
         <v>572</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="36" t="s">
         <v>573</v>
       </c>
-      <c r="C20" s="39">
-        <v>1</v>
-      </c>
-      <c r="D20" s="42" t="s">
+      <c r="C20" s="37">
+        <v>1</v>
+      </c>
+      <c r="D20" s="40" t="s">
         <v>574</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="38" t="s">
         <v>575</v>
       </c>
       <c r="F20" s="18"/>
@@ -15534,19 +15430,19 @@
       <c r="L20" s="18"/>
     </row>
     <row r="21" ht="17.25" spans="1:12">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="36" t="s">
         <v>576</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="C21" s="39">
-        <v>1</v>
-      </c>
-      <c r="D21" s="42" t="s">
+      <c r="C21" s="37">
+        <v>1</v>
+      </c>
+      <c r="D21" s="40" t="s">
         <v>574</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="38" t="s">
         <v>578</v>
       </c>
       <c r="F21" s="18"/>
@@ -15558,19 +15454,19 @@
       <c r="L21" s="18"/>
     </row>
     <row r="22" ht="17.25" spans="1:12">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="36" t="s">
         <v>483</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="36" t="s">
         <v>579</v>
       </c>
-      <c r="C22" s="41">
-        <v>0</v>
-      </c>
-      <c r="D22" s="41" t="s">
+      <c r="C22" s="39">
+        <v>0</v>
+      </c>
+      <c r="D22" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="38" t="s">
         <v>580</v>
       </c>
       <c r="F22" s="18"/>
@@ -15582,19 +15478,19 @@
       <c r="L22" s="18"/>
     </row>
     <row r="23" ht="17.25" spans="1:12">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="36" t="s">
         <v>391</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="36" t="s">
         <v>581</v>
       </c>
-      <c r="C23" s="41">
-        <v>0</v>
-      </c>
-      <c r="D23" s="41" t="s">
+      <c r="C23" s="39">
+        <v>0</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="38" t="s">
         <v>582</v>
       </c>
       <c r="F23" s="18"/>
@@ -15606,19 +15502,19 @@
       <c r="L23" s="18"/>
     </row>
     <row r="24" ht="17.25" spans="1:12">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="36" t="s">
         <v>583</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="36" t="s">
         <v>584</v>
       </c>
-      <c r="C24" s="41">
-        <v>0</v>
-      </c>
-      <c r="D24" s="41" t="s">
+      <c r="C24" s="39">
+        <v>0</v>
+      </c>
+      <c r="D24" s="39" t="s">
         <v>547</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="38" t="s">
         <v>585</v>
       </c>
       <c r="F24" s="18"/>
@@ -15630,19 +15526,19 @@
       <c r="L24" s="18"/>
     </row>
     <row r="25" ht="17.25" spans="1:12">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="36" t="s">
         <v>586</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="36" t="s">
         <v>587</v>
       </c>
-      <c r="C25" s="39">
-        <v>1</v>
-      </c>
-      <c r="D25" s="39">
-        <v>0</v>
-      </c>
-      <c r="E25" s="40" t="s">
+      <c r="C25" s="37">
+        <v>1</v>
+      </c>
+      <c r="D25" s="37">
+        <v>0</v>
+      </c>
+      <c r="E25" s="38" t="s">
         <v>588</v>
       </c>
       <c r="F25" s="18"/>
@@ -15654,19 +15550,19 @@
       <c r="L25" s="18"/>
     </row>
     <row r="26" ht="17.25" spans="1:12">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="36" t="s">
         <v>589</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="36" t="s">
         <v>590</v>
       </c>
-      <c r="C26" s="39">
-        <v>1</v>
-      </c>
-      <c r="D26" s="39">
-        <v>0</v>
-      </c>
-      <c r="E26" s="40" t="s">
+      <c r="C26" s="37">
+        <v>1</v>
+      </c>
+      <c r="D26" s="37">
+        <v>0</v>
+      </c>
+      <c r="E26" s="38" t="s">
         <v>591</v>
       </c>
       <c r="F26" s="18"/>
@@ -15749,7 +15645,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="10"/>
-      <c r="B32" s="43"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
       <c r="E32" s="18"/>
@@ -15758,8 +15654,8 @@
       <c r="H32" s="7"/>
       <c r="I32" s="18"/>
       <c r="J32" s="7"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="12"/>
@@ -16197,7 +16093,7 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="10"/>
-      <c r="B66" s="43"/>
+      <c r="B66" s="41"/>
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
       <c r="E66" s="18"/>
@@ -16206,8 +16102,8 @@
       <c r="H66" s="7"/>
       <c r="I66" s="18"/>
       <c r="J66" s="7"/>
-      <c r="K66" s="44"/>
-      <c r="L66" s="44"/>
+      <c r="K66" s="42"/>
+      <c r="L66" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17580" tabRatio="550" firstSheet="1" activeTab="9"/>
+    <workbookView windowHeight="17580" tabRatio="550" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2608F71-5AA3-497D-8330-DF29D6B6FCDE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08C869C-91E9-4FC8-A30F-C7F83F27E1F9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17150" tabRatio="550" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17150" tabRatio="550" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="981">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -1427,15 +1427,6 @@
     <t>Range_17</t>
   </si>
   <si>
-    <t>"Range_17"범위를 공격하며 "수치"의 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t>"Range_10"범위를 공격하며 "수치"의 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t>"Range_02"범위를 공격하며 "수치"의 피해를 줍니다.</t>
-  </si>
-  <si>
     <t>Range_X-axis</t>
   </si>
   <si>
@@ -1443,9 +1434,6 @@
   </si>
   <si>
     <t>Range_05</t>
-  </si>
-  <si>
-    <t>"Range_05"범위를 공격하며 "수치"의 피해를 줍니다.</t>
   </si>
   <si>
     <t>첫 위치에 "수치"의 피해를 줍니다.</t>
@@ -3231,6 +3219,123 @@
   </si>
   <si>
     <t>0;0</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>범위를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피해를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줍니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -4417,7 +4522,7 @@
         <v>28</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>29</v>
@@ -4908,7 +5013,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="24" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>1</v>
@@ -4931,7 +5036,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="75" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B2" s="75" t="s">
         <v>26</v>
@@ -4955,13 +5060,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B3" s="73" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>219</v>
@@ -4973,19 +5078,19 @@
         <v>1</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="H3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B4" s="73" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>219</v>
@@ -4997,19 +5102,19 @@
         <v>1</v>
       </c>
       <c r="G4" s="73" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="H4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B5" s="73" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>219</v>
@@ -5021,19 +5126,19 @@
         <v>1</v>
       </c>
       <c r="G5" s="73" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B6" s="73" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>219</v>
@@ -5045,19 +5150,19 @@
         <v>1</v>
       </c>
       <c r="G6" s="73" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="H6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B7" s="73" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>219</v>
@@ -5069,19 +5174,19 @@
         <v>1</v>
       </c>
       <c r="G7" s="73" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="H7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B8" s="73" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>219</v>
@@ -5093,19 +5198,19 @@
         <v>1</v>
       </c>
       <c r="G8" s="74" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="H8" s="43"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B9" s="73" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>219</v>
@@ -5117,19 +5222,19 @@
         <v>1</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B10" s="73" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>219</v>
@@ -5141,19 +5246,19 @@
         <v>1</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="H10" s="43"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B11" s="73" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>219</v>
@@ -5165,19 +5270,19 @@
         <v>1</v>
       </c>
       <c r="G11" s="73" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="H11" s="43"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B12" s="73" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>219</v>
@@ -5189,7 +5294,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="73" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="H12" s="43"/>
     </row>
@@ -5306,132 +5411,132 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
+        <v>821</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>822</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>823</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>824</v>
+      </c>
+      <c r="E1" s="43" t="s">
         <v>825</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="F1" s="43" t="s">
+        <v>680</v>
+      </c>
+      <c r="G1" s="43" t="s">
         <v>826</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>827</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>828</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>829</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>684</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>830</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B2" s="43" t="s">
+        <v>828</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>829</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>830</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>831</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>685</v>
+      </c>
+      <c r="G2" s="43" t="s">
         <v>832</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="H2" s="43" t="s">
         <v>833</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>834</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>835</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>689</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>836</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
+        <v>834</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>835</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>836</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>837</v>
+      </c>
+      <c r="E3" s="43" t="s">
         <v>838</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="F3" s="43" t="s">
         <v>839</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>840</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>841</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>842</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>843</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>218</v>
       </c>
       <c r="H3" s="43" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
+        <v>841</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>842</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>836</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>837</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>843</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>844</v>
+      </c>
+      <c r="G4" s="43" t="s">
         <v>845</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="H4" s="43" t="s">
         <v>846</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>840</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>841</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>847</v>
-      </c>
-      <c r="F4" s="43" t="s">
-        <v>848</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>849</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
+        <v>847</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>848</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>836</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>849</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>850</v>
+      </c>
+      <c r="F5" s="43" t="s">
         <v>851</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>852</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>840</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>853</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>854</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>855</v>
       </c>
       <c r="G5" s="43" t="s">
         <v>218</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -5465,104 +5570,104 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="43" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B1" s="43" t="s">
+        <v>853</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>854</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>855</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>856</v>
+      </c>
+      <c r="F1" s="43" t="s">
         <v>857</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>858</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>859</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="I1" s="43" t="s">
         <v>860</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="J1" s="43" t="s">
         <v>861</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="K1" s="43" t="s">
         <v>862</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>863</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>864</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>865</v>
-      </c>
-      <c r="K1" s="43" t="s">
-        <v>866</v>
-      </c>
-      <c r="L1" s="43" t="s">
-        <v>867</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>868</v>
-      </c>
-      <c r="N1" s="43" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="43" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B2" s="43" t="s">
+        <v>866</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>867</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>868</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>869</v>
+      </c>
+      <c r="F2" s="43" t="s">
         <v>870</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="G2" s="43" t="s">
         <v>871</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="H2" s="43" t="s">
         <v>872</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="I2" s="43" t="s">
         <v>873</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="J2" s="43" t="s">
         <v>874</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="K2" s="43" t="s">
         <v>875</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="L2" s="43" t="s">
         <v>876</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="M2" s="43" t="s">
         <v>877</v>
       </c>
-      <c r="J2" s="43" t="s">
+      <c r="N2" s="43" t="s">
         <v>878</v>
-      </c>
-      <c r="K2" s="43" t="s">
-        <v>879</v>
-      </c>
-      <c r="L2" s="43" t="s">
-        <v>880</v>
-      </c>
-      <c r="M2" s="43" t="s">
-        <v>881</v>
-      </c>
-      <c r="N2" s="43" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="43" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B3" s="43">
         <v>1</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>218</v>
@@ -5577,10 +5682,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="43" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="J3" s="43" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="K3" s="43">
         <v>1</v>
@@ -5594,16 +5699,16 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="43" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B4" s="43">
         <v>2</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="E4" s="43" t="s">
         <v>218</v>
@@ -5618,10 +5723,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="K4" s="43">
         <v>1</v>
@@ -5630,21 +5735,21 @@
         <v>0.7</v>
       </c>
       <c r="M4" s="43" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="43" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B5" s="43">
         <v>3</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="E5" s="43" t="s">
         <v>218</v>
@@ -5676,34 +5781,34 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="43" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B6" s="43">
         <v>1</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="E6" s="43" t="s">
         <v>218</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="H6" s="43">
         <v>100</v>
       </c>
       <c r="I6" s="43" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="K6" s="43">
         <v>1</v>
@@ -5717,16 +5822,16 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="43" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B7" s="43">
         <v>2</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="E7" s="43" t="s">
         <v>218</v>
@@ -5758,16 +5863,16 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="43" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B8" s="43">
         <v>1</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="E8" s="43" t="s">
         <v>218</v>
@@ -5782,10 +5887,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="J8" s="43" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="K8" s="43">
         <v>30</v>
@@ -5822,77 +5927,77 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>680</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>895</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>896</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>897</v>
+      </c>
+      <c r="G1" s="43" t="s">
         <v>898</v>
       </c>
-      <c r="B1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>684</v>
-      </c>
-      <c r="D1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>899</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>900</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>901</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>902</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D2" s="43" t="s">
+        <v>901</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>902</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>904</v>
+      </c>
+      <c r="H2" s="43" t="s">
         <v>905</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>906</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>907</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>908</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
+        <v>906</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>907</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>908</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>909</v>
+      </c>
+      <c r="E3" s="43" t="s">
         <v>910</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>911</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>912</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>913</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>914</v>
       </c>
       <c r="F3" s="43">
         <v>5</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="H3" s="43">
         <v>100</v>
@@ -5900,25 +6005,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E4" s="43" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="F4" s="43">
         <v>10</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="H4" s="43">
         <v>200</v>
@@ -5926,25 +6031,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
+        <v>916</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>917</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>918</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>909</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>919</v>
+      </c>
+      <c r="F5" s="43">
+        <v>1</v>
+      </c>
+      <c r="G5" s="43" t="s">
         <v>920</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>921</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>922</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>913</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>923</v>
-      </c>
-      <c r="F5" s="43">
-        <v>1</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>924</v>
       </c>
       <c r="H5" s="43">
         <v>50</v>
@@ -5952,25 +6057,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="43" t="s">
+        <v>921</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>922</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>923</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>924</v>
+      </c>
+      <c r="E6" s="43" t="s">
         <v>925</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>926</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>927</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>928</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>929</v>
       </c>
       <c r="F6" s="43">
         <v>3</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="H6" s="43">
         <v>150</v>
@@ -5978,25 +6083,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="43" t="s">
+        <v>926</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>927</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>928</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>929</v>
+      </c>
+      <c r="E7" s="43" t="s">
         <v>930</v>
       </c>
-      <c r="B7" s="43" t="s">
-        <v>931</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>933</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>934</v>
-      </c>
       <c r="F7" s="43">
         <v>1</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="H7" s="43">
         <v>30</v>
@@ -6021,30 +6126,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="77" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B1" s="77" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="24" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6052,13 +6157,13 @@
         <v>141</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C3" s="9">
         <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6066,13 +6171,13 @@
         <v>146</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C4" s="9">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -6080,13 +6185,13 @@
         <v>151</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C5" s="9">
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6094,13 +6199,13 @@
         <v>156</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C6" s="9">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6108,69 +6213,69 @@
         <v>160</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="C7" s="9">
         <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="9" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="C8" s="9">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="9" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C9" s="9">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="9" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C10" s="9">
         <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="9" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="C11" s="9">
         <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6178,41 +6283,41 @@
         <v>169</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C12" s="9">
         <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="9" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C13" s="9">
         <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="C14" s="9">
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
     </row>
   </sheetData>
@@ -7061,10 +7166,10 @@
         <v>210</v>
       </c>
       <c r="R2" s="24" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="S2" s="24" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="18" customHeight="1">
@@ -7592,10 +7697,10 @@
         <v>264</v>
       </c>
       <c r="R11" s="79" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="S11" s="28" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="18" customHeight="1">
@@ -7654,7 +7759,7 @@
         <v>273</v>
       </c>
       <c r="S12" s="28" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="T12" s="43"/>
       <c r="U12" s="43"/>
@@ -7728,7 +7833,7 @@
         <v>277</v>
       </c>
       <c r="S13" s="28" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="T13" s="43"/>
       <c r="U13" s="43"/>
@@ -7799,10 +7904,10 @@
         <v>282</v>
       </c>
       <c r="R14" s="79" t="s">
+        <v>972</v>
+      </c>
+      <c r="S14" s="28" t="s">
         <v>976</v>
-      </c>
-      <c r="S14" s="28" t="s">
-        <v>980</v>
       </c>
       <c r="T14" s="43"/>
       <c r="U14" s="43"/>
@@ -7876,7 +7981,7 @@
         <v>288</v>
       </c>
       <c r="S15" s="28" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="T15" s="43"/>
       <c r="U15" s="43"/>
@@ -7950,7 +8055,7 @@
         <v>291</v>
       </c>
       <c r="S16" s="28" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="T16" s="43"/>
       <c r="U16" s="43"/>
@@ -13263,13 +13368,13 @@
         <v>210</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="K2" s="23" t="s">
         <v>455</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="N2" s="43"/>
     </row>
@@ -13418,8 +13523,8 @@
       <c r="J6" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="K6" s="42" t="s">
-        <v>461</v>
+      <c r="K6" s="30" t="s">
+        <v>980</v>
       </c>
       <c r="L6" s="2">
         <v>2</v>
@@ -13456,8 +13561,8 @@
       <c r="J7" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="K7" s="42" t="s">
-        <v>462</v>
+      <c r="K7" s="30" t="s">
+        <v>980</v>
       </c>
       <c r="L7" s="2">
         <v>1</v>
@@ -13494,8 +13599,8 @@
       <c r="J8" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="K8" s="42" t="s">
-        <v>463</v>
+      <c r="K8" s="30" t="s">
+        <v>980</v>
       </c>
       <c r="L8" s="2">
         <v>2</v>
@@ -13527,13 +13632,13 @@
         <v>6</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>267</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="L9" s="2">
         <v>2</v>
@@ -13565,13 +13670,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="K10" s="42" t="s">
-        <v>467</v>
+      <c r="K10" s="30" t="s">
+        <v>980</v>
       </c>
       <c r="L10" s="2">
         <v>2</v>
@@ -13609,7 +13714,7 @@
         <v>267</v>
       </c>
       <c r="K11" s="30" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="L11" s="2">
         <v>1</v>
@@ -13620,13 +13725,13 @@
         <v>153</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>266</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>219</v>
@@ -13644,10 +13749,10 @@
         <v>221</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="K12" s="42" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
@@ -13658,13 +13763,13 @@
         <v>172</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>216</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>219</v>
@@ -13682,10 +13787,10 @@
         <v>382</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="K13" s="42" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
@@ -13696,13 +13801,13 @@
         <v>157</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>260</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>219</v>
@@ -13720,10 +13825,10 @@
         <v>221</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="K14" s="42" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -13734,7 +13839,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>260</v>
@@ -13758,10 +13863,10 @@
         <v>221</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="K15" s="42" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="L15" s="2">
         <v>0</v>
@@ -13947,16 +14052,16 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="24" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>451</v>
@@ -13974,7 +14079,7 @@
         <v>189</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="K1" s="24" t="s">
         <v>191</v>
@@ -13988,16 +14093,16 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="24" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>201</v>
@@ -14012,10 +14117,10 @@
         <v>204</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>209</v>
@@ -14032,7 +14137,7 @@
         <v>61</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -14041,7 +14146,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>219</v>
@@ -14065,7 +14170,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="32" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14073,7 +14178,7 @@
         <v>62</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>49</v>
@@ -14082,7 +14187,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>219</v>
@@ -14106,7 +14211,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="32" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14114,7 +14219,7 @@
         <v>63</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>49</v>
@@ -14123,7 +14228,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>219</v>
@@ -14147,7 +14252,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="32" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -14155,7 +14260,7 @@
         <v>64</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>49</v>
@@ -14164,7 +14269,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>219</v>
@@ -14188,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="32" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14196,7 +14301,7 @@
         <v>65</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>49</v>
@@ -14205,7 +14310,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>219</v>
@@ -14229,7 +14334,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="32" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -14237,7 +14342,7 @@
         <v>79</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>67</v>
@@ -14246,7 +14351,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>219</v>
@@ -14270,7 +14375,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="32" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14278,7 +14383,7 @@
         <v>80</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>67</v>
@@ -14287,7 +14392,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>219</v>
@@ -14311,7 +14416,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="32" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14319,7 +14424,7 @@
         <v>81</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>67</v>
@@ -14328,7 +14433,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>219</v>
@@ -14352,7 +14457,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="32" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14360,7 +14465,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>67</v>
@@ -14369,7 +14474,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>219</v>
@@ -14393,7 +14498,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="32" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -14401,7 +14506,7 @@
         <v>83</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>67</v>
@@ -14410,7 +14515,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>218</v>
@@ -14434,7 +14539,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -14442,7 +14547,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>85</v>
@@ -14451,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>218</v>
@@ -14475,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="32" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -14483,7 +14588,7 @@
         <v>98</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>85</v>
@@ -14492,7 +14597,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>218</v>
@@ -14516,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="32" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -14524,7 +14629,7 @@
         <v>99</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>85</v>
@@ -14533,7 +14638,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>218</v>
@@ -14557,7 +14662,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="32" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -14565,7 +14670,7 @@
         <v>100</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>85</v>
@@ -14574,7 +14679,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>219</v>
@@ -14598,7 +14703,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="34" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -14606,7 +14711,7 @@
         <v>101</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>85</v>
@@ -14615,7 +14720,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>218</v>
@@ -14639,24 +14744,24 @@
         <v>0</v>
       </c>
       <c r="M17" s="32" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="9" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>218</v>
@@ -14680,24 +14785,24 @@
         <v>0</v>
       </c>
       <c r="M18" s="32" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="9" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>218</v>
@@ -14721,24 +14826,24 @@
         <v>0</v>
       </c>
       <c r="M19" s="32" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="9" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>218</v>
@@ -14762,24 +14867,24 @@
         <v>0</v>
       </c>
       <c r="M20" s="32" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="9" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>219</v>
@@ -14803,24 +14908,24 @@
         <v>0</v>
       </c>
       <c r="M21" s="32" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="9" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D22" s="9">
         <v>0</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>218</v>
@@ -14844,24 +14949,24 @@
         <v>0</v>
       </c>
       <c r="M22" s="32" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="9" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D23" s="9">
         <v>0</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>218</v>
@@ -14885,24 +14990,24 @@
         <v>0</v>
       </c>
       <c r="M23" s="32" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="9" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D24" s="9">
         <v>0</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>218</v>
@@ -14926,24 +15031,24 @@
         <v>0</v>
       </c>
       <c r="M24" s="32" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="9" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D25" s="9">
         <v>0</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>218</v>
@@ -14967,24 +15072,24 @@
         <v>0</v>
       </c>
       <c r="M25" s="32" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="9" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D26" s="9">
         <v>0</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>219</v>
@@ -15008,24 +15113,24 @@
         <v>0</v>
       </c>
       <c r="M26" s="32" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="9" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D27" s="9">
         <v>0</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>219</v>
@@ -15049,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="32" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
@@ -15093,10 +15198,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>193</v>
@@ -15109,16 +15214,16 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="24" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>211</v>
@@ -15131,7 +15236,7 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="36" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B3" s="36" t="s">
         <v>2</v>
@@ -15143,7 +15248,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="M3" s="43"/>
       <c r="N3" s="43"/>
@@ -15153,7 +15258,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="40" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>3</v>
@@ -15165,7 +15270,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="M4" s="43"/>
       <c r="N4" s="43"/>
@@ -15175,10 +15280,10 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="36" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C5" s="37">
         <v>1</v>
@@ -15187,7 +15292,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="M5" s="43"/>
       <c r="N5" s="43"/>
@@ -15200,7 +15305,7 @@
         <v>290</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C6" s="37">
         <v>1</v>
@@ -15209,7 +15314,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="M6" s="43"/>
       <c r="N6" s="43"/>
@@ -15222,7 +15327,7 @@
         <v>275</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C7" s="37">
         <v>1</v>
@@ -15231,7 +15336,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="M7" s="43"/>
       <c r="N7" s="43"/>
@@ -15244,16 +15349,16 @@
         <v>330</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C8" s="37">
         <v>1</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="M8" s="43"/>
       <c r="N8" s="43"/>
@@ -15266,16 +15371,16 @@
         <v>372</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C9" s="37">
         <v>1</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="M9" s="43"/>
       <c r="N9" s="43"/>
@@ -15288,16 +15393,16 @@
         <v>321</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C10" s="37">
         <v>1</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="M10" s="43"/>
       <c r="N10" s="43"/>
@@ -15310,16 +15415,16 @@
         <v>235</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C11" s="37">
         <v>1</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="M11" s="43"/>
       <c r="N11" s="43"/>
@@ -15332,16 +15437,16 @@
         <v>230</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C12" s="37">
         <v>1</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="M12" s="43"/>
       <c r="N12" s="43"/>
@@ -15354,16 +15459,16 @@
         <v>240</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C13" s="38">
         <v>0</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="M13" s="43"/>
       <c r="N13" s="43"/>
@@ -15376,16 +15481,16 @@
         <v>381</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C14" s="38">
         <v>0</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E14" s="42" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
@@ -15398,16 +15503,16 @@
         <v>249</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C15" s="38">
         <v>0</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E15" s="42" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
@@ -15420,16 +15525,16 @@
         <v>254</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C16" s="38">
         <v>0</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E16" s="42" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="M16" s="43"/>
       <c r="N16" s="43"/>
@@ -15442,16 +15547,16 @@
         <v>245</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C17" s="38">
         <v>0</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="M17" s="43"/>
       <c r="N17" s="43"/>
@@ -15464,16 +15569,16 @@
         <v>285</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C18" s="37">
         <v>1</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="M18" s="43"/>
       <c r="N18" s="43"/>
@@ -15486,16 +15591,16 @@
         <v>364</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C19" s="37">
         <v>1</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="M19" s="43"/>
       <c r="N19" s="43"/>
@@ -15505,19 +15610,19 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="36" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C20" s="37">
         <v>1</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="E20" s="42" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="M20" s="43"/>
       <c r="N20" s="43"/>
@@ -15527,19 +15632,19 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="36" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C21" s="37">
         <v>1</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="M21" s="43"/>
       <c r="N21" s="43"/>
@@ -15549,19 +15654,19 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="36" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C22" s="38">
         <v>0</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="M22" s="43"/>
       <c r="N22" s="43"/>
@@ -15574,16 +15679,16 @@
         <v>397</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C23" s="38">
         <v>0</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="M23" s="43"/>
       <c r="N23" s="43"/>
@@ -15593,19 +15698,19 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="36" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C24" s="38">
         <v>0</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="M24" s="43"/>
       <c r="N24" s="43"/>
@@ -15615,10 +15720,10 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="36" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C25" s="37">
         <v>1</v>
@@ -15627,7 +15732,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="M25" s="43"/>
       <c r="N25" s="43"/>
@@ -15637,10 +15742,10 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="36" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C26" s="37">
         <v>1</v>
@@ -15649,7 +15754,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="M26" s="43"/>
       <c r="N26" s="43"/>
@@ -17107,7 +17212,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="4" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -17116,25 +17221,25 @@
         <v>182</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>612</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>616</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -17145,34 +17250,34 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>621</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>625</v>
       </c>
       <c r="K2" s="43"/>
       <c r="L2" s="43"/>
@@ -17183,25 +17288,25 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="E3" s="9">
         <v>0</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H3" s="9">
         <v>1</v>
@@ -17221,25 +17326,25 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="9" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E4" s="9">
         <v>0</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H4" s="9">
         <v>1</v>
@@ -17259,25 +17364,25 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="9" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E5" s="9">
         <v>0</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H5" s="9">
         <v>1</v>
@@ -17297,25 +17402,25 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="9" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E6" s="9">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H6" s="9">
         <v>1</v>
@@ -17335,25 +17440,25 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="9" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>168</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E7" s="9">
         <v>0</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H7" s="9">
         <v>1</v>
@@ -17373,25 +17478,25 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="9" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>168</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E8" s="9">
         <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H8" s="9">
         <v>1</v>
@@ -17411,31 +17516,31 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="9" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>176</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E9" s="9">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H9" s="9">
         <v>1</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="J9" s="39" t="s">
         <v>380</v>
@@ -17449,31 +17554,31 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>648</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="H10" s="9">
-        <v>1</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>652</v>
       </c>
       <c r="J10" s="39" t="s">
         <v>380</v>
@@ -17487,25 +17592,25 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="9" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D11" s="9">
         <v>0</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H11" s="9">
         <v>1</v>
@@ -17523,25 +17628,25 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="9" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H12" s="9">
         <v>1</v>
@@ -17559,25 +17664,25 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="9" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H13" s="9">
         <v>1</v>
@@ -17595,25 +17700,25 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="9" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H14" s="9">
         <v>1</v>
@@ -17631,25 +17736,25 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="9" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="D15" s="9">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>667</v>
-      </c>
       <c r="F15" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H15" s="9">
         <v>1</v>
@@ -17667,25 +17772,25 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="9" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H16" s="9">
         <v>1</v>
@@ -17703,25 +17808,25 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="9" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D17" s="9">
         <v>0</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H17" s="9">
         <v>1</v>
@@ -17739,25 +17844,25 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="9" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H18" s="9">
         <v>1</v>
@@ -17775,25 +17880,25 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="9" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H19" s="9">
         <v>1</v>
@@ -18106,25 +18211,25 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1">
       <c r="A1" s="24" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>103</v>
       </c>
       <c r="C1" s="24" t="s">
+        <v>676</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>677</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>678</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>679</v>
+      </c>
+      <c r="G1" s="24" t="s">
         <v>680</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>681</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>682</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>683</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>684</v>
       </c>
       <c r="H1" s="43"/>
       <c r="I1" s="43"/>
@@ -18132,25 +18237,25 @@
     </row>
     <row r="2" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A2" s="45" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B2" s="45" t="s">
         <v>121</v>
       </c>
       <c r="C2" s="45" t="s">
+        <v>681</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>682</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>683</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>684</v>
+      </c>
+      <c r="G2" s="45" t="s">
         <v>685</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>686</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>687</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>688</v>
-      </c>
-      <c r="G2" s="45" t="s">
-        <v>689</v>
       </c>
       <c r="H2" s="43"/>
       <c r="I2" s="43"/>
@@ -18158,7 +18263,7 @@
     </row>
     <row r="3" spans="1:10" ht="16.5" customHeight="1">
       <c r="A3" s="46" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B3" s="62" t="s">
         <v>138</v>
@@ -18176,7 +18281,7 @@
         <v>-1</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="H3" s="43"/>
       <c r="I3" s="43"/>
@@ -18184,7 +18289,7 @@
     </row>
     <row r="4" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A4" s="55" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B4" s="68" t="s">
         <v>138</v>
@@ -18208,7 +18313,7 @@
     </row>
     <row r="5" spans="1:10" ht="16.5" customHeight="1">
       <c r="A5" s="46" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B5" s="50" t="s">
         <v>158</v>
@@ -18226,7 +18331,7 @@
         <v>-1</v>
       </c>
       <c r="G5" s="47" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="H5" s="43"/>
       <c r="I5" s="43"/>
@@ -18234,7 +18339,7 @@
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A6" s="55" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B6" s="68" t="s">
         <v>158</v>
@@ -18258,7 +18363,7 @@
     </row>
     <row r="7" spans="1:10" ht="16.5" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B7" s="50" t="s">
         <v>138</v>
@@ -18276,7 +18381,7 @@
         <v>-1</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="H7" s="43"/>
       <c r="I7" s="43"/>
@@ -18284,7 +18389,7 @@
     </row>
     <row r="8" spans="1:10" ht="16.5" customHeight="1">
       <c r="A8" s="52" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B8" s="39" t="s">
         <v>138</v>
@@ -18308,7 +18413,7 @@
     </row>
     <row r="9" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A9" s="55" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B9" s="54" t="s">
         <v>149</v>
@@ -18332,7 +18437,7 @@
     </row>
     <row r="10" spans="1:10" ht="16.5" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B10" s="50" t="s">
         <v>158</v>
@@ -18350,7 +18455,7 @@
         <v>-1</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="H10" s="43"/>
       <c r="I10" s="43"/>
@@ -18358,7 +18463,7 @@
     </row>
     <row r="11" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A11" s="55" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B11" s="68" t="s">
         <v>154</v>
@@ -18382,7 +18487,7 @@
     </row>
     <row r="12" spans="1:10" ht="16.5" customHeight="1">
       <c r="A12" s="49" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B12" s="50" t="s">
         <v>138</v>
@@ -18400,7 +18505,7 @@
         <v>-1</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="H12" s="43"/>
       <c r="I12" s="43"/>
@@ -18408,7 +18513,7 @@
     </row>
     <row r="13" spans="1:10" ht="16.5" customHeight="1">
       <c r="A13" s="56" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B13" s="39" t="s">
         <v>158</v>
@@ -18432,7 +18537,7 @@
     </row>
     <row r="14" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A14" s="55" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B14" s="54" t="s">
         <v>149</v>
@@ -18456,7 +18561,7 @@
     </row>
     <row r="15" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A15" s="57" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B15" s="58" t="s">
         <v>166</v>
@@ -18474,7 +18579,7 @@
         <v>-1</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H15" s="43"/>
       <c r="I15" s="43"/>
@@ -18564,94 +18669,94 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>721</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="17.25" customHeight="1" thickBot="1">
@@ -18662,94 +18767,94 @@
         <v>26</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>729</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>732</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>734</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>740</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>742</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>743</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="AC2" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AE2" s="5" t="s">
         <v>750</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AF2" s="5" t="s">
         <v>751</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>753</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="20.149999999999999" customHeight="1">
@@ -18757,22 +18862,22 @@
         <v>264</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C3" s="80" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D3" s="61" t="s">
         <v>280</v>
       </c>
       <c r="E3" s="61" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="F3" s="61" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="G3" s="61" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="H3" s="62">
         <v>0</v>
@@ -18855,34 +18960,34 @@
         <v>339</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>757</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>758</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>761</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>271</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="L4" s="9">
         <v>0</v>
@@ -18953,46 +19058,46 @@
         <v>390</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>271</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>280</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="P5" s="9">
         <v>0</v>
@@ -19051,34 +19156,34 @@
         <v>458</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E6" s="67" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F6" s="67" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="H6" s="67" t="s">
         <v>280</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="J6" s="67" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="K6" s="67" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="L6" s="68">
         <v>0</v>
@@ -19149,10 +19254,10 @@
         <v>424</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D7" s="61" t="s">
         <v>280</v>
@@ -19247,16 +19352,16 @@
         <v>357</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
@@ -19345,19 +19450,19 @@
         <v>309</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -19443,22 +19548,22 @@
         <v>287</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -19541,28 +19646,28 @@
         <v>276</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>270</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -19639,25 +19744,25 @@
         <v>272</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>271</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="I12" s="9">
         <v>0</v>
@@ -19737,28 +19842,28 @@
         <v>301</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>271</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -19835,10 +19940,10 @@
         <v>369</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>271</v>
@@ -19847,22 +19952,22 @@
         <v>281</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>280</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="L14" s="9">
         <v>0</v>
@@ -19933,22 +20038,22 @@
         <v>294</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>271</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -20031,10 +20136,10 @@
         <v>322</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>271</v>
@@ -20046,16 +20151,16 @@
         <v>280</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="K16" s="9">
         <v>0</v>
@@ -20129,16 +20234,16 @@
         <v>282</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>271</v>
@@ -20147,10 +20252,10 @@
         <v>281</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -20227,10 +20332,10 @@
         <v>327</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>271</v>
@@ -20239,25 +20344,25 @@
         <v>281</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>280</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="M18" s="9">
         <v>0</v>
@@ -20325,25 +20430,25 @@
         <v>331</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D19" s="67" t="s">
         <v>280</v>
       </c>
       <c r="E19" s="67" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F19" s="67" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="G19" s="67" t="s">
         <v>281</v>
       </c>
       <c r="H19" s="67" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="I19" s="68">
         <v>0</v>
@@ -20423,13 +20528,13 @@
         <v>382</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E20" s="62">
         <v>0</v>
@@ -20521,25 +20626,25 @@
         <v>460</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>280</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="I21" s="9">
         <v>0</v>
@@ -20616,37 +20721,37 @@
     </row>
     <row r="22" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A22" s="64" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>280</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="L22" s="9">
         <v>0</v>
@@ -20717,10 +20822,10 @@
         <v>221</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D23" s="68">
         <v>0</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08C869C-91E9-4FC8-A30F-C7F83F27E1F9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F37B62A-610A-479C-9230-7311DAE00B43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17150" tabRatio="550" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17150" tabRatio="550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -4611,7 +4611,7 @@
         <v>52</v>
       </c>
       <c r="I3" s="9">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="J3" s="9">
         <v>1</v>
@@ -4993,7 +4993,7 @@
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F37B62A-610A-479C-9230-7311DAE00B43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEFBA90-443A-4E74-B9F6-77210651FF02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17150" tabRatio="550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17145" tabRatio="550" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -1631,18 +1631,12 @@
     <t>원천</t>
   </si>
   <si>
-    <t>Cost +1</t>
-  </si>
-  <si>
     <t>Rune_21</t>
   </si>
   <si>
     <t>범람</t>
   </si>
   <si>
-    <t>Cost +2</t>
-  </si>
-  <si>
     <t>Rune_22</t>
   </si>
   <si>
@@ -1667,18 +1661,12 @@
     <t>첫걸음</t>
   </si>
   <si>
-    <t>첫 이동스킬 Cost -1</t>
-  </si>
-  <si>
     <t>Rune_25</t>
   </si>
   <si>
     <t>균형</t>
   </si>
   <si>
-    <t>최대 HP +3, 이동수치 +3, Cost +1</t>
-  </si>
-  <si>
     <t>중첩</t>
   </si>
   <si>
@@ -2423,18 +2411,12 @@
     <t>선봉의 날개</t>
   </si>
   <si>
-    <t>첫 번째 턴 시작시 Cost +2</t>
-  </si>
-  <si>
     <t>Relic_02</t>
   </si>
   <si>
     <t>흑요석 반지</t>
   </si>
   <si>
-    <t>마지막 슬롯에 중복사용으로 증가하는 Cost 증가량 제거</t>
-  </si>
-  <si>
     <t>Relic_03</t>
   </si>
   <si>
@@ -2459,9 +2441,6 @@
     <t>도약의 뿔조각</t>
   </si>
   <si>
-    <t>첫 슬롯에 사용하는 행동의 Cost 사용량 -1</t>
-  </si>
-  <si>
     <t>Relic_06</t>
   </si>
   <si>
@@ -2484,9 +2463,6 @@
   </si>
   <si>
     <t>에테르 조각</t>
-  </si>
-  <si>
-    <t>장착 시 해당 캐릭터의 Cost +1</t>
   </si>
   <si>
     <t>Relic_09</t>
@@ -3338,12 +3314,137 @@
     </r>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
+  <si>
+    <t>첫 번째 턴 시작시 코스트 +2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막 슬롯에 중복사용으로 증가하는 코스트 증가량 제거</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 슬롯에 사용하는 행동의 코스트 사용량 -1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>장착 시 해당 캐릭터의 코스트 +1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>코스트 +1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>코스트 +2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> HP +3, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이동수치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> +3, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> +1</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이동 스킬 사용 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> -1</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3425,6 +3526,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3703,7 +3811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3935,6 +4043,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4410,23 +4519,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12.08203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="43" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="11.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="13" style="43" customWidth="1"/>
-    <col min="5" max="5" width="17.58203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.08203125" style="43" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" style="43" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="17.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="22.375" style="43" customWidth="1"/>
+    <col min="9" max="9" width="11.375" style="43" customWidth="1"/>
     <col min="10" max="10" width="17" style="43" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" style="43" customWidth="1"/>
-    <col min="12" max="13" width="12.08203125" style="43" customWidth="1"/>
-    <col min="14" max="15" width="12.33203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="16.375" style="43" customWidth="1"/>
+    <col min="12" max="13" width="12.125" style="43" customWidth="1"/>
+    <col min="14" max="15" width="12.375" style="43" customWidth="1"/>
     <col min="16" max="17" width="14.5" style="43" customWidth="1"/>
-    <col min="18" max="19" width="14.08203125" style="43" customWidth="1"/>
+    <col min="18" max="19" width="14.125" style="43" customWidth="1"/>
     <col min="20" max="24" width="8.5" style="43" customWidth="1"/>
     <col min="25" max="25" width="58.25" style="3" customWidth="1"/>
   </cols>
@@ -4522,7 +4631,7 @@
         <v>28</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>29</v>
@@ -4593,7 +4702,7 @@
         <v>50</v>
       </c>
       <c r="C3" s="6">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D3" s="6">
         <v>8</v>
@@ -5001,19 +5110,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="22.875" style="43" customWidth="1"/>
     <col min="3" max="4" width="19.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="20.08203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="18.58203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="20.125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="18.625" style="43" customWidth="1"/>
     <col min="7" max="7" width="57.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="24" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>1</v>
@@ -5036,7 +5145,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="75" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B2" s="75" t="s">
         <v>26</v>
@@ -5060,10 +5169,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B3" s="73" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>484</v>
@@ -5078,16 +5187,16 @@
         <v>1</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>793</v>
+        <v>973</v>
       </c>
       <c r="H3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="B4" s="73" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>484</v>
@@ -5101,17 +5210,17 @@
       <c r="F4" s="73">
         <v>1</v>
       </c>
-      <c r="G4" s="73" t="s">
-        <v>796</v>
+      <c r="G4" s="74" t="s">
+        <v>974</v>
       </c>
       <c r="H4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="B5" s="73" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>484</v>
@@ -5126,16 +5235,16 @@
         <v>1</v>
       </c>
       <c r="G5" s="73" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="B6" s="73" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>484</v>
@@ -5150,16 +5259,16 @@
         <v>1</v>
       </c>
       <c r="G6" s="73" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="H6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="B7" s="73" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>484</v>
@@ -5173,17 +5282,17 @@
       <c r="F7" s="73">
         <v>1</v>
       </c>
-      <c r="G7" s="73" t="s">
-        <v>805</v>
+      <c r="G7" s="74" t="s">
+        <v>975</v>
       </c>
       <c r="H7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="B8" s="73" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>484</v>
@@ -5198,16 +5307,16 @@
         <v>1</v>
       </c>
       <c r="G8" s="74" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="H8" s="43"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B9" s="73" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>484</v>
@@ -5222,16 +5331,16 @@
         <v>1</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="B10" s="73" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>484</v>
@@ -5246,16 +5355,16 @@
         <v>1</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>814</v>
+        <v>976</v>
       </c>
       <c r="H10" s="43"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="B11" s="73" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>484</v>
@@ -5270,16 +5379,16 @@
         <v>1</v>
       </c>
       <c r="G11" s="73" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="H11" s="43"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="B12" s="73" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>484</v>
@@ -5294,7 +5403,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="73" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="H12" s="43"/>
     </row>
@@ -5397,146 +5506,146 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
     <col min="2" max="2" width="14" style="43" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="43" customWidth="1"/>
     <col min="4" max="4" width="10.75" style="43" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" customWidth="1"/>
     <col min="6" max="6" width="37" style="43" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="43" customWidth="1"/>
     <col min="8" max="8" width="20.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>218</v>
       </c>
       <c r="H3" s="43" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="C4" s="43" t="s">
+        <v>828</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>829</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>835</v>
+      </c>
+      <c r="F4" s="43" t="s">
         <v>836</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="G4" s="43" t="s">
         <v>837</v>
       </c>
-      <c r="E4" s="43" t="s">
-        <v>843</v>
-      </c>
-      <c r="F4" s="43" t="s">
-        <v>844</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>845</v>
-      </c>
       <c r="H4" s="43" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="E5" s="43" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="F5" s="43" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="G5" s="43" t="s">
         <v>218</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -5550,124 +5659,124 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="20.375" style="43" customWidth="1"/>
     <col min="4" max="4" width="12" style="43" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
     <col min="6" max="6" width="9.75" style="43" customWidth="1"/>
     <col min="7" max="7" width="11" style="43" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="10.375" style="43" customWidth="1"/>
     <col min="9" max="9" width="11" style="43" customWidth="1"/>
     <col min="10" max="10" width="20.25" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
-    <col min="12" max="12" width="12.08203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
+    <col min="12" max="12" width="12.125" style="43" customWidth="1"/>
     <col min="13" max="13" width="12.75" style="43" customWidth="1"/>
-    <col min="14" max="14" width="14.58203125" style="43" customWidth="1"/>
+    <col min="14" max="14" width="14.625" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="43" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="B1" s="43" t="s">
+        <v>845</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>846</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>847</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>848</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>849</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>850</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>851</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>852</v>
+      </c>
+      <c r="J1" s="43" t="s">
         <v>853</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="K1" s="43" t="s">
         <v>854</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>855</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>856</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>857</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>858</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>859</v>
-      </c>
-      <c r="I1" s="43" t="s">
-        <v>860</v>
-      </c>
-      <c r="J1" s="43" t="s">
-        <v>861</v>
-      </c>
-      <c r="K1" s="43" t="s">
-        <v>862</v>
-      </c>
-      <c r="L1" s="43" t="s">
-        <v>863</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>864</v>
-      </c>
-      <c r="N1" s="43" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="43" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B2" s="43" t="s">
+        <v>858</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>859</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>861</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>862</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>863</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>864</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>865</v>
+      </c>
+      <c r="J2" s="43" t="s">
         <v>866</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="K2" s="43" t="s">
         <v>867</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="L2" s="43" t="s">
         <v>868</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="M2" s="43" t="s">
         <v>869</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="N2" s="43" t="s">
         <v>870</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>871</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>872</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>873</v>
-      </c>
-      <c r="J2" s="43" t="s">
-        <v>874</v>
-      </c>
-      <c r="K2" s="43" t="s">
-        <v>875</v>
-      </c>
-      <c r="L2" s="43" t="s">
-        <v>876</v>
-      </c>
-      <c r="M2" s="43" t="s">
-        <v>877</v>
-      </c>
-      <c r="N2" s="43" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="43" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="B3" s="43">
         <v>1</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>218</v>
@@ -5682,10 +5791,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="43" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="J3" s="43" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="K3" s="43">
         <v>1</v>
@@ -5699,16 +5808,16 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="43" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="B4" s="43">
         <v>2</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="E4" s="43" t="s">
         <v>218</v>
@@ -5723,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="K4" s="43">
         <v>1</v>
@@ -5735,21 +5844,21 @@
         <v>0.7</v>
       </c>
       <c r="M4" s="43" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="43" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="B5" s="43">
         <v>3</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="E5" s="43" t="s">
         <v>218</v>
@@ -5781,34 +5890,34 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="43" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="B6" s="43">
         <v>1</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="E6" s="43" t="s">
         <v>218</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="H6" s="43">
         <v>100</v>
       </c>
       <c r="I6" s="43" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="K6" s="43">
         <v>1</v>
@@ -5822,16 +5931,16 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="43" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="B7" s="43">
         <v>2</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="E7" s="43" t="s">
         <v>218</v>
@@ -5863,16 +5972,16 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="43" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="B8" s="43">
         <v>1</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="E8" s="43" t="s">
         <v>218</v>
@@ -5887,10 +5996,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="J8" s="43" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="K8" s="43">
         <v>30</v>
@@ -5913,91 +6022,91 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
     <col min="2" max="2" width="15.75" style="43" customWidth="1"/>
-    <col min="3" max="3" width="24.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="24.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="14" style="43" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="43" customWidth="1"/>
     <col min="7" max="7" width="12.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="B1" s="43" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="F3" s="43">
         <v>5</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="H3" s="43">
         <v>100</v>
@@ -6005,25 +6114,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="E4" s="43" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="F4" s="43">
         <v>10</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="H4" s="43">
         <v>200</v>
@@ -6031,25 +6140,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="E5" s="43" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="F5" s="43">
         <v>1</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="H5" s="43">
         <v>50</v>
@@ -6057,25 +6166,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="43" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="F6" s="43">
         <v>3</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="H6" s="43">
         <v>150</v>
@@ -6083,25 +6192,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="43" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="F7" s="43">
         <v>1</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="H7" s="43">
         <v>30</v>
@@ -6118,38 +6227,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="3" width="15.58203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="80.33203125" style="43" customWidth="1"/>
+    <col min="1" max="3" width="15.625" style="43" customWidth="1"/>
+    <col min="4" max="4" width="80.375" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="77" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="B1" s="77" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="24" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6157,13 +6266,13 @@
         <v>141</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="C3" s="9">
         <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6171,13 +6280,13 @@
         <v>146</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="C4" s="9">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -6185,13 +6294,13 @@
         <v>151</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="C5" s="9">
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6199,13 +6308,13 @@
         <v>156</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="C6" s="9">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6213,69 +6322,69 @@
         <v>160</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="C7" s="9">
         <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="9" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="C8" s="9">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="9" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="C9" s="9">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="9" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="C10" s="9">
         <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="9" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="C11" s="9">
         <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6283,41 +6392,41 @@
         <v>169</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="C12" s="9">
         <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="9" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="C13" s="9">
         <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="C14" s="9">
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
     </row>
   </sheetData>
@@ -6331,19 +6440,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="43" customWidth="1"/>
     <col min="2" max="2" width="17.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="43" customWidth="1"/>
-    <col min="5" max="5" width="19.08203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.58203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="18.08203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="19.125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="43" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="43" customWidth="1"/>
     <col min="8" max="8" width="19.75" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.58203125" style="43" customWidth="1"/>
-    <col min="10" max="16" width="15.58203125" style="43" customWidth="1"/>
-    <col min="17" max="19" width="15.58203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.625" style="43" customWidth="1"/>
+    <col min="10" max="16" width="15.625" style="43" customWidth="1"/>
+    <col min="17" max="19" width="15.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -7031,27 +7140,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AH288"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.875" style="43" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="43" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="43" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="43" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.375" style="43" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.75" style="43" customWidth="1"/>
-    <col min="7" max="7" width="9.08203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="43" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" style="43" customWidth="1"/>
-    <col min="10" max="10" width="10.08203125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="10.58203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="15.375" style="43" customWidth="1"/>
+    <col min="10" max="10" width="10.125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="43" customWidth="1"/>
     <col min="12" max="12" width="30.25" style="43" customWidth="1"/>
-    <col min="13" max="13" width="18.08203125" style="43" customWidth="1"/>
-    <col min="14" max="14" width="18.83203125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="18.125" style="43" customWidth="1"/>
+    <col min="14" max="14" width="18.875" style="43" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="43" customWidth="1"/>
-    <col min="16" max="16" width="11.08203125" style="43" customWidth="1"/>
+    <col min="16" max="16" width="11.125" style="43" customWidth="1"/>
     <col min="17" max="17" width="19.75" style="43" customWidth="1"/>
-    <col min="18" max="18" width="44.08203125" style="43" customWidth="1"/>
-    <col min="19" max="19" width="99.9140625" style="43" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="44.125" style="43" customWidth="1"/>
+    <col min="19" max="19" width="99.875" style="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -7166,10 +7275,10 @@
         <v>210</v>
       </c>
       <c r="R2" s="24" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="S2" s="24" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="18" customHeight="1">
@@ -7697,10 +7806,10 @@
         <v>264</v>
       </c>
       <c r="R11" s="79" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="S11" s="28" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="18" customHeight="1">
@@ -7759,7 +7868,7 @@
         <v>273</v>
       </c>
       <c r="S12" s="28" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="T12" s="43"/>
       <c r="U12" s="43"/>
@@ -7833,7 +7942,7 @@
         <v>277</v>
       </c>
       <c r="S13" s="28" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="T13" s="43"/>
       <c r="U13" s="43"/>
@@ -7904,10 +8013,10 @@
         <v>282</v>
       </c>
       <c r="R14" s="79" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="S14" s="28" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="T14" s="43"/>
       <c r="U14" s="43"/>
@@ -7981,7 +8090,7 @@
         <v>288</v>
       </c>
       <c r="S15" s="28" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="T15" s="43"/>
       <c r="U15" s="43"/>
@@ -8055,7 +8164,7 @@
         <v>291</v>
       </c>
       <c r="S16" s="28" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="T16" s="43"/>
       <c r="U16" s="43"/>
@@ -13286,18 +13395,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:N53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="20.08203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.375" style="43" customWidth="1"/>
+    <col min="2" max="2" width="20.125" style="43" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="43" customWidth="1"/>
     <col min="4" max="4" width="12.75" style="43" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="43" customWidth="1"/>
     <col min="6" max="7" width="14.25" style="43" customWidth="1"/>
     <col min="8" max="8" width="11.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="12.58203125" style="43" customWidth="1"/>
-    <col min="10" max="10" width="17.83203125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="36.58203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.625" style="43" customWidth="1"/>
+    <col min="10" max="10" width="17.875" style="43" customWidth="1"/>
+    <col min="11" max="11" width="36.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13368,13 +13477,13 @@
         <v>210</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="K2" s="23" t="s">
         <v>455</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="N2" s="43"/>
     </row>
@@ -13524,7 +13633,7 @@
         <v>267</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="L6" s="2">
         <v>2</v>
@@ -13562,7 +13671,7 @@
         <v>267</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="L7" s="2">
         <v>1</v>
@@ -13600,7 +13709,7 @@
         <v>267</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="L8" s="2">
         <v>2</v>
@@ -13676,7 +13785,7 @@
         <v>267</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="L10" s="2">
         <v>2</v>
@@ -14035,19 +14144,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="21.58203125" style="43" customWidth="1"/>
-    <col min="3" max="3" width="18.58203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="21.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="18.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="13" style="43" customWidth="1"/>
     <col min="5" max="6" width="19.25" style="43" customWidth="1"/>
     <col min="7" max="7" width="14.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="14.875" style="43" customWidth="1"/>
     <col min="9" max="9" width="14" style="43" customWidth="1"/>
     <col min="10" max="10" width="19" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
-    <col min="12" max="12" width="9.58203125" style="43" customWidth="1"/>
-    <col min="13" max="13" width="44.08203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="43" customWidth="1"/>
+    <col min="13" max="13" width="44.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -14948,16 +15057,16 @@
       <c r="L22" s="9">
         <v>0</v>
       </c>
-      <c r="M22" s="32" t="s">
-        <v>529</v>
+      <c r="M22" s="34" t="s">
+        <v>977</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="B23" s="33" t="s">
         <v>530</v>
-      </c>
-      <c r="B23" s="33" t="s">
-        <v>531</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>516</v>
@@ -14989,16 +15098,16 @@
       <c r="L23" s="9">
         <v>0</v>
       </c>
-      <c r="M23" s="32" t="s">
-        <v>532</v>
+      <c r="M23" s="34" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="9" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>516</v>
@@ -15031,15 +15140,15 @@
         <v>0</v>
       </c>
       <c r="M24" s="32" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="9" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>516</v>
@@ -15072,15 +15181,15 @@
         <v>0</v>
       </c>
       <c r="M25" s="32" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="9" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>516</v>
@@ -15112,16 +15221,16 @@
       <c r="L26" s="9">
         <v>0</v>
       </c>
-      <c r="M26" s="32" t="s">
-        <v>541</v>
+      <c r="M26" s="81" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="9" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>516</v>
@@ -15153,8 +15262,8 @@
       <c r="L27" s="9">
         <v>0</v>
       </c>
-      <c r="M27" s="32" t="s">
-        <v>544</v>
+      <c r="M27" s="81" t="s">
+        <v>979</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
@@ -15174,18 +15283,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AH91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="18.08203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="18.125" style="43" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="43" customWidth="1"/>
-    <col min="5" max="5" width="34.58203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="11.08203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="43" customWidth="1"/>
+    <col min="4" max="4" width="17.375" style="43" customWidth="1"/>
+    <col min="5" max="5" width="34.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="43" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" style="43" customWidth="1"/>
-    <col min="9" max="9" width="10.58203125" style="43" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="43" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="43" customWidth="1"/>
+    <col min="10" max="10" width="14.875" style="43" customWidth="1"/>
     <col min="11" max="11" width="34.5" style="43" customWidth="1"/>
     <col min="12" max="12" width="20" style="43" customWidth="1"/>
   </cols>
@@ -15198,10 +15307,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>193</v>
@@ -15214,16 +15323,16 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="24" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>211</v>
@@ -15236,7 +15345,7 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="36" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B3" s="36" t="s">
         <v>2</v>
@@ -15248,7 +15357,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="M3" s="43"/>
       <c r="N3" s="43"/>
@@ -15258,7 +15367,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="40" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>3</v>
@@ -15270,7 +15379,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="M4" s="43"/>
       <c r="N4" s="43"/>
@@ -15280,10 +15389,10 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="36" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C5" s="37">
         <v>1</v>
@@ -15292,7 +15401,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="M5" s="43"/>
       <c r="N5" s="43"/>
@@ -15305,7 +15414,7 @@
         <v>290</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C6" s="37">
         <v>1</v>
@@ -15314,7 +15423,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="M6" s="43"/>
       <c r="N6" s="43"/>
@@ -15327,7 +15436,7 @@
         <v>275</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C7" s="37">
         <v>1</v>
@@ -15336,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="M7" s="43"/>
       <c r="N7" s="43"/>
@@ -15349,16 +15458,16 @@
         <v>330</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C8" s="37">
         <v>1</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="M8" s="43"/>
       <c r="N8" s="43"/>
@@ -15371,16 +15480,16 @@
         <v>372</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C9" s="37">
         <v>1</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="M9" s="43"/>
       <c r="N9" s="43"/>
@@ -15393,16 +15502,16 @@
         <v>321</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C10" s="37">
         <v>1</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="M10" s="43"/>
       <c r="N10" s="43"/>
@@ -15415,16 +15524,16 @@
         <v>235</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C11" s="37">
         <v>1</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="M11" s="43"/>
       <c r="N11" s="43"/>
@@ -15437,16 +15546,16 @@
         <v>230</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C12" s="37">
         <v>1</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="M12" s="43"/>
       <c r="N12" s="43"/>
@@ -15459,16 +15568,16 @@
         <v>240</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C13" s="38">
         <v>0</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="M13" s="43"/>
       <c r="N13" s="43"/>
@@ -15481,16 +15590,16 @@
         <v>381</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C14" s="38">
         <v>0</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E14" s="42" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
@@ -15503,16 +15612,16 @@
         <v>249</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C15" s="38">
         <v>0</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E15" s="42" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
@@ -15525,16 +15634,16 @@
         <v>254</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C16" s="38">
         <v>0</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E16" s="42" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="M16" s="43"/>
       <c r="N16" s="43"/>
@@ -15547,16 +15656,16 @@
         <v>245</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C17" s="38">
         <v>0</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="M17" s="43"/>
       <c r="N17" s="43"/>
@@ -15569,16 +15678,16 @@
         <v>285</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C18" s="37">
         <v>1</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="M18" s="43"/>
       <c r="N18" s="43"/>
@@ -15591,16 +15700,16 @@
         <v>364</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C19" s="37">
         <v>1</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="M19" s="43"/>
       <c r="N19" s="43"/>
@@ -15613,16 +15722,16 @@
         <v>471</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C20" s="37">
         <v>1</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="E20" s="42" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="M20" s="43"/>
       <c r="N20" s="43"/>
@@ -15635,16 +15744,16 @@
         <v>466</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C21" s="37">
         <v>1</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="M21" s="43"/>
       <c r="N21" s="43"/>
@@ -15657,16 +15766,16 @@
         <v>469</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C22" s="38">
         <v>0</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="M22" s="43"/>
       <c r="N22" s="43"/>
@@ -15679,16 +15788,16 @@
         <v>397</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C23" s="38">
         <v>0</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="M23" s="43"/>
       <c r="N23" s="43"/>
@@ -15698,19 +15807,19 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C24" s="38">
         <v>0</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="M24" s="43"/>
       <c r="N24" s="43"/>
@@ -15720,10 +15829,10 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="36" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C25" s="37">
         <v>1</v>
@@ -15732,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="M25" s="43"/>
       <c r="N25" s="43"/>
@@ -15742,10 +15851,10 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="36" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C26" s="37">
         <v>1</v>
@@ -15754,7 +15863,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="M26" s="43"/>
       <c r="N26" s="43"/>
@@ -17197,22 +17306,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="16" style="43" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="43" customWidth="1"/>
     <col min="4" max="4" width="16.25" style="43" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" customWidth="1"/>
-    <col min="6" max="6" width="12.08203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="43" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="13.875" style="43" customWidth="1"/>
     <col min="10" max="10" width="19" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="4" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -17221,25 +17330,25 @@
         <v>182</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>608</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>612</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -17250,34 +17359,34 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>621</v>
       </c>
       <c r="K2" s="43"/>
       <c r="L2" s="43"/>
@@ -17288,25 +17397,25 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="9" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="E3" s="9">
         <v>0</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H3" s="9">
         <v>1</v>
@@ -17326,25 +17435,25 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="9" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="E4" s="9">
         <v>0</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H4" s="9">
         <v>1</v>
@@ -17364,25 +17473,25 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="E5" s="9">
         <v>0</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H5" s="9">
         <v>1</v>
@@ -17402,25 +17511,25 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="9" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>140</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="E6" s="9">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H6" s="9">
         <v>1</v>
@@ -17440,25 +17549,25 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="9" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>168</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="E7" s="9">
         <v>0</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H7" s="9">
         <v>1</v>
@@ -17478,25 +17587,25 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="9" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>168</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="E8" s="9">
         <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H8" s="9">
         <v>1</v>
@@ -17516,31 +17625,31 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="9" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>176</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E9" s="9">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H9" s="9">
         <v>1</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J9" s="39" t="s">
         <v>380</v>
@@ -17554,31 +17663,31 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>644</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>646</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="H10" s="9">
-        <v>1</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>648</v>
       </c>
       <c r="J10" s="39" t="s">
         <v>380</v>
@@ -17592,25 +17701,25 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="9" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D11" s="9">
         <v>0</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H11" s="9">
         <v>1</v>
@@ -17628,25 +17737,25 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="9" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H12" s="9">
         <v>1</v>
@@ -17664,25 +17773,25 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="9" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H13" s="9">
         <v>1</v>
@@ -17700,25 +17809,25 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="9" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H14" s="9">
         <v>1</v>
@@ -17736,25 +17845,25 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="9" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>659</v>
       </c>
-      <c r="D15" s="9">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>663</v>
-      </c>
       <c r="F15" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H15" s="9">
         <v>1</v>
@@ -17772,25 +17881,25 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="9" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H16" s="9">
         <v>1</v>
@@ -17808,25 +17917,25 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="9" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D17" s="9">
         <v>0</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H17" s="9">
         <v>1</v>
@@ -17844,25 +17953,25 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="9" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H18" s="9">
         <v>1</v>
@@ -17880,25 +17989,25 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="9" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H19" s="9">
         <v>1</v>
@@ -18201,35 +18310,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16.25" style="43" customWidth="1"/>
     <col min="2" max="2" width="11.25" style="43" customWidth="1"/>
-    <col min="3" max="6" width="14.58203125" style="43" customWidth="1"/>
+    <col min="3" max="6" width="14.625" style="43" customWidth="1"/>
     <col min="7" max="7" width="41.5" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1">
       <c r="A1" s="24" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>103</v>
       </c>
       <c r="C1" s="24" t="s">
+        <v>672</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>673</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>674</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>675</v>
+      </c>
+      <c r="G1" s="24" t="s">
         <v>676</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>677</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>678</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>679</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>680</v>
       </c>
       <c r="H1" s="43"/>
       <c r="I1" s="43"/>
@@ -18237,25 +18346,25 @@
     </row>
     <row r="2" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A2" s="45" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B2" s="45" t="s">
         <v>121</v>
       </c>
       <c r="C2" s="45" t="s">
+        <v>677</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>678</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>679</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>680</v>
+      </c>
+      <c r="G2" s="45" t="s">
         <v>681</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>682</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>683</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>684</v>
-      </c>
-      <c r="G2" s="45" t="s">
-        <v>685</v>
       </c>
       <c r="H2" s="43"/>
       <c r="I2" s="43"/>
@@ -18263,7 +18372,7 @@
     </row>
     <row r="3" spans="1:10" ht="16.5" customHeight="1">
       <c r="A3" s="46" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B3" s="62" t="s">
         <v>138</v>
@@ -18281,7 +18390,7 @@
         <v>-1</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="H3" s="43"/>
       <c r="I3" s="43"/>
@@ -18289,7 +18398,7 @@
     </row>
     <row r="4" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A4" s="55" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B4" s="68" t="s">
         <v>138</v>
@@ -18313,7 +18422,7 @@
     </row>
     <row r="5" spans="1:10" ht="16.5" customHeight="1">
       <c r="A5" s="46" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B5" s="50" t="s">
         <v>158</v>
@@ -18331,7 +18440,7 @@
         <v>-1</v>
       </c>
       <c r="G5" s="47" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="H5" s="43"/>
       <c r="I5" s="43"/>
@@ -18339,7 +18448,7 @@
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A6" s="55" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B6" s="68" t="s">
         <v>158</v>
@@ -18363,7 +18472,7 @@
     </row>
     <row r="7" spans="1:10" ht="16.5" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B7" s="50" t="s">
         <v>138</v>
@@ -18381,7 +18490,7 @@
         <v>-1</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="H7" s="43"/>
       <c r="I7" s="43"/>
@@ -18389,7 +18498,7 @@
     </row>
     <row r="8" spans="1:10" ht="16.5" customHeight="1">
       <c r="A8" s="52" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B8" s="39" t="s">
         <v>138</v>
@@ -18413,7 +18522,7 @@
     </row>
     <row r="9" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A9" s="55" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B9" s="54" t="s">
         <v>149</v>
@@ -18437,7 +18546,7 @@
     </row>
     <row r="10" spans="1:10" ht="16.5" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B10" s="50" t="s">
         <v>158</v>
@@ -18455,7 +18564,7 @@
         <v>-1</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="H10" s="43"/>
       <c r="I10" s="43"/>
@@ -18463,7 +18572,7 @@
     </row>
     <row r="11" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A11" s="55" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B11" s="68" t="s">
         <v>154</v>
@@ -18487,7 +18596,7 @@
     </row>
     <row r="12" spans="1:10" ht="16.5" customHeight="1">
       <c r="A12" s="49" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B12" s="50" t="s">
         <v>138</v>
@@ -18505,7 +18614,7 @@
         <v>-1</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="H12" s="43"/>
       <c r="I12" s="43"/>
@@ -18513,7 +18622,7 @@
     </row>
     <row r="13" spans="1:10" ht="16.5" customHeight="1">
       <c r="A13" s="56" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B13" s="39" t="s">
         <v>158</v>
@@ -18537,7 +18646,7 @@
     </row>
     <row r="14" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A14" s="55" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B14" s="54" t="s">
         <v>149</v>
@@ -18561,7 +18670,7 @@
     </row>
     <row r="15" spans="1:10" ht="16.5" customHeight="1" thickBot="1">
       <c r="A15" s="57" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B15" s="58" t="s">
         <v>166</v>
@@ -18579,7 +18688,7 @@
         <v>-1</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="H15" s="43"/>
       <c r="I15" s="43"/>
@@ -18654,11 +18763,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:AF32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="18.58203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="43" customWidth="1"/>
+    <col min="2" max="2" width="18.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.875" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -18669,94 +18778,94 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>717</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="17.25" customHeight="1" thickBot="1">
@@ -18767,117 +18876,117 @@
         <v>26</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>724</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>729</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>732</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>734</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>740</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>742</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>743</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="AC2" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AE2" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AF2" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="AC2" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" ht="20.149999999999999" customHeight="1">
+    </row>
+    <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="60" t="s">
         <v>264</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C3" s="80" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D3" s="61" t="s">
         <v>280</v>
       </c>
       <c r="E3" s="61" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="F3" s="61" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="G3" s="61" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="H3" s="62">
         <v>0</v>
@@ -18955,39 +19064,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="4" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="64" t="s">
         <v>339</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>753</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>754</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>755</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>757</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>271</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="L4" s="9">
         <v>0</v>
@@ -19053,51 +19162,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="5" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="64" t="s">
         <v>390</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>271</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>280</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="P5" s="9">
         <v>0</v>
@@ -19151,39 +19260,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="20.149999999999999" customHeight="1" thickBot="1">
+    <row r="6" spans="1:32" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="A6" s="66" t="s">
         <v>458</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="E6" s="67" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="F6" s="67" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="H6" s="67" t="s">
         <v>280</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="J6" s="67" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="K6" s="67" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="L6" s="68">
         <v>0</v>
@@ -19249,15 +19358,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="7" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="60" t="s">
         <v>424</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D7" s="61" t="s">
         <v>280</v>
@@ -19347,21 +19456,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="8" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="64" t="s">
         <v>357</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
@@ -19445,24 +19554,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="9" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="64" t="s">
         <v>309</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -19543,27 +19652,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="10" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="64" t="s">
         <v>287</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -19641,33 +19750,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="11" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="70" t="s">
         <v>276</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>270</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -19739,30 +19848,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="12" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="64" t="s">
         <v>272</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>271</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="I12" s="9">
         <v>0</v>
@@ -19837,33 +19946,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="13" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="64" t="s">
         <v>301</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>271</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -19935,15 +20044,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="14" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="64" t="s">
         <v>369</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>271</v>
@@ -19952,22 +20061,22 @@
         <v>281</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>280</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="L14" s="9">
         <v>0</v>
@@ -20033,27 +20142,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="15" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="64" t="s">
         <v>294</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>271</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -20131,15 +20240,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="16" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="64" t="s">
         <v>322</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>271</v>
@@ -20151,16 +20260,16 @@
         <v>280</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="K16" s="9">
         <v>0</v>
@@ -20229,21 +20338,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="17" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="64" t="s">
         <v>282</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>280</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>271</v>
@@ -20252,10 +20361,10 @@
         <v>281</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -20327,15 +20436,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="18" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="64" t="s">
         <v>327</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>271</v>
@@ -20344,25 +20453,25 @@
         <v>281</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>280</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="M18" s="9">
         <v>0</v>
@@ -20425,30 +20534,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="20.149999999999999" customHeight="1" thickBot="1">
+    <row r="19" spans="1:32" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="A19" s="66" t="s">
         <v>331</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D19" s="67" t="s">
         <v>280</v>
       </c>
       <c r="E19" s="67" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="F19" s="67" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="G19" s="67" t="s">
         <v>281</v>
       </c>
       <c r="H19" s="67" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="I19" s="68">
         <v>0</v>
@@ -20523,18 +20632,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="20" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="71" t="s">
         <v>382</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E20" s="62">
         <v>0</v>
@@ -20621,30 +20730,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="21" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="64" t="s">
         <v>460</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>280</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="I21" s="9">
         <v>0</v>
@@ -20719,39 +20828,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="22" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="64" t="s">
         <v>463</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>280</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="L22" s="9">
         <v>0</v>
@@ -20817,7 +20926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="20.149999999999999" customHeight="1" thickBot="1">
+    <row r="23" spans="1:32" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="A23" s="72" t="s">
         <v>221</v>
       </c>
@@ -20825,7 +20934,7 @@
         <v>516</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D23" s="68">
         <v>0</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEFBA90-443A-4E74-B9F6-77210651FF02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE71FBB-8BBD-441C-963C-026033B8CBF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17145" tabRatio="550" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17145" tabRatio="550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -4720,7 +4720,7 @@
         <v>52</v>
       </c>
       <c r="I3" s="9">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="J3" s="9">
         <v>1</v>
@@ -4797,7 +4797,7 @@
         <v>70</v>
       </c>
       <c r="I4" s="9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
@@ -4874,7 +4874,7 @@
         <v>88</v>
       </c>
       <c r="I5" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J5" s="9">
         <v>1</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33E4FF7-3EF6-4C69-BE68-71619955B0A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CBF885-8A79-4142-BF83-E14C059D209B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17530" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17530" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="1000">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -3033,26 +3033,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>슬라임</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>미니슬</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>버프</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>디버프</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌진</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>S_Monster_05</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -3066,10 +3046,6 @@
   </si>
   <si>
     <t>Range_20</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Range_02</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -5864,7 +5840,7 @@
         <v>111</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="K1" s="24" t="s">
         <v>994</v>
@@ -5926,7 +5902,7 @@
         <v>127</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>128</v>
@@ -5988,7 +5964,7 @@
         <v>0.05</v>
       </c>
       <c r="J3" s="87" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>142</v>
@@ -6049,8 +6025,8 @@
       <c r="I4" s="11">
         <v>0</v>
       </c>
-      <c r="J4" s="87" t="s">
-        <v>1003</v>
+      <c r="J4" s="87">
+        <v>0</v>
       </c>
       <c r="K4" s="39" t="s">
         <v>147</v>
@@ -6111,8 +6087,8 @@
       <c r="I5" s="11">
         <v>0</v>
       </c>
-      <c r="J5" s="87" t="s">
-        <v>1004</v>
+      <c r="J5" s="87">
+        <v>0</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>147</v>
@@ -6173,8 +6149,8 @@
       <c r="I6" s="11">
         <v>0</v>
       </c>
-      <c r="J6" s="87" t="s">
-        <v>1004</v>
+      <c r="J6" s="87">
+        <v>0</v>
       </c>
       <c r="K6" s="39" t="s">
         <v>993</v>
@@ -6235,8 +6211,8 @@
       <c r="I7" s="11">
         <v>0</v>
       </c>
-      <c r="J7" s="72" t="s">
-        <v>224</v>
+      <c r="J7" s="72">
+        <v>0</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>142</v>
@@ -6410,7 +6386,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="87" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>474</v>
@@ -12951,7 +12927,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="39" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>476</v>
@@ -13296,52 +13272,32 @@
       <c r="L16" s="43"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="86" t="s">
-        <v>995</v>
-      </c>
+      <c r="A17" s="9"/>
+      <c r="B17" s="86"/>
       <c r="K17" s="43"/>
       <c r="L17" s="43"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B18" s="86" t="s">
-        <v>996</v>
-      </c>
+      <c r="A18" s="9"/>
+      <c r="B18" s="86"/>
       <c r="K18" s="43"/>
       <c r="L18" s="43"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B19" s="86" t="s">
-        <v>997</v>
-      </c>
+      <c r="A19" s="9"/>
+      <c r="B19" s="86"/>
       <c r="K19" s="43"/>
       <c r="L19" s="43"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B20" s="86" t="s">
-        <v>998</v>
-      </c>
+      <c r="A20" s="9"/>
+      <c r="B20" s="86"/>
       <c r="K20" s="43"/>
       <c r="L20" s="43"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="86" t="s">
-        <v>999</v>
-      </c>
+      <c r="A21" s="9"/>
+      <c r="B21" s="86"/>
       <c r="K21" s="43"/>
       <c r="L21" s="43"/>
     </row>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33E4FF7-3EF6-4C69-BE68-71619955B0A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E74610-9B9A-4CC2-B4E2-BCA626D08A2C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17530" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17535" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="1001">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -3030,26 +3030,6 @@
   </si>
   <si>
     <t>보유스킬1 ID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>슬라임</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>미니슬</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>버프</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>디버프</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌진</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -3444,7 +3424,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3689,9 +3669,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3910,23 +3887,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12.08203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="43" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="11.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="13" style="43" customWidth="1"/>
-    <col min="5" max="5" width="17.58203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.08203125" style="43" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" style="43" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="17.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="22.375" style="43" customWidth="1"/>
+    <col min="9" max="9" width="11.375" style="43" customWidth="1"/>
     <col min="10" max="10" width="17" style="43" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" style="43" customWidth="1"/>
-    <col min="12" max="13" width="12.08203125" style="43" customWidth="1"/>
-    <col min="14" max="15" width="12.33203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="16.375" style="43" customWidth="1"/>
+    <col min="12" max="13" width="12.125" style="43" customWidth="1"/>
+    <col min="14" max="15" width="12.375" style="43" customWidth="1"/>
     <col min="16" max="17" width="14.5" style="43" customWidth="1"/>
-    <col min="18" max="19" width="14.08203125" style="43" customWidth="1"/>
+    <col min="18" max="19" width="14.125" style="43" customWidth="1"/>
     <col min="20" max="24" width="8.5" style="43" customWidth="1"/>
     <col min="25" max="25" width="58.25" style="3" customWidth="1"/>
   </cols>
@@ -4499,13 +4476,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="22.875" style="43" customWidth="1"/>
     <col min="3" max="4" width="19.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="20.08203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="18.58203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="20.125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="18.625" style="43" customWidth="1"/>
     <col min="7" max="7" width="57.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4893,15 +4870,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
     <col min="2" max="2" width="14" style="43" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="43" customWidth="1"/>
     <col min="4" max="4" width="10.75" style="43" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" customWidth="1"/>
     <col min="6" max="6" width="37" style="43" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="43" customWidth="1"/>
     <col min="8" max="8" width="20.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5044,22 +5021,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="20.375" style="43" customWidth="1"/>
     <col min="4" max="4" width="12" style="43" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
     <col min="6" max="6" width="9.75" style="43" customWidth="1"/>
     <col min="7" max="7" width="11" style="43" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="10.375" style="43" customWidth="1"/>
     <col min="9" max="9" width="11" style="43" customWidth="1"/>
     <col min="10" max="10" width="20.25" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
-    <col min="12" max="12" width="12.08203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
+    <col min="12" max="12" width="12.125" style="43" customWidth="1"/>
     <col min="13" max="13" width="12.75" style="43" customWidth="1"/>
-    <col min="14" max="14" width="14.58203125" style="43" customWidth="1"/>
+    <col min="14" max="14" width="14.625" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -5405,16 +5382,16 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
     <col min="2" max="2" width="15.75" style="43" customWidth="1"/>
-    <col min="3" max="3" width="24.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="24.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="14" style="43" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="43" customWidth="1"/>
     <col min="7" max="7" width="12.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -5608,10 +5585,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="3" width="15.58203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="80.33203125" style="43" customWidth="1"/>
+    <col min="1" max="3" width="15.625" style="43" customWidth="1"/>
+    <col min="4" max="4" width="80.375" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5820,19 +5797,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="43" customWidth="1"/>
     <col min="2" max="2" width="17.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="43" customWidth="1"/>
-    <col min="5" max="5" width="19.08203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.58203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="18.08203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="19.125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="43" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="43" customWidth="1"/>
     <col min="8" max="8" width="19.75" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.58203125" style="43" customWidth="1"/>
-    <col min="10" max="16" width="15.58203125" style="43" customWidth="1"/>
-    <col min="17" max="19" width="15.58203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.625" style="43" customWidth="1"/>
+    <col min="10" max="16" width="15.625" style="43" customWidth="1"/>
+    <col min="17" max="19" width="15.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -5864,7 +5841,7 @@
         <v>111</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="K1" s="24" t="s">
         <v>994</v>
@@ -5926,7 +5903,7 @@
         <v>127</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>128</v>
@@ -5987,8 +5964,8 @@
       <c r="I3" s="11">
         <v>0.05</v>
       </c>
-      <c r="J3" s="87" t="s">
-        <v>1003</v>
+      <c r="J3" s="86" t="s">
+        <v>998</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>142</v>
@@ -6049,8 +6026,8 @@
       <c r="I4" s="11">
         <v>0</v>
       </c>
-      <c r="J4" s="87" t="s">
-        <v>1003</v>
+      <c r="J4" s="86" t="s">
+        <v>998</v>
       </c>
       <c r="K4" s="39" t="s">
         <v>147</v>
@@ -6111,8 +6088,8 @@
       <c r="I5" s="11">
         <v>0</v>
       </c>
-      <c r="J5" s="87" t="s">
-        <v>1004</v>
+      <c r="J5" s="86" t="s">
+        <v>999</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>147</v>
@@ -6173,8 +6150,8 @@
       <c r="I6" s="11">
         <v>0</v>
       </c>
-      <c r="J6" s="87" t="s">
-        <v>1004</v>
+      <c r="J6" s="86" t="s">
+        <v>999</v>
       </c>
       <c r="K6" s="39" t="s">
         <v>993</v>
@@ -6207,7 +6184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.5" thickBot="1">
+    <row r="7" spans="1:20" ht="17.25" thickBot="1">
       <c r="A7" s="9" t="s">
         <v>158</v>
       </c>
@@ -6409,8 +6386,8 @@
       <c r="I12" s="11">
         <v>1</v>
       </c>
-      <c r="J12" s="87" t="s">
-        <v>1005</v>
+      <c r="J12" s="86" t="s">
+        <v>1000</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>474</v>
@@ -6548,28 +6525,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH288"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.875" style="43" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="43" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="43" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="11.375" style="43" customWidth="1"/>
     <col min="6" max="6" width="5.75" style="43" customWidth="1"/>
-    <col min="7" max="7" width="9.08203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="43" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" style="43" customWidth="1"/>
-    <col min="10" max="10" width="10.08203125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="10.58203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="15.375" style="43" customWidth="1"/>
+    <col min="10" max="10" width="10.125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="43" customWidth="1"/>
     <col min="12" max="12" width="30.25" style="43" customWidth="1"/>
-    <col min="13" max="13" width="18.08203125" style="43" customWidth="1"/>
-    <col min="14" max="14" width="18.83203125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="18.125" style="43" customWidth="1"/>
+    <col min="14" max="14" width="18.875" style="43" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="43" customWidth="1"/>
-    <col min="16" max="16" width="11.08203125" style="43" customWidth="1"/>
+    <col min="16" max="16" width="11.125" style="43" customWidth="1"/>
     <col min="17" max="17" width="19.75" style="43" customWidth="1"/>
-    <col min="18" max="18" width="44.08203125" style="43" customWidth="1"/>
-    <col min="19" max="19" width="99.83203125" style="43" customWidth="1"/>
-    <col min="20" max="20" width="99.83203125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="44.125" style="43" customWidth="1"/>
+    <col min="19" max="19" width="99.875" style="43" customWidth="1"/>
+    <col min="20" max="20" width="99.875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -12705,18 +12682,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="20.08203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.375" style="43" customWidth="1"/>
+    <col min="2" max="2" width="20.125" style="43" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="43" customWidth="1"/>
     <col min="4" max="4" width="12.75" style="43" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="43" customWidth="1"/>
     <col min="6" max="7" width="14.25" style="43" customWidth="1"/>
     <col min="8" max="8" width="11.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="12.58203125" style="43" customWidth="1"/>
-    <col min="10" max="10" width="17.83203125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="36.58203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.625" style="43" customWidth="1"/>
+    <col min="10" max="10" width="17.875" style="43" customWidth="1"/>
+    <col min="11" max="11" width="36.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12951,7 +12928,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="39" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>476</v>
@@ -13295,97 +13272,67 @@
       <c r="K16" s="43"/>
       <c r="L16" s="43"/>
     </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="86" t="s">
-        <v>995</v>
-      </c>
+    <row r="17" spans="11:12">
       <c r="K17" s="43"/>
       <c r="L17" s="43"/>
     </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B18" s="86" t="s">
-        <v>996</v>
-      </c>
+    <row r="18" spans="11:12">
       <c r="K18" s="43"/>
       <c r="L18" s="43"/>
     </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B19" s="86" t="s">
-        <v>997</v>
-      </c>
+    <row r="19" spans="11:12">
       <c r="K19" s="43"/>
       <c r="L19" s="43"/>
     </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B20" s="86" t="s">
-        <v>998</v>
-      </c>
+    <row r="20" spans="11:12">
       <c r="K20" s="43"/>
       <c r="L20" s="43"/>
     </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="86" t="s">
-        <v>999</v>
-      </c>
+    <row r="21" spans="11:12">
       <c r="K21" s="43"/>
       <c r="L21" s="43"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="11:12">
       <c r="K22" s="43"/>
       <c r="L22" s="43"/>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="11:12">
       <c r="K23" s="43"/>
       <c r="L23" s="43"/>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="11:12">
       <c r="K24" s="43"/>
       <c r="L24" s="43"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="11:12">
       <c r="K25" s="43"/>
       <c r="L25" s="43"/>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="11:12">
       <c r="K26" s="43"/>
       <c r="L26" s="43"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="11:12">
       <c r="K27" s="43"/>
       <c r="L27" s="43"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="11:12">
       <c r="K28" s="43"/>
       <c r="L28" s="43"/>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="11:12">
       <c r="K29" s="43"/>
       <c r="L29" s="43"/>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="11:12">
       <c r="K30" s="43"/>
       <c r="L30" s="43"/>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="11:12">
       <c r="K31" s="43"/>
       <c r="L31" s="43"/>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="11:12">
       <c r="K32" s="43"/>
       <c r="L32" s="43"/>
     </row>
@@ -13482,19 +13429,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="21.58203125" style="43" customWidth="1"/>
-    <col min="3" max="3" width="18.58203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="21.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="18.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="13" style="43" customWidth="1"/>
     <col min="5" max="6" width="19.25" style="43" customWidth="1"/>
     <col min="7" max="7" width="14.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="14.875" style="43" customWidth="1"/>
     <col min="9" max="9" width="14" style="43" customWidth="1"/>
     <col min="10" max="10" width="19" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
-    <col min="12" max="12" width="9.58203125" style="43" customWidth="1"/>
-    <col min="13" max="13" width="44.08203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="43" customWidth="1"/>
+    <col min="13" max="13" width="44.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -14619,18 +14566,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AH91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="18.08203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="18.125" style="43" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="43" customWidth="1"/>
-    <col min="5" max="5" width="34.58203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="11.08203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="43" customWidth="1"/>
+    <col min="4" max="4" width="17.375" style="43" customWidth="1"/>
+    <col min="5" max="5" width="34.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="43" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" style="43" customWidth="1"/>
-    <col min="9" max="9" width="10.58203125" style="43" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="43" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="43" customWidth="1"/>
+    <col min="10" max="10" width="14.875" style="43" customWidth="1"/>
     <col min="11" max="11" width="34.5" style="43" customWidth="1"/>
     <col min="12" max="12" width="20" style="43" customWidth="1"/>
   </cols>
@@ -16640,16 +16587,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="16" style="43" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="43" customWidth="1"/>
     <col min="4" max="4" width="16.25" style="43" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" customWidth="1"/>
-    <col min="6" max="6" width="12.08203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="43" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="13.875" style="43" customWidth="1"/>
     <col min="10" max="10" width="19" style="43" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17642,11 +17589,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16.25" style="43" customWidth="1"/>
     <col min="2" max="2" width="11.25" style="43" customWidth="1"/>
-    <col min="3" max="6" width="14.58203125" style="43" customWidth="1"/>
+    <col min="3" max="6" width="14.625" style="43" customWidth="1"/>
     <col min="7" max="7" width="41.5" style="43" customWidth="1"/>
     <col min="8" max="11" width="41.5" style="3" customWidth="1"/>
   </cols>
@@ -18117,11 +18064,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AF32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="18.58203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="43" customWidth="1"/>
+    <col min="2" max="2" width="18.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.875" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -18320,7 +18267,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="60" t="s">
         <v>267</v>
       </c>
@@ -18418,7 +18365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="4" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="64" t="s">
         <v>351</v>
       </c>
@@ -18516,7 +18463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="5" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="64" t="s">
         <v>404</v>
       </c>
@@ -18614,7 +18561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="6" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="66" t="s">
         <v>475</v>
       </c>
@@ -18712,7 +18659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="7" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="60" t="s">
         <v>439</v>
       </c>
@@ -18810,7 +18757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="8" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="64" t="s">
         <v>370</v>
       </c>
@@ -18908,7 +18855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="9" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="64" t="s">
         <v>321</v>
       </c>
@@ -19006,7 +18953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="10" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="64" t="s">
         <v>296</v>
       </c>
@@ -19104,7 +19051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="11" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="70" t="s">
         <v>282</v>
       </c>
@@ -19202,7 +19149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="12" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="64" t="s">
         <v>277</v>
       </c>
@@ -19300,7 +19247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="13" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="64" t="s">
         <v>313</v>
       </c>
@@ -19398,7 +19345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="14" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="64" t="s">
         <v>382</v>
       </c>
@@ -19496,7 +19443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="15" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="64" t="s">
         <v>305</v>
       </c>
@@ -19594,7 +19541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="16" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="64" t="s">
         <v>334</v>
       </c>
@@ -19692,7 +19639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="17" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="64" t="s">
         <v>289</v>
       </c>
@@ -19790,7 +19737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="18" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="64" t="s">
         <v>339</v>
       </c>
@@ -19888,7 +19835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="19" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="66" t="s">
         <v>343</v>
       </c>
@@ -19986,7 +19933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="20" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="71" t="s">
         <v>395</v>
       </c>
@@ -20084,7 +20031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="21" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="64" t="s">
         <v>477</v>
       </c>
@@ -20182,7 +20129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="22" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="64" t="s">
         <v>481</v>
       </c>
@@ -20280,7 +20227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="20.149999999999999" customHeight="1">
+    <row r="23" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="72" t="s">
         <v>224</v>
       </c>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B6F454-C983-47BA-96BA-E5BD3B94D23F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF736D2-7B47-4CBF-80F4-31CBCE470A40}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17540" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="1001">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -3894,23 +3894,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="12.08203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="11.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="11.58203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="13" style="43" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="43" customWidth="1"/>
-    <col min="8" max="8" width="22.375" style="43" customWidth="1"/>
-    <col min="9" max="9" width="11.375" style="43" customWidth="1"/>
+    <col min="5" max="5" width="17.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.08203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" style="43" customWidth="1"/>
     <col min="10" max="10" width="17" style="43" customWidth="1"/>
-    <col min="11" max="11" width="16.375" style="43" customWidth="1"/>
-    <col min="12" max="13" width="12.125" style="43" customWidth="1"/>
-    <col min="14" max="15" width="12.375" style="43" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" style="43" customWidth="1"/>
+    <col min="12" max="13" width="12.08203125" style="43" customWidth="1"/>
+    <col min="14" max="15" width="12.33203125" style="43" customWidth="1"/>
     <col min="16" max="17" width="14.5" style="43" customWidth="1"/>
-    <col min="18" max="19" width="14.125" style="43" customWidth="1"/>
+    <col min="18" max="19" width="14.08203125" style="43" customWidth="1"/>
     <col min="20" max="24" width="8.5" style="43" customWidth="1"/>
     <col min="25" max="25" width="58.25" style="3" customWidth="1"/>
   </cols>
@@ -4069,7 +4069,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="115.5">
+    <row r="3" spans="1:25" ht="119">
       <c r="A3" s="9" t="s">
         <v>50</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="115.5">
+    <row r="4" spans="1:25" ht="102">
       <c r="A4" s="9" t="s">
         <v>67</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="115.5">
+    <row r="5" spans="1:25" ht="119">
       <c r="A5" s="9" t="s">
         <v>84</v>
       </c>
@@ -4483,13 +4483,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
-    <col min="2" max="2" width="22.875" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" style="43" customWidth="1"/>
     <col min="3" max="4" width="19.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="20.125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="18.625" style="43" customWidth="1"/>
+    <col min="5" max="5" width="20.08203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="18.58203125" style="43" customWidth="1"/>
     <col min="7" max="7" width="57.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4877,15 +4877,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="14" style="43" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="43" customWidth="1"/>
     <col min="4" max="4" width="10.75" style="43" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" customWidth="1"/>
     <col min="6" max="6" width="37" style="43" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="43" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" style="43" customWidth="1"/>
     <col min="8" max="8" width="20.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5028,22 +5028,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="20.375" style="43" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="12" style="43" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
     <col min="6" max="6" width="9.75" style="43" customWidth="1"/>
     <col min="7" max="7" width="11" style="43" customWidth="1"/>
-    <col min="8" max="8" width="10.375" style="43" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="43" customWidth="1"/>
     <col min="9" max="9" width="11" style="43" customWidth="1"/>
     <col min="10" max="10" width="20.25" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
-    <col min="12" max="12" width="12.125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
+    <col min="12" max="12" width="12.08203125" style="43" customWidth="1"/>
     <col min="13" max="13" width="12.75" style="43" customWidth="1"/>
-    <col min="14" max="14" width="14.625" style="43" customWidth="1"/>
+    <col min="14" max="14" width="14.58203125" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -5389,16 +5389,16 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="15.75" style="43" customWidth="1"/>
-    <col min="3" max="3" width="24.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="24.58203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="14" style="43" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.58203125" style="43" customWidth="1"/>
     <col min="7" max="7" width="12.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="43" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -5592,10 +5592,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="3" width="15.625" style="43" customWidth="1"/>
-    <col min="4" max="4" width="80.375" style="43" customWidth="1"/>
+    <col min="1" max="3" width="15.58203125" style="43" customWidth="1"/>
+    <col min="4" max="4" width="80.33203125" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5804,19 +5804,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="43" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="17.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.58203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="43" customWidth="1"/>
-    <col min="5" max="5" width="19.125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="43" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="19.08203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.58203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="18.08203125" style="43" customWidth="1"/>
     <col min="8" max="8" width="19.75" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.625" style="43" customWidth="1"/>
-    <col min="10" max="16" width="15.625" style="43" customWidth="1"/>
-    <col min="17" max="19" width="15.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.58203125" style="43" customWidth="1"/>
+    <col min="10" max="16" width="15.58203125" style="43" customWidth="1"/>
+    <col min="17" max="19" width="15.58203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.25" thickBot="1">
+    <row r="7" spans="1:20" ht="17.5" thickBot="1">
       <c r="A7" s="9" t="s">
         <v>155</v>
       </c>
@@ -6532,28 +6532,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH288"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="13.875" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="43" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="43" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="11.375" style="43" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="43" customWidth="1"/>
     <col min="6" max="6" width="5.75" style="43" customWidth="1"/>
-    <col min="7" max="7" width="9.125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="9.08203125" style="43" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="15.375" style="43" customWidth="1"/>
-    <col min="10" max="10" width="10.125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="43" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="43" customWidth="1"/>
+    <col min="10" max="10" width="10.08203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="10.58203125" style="43" customWidth="1"/>
     <col min="12" max="12" width="30.25" style="43" customWidth="1"/>
-    <col min="13" max="13" width="18.125" style="43" customWidth="1"/>
-    <col min="14" max="14" width="18.875" style="43" customWidth="1"/>
+    <col min="13" max="13" width="18.08203125" style="43" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" style="43" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="43" customWidth="1"/>
-    <col min="16" max="16" width="11.125" style="43" customWidth="1"/>
+    <col min="16" max="16" width="11.08203125" style="43" customWidth="1"/>
     <col min="17" max="17" width="19.75" style="43" customWidth="1"/>
-    <col min="18" max="18" width="44.125" style="43" customWidth="1"/>
-    <col min="19" max="19" width="99.875" style="43" customWidth="1"/>
-    <col min="20" max="20" width="99.875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="44.08203125" style="43" customWidth="1"/>
+    <col min="19" max="19" width="99.83203125" style="43" customWidth="1"/>
+    <col min="20" max="20" width="99.83203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -12689,18 +12689,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="13.375" style="43" customWidth="1"/>
-    <col min="2" max="2" width="20.125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="20.08203125" style="43" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="43" customWidth="1"/>
     <col min="4" max="4" width="12.75" style="43" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="43" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" style="43" customWidth="1"/>
     <col min="6" max="7" width="14.25" style="43" customWidth="1"/>
     <col min="8" max="8" width="11.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="12.625" style="43" customWidth="1"/>
-    <col min="10" max="10" width="17.875" style="43" customWidth="1"/>
-    <col min="11" max="11" width="36.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.58203125" style="43" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="36.58203125" style="3" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13436,19 +13436,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="21.625" style="43" customWidth="1"/>
-    <col min="3" max="3" width="18.625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="21.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="18.58203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="13" style="43" customWidth="1"/>
     <col min="5" max="6" width="19.25" style="43" customWidth="1"/>
     <col min="7" max="7" width="14.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="14.875" style="43" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" style="43" customWidth="1"/>
     <col min="9" max="9" width="14" style="43" customWidth="1"/>
     <col min="10" max="10" width="19" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="43" customWidth="1"/>
-    <col min="13" max="13" width="44.125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
+    <col min="12" max="12" width="9.58203125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="44.08203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -14573,18 +14573,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AH91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="18.125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="43" customWidth="1"/>
-    <col min="4" max="4" width="17.375" style="43" customWidth="1"/>
-    <col min="5" max="5" width="34.625" style="43" customWidth="1"/>
-    <col min="6" max="6" width="11.125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="43" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="34.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="11.08203125" style="43" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="13.875" style="43" customWidth="1"/>
-    <col min="9" max="9" width="10.625" style="43" customWidth="1"/>
-    <col min="10" max="10" width="14.875" style="43" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="10.58203125" style="43" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" style="43" customWidth="1"/>
     <col min="11" max="11" width="34.5" style="43" customWidth="1"/>
     <col min="12" max="12" width="20" style="43" customWidth="1"/>
   </cols>
@@ -16594,16 +16594,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="16" style="43" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="43" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="16.25" style="43" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="12.08203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.58203125" style="43" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.875" style="43" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" style="43" customWidth="1"/>
     <col min="10" max="10" width="19" style="43" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17596,11 +17596,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="16.25" style="43" customWidth="1"/>
     <col min="2" max="2" width="11.25" style="43" customWidth="1"/>
-    <col min="3" max="6" width="14.625" style="43" customWidth="1"/>
+    <col min="3" max="6" width="14.58203125" style="43" customWidth="1"/>
     <col min="7" max="7" width="41.5" style="43" customWidth="1"/>
     <col min="8" max="11" width="41.5" style="3" customWidth="1"/>
   </cols>
@@ -18071,11 +18071,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AF32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="9.375" style="43" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.875" style="43" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="18.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -18274,7 +18274,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="3" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A3" s="60" t="s">
         <v>264</v>
       </c>
@@ -18372,7 +18372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A4" s="64" t="s">
         <v>348</v>
       </c>
@@ -18470,7 +18470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A5" s="64" t="s">
         <v>401</v>
       </c>
@@ -18568,7 +18568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A6" s="66" t="s">
         <v>472</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A7" s="60" t="s">
         <v>436</v>
       </c>
@@ -18764,7 +18764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A8" s="64" t="s">
         <v>367</v>
       </c>
@@ -18862,7 +18862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A9" s="64" t="s">
         <v>318</v>
       </c>
@@ -18960,7 +18960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A10" s="64" t="s">
         <v>293</v>
       </c>
@@ -19058,7 +19058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A11" s="70" t="s">
         <v>279</v>
       </c>
@@ -19156,7 +19156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A12" s="64" t="s">
         <v>274</v>
       </c>
@@ -19254,7 +19254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A13" s="64" t="s">
         <v>310</v>
       </c>
@@ -19352,7 +19352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A14" s="64" t="s">
         <v>379</v>
       </c>
@@ -19450,7 +19450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A15" s="64" t="s">
         <v>302</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A16" s="64" t="s">
         <v>331</v>
       </c>
@@ -19646,7 +19646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A17" s="64" t="s">
         <v>286</v>
       </c>
@@ -19744,7 +19744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A18" s="64" t="s">
         <v>336</v>
       </c>
@@ -19842,7 +19842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A19" s="66" t="s">
         <v>340</v>
       </c>
@@ -19940,7 +19940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A20" s="71" t="s">
         <v>392</v>
       </c>
@@ -20038,7 +20038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A21" s="64" t="s">
         <v>474</v>
       </c>
@@ -20049,20 +20049,20 @@
         <v>776</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>778</v>
+        <v>284</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>284</v>
+        <v>779</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="H21" s="6" t="s">
         <v>777</v>
       </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
       <c r="I21" s="9">
         <v>0</v>
       </c>
@@ -20136,7 +20136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A22" s="64" t="s">
         <v>478</v>
       </c>
@@ -20234,7 +20234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A23" s="72" t="s">
         <v>221</v>
       </c>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF736D2-7B47-4CBF-80F4-31CBCE470A40}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8BE370-035C-47E2-8787-43C85B4131FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17540" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="1003">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -1847,13 +1847,7 @@
     <t>Maintain</t>
   </si>
   <si>
-    <t>수치만큼 받는 피해가 증가함</t>
-  </si>
-  <si>
     <t>침식</t>
-  </si>
-  <si>
-    <t>수치만큼 주는 피해가 감소함</t>
   </si>
   <si>
     <t>차단</t>
@@ -3060,12 +3054,151 @@
 자원(에테르)을 얻습니다.</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수치만큼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피해가 증가함</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수치만큼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>받는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피해가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_Grudge</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_Corrosion</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3151,6 +3284,20 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -3428,7 +3575,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3679,6 +3826,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4143,7 +4293,7 @@
         <v>66</v>
       </c>
       <c r="Y3" s="87" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="102">
@@ -4220,7 +4370,7 @@
         <v>83</v>
       </c>
       <c r="Y4" s="87" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="119">
@@ -4297,7 +4447,7 @@
         <v>100</v>
       </c>
       <c r="Y5" s="87" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -4495,7 +4645,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="24" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>1</v>
@@ -4518,7 +4668,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="75" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B2" s="75" t="s">
         <v>26</v>
@@ -4542,10 +4692,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B3" s="73" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>499</v>
@@ -4560,16 +4710,16 @@
         <v>1</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="H3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B4" s="73" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>499</v>
@@ -4584,16 +4734,16 @@
         <v>1</v>
       </c>
       <c r="G4" s="74" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="H4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B5" s="73" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>499</v>
@@ -4608,16 +4758,16 @@
         <v>1</v>
       </c>
       <c r="G5" s="73" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B6" s="73" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>499</v>
@@ -4632,16 +4782,16 @@
         <v>1</v>
       </c>
       <c r="G6" s="73" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="H6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B7" s="73" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>499</v>
@@ -4656,16 +4806,16 @@
         <v>1</v>
       </c>
       <c r="G7" s="74" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="H7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B8" s="73" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>499</v>
@@ -4680,16 +4830,16 @@
         <v>1</v>
       </c>
       <c r="G8" s="74" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="H8" s="43"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B9" s="73" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>499</v>
@@ -4704,16 +4854,16 @@
         <v>1</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B10" s="73" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>499</v>
@@ -4728,16 +4878,16 @@
         <v>1</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="H10" s="43"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B11" s="73" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>499</v>
@@ -4752,16 +4902,16 @@
         <v>1</v>
       </c>
       <c r="G11" s="73" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="H11" s="43"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B12" s="73" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>499</v>
@@ -4776,7 +4926,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="73" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="H12" s="43"/>
     </row>
@@ -4891,132 +5041,132 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
+        <v>842</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>843</v>
+      </c>
+      <c r="C1" s="43" t="s">
         <v>844</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="D1" s="43" t="s">
         <v>845</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>846</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="F1" s="43" t="s">
+        <v>693</v>
+      </c>
+      <c r="G1" s="43" t="s">
         <v>847</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>848</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>695</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>849</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B2" s="43" t="s">
+        <v>849</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>850</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>851</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="E2" s="43" t="s">
         <v>852</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="F2" s="43" t="s">
+        <v>702</v>
+      </c>
+      <c r="G2" s="43" t="s">
         <v>853</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="H2" s="43" t="s">
         <v>854</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>704</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>855</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
+        <v>855</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>856</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>857</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="D3" s="43" t="s">
         <v>858</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="E3" s="43" t="s">
         <v>859</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="F3" s="43" t="s">
         <v>860</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>861</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>862</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>218</v>
       </c>
       <c r="H3" s="43" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
+        <v>862</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>863</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>857</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>858</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>864</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="F4" s="43" t="s">
         <v>865</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>859</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>860</v>
-      </c>
-      <c r="E4" s="43" t="s">
+      <c r="G4" s="43" t="s">
         <v>866</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="H4" s="43" t="s">
         <v>867</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>868</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
+        <v>868</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>869</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>857</v>
+      </c>
+      <c r="D5" s="43" t="s">
         <v>870</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="E5" s="43" t="s">
         <v>871</v>
       </c>
-      <c r="C5" s="43" t="s">
-        <v>859</v>
-      </c>
-      <c r="D5" s="43" t="s">
+      <c r="F5" s="43" t="s">
         <v>872</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>873</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>874</v>
       </c>
       <c r="G5" s="43" t="s">
         <v>218</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
   </sheetData>
@@ -5048,104 +5198,104 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="43" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B1" s="43" t="s">
+        <v>874</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>875</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>876</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>877</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>878</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>879</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>880</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="I1" s="43" t="s">
         <v>881</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="J1" s="43" t="s">
         <v>882</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="K1" s="43" t="s">
         <v>883</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>884</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>885</v>
       </c>
-      <c r="L1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>886</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>887</v>
-      </c>
-      <c r="N1" s="43" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="43" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B2" s="43" t="s">
+        <v>887</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>888</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>889</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="E2" s="43" t="s">
         <v>890</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="F2" s="43" t="s">
         <v>891</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="G2" s="43" t="s">
         <v>892</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="H2" s="43" t="s">
         <v>893</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="I2" s="43" t="s">
         <v>894</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="J2" s="43" t="s">
         <v>895</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="K2" s="43" t="s">
         <v>896</v>
       </c>
-      <c r="J2" s="43" t="s">
+      <c r="L2" s="43" t="s">
         <v>897</v>
       </c>
-      <c r="K2" s="43" t="s">
+      <c r="M2" s="43" t="s">
         <v>898</v>
       </c>
-      <c r="L2" s="43" t="s">
+      <c r="N2" s="43" t="s">
         <v>899</v>
-      </c>
-      <c r="M2" s="43" t="s">
-        <v>900</v>
-      </c>
-      <c r="N2" s="43" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="43" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B3" s="43">
         <v>1</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>218</v>
@@ -5160,10 +5310,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="43" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="J3" s="43" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="K3" s="43">
         <v>1</v>
@@ -5177,16 +5327,16 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="43" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B4" s="43">
         <v>2</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="E4" s="43" t="s">
         <v>218</v>
@@ -5201,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="K4" s="43">
         <v>1</v>
@@ -5213,21 +5363,21 @@
         <v>0.7</v>
       </c>
       <c r="M4" s="43" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="43" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B5" s="43">
         <v>3</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="E5" s="43" t="s">
         <v>218</v>
@@ -5259,34 +5409,34 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="43" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B6" s="43">
         <v>1</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E6" s="43" t="s">
         <v>218</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="H6" s="43">
         <v>100</v>
       </c>
       <c r="I6" s="43" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="K6" s="43">
         <v>1</v>
@@ -5300,16 +5450,16 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="43" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B7" s="43">
         <v>2</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="E7" s="43" t="s">
         <v>218</v>
@@ -5341,16 +5491,16 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="43" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B8" s="43">
         <v>1</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="E8" s="43" t="s">
         <v>218</v>
@@ -5365,10 +5515,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="J8" s="43" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="K8" s="43">
         <v>30</v>
@@ -5403,77 +5553,77 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
+        <v>915</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>693</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>916</v>
+      </c>
+      <c r="E1" s="43" t="s">
         <v>917</v>
       </c>
-      <c r="B1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>695</v>
-      </c>
-      <c r="D1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>918</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>919</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>920</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>921</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D2" s="43" t="s">
+        <v>922</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>923</v>
+      </c>
+      <c r="F2" s="43" t="s">
         <v>924</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="G2" s="43" t="s">
         <v>925</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="H2" s="43" t="s">
         <v>926</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>927</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
+        <v>927</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>928</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>929</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="D3" s="43" t="s">
         <v>930</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="E3" s="43" t="s">
         <v>931</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>933</v>
       </c>
       <c r="F3" s="43">
         <v>5</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="H3" s="43">
         <v>100</v>
@@ -5481,25 +5631,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
+        <v>933</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="C4" s="43" t="s">
         <v>935</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="D4" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>936</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>937</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>938</v>
       </c>
       <c r="F4" s="43">
         <v>10</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="H4" s="43">
         <v>200</v>
@@ -5507,25 +5657,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
+        <v>937</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>938</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>939</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="D5" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="E5" s="43" t="s">
         <v>940</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="F5" s="43">
+        <v>1</v>
+      </c>
+      <c r="G5" s="43" t="s">
         <v>941</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>942</v>
-      </c>
-      <c r="F5" s="43">
-        <v>1</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>943</v>
       </c>
       <c r="H5" s="43">
         <v>50</v>
@@ -5533,25 +5683,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="43" t="s">
+        <v>942</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>943</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>944</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="D6" s="43" t="s">
         <v>945</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="E6" s="43" t="s">
         <v>946</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>947</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>948</v>
       </c>
       <c r="F6" s="43">
         <v>3</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="H6" s="43">
         <v>150</v>
@@ -5559,25 +5709,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="43" t="s">
+        <v>947</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>948</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>949</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="D7" s="43" t="s">
         <v>950</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="E7" s="43" t="s">
         <v>951</v>
       </c>
-      <c r="D7" s="43" t="s">
-        <v>952</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>953</v>
-      </c>
       <c r="F7" s="43">
         <v>1</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="H7" s="43">
         <v>30</v>
@@ -5600,30 +5750,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="77" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B1" s="77" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="24" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5631,13 +5781,13 @@
         <v>138</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C3" s="9">
         <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5645,13 +5795,13 @@
         <v>143</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C4" s="9">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5659,13 +5809,13 @@
         <v>148</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C5" s="9">
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5673,13 +5823,13 @@
         <v>153</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C6" s="9">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5687,69 +5837,69 @@
         <v>157</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C7" s="9">
         <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="9" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C8" s="9">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="9" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C9" s="9">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="9" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C10" s="9">
         <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="9" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C11" s="9">
         <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5757,41 +5907,41 @@
         <v>166</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C12" s="9">
         <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C13" s="9">
         <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C14" s="9">
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
   </sheetData>
@@ -5848,10 +5998,10 @@
         <v>108</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>109</v>
@@ -5910,7 +6060,7 @@
         <v>124</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>125</v>
@@ -5972,7 +6122,7 @@
         <v>0.05</v>
       </c>
       <c r="J3" s="86" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>139</v>
@@ -6034,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="86" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="K4" s="39" t="s">
         <v>144</v>
@@ -6096,7 +6246,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="86" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>144</v>
@@ -6158,10 +6308,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="86" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>149</v>
@@ -6394,7 +6544,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="86" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>471</v>
@@ -12771,7 +12921,7 @@
         <v>208</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="K2" s="23" t="s">
         <v>468</v>
@@ -12935,7 +13085,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="39" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>473</v>
@@ -15009,7 +15159,7 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="36" t="s">
-        <v>486</v>
+        <v>1001</v>
       </c>
       <c r="B20" s="36" t="s">
         <v>602</v>
@@ -15020,8 +15170,8 @@
       <c r="D20" s="39" t="s">
         <v>603</v>
       </c>
-      <c r="E20" s="42" t="s">
-        <v>604</v>
+      <c r="E20" s="88" t="s">
+        <v>1000</v>
       </c>
       <c r="M20" s="43"/>
       <c r="N20" s="43"/>
@@ -15031,10 +15181,10 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="36" t="s">
-        <v>481</v>
+        <v>1002</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C21" s="37">
         <v>1</v>
@@ -15042,8 +15192,8 @@
       <c r="D21" s="39" t="s">
         <v>603</v>
       </c>
-      <c r="E21" s="42" t="s">
-        <v>606</v>
+      <c r="E21" s="88" t="s">
+        <v>999</v>
       </c>
       <c r="M21" s="43"/>
       <c r="N21" s="43"/>
@@ -15056,7 +15206,7 @@
         <v>484</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C22" s="38">
         <v>0</v>
@@ -15065,7 +15215,7 @@
         <v>577</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="M22" s="43"/>
       <c r="N22" s="43"/>
@@ -15078,7 +15228,7 @@
         <v>408</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C23" s="38">
         <v>0</v>
@@ -15087,7 +15237,7 @@
         <v>577</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M23" s="43"/>
       <c r="N23" s="43"/>
@@ -15097,10 +15247,10 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="36" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C24" s="38">
         <v>0</v>
@@ -15109,7 +15259,7 @@
         <v>577</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="M24" s="43"/>
       <c r="N24" s="43"/>
@@ -15119,19 +15269,19 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="36" t="s">
+        <v>612</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="C25" s="37">
+        <v>1</v>
+      </c>
+      <c r="D25" s="37">
+        <v>0</v>
+      </c>
+      <c r="E25" s="42" t="s">
         <v>614</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>615</v>
-      </c>
-      <c r="C25" s="37">
-        <v>1</v>
-      </c>
-      <c r="D25" s="37">
-        <v>0</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>616</v>
       </c>
       <c r="M25" s="43"/>
       <c r="N25" s="43"/>
@@ -15141,19 +15291,19 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="36" t="s">
+        <v>615</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>616</v>
+      </c>
+      <c r="C26" s="37">
+        <v>1</v>
+      </c>
+      <c r="D26" s="37">
+        <v>0</v>
+      </c>
+      <c r="E26" s="42" t="s">
         <v>617</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>618</v>
-      </c>
-      <c r="C26" s="37">
-        <v>1</v>
-      </c>
-      <c r="D26" s="37">
-        <v>0</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>619</v>
       </c>
       <c r="M26" s="43"/>
       <c r="N26" s="43"/>
@@ -16609,7 +16759,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -16618,25 +16768,25 @@
         <v>179</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>625</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>627</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -16647,34 +16797,34 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>634</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>636</v>
       </c>
       <c r="K2" s="43"/>
       <c r="L2" s="43"/>
@@ -16685,25 +16835,25 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="9" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>137</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>639</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>641</v>
       </c>
       <c r="H3" s="9">
         <v>1</v>
@@ -16723,25 +16873,25 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="9" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E4" s="9">
         <v>0</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H4" s="9">
         <v>1</v>
@@ -16761,25 +16911,25 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E5" s="9">
         <v>0</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H5" s="9">
         <v>1</v>
@@ -16799,25 +16949,25 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="9" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>137</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E6" s="9">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H6" s="9">
         <v>1</v>
@@ -16837,25 +16987,25 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="9" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>165</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E7" s="9">
         <v>0</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H7" s="9">
         <v>1</v>
@@ -16875,25 +17025,25 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="9" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>165</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E8" s="9">
         <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H8" s="9">
         <v>1</v>
@@ -16913,31 +17063,31 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="9" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>173</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E9" s="9">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H9" s="9">
         <v>1</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="J9" s="39" t="s">
         <v>390</v>
@@ -16951,31 +17101,31 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>659</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="F10" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>661</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="H10" s="9">
-        <v>1</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>663</v>
       </c>
       <c r="J10" s="39" t="s">
         <v>390</v>
@@ -16989,25 +17139,25 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="9" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D11" s="9">
         <v>0</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H11" s="9">
         <v>1</v>
@@ -17025,25 +17175,25 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>666</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>668</v>
-      </c>
       <c r="F12" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H12" s="9">
         <v>1</v>
@@ -17061,25 +17211,25 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>671</v>
-      </c>
       <c r="F13" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H13" s="9">
         <v>1</v>
@@ -17097,25 +17247,25 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>673</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>675</v>
-      </c>
       <c r="F14" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H14" s="9">
         <v>1</v>
@@ -17133,25 +17283,25 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>676</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="D15" s="9">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>678</v>
-      </c>
       <c r="F15" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H15" s="9">
         <v>1</v>
@@ -17169,25 +17319,25 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>681</v>
-      </c>
       <c r="F16" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H16" s="9">
         <v>1</v>
@@ -17205,25 +17355,25 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>682</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>684</v>
-      </c>
       <c r="F17" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H17" s="9">
         <v>1</v>
@@ -17241,25 +17391,25 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>686</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>687</v>
-      </c>
       <c r="F18" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H18" s="9">
         <v>1</v>
@@ -17277,25 +17427,25 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="D19" s="9">
-        <v>0</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>690</v>
-      </c>
       <c r="F19" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H19" s="9">
         <v>1</v>
@@ -17607,77 +17757,77 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" customHeight="1">
       <c r="A1" s="24" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>101</v>
       </c>
       <c r="C1" s="24" t="s">
+        <v>689</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>690</v>
+      </c>
+      <c r="E1" s="24" t="s">
         <v>691</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="F1" s="24" t="s">
         <v>692</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="G1" s="24" t="s">
         <v>693</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="H1" s="24" t="s">
         <v>694</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="I1" s="24" t="s">
         <v>695</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="J1" s="24" t="s">
         <v>696</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="K1" s="24" t="s">
         <v>697</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>698</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.5" customHeight="1">
       <c r="A2" s="45" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B2" s="45" t="s">
         <v>118</v>
       </c>
       <c r="C2" s="45" t="s">
+        <v>698</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>699</v>
+      </c>
+      <c r="E2" s="45" t="s">
         <v>700</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="F2" s="45" t="s">
         <v>701</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="G2" s="45" t="s">
         <v>702</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="H2" s="45" t="s">
         <v>703</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="I2" s="45" t="s">
         <v>704</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="J2" s="45" t="s">
         <v>705</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="K2" s="45" t="s">
         <v>706</v>
-      </c>
-      <c r="J2" s="45" t="s">
-        <v>707</v>
-      </c>
-      <c r="K2" s="45" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.5" customHeight="1">
       <c r="A3" s="46" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B3" s="62" t="s">
         <v>135</v>
@@ -17695,7 +17845,7 @@
         <v>-1</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H3" s="83">
         <v>1</v>
@@ -17712,7 +17862,7 @@
     </row>
     <row r="4" spans="1:11" ht="16.5" customHeight="1">
       <c r="A4" s="55" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B4" s="68" t="s">
         <v>135</v>
@@ -17737,7 +17887,7 @@
     </row>
     <row r="5" spans="1:11" ht="16.5" customHeight="1">
       <c r="A5" s="46" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B5" s="50" t="s">
         <v>155</v>
@@ -17755,7 +17905,7 @@
         <v>-1</v>
       </c>
       <c r="G5" s="47" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H5" s="83">
         <v>1</v>
@@ -17772,7 +17922,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" customHeight="1">
       <c r="A6" s="55" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B6" s="68" t="s">
         <v>155</v>
@@ -17797,7 +17947,7 @@
     </row>
     <row r="7" spans="1:11" ht="16.5" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B7" s="50" t="s">
         <v>135</v>
@@ -17815,7 +17965,7 @@
         <v>-1</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H7" s="84">
         <v>1</v>
@@ -17832,7 +17982,7 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" customHeight="1">
       <c r="A8" s="52" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B8" s="39" t="s">
         <v>135</v>
@@ -17857,7 +18007,7 @@
     </row>
     <row r="9" spans="1:11" ht="16.5" customHeight="1">
       <c r="A9" s="55" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B9" s="54" t="s">
         <v>146</v>
@@ -17882,7 +18032,7 @@
     </row>
     <row r="10" spans="1:11" ht="16.5" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B10" s="50" t="s">
         <v>155</v>
@@ -17900,7 +18050,7 @@
         <v>-1</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H10" s="84">
         <v>1</v>
@@ -17917,7 +18067,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" customHeight="1">
       <c r="A11" s="55" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B11" s="68" t="s">
         <v>151</v>
@@ -17942,7 +18092,7 @@
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
       <c r="A12" s="49" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B12" s="50" t="s">
         <v>135</v>
@@ -17960,7 +18110,7 @@
         <v>-1</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H12" s="84">
         <v>1</v>
@@ -17977,7 +18127,7 @@
     </row>
     <row r="13" spans="1:11" ht="16.5" customHeight="1">
       <c r="A13" s="56" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B13" s="39" t="s">
         <v>155</v>
@@ -18002,7 +18152,7 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" customHeight="1">
       <c r="A14" s="55" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B14" s="54" t="s">
         <v>146</v>
@@ -18027,7 +18177,7 @@
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1">
       <c r="A15" s="57" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B15" s="58" t="s">
         <v>163</v>
@@ -18045,7 +18195,7 @@
         <v>-1</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H15" s="85">
         <v>1</v>
@@ -18086,94 +18236,94 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>741</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>742</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="17.25" customHeight="1">
@@ -18184,94 +18334,94 @@
         <v>26</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>750</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>751</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>752</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>754</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AC2" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AE2" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AF2" s="5" t="s">
         <v>772</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="20.149999999999999" customHeight="1">
@@ -18279,22 +18429,22 @@
         <v>264</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C3" s="80" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D3" s="61" t="s">
         <v>284</v>
       </c>
       <c r="E3" s="61" t="s">
+        <v>775</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>776</v>
+      </c>
+      <c r="G3" s="61" t="s">
         <v>777</v>
-      </c>
-      <c r="F3" s="61" t="s">
-        <v>778</v>
-      </c>
-      <c r="G3" s="61" t="s">
-        <v>779</v>
       </c>
       <c r="H3" s="62">
         <v>0</v>
@@ -18377,34 +18527,34 @@
         <v>348</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>284</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>778</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>779</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>781</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>273</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="L4" s="9">
         <v>0</v>
@@ -18475,46 +18625,46 @@
         <v>401</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C5" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>776</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>778</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>273</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>284</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="P5" s="9">
         <v>0</v>
@@ -18573,34 +18723,34 @@
         <v>472</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C6" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D6" s="67" t="s">
+        <v>783</v>
+      </c>
+      <c r="E6" s="67" t="s">
         <v>776</v>
       </c>
-      <c r="D6" s="67" t="s">
-        <v>785</v>
-      </c>
-      <c r="E6" s="67" t="s">
-        <v>778</v>
-      </c>
       <c r="F6" s="67" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H6" s="67" t="s">
         <v>284</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J6" s="67" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="K6" s="67" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="L6" s="68">
         <v>0</v>
@@ -18671,10 +18821,10 @@
         <v>436</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D7" s="61" t="s">
         <v>284</v>
@@ -18769,16 +18919,16 @@
         <v>367</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>284</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
@@ -18867,19 +19017,19 @@
         <v>318</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>284</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -18965,22 +19115,22 @@
         <v>293</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>284</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>793</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>795</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -19063,28 +19213,28 @@
         <v>279</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>284</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F11" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>793</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>795</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>272</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -19161,25 +19311,25 @@
         <v>274</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>284</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>273</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="I12" s="9">
         <v>0</v>
@@ -19259,28 +19409,28 @@
         <v>310</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>284</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>273</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -19357,10 +19507,10 @@
         <v>379</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>273</v>
@@ -19369,22 +19519,22 @@
         <v>285</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>284</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="L14" s="9">
         <v>0</v>
@@ -19455,22 +19605,22 @@
         <v>302</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>284</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>273</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -19553,10 +19703,10 @@
         <v>331</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>273</v>
@@ -19568,16 +19718,16 @@
         <v>284</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="K16" s="9">
         <v>0</v>
@@ -19651,16 +19801,16 @@
         <v>286</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>284</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>273</v>
@@ -19669,10 +19819,10 @@
         <v>285</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -19749,10 +19899,10 @@
         <v>336</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>273</v>
@@ -19761,25 +19911,25 @@
         <v>285</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>284</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="M18" s="9">
         <v>0</v>
@@ -19847,25 +19997,25 @@
         <v>340</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D19" s="67" t="s">
         <v>284</v>
       </c>
       <c r="E19" s="67" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F19" s="67" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G19" s="67" t="s">
         <v>285</v>
       </c>
       <c r="H19" s="67" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="I19" s="68">
         <v>0</v>
@@ -19945,13 +20095,13 @@
         <v>392</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="E20" s="62">
         <v>0</v>
@@ -20043,22 +20193,22 @@
         <v>474</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C21" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>776</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>778</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>284</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -20141,34 +20291,34 @@
         <v>478</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C22" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>778</v>
-      </c>
       <c r="F22" s="6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>284</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="L22" s="9">
         <v>0</v>
@@ -20242,7 +20392,7 @@
         <v>531</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D23" s="68">
         <v>0</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -5,35 +5,36 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8BE370-035C-47E2-8787-43C85B4131FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5D3AE7-8554-4D01-BB23-EA191C578268}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17535" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
     <sheet name="Monster" sheetId="2" r:id="rId2"/>
     <sheet name="SkillMaster" sheetId="3" r:id="rId3"/>
     <sheet name="MonsterSkill" sheetId="4" r:id="rId4"/>
-    <sheet name="Rune" sheetId="5" r:id="rId5"/>
-    <sheet name="Effect" sheetId="6" r:id="rId6"/>
-    <sheet name="Map" sheetId="7" r:id="rId7"/>
-    <sheet name="BattleMap" sheetId="8" r:id="rId8"/>
-    <sheet name="SkillRange" sheetId="9" r:id="rId9"/>
-    <sheet name="Relic" sheetId="10" r:id="rId10"/>
-    <sheet name="EventMaster" sheetId="11" r:id="rId11"/>
-    <sheet name="EventChoice" sheetId="12" r:id="rId12"/>
-    <sheet name="Quest" sheetId="13" r:id="rId13"/>
-    <sheet name="Item" sheetId="14" r:id="rId14"/>
+    <sheet name="MonsterPatternInfo" sheetId="15" r:id="rId5"/>
+    <sheet name="Rune" sheetId="5" r:id="rId6"/>
+    <sheet name="Effect" sheetId="6" r:id="rId7"/>
+    <sheet name="Map" sheetId="7" r:id="rId8"/>
+    <sheet name="BattleMap" sheetId="8" r:id="rId9"/>
+    <sheet name="SkillRange" sheetId="9" r:id="rId10"/>
+    <sheet name="Relic" sheetId="10" r:id="rId11"/>
+    <sheet name="EventMaster" sheetId="11" r:id="rId12"/>
+    <sheet name="EventChoice" sheetId="12" r:id="rId13"/>
+    <sheet name="Quest" sheetId="13" r:id="rId14"/>
+    <sheet name="Item" sheetId="14" r:id="rId15"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="1015">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -3193,12 +3194,52 @@
     <t>E_Corrosion</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
+  <si>
+    <t>PatternId</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>PatternInfo_Muck_01</t>
+  </si>
+  <si>
+    <t>가까운 캐릭터에게 이동합니다.</t>
+  </si>
+  <si>
+    <t>PatternInfo_Muck_02</t>
+  </si>
+  <si>
+    <t>본인 기준 십자범위에 5칸범위를 공격합니다.</t>
+  </si>
+  <si>
+    <t>PatternInfo_Muck_03</t>
+  </si>
+  <si>
+    <t>사망 시 2마리의 Blob로 분열합니다.</t>
+  </si>
+  <si>
+    <t>패턴ID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터ID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>순서</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3298,6 +3339,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -3575,7 +3624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3829,6 +3878,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4044,23 +4096,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12.08203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="43" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="11.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="13" style="43" customWidth="1"/>
-    <col min="5" max="5" width="17.58203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.08203125" style="43" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" style="43" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="17.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="22.375" style="43" customWidth="1"/>
+    <col min="9" max="9" width="11.375" style="43" customWidth="1"/>
     <col min="10" max="10" width="17" style="43" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" style="43" customWidth="1"/>
-    <col min="12" max="13" width="12.08203125" style="43" customWidth="1"/>
-    <col min="14" max="15" width="12.33203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="16.375" style="43" customWidth="1"/>
+    <col min="12" max="13" width="12.125" style="43" customWidth="1"/>
+    <col min="14" max="15" width="12.375" style="43" customWidth="1"/>
     <col min="16" max="17" width="14.5" style="43" customWidth="1"/>
-    <col min="18" max="19" width="14.08203125" style="43" customWidth="1"/>
+    <col min="18" max="19" width="14.125" style="43" customWidth="1"/>
     <col min="20" max="24" width="8.5" style="43" customWidth="1"/>
     <col min="25" max="25" width="58.25" style="3" customWidth="1"/>
   </cols>
@@ -4219,7 +4271,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="119">
+    <row r="3" spans="1:25" ht="115.5">
       <c r="A3" s="9" t="s">
         <v>50</v>
       </c>
@@ -4296,7 +4348,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="102">
+    <row r="4" spans="1:25" ht="115.5">
       <c r="A4" s="9" t="s">
         <v>67</v>
       </c>
@@ -4373,7 +4425,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="119">
+    <row r="5" spans="1:25" ht="115.5">
       <c r="A5" s="9" t="s">
         <v>84</v>
       </c>
@@ -4631,392 +4683,2313 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:AF32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" style="43" customWidth="1"/>
-    <col min="3" max="4" width="19.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="20.08203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="18.58203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="57.25" style="43" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="43" customWidth="1"/>
+    <col min="2" max="2" width="18.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.875" style="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="24" t="s">
-        <v>810</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>464</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="75" t="s">
-        <v>811</v>
-      </c>
-      <c r="B2" s="75" t="s">
+    <row r="1" spans="1:32">
+      <c r="A1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="17.25" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="75" t="s">
-        <v>199</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="76" t="s">
-        <v>468</v>
-      </c>
-      <c r="H2" s="43"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="B3" s="73" t="s">
-        <v>813</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="73">
-        <v>1</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>814</v>
-      </c>
-      <c r="H3" s="43"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="B4" s="73" t="s">
-        <v>816</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4" s="73">
-        <v>1</v>
-      </c>
-      <c r="G4" s="74" t="s">
-        <v>817</v>
-      </c>
-      <c r="H4" s="43"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="B5" s="73" t="s">
-        <v>819</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="F5" s="73">
-        <v>1</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>820</v>
-      </c>
-      <c r="H5" s="43"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="B6" s="73" t="s">
-        <v>822</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E6" s="1">
-        <v>-2</v>
-      </c>
-      <c r="F6" s="73">
-        <v>1</v>
-      </c>
-      <c r="G6" s="73" t="s">
-        <v>823</v>
-      </c>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="B7" s="73" t="s">
-        <v>825</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="73">
-        <v>1</v>
-      </c>
-      <c r="G7" s="74" t="s">
-        <v>826</v>
-      </c>
-      <c r="H7" s="43"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="B8" s="73" t="s">
-        <v>828</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="73">
-        <v>1</v>
-      </c>
-      <c r="G8" s="74" t="s">
-        <v>829</v>
-      </c>
-      <c r="H8" s="43"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>831</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="73">
-        <v>1</v>
-      </c>
-      <c r="G9" s="74" t="s">
-        <v>832</v>
-      </c>
-      <c r="H9" s="43"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="B10" s="73" t="s">
-        <v>834</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="73">
-        <v>1</v>
-      </c>
-      <c r="G10" s="74" t="s">
-        <v>835</v>
-      </c>
-      <c r="H10" s="43"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="B11" s="73" t="s">
-        <v>837</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="73">
-        <v>1</v>
-      </c>
-      <c r="G11" s="73" t="s">
-        <v>838</v>
-      </c>
-      <c r="H11" s="43"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="B12" s="73" t="s">
-        <v>840</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="73">
-        <v>1</v>
-      </c>
-      <c r="G12" s="73" t="s">
-        <v>841</v>
-      </c>
-      <c r="H12" s="43"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-    </row>
-    <row r="17" spans="8:9">
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-    </row>
-    <row r="18" spans="8:9">
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-    </row>
-    <row r="19" spans="8:9">
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-    </row>
-    <row r="20" spans="8:9">
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-    </row>
-    <row r="21" spans="8:9">
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-    </row>
-    <row r="22" spans="8:9">
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-    </row>
-    <row r="23" spans="8:9">
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-    </row>
-    <row r="24" spans="8:9">
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-    </row>
-    <row r="25" spans="8:9">
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-    </row>
-    <row r="26" spans="8:9">
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-    </row>
-    <row r="27" spans="8:9">
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-    </row>
-    <row r="28" spans="8:9">
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-    </row>
-    <row r="29" spans="8:9">
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-    </row>
-    <row r="30" spans="8:9">
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-    </row>
-    <row r="31" spans="8:9">
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-    </row>
-    <row r="32" spans="8:9">
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-    </row>
-    <row r="33" spans="8:9">
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-    </row>
-    <row r="34" spans="8:9">
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
+      <c r="C2" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>773</v>
+      </c>
+      <c r="C3" s="80" t="s">
+        <v>774</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>284</v>
+      </c>
+      <c r="E3" s="61" t="s">
+        <v>775</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>776</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>777</v>
+      </c>
+      <c r="H3" s="62">
+        <v>0</v>
+      </c>
+      <c r="I3" s="62">
+        <v>0</v>
+      </c>
+      <c r="J3" s="62">
+        <v>0</v>
+      </c>
+      <c r="K3" s="62">
+        <v>0</v>
+      </c>
+      <c r="L3" s="62">
+        <v>0</v>
+      </c>
+      <c r="M3" s="62">
+        <v>0</v>
+      </c>
+      <c r="N3" s="62">
+        <v>0</v>
+      </c>
+      <c r="O3" s="62">
+        <v>0</v>
+      </c>
+      <c r="P3" s="62">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="62">
+        <v>0</v>
+      </c>
+      <c r="R3" s="62">
+        <v>0</v>
+      </c>
+      <c r="S3" s="62">
+        <v>0</v>
+      </c>
+      <c r="T3" s="62">
+        <v>0</v>
+      </c>
+      <c r="U3" s="62">
+        <v>0</v>
+      </c>
+      <c r="V3" s="62">
+        <v>0</v>
+      </c>
+      <c r="W3" s="62">
+        <v>0</v>
+      </c>
+      <c r="X3" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="62">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="64" t="s">
+        <v>348</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
+      <c r="R4" s="9">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9">
+        <v>0</v>
+      </c>
+      <c r="T4" s="9">
+        <v>0</v>
+      </c>
+      <c r="U4" s="9">
+        <v>0</v>
+      </c>
+      <c r="V4" s="9">
+        <v>0</v>
+      </c>
+      <c r="W4" s="9">
+        <v>0</v>
+      </c>
+      <c r="X4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A5" s="64" t="s">
+        <v>401</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0</v>
+      </c>
+      <c r="S5" s="9">
+        <v>0</v>
+      </c>
+      <c r="T5" s="9">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9">
+        <v>0</v>
+      </c>
+      <c r="V5" s="9">
+        <v>0</v>
+      </c>
+      <c r="W5" s="9">
+        <v>0</v>
+      </c>
+      <c r="X5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="66" t="s">
+        <v>472</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>787</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D6" s="67" t="s">
+        <v>783</v>
+      </c>
+      <c r="E6" s="67" t="s">
+        <v>776</v>
+      </c>
+      <c r="F6" s="67" t="s">
+        <v>784</v>
+      </c>
+      <c r="G6" s="67" t="s">
+        <v>775</v>
+      </c>
+      <c r="H6" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="I6" s="67" t="s">
+        <v>785</v>
+      </c>
+      <c r="J6" s="67" t="s">
+        <v>777</v>
+      </c>
+      <c r="K6" s="67" t="s">
+        <v>786</v>
+      </c>
+      <c r="L6" s="68">
+        <v>0</v>
+      </c>
+      <c r="M6" s="68">
+        <v>0</v>
+      </c>
+      <c r="N6" s="68">
+        <v>0</v>
+      </c>
+      <c r="O6" s="68">
+        <v>0</v>
+      </c>
+      <c r="P6" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="68">
+        <v>0</v>
+      </c>
+      <c r="R6" s="68">
+        <v>0</v>
+      </c>
+      <c r="S6" s="68">
+        <v>0</v>
+      </c>
+      <c r="T6" s="68">
+        <v>0</v>
+      </c>
+      <c r="U6" s="68">
+        <v>0</v>
+      </c>
+      <c r="V6" s="68">
+        <v>0</v>
+      </c>
+      <c r="W6" s="68">
+        <v>0</v>
+      </c>
+      <c r="X6" s="68">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="68">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>788</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7" s="62">
+        <v>0</v>
+      </c>
+      <c r="F7" s="62">
+        <v>0</v>
+      </c>
+      <c r="G7" s="62">
+        <v>0</v>
+      </c>
+      <c r="H7" s="62">
+        <v>0</v>
+      </c>
+      <c r="I7" s="62">
+        <v>0</v>
+      </c>
+      <c r="J7" s="62">
+        <v>0</v>
+      </c>
+      <c r="K7" s="62">
+        <v>0</v>
+      </c>
+      <c r="L7" s="62">
+        <v>0</v>
+      </c>
+      <c r="M7" s="62">
+        <v>0</v>
+      </c>
+      <c r="N7" s="62">
+        <v>0</v>
+      </c>
+      <c r="O7" s="62">
+        <v>0</v>
+      </c>
+      <c r="P7" s="62">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="62">
+        <v>0</v>
+      </c>
+      <c r="R7" s="62">
+        <v>0</v>
+      </c>
+      <c r="S7" s="62">
+        <v>0</v>
+      </c>
+      <c r="T7" s="62">
+        <v>0</v>
+      </c>
+      <c r="U7" s="62">
+        <v>0</v>
+      </c>
+      <c r="V7" s="62">
+        <v>0</v>
+      </c>
+      <c r="W7" s="62">
+        <v>0</v>
+      </c>
+      <c r="X7" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="62">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="64" t="s">
+        <v>367</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9">
+        <v>0</v>
+      </c>
+      <c r="T8" s="9">
+        <v>0</v>
+      </c>
+      <c r="U8" s="9">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9">
+        <v>0</v>
+      </c>
+      <c r="W8" s="9">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="64" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>0</v>
+      </c>
+      <c r="S9" s="9">
+        <v>0</v>
+      </c>
+      <c r="T9" s="9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0</v>
+      </c>
+      <c r="W9" s="9">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="64" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
+      </c>
+      <c r="S10" s="9">
+        <v>0</v>
+      </c>
+      <c r="T10" s="9">
+        <v>0</v>
+      </c>
+      <c r="U10" s="9">
+        <v>0</v>
+      </c>
+      <c r="V10" s="9">
+        <v>0</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="70" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9">
+        <v>0</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0</v>
+      </c>
+      <c r="S12" s="9">
+        <v>0</v>
+      </c>
+      <c r="T12" s="9">
+        <v>0</v>
+      </c>
+      <c r="U12" s="9">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="64" t="s">
+        <v>310</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0</v>
+      </c>
+      <c r="S13" s="9">
+        <v>0</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="64" t="s">
+        <v>379</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9">
+        <v>0</v>
+      </c>
+      <c r="V14" s="9">
+        <v>0</v>
+      </c>
+      <c r="W14" s="9">
+        <v>0</v>
+      </c>
+      <c r="X14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="64" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9">
+        <v>0</v>
+      </c>
+      <c r="S15" s="9">
+        <v>0</v>
+      </c>
+      <c r="T15" s="9">
+        <v>0</v>
+      </c>
+      <c r="U15" s="9">
+        <v>0</v>
+      </c>
+      <c r="V15" s="9">
+        <v>0</v>
+      </c>
+      <c r="W15" s="9">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="64" t="s">
+        <v>331</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
+      </c>
+      <c r="P16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9">
+        <v>0</v>
+      </c>
+      <c r="S16" s="9">
+        <v>0</v>
+      </c>
+      <c r="T16" s="9">
+        <v>0</v>
+      </c>
+      <c r="U16" s="9">
+        <v>0</v>
+      </c>
+      <c r="V16" s="9">
+        <v>0</v>
+      </c>
+      <c r="W16" s="9">
+        <v>0</v>
+      </c>
+      <c r="X16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="64" t="s">
+        <v>286</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9">
+        <v>0</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0</v>
+      </c>
+      <c r="P17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9">
+        <v>0</v>
+      </c>
+      <c r="S17" s="9">
+        <v>0</v>
+      </c>
+      <c r="T17" s="9">
+        <v>0</v>
+      </c>
+      <c r="U17" s="9">
+        <v>0</v>
+      </c>
+      <c r="V17" s="9">
+        <v>0</v>
+      </c>
+      <c r="W17" s="9">
+        <v>0</v>
+      </c>
+      <c r="X17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="64" t="s">
+        <v>336</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+      <c r="O18" s="9">
+        <v>0</v>
+      </c>
+      <c r="P18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>0</v>
+      </c>
+      <c r="R18" s="9">
+        <v>0</v>
+      </c>
+      <c r="S18" s="9">
+        <v>0</v>
+      </c>
+      <c r="T18" s="9">
+        <v>0</v>
+      </c>
+      <c r="U18" s="9">
+        <v>0</v>
+      </c>
+      <c r="V18" s="9">
+        <v>0</v>
+      </c>
+      <c r="W18" s="9">
+        <v>0</v>
+      </c>
+      <c r="X18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="66" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>806</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D19" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="E19" s="67" t="s">
+        <v>785</v>
+      </c>
+      <c r="F19" s="67" t="s">
+        <v>791</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>285</v>
+      </c>
+      <c r="H19" s="67" t="s">
+        <v>800</v>
+      </c>
+      <c r="I19" s="68">
+        <v>0</v>
+      </c>
+      <c r="J19" s="68">
+        <v>0</v>
+      </c>
+      <c r="K19" s="68">
+        <v>0</v>
+      </c>
+      <c r="L19" s="68">
+        <v>0</v>
+      </c>
+      <c r="M19" s="68">
+        <v>0</v>
+      </c>
+      <c r="N19" s="68">
+        <v>0</v>
+      </c>
+      <c r="O19" s="68">
+        <v>0</v>
+      </c>
+      <c r="P19" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="68">
+        <v>0</v>
+      </c>
+      <c r="R19" s="68">
+        <v>0</v>
+      </c>
+      <c r="S19" s="68">
+        <v>0</v>
+      </c>
+      <c r="T19" s="68">
+        <v>0</v>
+      </c>
+      <c r="U19" s="68">
+        <v>0</v>
+      </c>
+      <c r="V19" s="68">
+        <v>0</v>
+      </c>
+      <c r="W19" s="68">
+        <v>0</v>
+      </c>
+      <c r="X19" s="68">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="68">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="71" t="s">
+        <v>392</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>807</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>774</v>
+      </c>
+      <c r="E20" s="62">
+        <v>0</v>
+      </c>
+      <c r="F20" s="62">
+        <v>0</v>
+      </c>
+      <c r="G20" s="62">
+        <v>0</v>
+      </c>
+      <c r="H20" s="62">
+        <v>0</v>
+      </c>
+      <c r="I20" s="62">
+        <v>0</v>
+      </c>
+      <c r="J20" s="62">
+        <v>0</v>
+      </c>
+      <c r="K20" s="62">
+        <v>0</v>
+      </c>
+      <c r="L20" s="62">
+        <v>0</v>
+      </c>
+      <c r="M20" s="62">
+        <v>0</v>
+      </c>
+      <c r="N20" s="62">
+        <v>0</v>
+      </c>
+      <c r="O20" s="62">
+        <v>0</v>
+      </c>
+      <c r="P20" s="62">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="62">
+        <v>0</v>
+      </c>
+      <c r="R20" s="62">
+        <v>0</v>
+      </c>
+      <c r="S20" s="62">
+        <v>0</v>
+      </c>
+      <c r="T20" s="62">
+        <v>0</v>
+      </c>
+      <c r="U20" s="62">
+        <v>0</v>
+      </c>
+      <c r="V20" s="62">
+        <v>0</v>
+      </c>
+      <c r="W20" s="62">
+        <v>0</v>
+      </c>
+      <c r="X20" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="62">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="64" t="s">
+        <v>474</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="9">
+        <v>0</v>
+      </c>
+      <c r="P21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>0</v>
+      </c>
+      <c r="R21" s="9">
+        <v>0</v>
+      </c>
+      <c r="S21" s="9">
+        <v>0</v>
+      </c>
+      <c r="T21" s="9">
+        <v>0</v>
+      </c>
+      <c r="U21" s="9">
+        <v>0</v>
+      </c>
+      <c r="V21" s="9">
+        <v>0</v>
+      </c>
+      <c r="W21" s="9">
+        <v>0</v>
+      </c>
+      <c r="X21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="64" t="s">
+        <v>478</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+      <c r="O22" s="9">
+        <v>0</v>
+      </c>
+      <c r="P22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>0</v>
+      </c>
+      <c r="R22" s="9">
+        <v>0</v>
+      </c>
+      <c r="S22" s="9">
+        <v>0</v>
+      </c>
+      <c r="T22" s="9">
+        <v>0</v>
+      </c>
+      <c r="U22" s="9">
+        <v>0</v>
+      </c>
+      <c r="V22" s="9">
+        <v>0</v>
+      </c>
+      <c r="W22" s="9">
+        <v>0</v>
+      </c>
+      <c r="X22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>531</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D23" s="68">
+        <v>0</v>
+      </c>
+      <c r="E23" s="68">
+        <v>0</v>
+      </c>
+      <c r="F23" s="68">
+        <v>0</v>
+      </c>
+      <c r="G23" s="68">
+        <v>0</v>
+      </c>
+      <c r="H23" s="68">
+        <v>0</v>
+      </c>
+      <c r="I23" s="68">
+        <v>0</v>
+      </c>
+      <c r="J23" s="68">
+        <v>0</v>
+      </c>
+      <c r="K23" s="68">
+        <v>0</v>
+      </c>
+      <c r="L23" s="68">
+        <v>0</v>
+      </c>
+      <c r="M23" s="68">
+        <v>0</v>
+      </c>
+      <c r="N23" s="68">
+        <v>0</v>
+      </c>
+      <c r="O23" s="68">
+        <v>0</v>
+      </c>
+      <c r="P23" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="68">
+        <v>0</v>
+      </c>
+      <c r="R23" s="68">
+        <v>0</v>
+      </c>
+      <c r="S23" s="68">
+        <v>0</v>
+      </c>
+      <c r="T23" s="68">
+        <v>0</v>
+      </c>
+      <c r="U23" s="68">
+        <v>0</v>
+      </c>
+      <c r="V23" s="68">
+        <v>0</v>
+      </c>
+      <c r="W23" s="68">
+        <v>0</v>
+      </c>
+      <c r="X23" s="68">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="68">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32">
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+    </row>
+    <row r="25" spans="1:32">
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+    </row>
+    <row r="27" spans="1:32">
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+    </row>
+    <row r="28" spans="1:32">
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+    </row>
+    <row r="29" spans="1:32">
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+    </row>
+    <row r="30" spans="1:32">
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+    </row>
+    <row r="31" spans="1:32">
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+    </row>
+    <row r="32" spans="1:32">
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -5025,149 +6998,392 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="14" style="43" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="43" customWidth="1"/>
-    <col min="4" max="4" width="10.75" style="43" customWidth="1"/>
-    <col min="5" max="5" width="12" style="43" customWidth="1"/>
-    <col min="6" max="6" width="37" style="43" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" style="43" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="22.875" style="43" customWidth="1"/>
+    <col min="3" max="4" width="19.5" style="43" customWidth="1"/>
+    <col min="5" max="5" width="20.125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="18.625" style="43" customWidth="1"/>
+    <col min="7" max="7" width="57.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="43" t="s">
-        <v>842</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>843</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>844</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>845</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>846</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>693</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>847</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="43" t="s">
-        <v>629</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>849</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>850</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>851</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>852</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>702</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>853</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="43" t="s">
-        <v>855</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>856</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>857</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>858</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>859</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>860</v>
-      </c>
-      <c r="G3" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="43" t="s">
-        <v>862</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>863</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>857</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>858</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>864</v>
-      </c>
-      <c r="F4" s="43" t="s">
-        <v>865</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>866</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="43" t="s">
-        <v>868</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>869</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>857</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>870</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>871</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>872</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H5" s="43" t="s">
-        <v>873</v>
-      </c>
+    <row r="1" spans="1:9">
+      <c r="A1" s="24" t="s">
+        <v>810</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="75" t="s">
+        <v>811</v>
+      </c>
+      <c r="B2" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="75" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="76" t="s">
+        <v>468</v>
+      </c>
+      <c r="H2" s="43"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>813</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="73">
+        <v>1</v>
+      </c>
+      <c r="G3" s="74" t="s">
+        <v>814</v>
+      </c>
+      <c r="H3" s="43"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>816</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="73">
+        <v>1</v>
+      </c>
+      <c r="G4" s="74" t="s">
+        <v>817</v>
+      </c>
+      <c r="H4" s="43"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>819</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="73">
+        <v>1</v>
+      </c>
+      <c r="G5" s="73" t="s">
+        <v>820</v>
+      </c>
+      <c r="H5" s="43"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B6" s="73" t="s">
+        <v>822</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-2</v>
+      </c>
+      <c r="F6" s="73">
+        <v>1</v>
+      </c>
+      <c r="G6" s="73" t="s">
+        <v>823</v>
+      </c>
+      <c r="H6" s="43"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B7" s="73" t="s">
+        <v>825</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="73">
+        <v>1</v>
+      </c>
+      <c r="G7" s="74" t="s">
+        <v>826</v>
+      </c>
+      <c r="H7" s="43"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B8" s="73" t="s">
+        <v>828</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="73">
+        <v>1</v>
+      </c>
+      <c r="G8" s="74" t="s">
+        <v>829</v>
+      </c>
+      <c r="H8" s="43"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>831</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="73">
+        <v>1</v>
+      </c>
+      <c r="G9" s="74" t="s">
+        <v>832</v>
+      </c>
+      <c r="H9" s="43"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B10" s="73" t="s">
+        <v>834</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="73">
+        <v>1</v>
+      </c>
+      <c r="G10" s="74" t="s">
+        <v>835</v>
+      </c>
+      <c r="H10" s="43"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B11" s="73" t="s">
+        <v>837</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="73">
+        <v>1</v>
+      </c>
+      <c r="G11" s="73" t="s">
+        <v>838</v>
+      </c>
+      <c r="H11" s="43"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B12" s="73" t="s">
+        <v>840</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="73">
+        <v>1</v>
+      </c>
+      <c r="G12" s="73" t="s">
+        <v>841</v>
+      </c>
+      <c r="H12" s="43"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+    </row>
+    <row r="17" spans="8:9">
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+    </row>
+    <row r="18" spans="8:9">
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+    </row>
+    <row r="19" spans="8:9">
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+    </row>
+    <row r="20" spans="8:9">
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+    </row>
+    <row r="21" spans="8:9">
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+    </row>
+    <row r="22" spans="8:9">
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+    </row>
+    <row r="23" spans="8:9">
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+    </row>
+    <row r="24" spans="8:9">
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+    </row>
+    <row r="25" spans="8:9">
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+    </row>
+    <row r="26" spans="8:9">
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+    </row>
+    <row r="27" spans="8:9">
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+    </row>
+    <row r="28" spans="8:9">
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+    </row>
+    <row r="29" spans="8:9">
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+    </row>
+    <row r="30" spans="8:9">
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+    </row>
+    <row r="31" spans="8:9">
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+    </row>
+    <row r="32" spans="8:9">
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+    </row>
+    <row r="33" spans="8:9">
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+    </row>
+    <row r="34" spans="8:9">
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -5176,358 +7392,148 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="12" style="43" customWidth="1"/>
-    <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="43" customWidth="1"/>
-    <col min="7" max="7" width="11" style="43" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="43" customWidth="1"/>
-    <col min="9" max="9" width="11" style="43" customWidth="1"/>
-    <col min="10" max="10" width="20.25" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
-    <col min="12" max="12" width="12.08203125" style="43" customWidth="1"/>
-    <col min="13" max="13" width="12.75" style="43" customWidth="1"/>
-    <col min="14" max="14" width="14.58203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
+    <col min="2" max="2" width="14" style="43" customWidth="1"/>
+    <col min="3" max="3" width="15.75" style="43" customWidth="1"/>
+    <col min="4" max="4" width="10.75" style="43" customWidth="1"/>
+    <col min="5" max="5" width="12" style="43" customWidth="1"/>
+    <col min="6" max="6" width="37" style="43" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="43" customWidth="1"/>
+    <col min="8" max="8" width="20.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
         <v>842</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>874</v>
+        <v>843</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>875</v>
+        <v>844</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>876</v>
+        <v>845</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>877</v>
+        <v>846</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>878</v>
+        <v>693</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>879</v>
+        <v>847</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>880</v>
-      </c>
-      <c r="I1" s="43" t="s">
-        <v>881</v>
-      </c>
-      <c r="J1" s="43" t="s">
-        <v>882</v>
-      </c>
-      <c r="K1" s="43" t="s">
-        <v>883</v>
-      </c>
-      <c r="L1" s="43" t="s">
-        <v>884</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>885</v>
-      </c>
-      <c r="N1" s="43" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
         <v>629</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>889</v>
+        <v>851</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>890</v>
+        <v>852</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>891</v>
+        <v>702</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>892</v>
+        <v>853</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>893</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>894</v>
-      </c>
-      <c r="J2" s="43" t="s">
-        <v>895</v>
-      </c>
-      <c r="K2" s="43" t="s">
-        <v>896</v>
-      </c>
-      <c r="L2" s="43" t="s">
-        <v>897</v>
-      </c>
-      <c r="M2" s="43" t="s">
-        <v>898</v>
-      </c>
-      <c r="N2" s="43" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
         <v>855</v>
       </c>
-      <c r="B3" s="43">
-        <v>1</v>
+      <c r="B3" s="43" t="s">
+        <v>856</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>900</v>
+        <v>857</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>901</v>
+        <v>858</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>218</v>
+        <v>859</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>218</v>
+        <v>860</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="H3" s="43">
-        <v>0</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>901</v>
-      </c>
-      <c r="J3" s="43" t="s">
+      <c r="H3" s="43" t="s">
         <v>861</v>
       </c>
-      <c r="K3" s="43">
-        <v>1</v>
-      </c>
-      <c r="L3" s="43">
-        <v>1</v>
-      </c>
-      <c r="M3" s="43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
-        <v>855</v>
-      </c>
-      <c r="B4" s="43">
-        <v>2</v>
+        <v>862</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>863</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>902</v>
+        <v>857</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>903</v>
+        <v>858</v>
       </c>
       <c r="E4" s="43" t="s">
-        <v>218</v>
+        <v>864</v>
       </c>
       <c r="F4" s="43" t="s">
-        <v>218</v>
+        <v>865</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H4" s="43">
-        <v>0</v>
-      </c>
-      <c r="I4" s="43" t="s">
-        <v>901</v>
-      </c>
-      <c r="J4" s="43" t="s">
-        <v>861</v>
-      </c>
-      <c r="K4" s="43">
-        <v>1</v>
-      </c>
-      <c r="L4" s="43">
-        <v>0.7</v>
-      </c>
-      <c r="M4" s="43" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>866</v>
+      </c>
+      <c r="H4" s="43" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
-        <v>855</v>
-      </c>
-      <c r="B5" s="43">
-        <v>3</v>
+        <v>868</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>869</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>905</v>
+        <v>857</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>906</v>
+        <v>870</v>
       </c>
       <c r="E5" s="43" t="s">
-        <v>218</v>
+        <v>871</v>
       </c>
       <c r="F5" s="43" t="s">
-        <v>218</v>
+        <v>872</v>
       </c>
       <c r="G5" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="H5" s="43">
-        <v>0</v>
-      </c>
-      <c r="I5" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="J5" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="K5" s="43">
-        <v>0</v>
-      </c>
-      <c r="L5" s="43">
-        <v>1</v>
-      </c>
-      <c r="M5" s="43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="43" t="s">
-        <v>862</v>
-      </c>
-      <c r="B6" s="43">
-        <v>1</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>907</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>908</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>909</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>910</v>
-      </c>
-      <c r="H6" s="43">
-        <v>100</v>
-      </c>
-      <c r="I6" s="43" t="s">
-        <v>901</v>
-      </c>
-      <c r="J6" s="43" t="s">
-        <v>867</v>
-      </c>
-      <c r="K6" s="43">
-        <v>1</v>
-      </c>
-      <c r="L6" s="43">
-        <v>1</v>
-      </c>
-      <c r="M6" s="43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="43" t="s">
-        <v>862</v>
-      </c>
-      <c r="B7" s="43">
-        <v>2</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>911</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>906</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="G7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H7" s="43">
-        <v>0</v>
-      </c>
-      <c r="I7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="K7" s="43">
-        <v>0</v>
-      </c>
-      <c r="L7" s="43">
-        <v>1</v>
-      </c>
-      <c r="M7" s="43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="43" t="s">
-        <v>868</v>
-      </c>
-      <c r="B8" s="43">
-        <v>1</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>912</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>913</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H8" s="43">
-        <v>0</v>
-      </c>
-      <c r="I8" s="43" t="s">
-        <v>913</v>
-      </c>
-      <c r="J8" s="43" t="s">
-        <v>914</v>
-      </c>
-      <c r="K8" s="43">
-        <v>30</v>
-      </c>
-      <c r="L8" s="43">
-        <v>1</v>
-      </c>
-      <c r="M8" s="43" t="s">
-        <v>218</v>
+      <c r="H5" s="43" t="s">
+        <v>873</v>
       </c>
     </row>
   </sheetData>
@@ -5537,200 +7543,358 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="15.75" style="43" customWidth="1"/>
-    <col min="3" max="3" width="24.58203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="14" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
+    <col min="3" max="3" width="20.375" style="43" customWidth="1"/>
+    <col min="4" max="4" width="12" style="43" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.58203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="43" customWidth="1"/>
+    <col min="7" max="7" width="11" style="43" customWidth="1"/>
+    <col min="8" max="8" width="10.375" style="43" customWidth="1"/>
+    <col min="9" max="9" width="11" style="43" customWidth="1"/>
+    <col min="10" max="10" width="20.25" style="43" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
+    <col min="12" max="12" width="12.125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="12.75" style="43" customWidth="1"/>
+    <col min="14" max="14" width="14.625" style="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:14">
       <c r="A1" s="43" t="s">
-        <v>915</v>
+        <v>842</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>1</v>
+        <v>874</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>693</v>
+        <v>875</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>916</v>
+        <v>876</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>917</v>
+        <v>877</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>918</v>
+        <v>878</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>919</v>
+        <v>879</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>880</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>881</v>
+      </c>
+      <c r="J1" s="43" t="s">
+        <v>882</v>
+      </c>
+      <c r="K1" s="43" t="s">
+        <v>883</v>
+      </c>
+      <c r="L1" s="43" t="s">
+        <v>884</v>
+      </c>
+      <c r="M1" s="43" t="s">
+        <v>885</v>
+      </c>
+      <c r="N1" s="43" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="43" t="s">
-        <v>921</v>
+        <v>629</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>26</v>
+        <v>887</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>702</v>
+        <v>888</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>922</v>
+        <v>889</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>923</v>
+        <v>890</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>924</v>
+        <v>891</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>925</v>
+        <v>892</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>893</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>894</v>
+      </c>
+      <c r="J2" s="43" t="s">
+        <v>895</v>
+      </c>
+      <c r="K2" s="43" t="s">
+        <v>896</v>
+      </c>
+      <c r="L2" s="43" t="s">
+        <v>897</v>
+      </c>
+      <c r="M2" s="43" t="s">
+        <v>898</v>
+      </c>
+      <c r="N2" s="43" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="43" t="s">
-        <v>927</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>928</v>
+        <v>855</v>
+      </c>
+      <c r="B3" s="43">
+        <v>1</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>929</v>
+        <v>900</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>930</v>
+        <v>901</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>931</v>
-      </c>
-      <c r="F3" s="43">
-        <v>5</v>
+        <v>218</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>218</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>932</v>
+        <v>218</v>
       </c>
       <c r="H3" s="43">
+        <v>0</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>901</v>
+      </c>
+      <c r="J3" s="43" t="s">
+        <v>861</v>
+      </c>
+      <c r="K3" s="43">
+        <v>1</v>
+      </c>
+      <c r="L3" s="43">
+        <v>1</v>
+      </c>
+      <c r="M3" s="43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="43" t="s">
+        <v>855</v>
+      </c>
+      <c r="B4" s="43">
+        <v>2</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>902</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" s="43">
+        <v>0</v>
+      </c>
+      <c r="I4" s="43" t="s">
+        <v>901</v>
+      </c>
+      <c r="J4" s="43" t="s">
+        <v>861</v>
+      </c>
+      <c r="K4" s="43">
+        <v>1</v>
+      </c>
+      <c r="L4" s="43">
+        <v>0.7</v>
+      </c>
+      <c r="M4" s="43" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="43" t="s">
+        <v>855</v>
+      </c>
+      <c r="B5" s="43">
+        <v>3</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>905</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>906</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="H5" s="43">
+        <v>0</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="K5" s="43">
+        <v>0</v>
+      </c>
+      <c r="L5" s="43">
+        <v>1</v>
+      </c>
+      <c r="M5" s="43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="43" t="s">
+        <v>862</v>
+      </c>
+      <c r="B6" s="43">
+        <v>1</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>907</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>908</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>909</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>910</v>
+      </c>
+      <c r="H6" s="43">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="43" t="s">
-        <v>933</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>934</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>935</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>930</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>936</v>
-      </c>
-      <c r="F4" s="43">
-        <v>10</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="H4" s="43">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="43" t="s">
-        <v>937</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>938</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>939</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>930</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>940</v>
-      </c>
-      <c r="F5" s="43">
-        <v>1</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>941</v>
-      </c>
-      <c r="H5" s="43">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="43" t="s">
-        <v>942</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>943</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>944</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>945</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>946</v>
-      </c>
-      <c r="F6" s="43">
-        <v>3</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="H6" s="43">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="43" t="s">
+        <v>901</v>
+      </c>
+      <c r="J6" s="43" t="s">
+        <v>867</v>
+      </c>
+      <c r="K6" s="43">
+        <v>1</v>
+      </c>
+      <c r="L6" s="43">
+        <v>1</v>
+      </c>
+      <c r="M6" s="43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="43" t="s">
-        <v>947</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>948</v>
+        <v>862</v>
+      </c>
+      <c r="B7" s="43">
+        <v>2</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>949</v>
+        <v>911</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>950</v>
+        <v>906</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>951</v>
-      </c>
-      <c r="F7" s="43">
-        <v>1</v>
+        <v>218</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>218</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>941</v>
+        <v>218</v>
       </c>
       <c r="H7" s="43">
+        <v>0</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="J7" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="K7" s="43">
+        <v>0</v>
+      </c>
+      <c r="L7" s="43">
+        <v>1</v>
+      </c>
+      <c r="M7" s="43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="43" t="s">
+        <v>868</v>
+      </c>
+      <c r="B8" s="43">
+        <v>1</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>912</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>913</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="H8" s="43">
+        <v>0</v>
+      </c>
+      <c r="I8" s="43" t="s">
+        <v>913</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>914</v>
+      </c>
+      <c r="K8" s="43">
         <v>30</v>
+      </c>
+      <c r="L8" s="43">
+        <v>1</v>
+      </c>
+      <c r="M8" s="43" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -5740,12 +7904,215 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="43" customWidth="1"/>
+    <col min="3" max="3" width="24.625" style="43" customWidth="1"/>
+    <col min="4" max="4" width="14" style="43" customWidth="1"/>
+    <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="43" customWidth="1"/>
+    <col min="7" max="7" width="12.25" style="43" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="43" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="43" t="s">
+        <v>915</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>693</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>916</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>917</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>918</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="43" t="s">
+        <v>921</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>702</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>922</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>923</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>924</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>925</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="43" t="s">
+        <v>927</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>928</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>929</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>931</v>
+      </c>
+      <c r="F3" s="43">
+        <v>5</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>932</v>
+      </c>
+      <c r="H3" s="43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="43" t="s">
+        <v>933</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>935</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>936</v>
+      </c>
+      <c r="F4" s="43">
+        <v>10</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>932</v>
+      </c>
+      <c r="H4" s="43">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="43" t="s">
+        <v>937</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>938</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>939</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>940</v>
+      </c>
+      <c r="F5" s="43">
+        <v>1</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>941</v>
+      </c>
+      <c r="H5" s="43">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="43" t="s">
+        <v>942</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>943</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>944</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>946</v>
+      </c>
+      <c r="F6" s="43">
+        <v>3</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>932</v>
+      </c>
+      <c r="H6" s="43">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="43" t="s">
+        <v>947</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>948</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>949</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>950</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>951</v>
+      </c>
+      <c r="F7" s="43">
+        <v>1</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>941</v>
+      </c>
+      <c r="H7" s="43">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="3" width="15.58203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="80.33203125" style="43" customWidth="1"/>
+    <col min="1" max="3" width="15.625" style="43" customWidth="1"/>
+    <col min="4" max="4" width="80.375" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5954,19 +8321,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="43" customWidth="1"/>
     <col min="2" max="2" width="17.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="43" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="43" customWidth="1"/>
-    <col min="5" max="5" width="19.08203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.58203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="18.08203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="19.125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="43" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="43" customWidth="1"/>
     <col min="8" max="8" width="19.75" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.58203125" style="43" customWidth="1"/>
-    <col min="10" max="16" width="15.58203125" style="43" customWidth="1"/>
-    <col min="17" max="19" width="15.58203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.625" style="43" customWidth="1"/>
+    <col min="10" max="16" width="15.625" style="43" customWidth="1"/>
+    <col min="17" max="19" width="15.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -6341,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.5" thickBot="1">
+    <row r="7" spans="1:20" ht="17.25" thickBot="1">
       <c r="A7" s="9" t="s">
         <v>155</v>
       </c>
@@ -6682,28 +9049,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH288"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.875" style="43" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="43" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="43" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="11.375" style="43" customWidth="1"/>
     <col min="6" max="6" width="5.75" style="43" customWidth="1"/>
-    <col min="7" max="7" width="9.08203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="43" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" style="43" customWidth="1"/>
-    <col min="10" max="10" width="10.08203125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="10.58203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="15.375" style="43" customWidth="1"/>
+    <col min="10" max="10" width="10.125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="43" customWidth="1"/>
     <col min="12" max="12" width="30.25" style="43" customWidth="1"/>
-    <col min="13" max="13" width="18.08203125" style="43" customWidth="1"/>
-    <col min="14" max="14" width="18.83203125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="18.125" style="43" customWidth="1"/>
+    <col min="14" max="14" width="18.875" style="43" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="43" customWidth="1"/>
-    <col min="16" max="16" width="11.08203125" style="43" customWidth="1"/>
+    <col min="16" max="16" width="11.125" style="43" customWidth="1"/>
     <col min="17" max="17" width="19.75" style="43" customWidth="1"/>
-    <col min="18" max="18" width="44.08203125" style="43" customWidth="1"/>
-    <col min="19" max="19" width="99.83203125" style="43" customWidth="1"/>
-    <col min="20" max="20" width="99.83203125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="44.125" style="43" customWidth="1"/>
+    <col min="19" max="19" width="99.875" style="43" customWidth="1"/>
+    <col min="20" max="20" width="99.875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -12839,18 +15206,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="20.08203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.375" style="43" customWidth="1"/>
+    <col min="2" max="2" width="20.125" style="43" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="43" customWidth="1"/>
     <col min="4" max="4" width="12.75" style="43" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="43" customWidth="1"/>
     <col min="6" max="7" width="14.25" style="43" customWidth="1"/>
     <col min="8" max="8" width="11.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="12.58203125" style="43" customWidth="1"/>
-    <col min="10" max="10" width="17.83203125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="36.58203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.625" style="43" customWidth="1"/>
+    <col min="10" max="10" width="17.875" style="43" customWidth="1"/>
+    <col min="11" max="11" width="36.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13584,1135 +15951,85 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{691955B9-B5D3-4198-86F9-315C3F5DF400}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="21.58203125" style="43" customWidth="1"/>
-    <col min="3" max="3" width="18.58203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="13" style="43" customWidth="1"/>
-    <col min="5" max="6" width="19.25" style="43" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" style="43" customWidth="1"/>
-    <col min="9" max="9" width="14" style="43" customWidth="1"/>
-    <col min="10" max="10" width="19" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
-    <col min="12" max="12" width="9.58203125" style="43" customWidth="1"/>
-    <col min="13" max="13" width="44.08203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.25" customWidth="1"/>
+    <col min="2" max="2" width="23.125" customWidth="1"/>
+    <col min="3" max="3" width="26.625" customWidth="1"/>
+    <col min="4" max="4" width="42.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="24" t="s">
-        <v>489</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>490</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>491</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>464</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>492</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="24" t="s">
-        <v>493</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>494</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>495</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>496</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>497</v>
-      </c>
-      <c r="K2" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L2" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G3" s="9">
-        <v>1</v>
-      </c>
-      <c r="H3" s="9">
-        <v>1</v>
-      </c>
-      <c r="I3" s="9">
-        <v>0</v>
-      </c>
-      <c r="J3" s="9">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9">
-        <v>0</v>
-      </c>
-      <c r="L3" s="9">
-        <v>0</v>
-      </c>
-      <c r="M3" s="32" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>501</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G4" s="9">
+    <row r="1" spans="1:4">
+      <c r="A1" s="80" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C1" s="80" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="89" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B2" s="89" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="89" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D2" s="89" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="80" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B3" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="80">
+        <v>1</v>
+      </c>
+      <c r="D3" s="80" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="80" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B4" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="80">
         <v>2</v>
       </c>
-      <c r="H4" s="9">
-        <v>1</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9">
-        <v>0</v>
-      </c>
-      <c r="K4" s="9">
-        <v>0</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>503</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G5" s="9">
-        <v>2</v>
-      </c>
-      <c r="H5" s="9">
-        <v>1</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0</v>
-      </c>
-      <c r="K5" s="9">
-        <v>0</v>
-      </c>
-      <c r="L5" s="9">
-        <v>0</v>
-      </c>
-      <c r="M5" s="32" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>505</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G6" s="9">
+      <c r="D4" s="80" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="80" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B5" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="80">
         <v>3</v>
       </c>
-      <c r="H6" s="9">
-        <v>1</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9">
-        <v>0</v>
-      </c>
-      <c r="L6" s="9">
-        <v>0</v>
-      </c>
-      <c r="M6" s="32" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>507</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G7" s="9">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9">
-        <v>1</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="32" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>509</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G8" s="9">
-        <v>2</v>
-      </c>
-      <c r="H8" s="9">
-        <v>1</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0</v>
-      </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9">
-        <v>0</v>
-      </c>
-      <c r="M8" s="32" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>511</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G9" s="9">
-        <v>2</v>
-      </c>
-      <c r="H9" s="9">
-        <v>1</v>
-      </c>
-      <c r="I9" s="9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="9">
-        <v>0</v>
-      </c>
-      <c r="M9" s="32" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>513</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G10" s="9">
-        <v>3</v>
-      </c>
-      <c r="H10" s="9">
-        <v>1</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="32" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>515</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="9">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G11" s="9">
-        <v>1</v>
-      </c>
-      <c r="H11" s="9">
-        <v>1</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9">
-        <v>0</v>
-      </c>
-      <c r="M11" s="32" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>517</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>1</v>
-      </c>
-      <c r="I12" s="9">
-        <v>-3</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9">
-        <v>0</v>
-      </c>
-      <c r="M12" s="32" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>519</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>1</v>
-      </c>
-      <c r="I13" s="9">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9">
-        <v>0</v>
-      </c>
-      <c r="M13" s="32" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>521</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>1</v>
-      </c>
-      <c r="I14" s="9">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9">
-        <v>1</v>
-      </c>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0</v>
-      </c>
-      <c r="M14" s="32" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>523</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="9">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G15" s="9">
-        <v>0</v>
-      </c>
-      <c r="H15" s="9">
-        <v>1</v>
-      </c>
-      <c r="I15" s="9">
-        <v>0</v>
-      </c>
-      <c r="J15" s="9">
-        <v>0</v>
-      </c>
-      <c r="K15" s="9">
-        <v>0</v>
-      </c>
-      <c r="L15" s="9">
-        <v>0</v>
-      </c>
-      <c r="M15" s="32" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>525</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G16" s="9">
-        <v>1</v>
-      </c>
-      <c r="H16" s="9">
-        <v>1</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="34" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>527</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>1</v>
-      </c>
-      <c r="I17" s="9">
-        <v>-3</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9">
-        <v>0</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0</v>
-      </c>
-      <c r="M17" s="32" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>530</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>1</v>
-      </c>
-      <c r="I18" s="9">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9">
-        <v>0</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0</v>
-      </c>
-      <c r="M18" s="32" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>534</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D19" s="9">
-        <v>0</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G19" s="9">
-        <v>0</v>
-      </c>
-      <c r="H19" s="9">
-        <v>1</v>
-      </c>
-      <c r="I19" s="9">
-        <v>0</v>
-      </c>
-      <c r="J19" s="9">
-        <v>1</v>
-      </c>
-      <c r="K19" s="9">
-        <v>0</v>
-      </c>
-      <c r="L19" s="9">
-        <v>0</v>
-      </c>
-      <c r="M19" s="32" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="B20" s="33" t="s">
-        <v>537</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D20" s="9">
-        <v>0</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G20" s="9">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9">
-        <v>1</v>
-      </c>
-      <c r="I20" s="9">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-      <c r="L20" s="9">
-        <v>0</v>
-      </c>
-      <c r="M20" s="32" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="B21" s="33" t="s">
-        <v>540</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G21" s="9">
-        <v>1</v>
-      </c>
-      <c r="H21" s="9">
-        <v>1</v>
-      </c>
-      <c r="I21" s="9">
-        <v>0</v>
-      </c>
-      <c r="J21" s="9">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9">
-        <v>0</v>
-      </c>
-      <c r="M21" s="32" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>543</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D22" s="9">
-        <v>0</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G22" s="9">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>1</v>
-      </c>
-      <c r="I22" s="9">
-        <v>-3</v>
-      </c>
-      <c r="J22" s="9">
-        <v>0</v>
-      </c>
-      <c r="K22" s="9">
-        <v>0</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0</v>
-      </c>
-      <c r="M22" s="34" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="B23" s="33" t="s">
-        <v>546</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D23" s="9">
-        <v>0</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G23" s="9">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>1</v>
-      </c>
-      <c r="I23" s="9">
-        <v>0</v>
-      </c>
-      <c r="J23" s="9">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9">
-        <v>0</v>
-      </c>
-      <c r="L23" s="9">
-        <v>0</v>
-      </c>
-      <c r="M23" s="34" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>549</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D24" s="9">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>1</v>
-      </c>
-      <c r="I24" s="9">
-        <v>0</v>
-      </c>
-      <c r="J24" s="9">
-        <v>1</v>
-      </c>
-      <c r="K24" s="9">
-        <v>0</v>
-      </c>
-      <c r="L24" s="9">
-        <v>0</v>
-      </c>
-      <c r="M24" s="32" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>552</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D25" s="9">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G25" s="9">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>1</v>
-      </c>
-      <c r="I25" s="9">
-        <v>0</v>
-      </c>
-      <c r="J25" s="9">
-        <v>0</v>
-      </c>
-      <c r="K25" s="9">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9">
-        <v>0</v>
-      </c>
-      <c r="M25" s="32" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>555</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D26" s="9">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G26" s="9">
-        <v>0</v>
-      </c>
-      <c r="H26" s="9">
-        <v>0</v>
-      </c>
-      <c r="I26" s="9">
-        <v>0</v>
-      </c>
-      <c r="J26" s="9">
-        <v>0</v>
-      </c>
-      <c r="K26" s="9">
-        <v>0</v>
-      </c>
-      <c r="L26" s="9">
-        <v>0</v>
-      </c>
-      <c r="M26" s="81" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>558</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D27" s="9">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G27" s="9">
-        <v>0</v>
-      </c>
-      <c r="H27" s="9">
-        <v>0</v>
-      </c>
-      <c r="I27" s="9">
-        <v>0</v>
-      </c>
-      <c r="J27" s="9">
-        <v>0</v>
-      </c>
-      <c r="K27" s="9">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9">
-        <v>0</v>
-      </c>
-      <c r="M27" s="81" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="17.25" customHeight="1">
-      <c r="B28" s="31"/>
-    </row>
-    <row r="29" spans="1:13" ht="17.25" customHeight="1">
-      <c r="B29" s="7"/>
+      <c r="D5" s="80" t="s">
+        <v>1010</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -14721,20 +16038,1157 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:M29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="21.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="18.625" style="43" customWidth="1"/>
+    <col min="4" max="4" width="13" style="43" customWidth="1"/>
+    <col min="5" max="6" width="19.25" style="43" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="43" customWidth="1"/>
+    <col min="8" max="8" width="14.875" style="43" customWidth="1"/>
+    <col min="9" max="9" width="14" style="43" customWidth="1"/>
+    <col min="10" max="10" width="19" style="43" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="43" customWidth="1"/>
+    <col min="13" max="13" width="44.125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>495</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>497</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>498</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G3" s="9">
+        <v>1</v>
+      </c>
+      <c r="H3" s="9">
+        <v>1</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="9">
+        <v>0</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>501</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G4" s="9">
+        <v>2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>1</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G5" s="9">
+        <v>2</v>
+      </c>
+      <c r="H5" s="9">
+        <v>1</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9">
+        <v>0</v>
+      </c>
+      <c r="M5" s="32" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G6" s="9">
+        <v>3</v>
+      </c>
+      <c r="H6" s="9">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0</v>
+      </c>
+      <c r="M6" s="32" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>507</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G7" s="9">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9">
+        <v>0</v>
+      </c>
+      <c r="M7" s="32" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>509</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G8" s="9">
+        <v>2</v>
+      </c>
+      <c r="H8" s="9">
+        <v>1</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="32" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G9" s="9">
+        <v>2</v>
+      </c>
+      <c r="H9" s="9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="32" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G10" s="9">
+        <v>3</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="32" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1</v>
+      </c>
+      <c r="H11" s="9">
+        <v>1</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0</v>
+      </c>
+      <c r="M11" s="32" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
+      <c r="I12" s="9">
+        <v>-3</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="32" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>519</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>1</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="32" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>521</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>1</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>1</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="32" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>523</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>1</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0</v>
+      </c>
+      <c r="M15" s="32" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>525</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9">
+        <v>1</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="34" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>527</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>1</v>
+      </c>
+      <c r="I17" s="9">
+        <v>-3</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9">
+        <v>0</v>
+      </c>
+      <c r="M17" s="32" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>530</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>1</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="32" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>1</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9">
+        <v>1</v>
+      </c>
+      <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
+      <c r="M19" s="32" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>1</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="32" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G21" s="9">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9">
+        <v>1</v>
+      </c>
+      <c r="I21" s="9">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9">
+        <v>0</v>
+      </c>
+      <c r="M21" s="32" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>1</v>
+      </c>
+      <c r="I22" s="9">
+        <v>-3</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>546</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>1</v>
+      </c>
+      <c r="I23" s="9">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9">
+        <v>0</v>
+      </c>
+      <c r="M23" s="34" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>1</v>
+      </c>
+      <c r="I24" s="9">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <v>1</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="32" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>552</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>1</v>
+      </c>
+      <c r="I25" s="9">
+        <v>0</v>
+      </c>
+      <c r="J25" s="9">
+        <v>0</v>
+      </c>
+      <c r="K25" s="9">
+        <v>0</v>
+      </c>
+      <c r="L25" s="9">
+        <v>0</v>
+      </c>
+      <c r="M25" s="32" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
+      <c r="M26" s="81" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0</v>
+      </c>
+      <c r="J27" s="9">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9">
+        <v>0</v>
+      </c>
+      <c r="M27" s="81" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="17.25" customHeight="1">
+      <c r="B28" s="31"/>
+    </row>
+    <row r="29" spans="1:13" ht="17.25" customHeight="1">
+      <c r="B29" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AH91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="18.08203125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="18.125" style="43" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="43" customWidth="1"/>
-    <col min="5" max="5" width="34.58203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="11.08203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="43" customWidth="1"/>
+    <col min="4" max="4" width="17.375" style="43" customWidth="1"/>
+    <col min="5" max="5" width="34.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="43" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" style="43" customWidth="1"/>
-    <col min="9" max="9" width="10.58203125" style="43" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="43" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="43" customWidth="1"/>
+    <col min="10" max="10" width="14.875" style="43" customWidth="1"/>
     <col min="11" max="11" width="34.5" style="43" customWidth="1"/>
     <col min="12" max="12" width="20" style="43" customWidth="1"/>
   </cols>
@@ -16741,19 +19195,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="16" style="43" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="43" customWidth="1"/>
     <col min="4" max="4" width="16.25" style="43" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" customWidth="1"/>
-    <col min="6" max="6" width="12.08203125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="43" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="13.875" style="43" customWidth="1"/>
     <col min="10" max="10" width="19" style="43" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17743,14 +20197,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16.25" style="43" customWidth="1"/>
     <col min="2" max="2" width="11.25" style="43" customWidth="1"/>
-    <col min="3" max="6" width="14.58203125" style="43" customWidth="1"/>
+    <col min="3" max="6" width="14.625" style="43" customWidth="1"/>
     <col min="7" max="7" width="41.5" style="43" customWidth="1"/>
     <col min="8" max="11" width="41.5" style="3" customWidth="1"/>
   </cols>
@@ -18216,2319 +20670,4 @@
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AF32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
-  <cols>
-    <col min="1" max="1" width="9.33203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="18.58203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="43" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:32">
-      <c r="A1" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="17.25" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>743</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>744</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>746</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>753</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>760</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>762</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>766</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>768</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>769</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>771</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A3" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="B3" s="61" t="s">
-        <v>773</v>
-      </c>
-      <c r="C3" s="80" t="s">
-        <v>774</v>
-      </c>
-      <c r="D3" s="61" t="s">
-        <v>284</v>
-      </c>
-      <c r="E3" s="61" t="s">
-        <v>775</v>
-      </c>
-      <c r="F3" s="61" t="s">
-        <v>776</v>
-      </c>
-      <c r="G3" s="61" t="s">
-        <v>777</v>
-      </c>
-      <c r="H3" s="62">
-        <v>0</v>
-      </c>
-      <c r="I3" s="62">
-        <v>0</v>
-      </c>
-      <c r="J3" s="62">
-        <v>0</v>
-      </c>
-      <c r="K3" s="62">
-        <v>0</v>
-      </c>
-      <c r="L3" s="62">
-        <v>0</v>
-      </c>
-      <c r="M3" s="62">
-        <v>0</v>
-      </c>
-      <c r="N3" s="62">
-        <v>0</v>
-      </c>
-      <c r="O3" s="62">
-        <v>0</v>
-      </c>
-      <c r="P3" s="62">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="62">
-        <v>0</v>
-      </c>
-      <c r="R3" s="62">
-        <v>0</v>
-      </c>
-      <c r="S3" s="62">
-        <v>0</v>
-      </c>
-      <c r="T3" s="62">
-        <v>0</v>
-      </c>
-      <c r="U3" s="62">
-        <v>0</v>
-      </c>
-      <c r="V3" s="62">
-        <v>0</v>
-      </c>
-      <c r="W3" s="62">
-        <v>0</v>
-      </c>
-      <c r="X3" s="62">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="62">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A4" s="64" t="s">
-        <v>348</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>778</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9">
-        <v>0</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0</v>
-      </c>
-      <c r="P4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
-      </c>
-      <c r="R4" s="9">
-        <v>0</v>
-      </c>
-      <c r="S4" s="9">
-        <v>0</v>
-      </c>
-      <c r="T4" s="9">
-        <v>0</v>
-      </c>
-      <c r="U4" s="9">
-        <v>0</v>
-      </c>
-      <c r="V4" s="9">
-        <v>0</v>
-      </c>
-      <c r="W4" s="9">
-        <v>0</v>
-      </c>
-      <c r="X4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A5" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>782</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>784</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>786</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="9">
-        <v>0</v>
-      </c>
-      <c r="S5" s="9">
-        <v>0</v>
-      </c>
-      <c r="T5" s="9">
-        <v>0</v>
-      </c>
-      <c r="U5" s="9">
-        <v>0</v>
-      </c>
-      <c r="V5" s="9">
-        <v>0</v>
-      </c>
-      <c r="W5" s="9">
-        <v>0</v>
-      </c>
-      <c r="X5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A6" s="66" t="s">
-        <v>472</v>
-      </c>
-      <c r="B6" s="67" t="s">
-        <v>787</v>
-      </c>
-      <c r="C6" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D6" s="67" t="s">
-        <v>783</v>
-      </c>
-      <c r="E6" s="67" t="s">
-        <v>776</v>
-      </c>
-      <c r="F6" s="67" t="s">
-        <v>784</v>
-      </c>
-      <c r="G6" s="67" t="s">
-        <v>775</v>
-      </c>
-      <c r="H6" s="67" t="s">
-        <v>284</v>
-      </c>
-      <c r="I6" s="67" t="s">
-        <v>785</v>
-      </c>
-      <c r="J6" s="67" t="s">
-        <v>777</v>
-      </c>
-      <c r="K6" s="67" t="s">
-        <v>786</v>
-      </c>
-      <c r="L6" s="68">
-        <v>0</v>
-      </c>
-      <c r="M6" s="68">
-        <v>0</v>
-      </c>
-      <c r="N6" s="68">
-        <v>0</v>
-      </c>
-      <c r="O6" s="68">
-        <v>0</v>
-      </c>
-      <c r="P6" s="68">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="68">
-        <v>0</v>
-      </c>
-      <c r="R6" s="68">
-        <v>0</v>
-      </c>
-      <c r="S6" s="68">
-        <v>0</v>
-      </c>
-      <c r="T6" s="68">
-        <v>0</v>
-      </c>
-      <c r="U6" s="68">
-        <v>0</v>
-      </c>
-      <c r="V6" s="68">
-        <v>0</v>
-      </c>
-      <c r="W6" s="68">
-        <v>0</v>
-      </c>
-      <c r="X6" s="68">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="68">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A7" s="60" t="s">
-        <v>436</v>
-      </c>
-      <c r="B7" s="61" t="s">
-        <v>788</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>284</v>
-      </c>
-      <c r="E7" s="62">
-        <v>0</v>
-      </c>
-      <c r="F7" s="62">
-        <v>0</v>
-      </c>
-      <c r="G7" s="62">
-        <v>0</v>
-      </c>
-      <c r="H7" s="62">
-        <v>0</v>
-      </c>
-      <c r="I7" s="62">
-        <v>0</v>
-      </c>
-      <c r="J7" s="62">
-        <v>0</v>
-      </c>
-      <c r="K7" s="62">
-        <v>0</v>
-      </c>
-      <c r="L7" s="62">
-        <v>0</v>
-      </c>
-      <c r="M7" s="62">
-        <v>0</v>
-      </c>
-      <c r="N7" s="62">
-        <v>0</v>
-      </c>
-      <c r="O7" s="62">
-        <v>0</v>
-      </c>
-      <c r="P7" s="62">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="62">
-        <v>0</v>
-      </c>
-      <c r="R7" s="62">
-        <v>0</v>
-      </c>
-      <c r="S7" s="62">
-        <v>0</v>
-      </c>
-      <c r="T7" s="62">
-        <v>0</v>
-      </c>
-      <c r="U7" s="62">
-        <v>0</v>
-      </c>
-      <c r="V7" s="62">
-        <v>0</v>
-      </c>
-      <c r="W7" s="62">
-        <v>0</v>
-      </c>
-      <c r="X7" s="62">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="62">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A8" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F8" s="9">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>0</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0</v>
-      </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9">
-        <v>0</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9">
-        <v>0</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="9">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9">
-        <v>0</v>
-      </c>
-      <c r="T8" s="9">
-        <v>0</v>
-      </c>
-      <c r="U8" s="9">
-        <v>0</v>
-      </c>
-      <c r="V8" s="9">
-        <v>0</v>
-      </c>
-      <c r="W8" s="9">
-        <v>0</v>
-      </c>
-      <c r="X8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A9" s="64" t="s">
-        <v>318</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>790</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>0</v>
-      </c>
-      <c r="I9" s="9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="9">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9">
-        <v>0</v>
-      </c>
-      <c r="N9" s="9">
-        <v>0</v>
-      </c>
-      <c r="O9" s="9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="9">
-        <v>0</v>
-      </c>
-      <c r="S9" s="9">
-        <v>0</v>
-      </c>
-      <c r="T9" s="9">
-        <v>0</v>
-      </c>
-      <c r="U9" s="9">
-        <v>0</v>
-      </c>
-      <c r="V9" s="9">
-        <v>0</v>
-      </c>
-      <c r="W9" s="9">
-        <v>0</v>
-      </c>
-      <c r="X9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A10" s="64" t="s">
-        <v>293</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>792</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="9">
-        <v>0</v>
-      </c>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="9">
-        <v>0</v>
-      </c>
-      <c r="S10" s="9">
-        <v>0</v>
-      </c>
-      <c r="T10" s="9">
-        <v>0</v>
-      </c>
-      <c r="U10" s="9">
-        <v>0</v>
-      </c>
-      <c r="V10" s="9">
-        <v>0</v>
-      </c>
-      <c r="W10" s="9">
-        <v>0</v>
-      </c>
-      <c r="X10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A11" s="70" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>794</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>795</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9">
-        <v>0</v>
-      </c>
-      <c r="N11" s="9">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9">
-        <v>0</v>
-      </c>
-      <c r="P11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0</v>
-      </c>
-      <c r="R11" s="9">
-        <v>0</v>
-      </c>
-      <c r="S11" s="9">
-        <v>0</v>
-      </c>
-      <c r="T11" s="9">
-        <v>0</v>
-      </c>
-      <c r="U11" s="9">
-        <v>0</v>
-      </c>
-      <c r="V11" s="9">
-        <v>0</v>
-      </c>
-      <c r="W11" s="9">
-        <v>0</v>
-      </c>
-      <c r="X11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A12" s="64" t="s">
-        <v>274</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>796</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9">
-        <v>0</v>
-      </c>
-      <c r="O12" s="9">
-        <v>0</v>
-      </c>
-      <c r="P12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-      <c r="R12" s="9">
-        <v>0</v>
-      </c>
-      <c r="S12" s="9">
-        <v>0</v>
-      </c>
-      <c r="T12" s="9">
-        <v>0</v>
-      </c>
-      <c r="U12" s="9">
-        <v>0</v>
-      </c>
-      <c r="V12" s="9">
-        <v>0</v>
-      </c>
-      <c r="W12" s="9">
-        <v>0</v>
-      </c>
-      <c r="X12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A13" s="64" t="s">
-        <v>310</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>797</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="J13" s="9">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9">
-        <v>0</v>
-      </c>
-      <c r="N13" s="9">
-        <v>0</v>
-      </c>
-      <c r="O13" s="9">
-        <v>0</v>
-      </c>
-      <c r="P13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9">
-        <v>0</v>
-      </c>
-      <c r="S13" s="9">
-        <v>0</v>
-      </c>
-      <c r="T13" s="9">
-        <v>0</v>
-      </c>
-      <c r="U13" s="9">
-        <v>0</v>
-      </c>
-      <c r="V13" s="9">
-        <v>0</v>
-      </c>
-      <c r="W13" s="9">
-        <v>0</v>
-      </c>
-      <c r="X13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A14" s="64" t="s">
-        <v>379</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>799</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9">
-        <v>0</v>
-      </c>
-      <c r="P14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>0</v>
-      </c>
-      <c r="R14" s="9">
-        <v>0</v>
-      </c>
-      <c r="S14" s="9">
-        <v>0</v>
-      </c>
-      <c r="T14" s="9">
-        <v>0</v>
-      </c>
-      <c r="U14" s="9">
-        <v>0</v>
-      </c>
-      <c r="V14" s="9">
-        <v>0</v>
-      </c>
-      <c r="W14" s="9">
-        <v>0</v>
-      </c>
-      <c r="X14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A15" s="64" t="s">
-        <v>302</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="H15" s="9">
-        <v>0</v>
-      </c>
-      <c r="I15" s="9">
-        <v>0</v>
-      </c>
-      <c r="J15" s="9">
-        <v>0</v>
-      </c>
-      <c r="K15" s="9">
-        <v>0</v>
-      </c>
-      <c r="L15" s="9">
-        <v>0</v>
-      </c>
-      <c r="M15" s="9">
-        <v>0</v>
-      </c>
-      <c r="N15" s="9">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9">
-        <v>0</v>
-      </c>
-      <c r="P15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>0</v>
-      </c>
-      <c r="R15" s="9">
-        <v>0</v>
-      </c>
-      <c r="S15" s="9">
-        <v>0</v>
-      </c>
-      <c r="T15" s="9">
-        <v>0</v>
-      </c>
-      <c r="U15" s="9">
-        <v>0</v>
-      </c>
-      <c r="V15" s="9">
-        <v>0</v>
-      </c>
-      <c r="W15" s="9">
-        <v>0</v>
-      </c>
-      <c r="X15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A16" s="64" t="s">
-        <v>331</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>803</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
-        <v>0</v>
-      </c>
-      <c r="O16" s="9">
-        <v>0</v>
-      </c>
-      <c r="P16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>0</v>
-      </c>
-      <c r="R16" s="9">
-        <v>0</v>
-      </c>
-      <c r="S16" s="9">
-        <v>0</v>
-      </c>
-      <c r="T16" s="9">
-        <v>0</v>
-      </c>
-      <c r="U16" s="9">
-        <v>0</v>
-      </c>
-      <c r="V16" s="9">
-        <v>0</v>
-      </c>
-      <c r="W16" s="9">
-        <v>0</v>
-      </c>
-      <c r="X16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A17" s="64" t="s">
-        <v>286</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9">
-        <v>0</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9">
-        <v>0</v>
-      </c>
-      <c r="N17" s="9">
-        <v>0</v>
-      </c>
-      <c r="O17" s="9">
-        <v>0</v>
-      </c>
-      <c r="P17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>0</v>
-      </c>
-      <c r="R17" s="9">
-        <v>0</v>
-      </c>
-      <c r="S17" s="9">
-        <v>0</v>
-      </c>
-      <c r="T17" s="9">
-        <v>0</v>
-      </c>
-      <c r="U17" s="9">
-        <v>0</v>
-      </c>
-      <c r="V17" s="9">
-        <v>0</v>
-      </c>
-      <c r="W17" s="9">
-        <v>0</v>
-      </c>
-      <c r="X17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A18" s="64" t="s">
-        <v>336</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>805</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>799</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9">
-        <v>0</v>
-      </c>
-      <c r="O18" s="9">
-        <v>0</v>
-      </c>
-      <c r="P18" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="9">
-        <v>0</v>
-      </c>
-      <c r="R18" s="9">
-        <v>0</v>
-      </c>
-      <c r="S18" s="9">
-        <v>0</v>
-      </c>
-      <c r="T18" s="9">
-        <v>0</v>
-      </c>
-      <c r="U18" s="9">
-        <v>0</v>
-      </c>
-      <c r="V18" s="9">
-        <v>0</v>
-      </c>
-      <c r="W18" s="9">
-        <v>0</v>
-      </c>
-      <c r="X18" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A19" s="66" t="s">
-        <v>340</v>
-      </c>
-      <c r="B19" s="67" t="s">
-        <v>806</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D19" s="67" t="s">
-        <v>284</v>
-      </c>
-      <c r="E19" s="67" t="s">
-        <v>785</v>
-      </c>
-      <c r="F19" s="67" t="s">
-        <v>791</v>
-      </c>
-      <c r="G19" s="67" t="s">
-        <v>285</v>
-      </c>
-      <c r="H19" s="67" t="s">
-        <v>800</v>
-      </c>
-      <c r="I19" s="68">
-        <v>0</v>
-      </c>
-      <c r="J19" s="68">
-        <v>0</v>
-      </c>
-      <c r="K19" s="68">
-        <v>0</v>
-      </c>
-      <c r="L19" s="68">
-        <v>0</v>
-      </c>
-      <c r="M19" s="68">
-        <v>0</v>
-      </c>
-      <c r="N19" s="68">
-        <v>0</v>
-      </c>
-      <c r="O19" s="68">
-        <v>0</v>
-      </c>
-      <c r="P19" s="68">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="68">
-        <v>0</v>
-      </c>
-      <c r="R19" s="68">
-        <v>0</v>
-      </c>
-      <c r="S19" s="68">
-        <v>0</v>
-      </c>
-      <c r="T19" s="68">
-        <v>0</v>
-      </c>
-      <c r="U19" s="68">
-        <v>0</v>
-      </c>
-      <c r="V19" s="68">
-        <v>0</v>
-      </c>
-      <c r="W19" s="68">
-        <v>0</v>
-      </c>
-      <c r="X19" s="68">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="68">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A20" s="71" t="s">
-        <v>392</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>807</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D20" s="61" t="s">
-        <v>774</v>
-      </c>
-      <c r="E20" s="62">
-        <v>0</v>
-      </c>
-      <c r="F20" s="62">
-        <v>0</v>
-      </c>
-      <c r="G20" s="62">
-        <v>0</v>
-      </c>
-      <c r="H20" s="62">
-        <v>0</v>
-      </c>
-      <c r="I20" s="62">
-        <v>0</v>
-      </c>
-      <c r="J20" s="62">
-        <v>0</v>
-      </c>
-      <c r="K20" s="62">
-        <v>0</v>
-      </c>
-      <c r="L20" s="62">
-        <v>0</v>
-      </c>
-      <c r="M20" s="62">
-        <v>0</v>
-      </c>
-      <c r="N20" s="62">
-        <v>0</v>
-      </c>
-      <c r="O20" s="62">
-        <v>0</v>
-      </c>
-      <c r="P20" s="62">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="62">
-        <v>0</v>
-      </c>
-      <c r="R20" s="62">
-        <v>0</v>
-      </c>
-      <c r="S20" s="62">
-        <v>0</v>
-      </c>
-      <c r="T20" s="62">
-        <v>0</v>
-      </c>
-      <c r="U20" s="62">
-        <v>0</v>
-      </c>
-      <c r="V20" s="62">
-        <v>0</v>
-      </c>
-      <c r="W20" s="62">
-        <v>0</v>
-      </c>
-      <c r="X20" s="62">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="62">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A21" s="64" t="s">
-        <v>474</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>808</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="H21" s="9">
-        <v>0</v>
-      </c>
-      <c r="I21" s="9">
-        <v>0</v>
-      </c>
-      <c r="J21" s="9">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-      <c r="N21" s="9">
-        <v>0</v>
-      </c>
-      <c r="O21" s="9">
-        <v>0</v>
-      </c>
-      <c r="P21" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>0</v>
-      </c>
-      <c r="R21" s="9">
-        <v>0</v>
-      </c>
-      <c r="S21" s="9">
-        <v>0</v>
-      </c>
-      <c r="T21" s="9">
-        <v>0</v>
-      </c>
-      <c r="U21" s="9">
-        <v>0</v>
-      </c>
-      <c r="V21" s="9">
-        <v>0</v>
-      </c>
-      <c r="W21" s="9">
-        <v>0</v>
-      </c>
-      <c r="X21" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A22" s="64" t="s">
-        <v>478</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>809</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>784</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>786</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9">
-        <v>0</v>
-      </c>
-      <c r="N22" s="9">
-        <v>0</v>
-      </c>
-      <c r="O22" s="9">
-        <v>0</v>
-      </c>
-      <c r="P22" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="9">
-        <v>0</v>
-      </c>
-      <c r="R22" s="9">
-        <v>0</v>
-      </c>
-      <c r="S22" s="9">
-        <v>0</v>
-      </c>
-      <c r="T22" s="9">
-        <v>0</v>
-      </c>
-      <c r="U22" s="9">
-        <v>0</v>
-      </c>
-      <c r="V22" s="9">
-        <v>0</v>
-      </c>
-      <c r="W22" s="9">
-        <v>0</v>
-      </c>
-      <c r="X22" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" ht="20.149999999999999" customHeight="1">
-      <c r="A23" s="72" t="s">
-        <v>221</v>
-      </c>
-      <c r="B23" s="67" t="s">
-        <v>531</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D23" s="68">
-        <v>0</v>
-      </c>
-      <c r="E23" s="68">
-        <v>0</v>
-      </c>
-      <c r="F23" s="68">
-        <v>0</v>
-      </c>
-      <c r="G23" s="68">
-        <v>0</v>
-      </c>
-      <c r="H23" s="68">
-        <v>0</v>
-      </c>
-      <c r="I23" s="68">
-        <v>0</v>
-      </c>
-      <c r="J23" s="68">
-        <v>0</v>
-      </c>
-      <c r="K23" s="68">
-        <v>0</v>
-      </c>
-      <c r="L23" s="68">
-        <v>0</v>
-      </c>
-      <c r="M23" s="68">
-        <v>0</v>
-      </c>
-      <c r="N23" s="68">
-        <v>0</v>
-      </c>
-      <c r="O23" s="68">
-        <v>0</v>
-      </c>
-      <c r="P23" s="68">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="68">
-        <v>0</v>
-      </c>
-      <c r="R23" s="68">
-        <v>0</v>
-      </c>
-      <c r="S23" s="68">
-        <v>0</v>
-      </c>
-      <c r="T23" s="68">
-        <v>0</v>
-      </c>
-      <c r="U23" s="68">
-        <v>0</v>
-      </c>
-      <c r="V23" s="68">
-        <v>0</v>
-      </c>
-      <c r="W23" s="68">
-        <v>0</v>
-      </c>
-      <c r="X23" s="68">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="68">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32">
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-    </row>
-    <row r="25" spans="1:32">
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-    </row>
-    <row r="26" spans="1:32">
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-    </row>
-    <row r="27" spans="1:32">
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-    </row>
-    <row r="28" spans="1:32">
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-    </row>
-    <row r="29" spans="1:32">
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-    </row>
-    <row r="30" spans="1:32">
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-    </row>
-    <row r="31" spans="1:32">
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-    </row>
-    <row r="32" spans="1:32">
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5D3AE7-8554-4D01-BB23-EA191C578268}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0925ADE7-1F66-4F7D-B78C-8D0FFE5F1DF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17535" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17540" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -19,22 +19,23 @@
     <sheet name="MonsterSkill" sheetId="4" r:id="rId4"/>
     <sheet name="MonsterPatternInfo" sheetId="15" r:id="rId5"/>
     <sheet name="Rune" sheetId="5" r:id="rId6"/>
-    <sheet name="Effect" sheetId="6" r:id="rId7"/>
-    <sheet name="Map" sheetId="7" r:id="rId8"/>
-    <sheet name="BattleMap" sheetId="8" r:id="rId9"/>
-    <sheet name="SkillRange" sheetId="9" r:id="rId10"/>
-    <sheet name="Relic" sheetId="10" r:id="rId11"/>
-    <sheet name="EventMaster" sheetId="11" r:id="rId12"/>
-    <sheet name="EventChoice" sheetId="12" r:id="rId13"/>
-    <sheet name="Quest" sheetId="13" r:id="rId14"/>
-    <sheet name="Item" sheetId="14" r:id="rId15"/>
+    <sheet name="GridEffect" sheetId="16" r:id="rId7"/>
+    <sheet name="Effect" sheetId="6" r:id="rId8"/>
+    <sheet name="Map" sheetId="7" r:id="rId9"/>
+    <sheet name="BattleMap" sheetId="8" r:id="rId10"/>
+    <sheet name="SkillRange" sheetId="9" r:id="rId11"/>
+    <sheet name="Relic" sheetId="10" r:id="rId12"/>
+    <sheet name="EventMaster" sheetId="11" r:id="rId13"/>
+    <sheet name="EventChoice" sheetId="12" r:id="rId14"/>
+    <sheet name="Quest" sheetId="13" r:id="rId15"/>
+    <sheet name="Item" sheetId="14" r:id="rId16"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="1015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="1036">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -3234,12 +3235,109 @@
     <t>내용</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
+  <si>
+    <t>그리드효과ID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>GR_debris</t>
+  </si>
+  <si>
+    <t>GridEffectID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>GR_thorn</t>
+  </si>
+  <si>
+    <t>GR_helmet</t>
+  </si>
+  <si>
+    <t>GR_bandage</t>
+  </si>
+  <si>
+    <t>GR_Poisson</t>
+  </si>
+  <si>
+    <t>잔해</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>가시</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>투구</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>붕대</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>독</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>통과유무</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passed</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>툴팁</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_Heal</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_Damage</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>치유</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">HP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 피해</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3349,6 +3447,12 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3624,7 +3728,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3881,6 +3985,15 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4096,23 +4209,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="12.08203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="11.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="11.58203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="13" style="43" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="43" customWidth="1"/>
-    <col min="8" max="8" width="22.375" style="43" customWidth="1"/>
-    <col min="9" max="9" width="11.375" style="43" customWidth="1"/>
+    <col min="5" max="5" width="17.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.08203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" style="43" customWidth="1"/>
     <col min="10" max="10" width="17" style="43" customWidth="1"/>
-    <col min="11" max="11" width="16.375" style="43" customWidth="1"/>
-    <col min="12" max="13" width="12.125" style="43" customWidth="1"/>
-    <col min="14" max="15" width="12.375" style="43" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" style="43" customWidth="1"/>
+    <col min="12" max="13" width="12.08203125" style="43" customWidth="1"/>
+    <col min="14" max="15" width="12.33203125" style="43" customWidth="1"/>
     <col min="16" max="17" width="14.5" style="43" customWidth="1"/>
-    <col min="18" max="19" width="14.125" style="43" customWidth="1"/>
+    <col min="18" max="19" width="14.08203125" style="43" customWidth="1"/>
     <col min="20" max="24" width="8.5" style="43" customWidth="1"/>
     <col min="25" max="25" width="58.25" style="3" customWidth="1"/>
   </cols>
@@ -4271,7 +4384,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="115.5">
+    <row r="3" spans="1:25" ht="119">
       <c r="A3" s="9" t="s">
         <v>50</v>
       </c>
@@ -4348,7 +4461,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="115.5">
+    <row r="4" spans="1:25" ht="102">
       <c r="A4" s="9" t="s">
         <v>67</v>
       </c>
@@ -4425,7 +4538,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="115.5">
+    <row r="5" spans="1:25" ht="119">
       <c r="A5" s="9" t="s">
         <v>84</v>
       </c>
@@ -4683,2314 +4796,474 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AF32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="9.375" style="43" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.875" style="43" customWidth="1"/>
+    <col min="1" max="1" width="16.25" style="43" customWidth="1"/>
+    <col min="2" max="2" width="11.25" style="43" customWidth="1"/>
+    <col min="3" max="6" width="14.58203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="41.5" style="43" customWidth="1"/>
+    <col min="8" max="11" width="41.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
-      <c r="A1" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="17.25" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="1" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A1" s="24" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>689</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>690</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>691</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>692</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>693</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>694</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>695</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>696</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A2" s="45" t="s">
+        <v>628</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>698</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>699</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>700</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>702</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>703</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>704</v>
+      </c>
+      <c r="J2" s="45" t="s">
+        <v>705</v>
+      </c>
+      <c r="K2" s="45" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A3" s="46" t="s">
+        <v>637</v>
+      </c>
+      <c r="B3" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="62">
+        <v>21</v>
+      </c>
+      <c r="D3" s="62">
+        <v>-1</v>
+      </c>
+      <c r="E3" s="62">
+        <v>-1</v>
+      </c>
+      <c r="F3" s="62">
+        <v>-1</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>707</v>
+      </c>
+      <c r="H3" s="83">
+        <v>1</v>
+      </c>
+      <c r="I3" s="83">
+        <v>60</v>
+      </c>
+      <c r="J3" s="83">
+        <v>30</v>
+      </c>
+      <c r="K3" s="83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A4" s="55" t="s">
+        <v>637</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="68">
+        <v>28</v>
+      </c>
+      <c r="D4" s="68">
+        <v>-1</v>
+      </c>
+      <c r="E4" s="68">
+        <v>-1</v>
+      </c>
+      <c r="F4" s="68">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A5" s="46" t="s">
+        <v>641</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="62">
         <v>26</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>743</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>744</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>746</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>753</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>760</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>762</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>766</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>768</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>769</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>771</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="B3" s="61" t="s">
-        <v>773</v>
-      </c>
-      <c r="C3" s="80" t="s">
-        <v>774</v>
-      </c>
-      <c r="D3" s="61" t="s">
-        <v>284</v>
-      </c>
-      <c r="E3" s="61" t="s">
-        <v>775</v>
-      </c>
-      <c r="F3" s="61" t="s">
-        <v>776</v>
-      </c>
-      <c r="G3" s="61" t="s">
-        <v>777</v>
-      </c>
-      <c r="H3" s="62">
-        <v>0</v>
-      </c>
-      <c r="I3" s="62">
-        <v>0</v>
-      </c>
-      <c r="J3" s="62">
-        <v>0</v>
-      </c>
-      <c r="K3" s="62">
-        <v>0</v>
-      </c>
-      <c r="L3" s="62">
-        <v>0</v>
-      </c>
-      <c r="M3" s="62">
-        <v>0</v>
-      </c>
-      <c r="N3" s="62">
-        <v>0</v>
-      </c>
-      <c r="O3" s="62">
-        <v>0</v>
-      </c>
-      <c r="P3" s="62">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="62">
-        <v>0</v>
-      </c>
-      <c r="R3" s="62">
-        <v>0</v>
-      </c>
-      <c r="S3" s="62">
-        <v>0</v>
-      </c>
-      <c r="T3" s="62">
-        <v>0</v>
-      </c>
-      <c r="U3" s="62">
-        <v>0</v>
-      </c>
-      <c r="V3" s="62">
-        <v>0</v>
-      </c>
-      <c r="W3" s="62">
-        <v>0</v>
-      </c>
-      <c r="X3" s="62">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="62">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="62">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="64" t="s">
-        <v>348</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>778</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9">
-        <v>0</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0</v>
-      </c>
-      <c r="P4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
-      </c>
-      <c r="R4" s="9">
-        <v>0</v>
-      </c>
-      <c r="S4" s="9">
-        <v>0</v>
-      </c>
-      <c r="T4" s="9">
-        <v>0</v>
-      </c>
-      <c r="U4" s="9">
-        <v>0</v>
-      </c>
-      <c r="V4" s="9">
-        <v>0</v>
-      </c>
-      <c r="W4" s="9">
-        <v>0</v>
-      </c>
-      <c r="X4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>782</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>784</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>786</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="9">
-        <v>0</v>
-      </c>
-      <c r="S5" s="9">
-        <v>0</v>
-      </c>
-      <c r="T5" s="9">
-        <v>0</v>
-      </c>
-      <c r="U5" s="9">
-        <v>0</v>
-      </c>
-      <c r="V5" s="9">
-        <v>0</v>
-      </c>
-      <c r="W5" s="9">
-        <v>0</v>
-      </c>
-      <c r="X5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="66" t="s">
-        <v>472</v>
-      </c>
-      <c r="B6" s="67" t="s">
-        <v>787</v>
-      </c>
-      <c r="C6" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D6" s="67" t="s">
-        <v>783</v>
-      </c>
-      <c r="E6" s="67" t="s">
-        <v>776</v>
-      </c>
-      <c r="F6" s="67" t="s">
-        <v>784</v>
-      </c>
-      <c r="G6" s="67" t="s">
-        <v>775</v>
-      </c>
-      <c r="H6" s="67" t="s">
-        <v>284</v>
-      </c>
-      <c r="I6" s="67" t="s">
-        <v>785</v>
-      </c>
-      <c r="J6" s="67" t="s">
-        <v>777</v>
-      </c>
-      <c r="K6" s="67" t="s">
-        <v>786</v>
-      </c>
-      <c r="L6" s="68">
-        <v>0</v>
-      </c>
-      <c r="M6" s="68">
-        <v>0</v>
-      </c>
-      <c r="N6" s="68">
-        <v>0</v>
-      </c>
-      <c r="O6" s="68">
-        <v>0</v>
-      </c>
-      <c r="P6" s="68">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="68">
-        <v>0</v>
-      </c>
-      <c r="R6" s="68">
-        <v>0</v>
-      </c>
-      <c r="S6" s="68">
-        <v>0</v>
-      </c>
-      <c r="T6" s="68">
-        <v>0</v>
-      </c>
-      <c r="U6" s="68">
-        <v>0</v>
-      </c>
-      <c r="V6" s="68">
-        <v>0</v>
-      </c>
-      <c r="W6" s="68">
-        <v>0</v>
-      </c>
-      <c r="X6" s="68">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="68">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="68">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="60" t="s">
-        <v>436</v>
-      </c>
-      <c r="B7" s="61" t="s">
-        <v>788</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>284</v>
+      <c r="D5" s="62">
+        <v>-1</v>
+      </c>
+      <c r="E5" s="62">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="62">
+        <v>-1</v>
+      </c>
+      <c r="G5" s="47" t="s">
+        <v>708</v>
+      </c>
+      <c r="H5" s="83">
+        <v>1</v>
+      </c>
+      <c r="I5" s="83">
+        <v>60</v>
+      </c>
+      <c r="J5" s="83">
+        <v>30</v>
+      </c>
+      <c r="K5" s="83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A6" s="55" t="s">
+        <v>641</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="68">
+        <v>23</v>
+      </c>
+      <c r="D6" s="68">
+        <v>-1</v>
+      </c>
+      <c r="E6" s="68">
+        <v>-1</v>
+      </c>
+      <c r="F6" s="68">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A7" s="49" t="s">
+        <v>644</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="62">
+        <v>25</v>
+      </c>
+      <c r="D7" s="62">
+        <v>-1</v>
       </c>
       <c r="E7" s="62">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F7" s="62">
-        <v>0</v>
-      </c>
-      <c r="G7" s="62">
-        <v>0</v>
-      </c>
-      <c r="H7" s="62">
-        <v>0</v>
-      </c>
-      <c r="I7" s="62">
-        <v>0</v>
-      </c>
-      <c r="J7" s="62">
-        <v>0</v>
-      </c>
-      <c r="K7" s="62">
-        <v>0</v>
-      </c>
-      <c r="L7" s="62">
-        <v>0</v>
-      </c>
-      <c r="M7" s="62">
-        <v>0</v>
-      </c>
-      <c r="N7" s="62">
-        <v>0</v>
-      </c>
-      <c r="O7" s="62">
-        <v>0</v>
-      </c>
-      <c r="P7" s="62">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="62">
-        <v>0</v>
-      </c>
-      <c r="R7" s="62">
-        <v>0</v>
-      </c>
-      <c r="S7" s="62">
-        <v>0</v>
-      </c>
-      <c r="T7" s="62">
-        <v>0</v>
-      </c>
-      <c r="U7" s="62">
-        <v>0</v>
-      </c>
-      <c r="V7" s="62">
-        <v>0</v>
-      </c>
-      <c r="W7" s="62">
-        <v>0</v>
-      </c>
-      <c r="X7" s="62">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="62">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="62">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>785</v>
+        <v>-1</v>
+      </c>
+      <c r="G7" s="51" t="s">
+        <v>709</v>
+      </c>
+      <c r="H7" s="84">
+        <v>1</v>
+      </c>
+      <c r="I7" s="84">
+        <v>60</v>
+      </c>
+      <c r="J7" s="84">
+        <v>30</v>
+      </c>
+      <c r="K7" s="84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A8" s="52" t="s">
+        <v>644</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="9">
+        <v>24</v>
+      </c>
+      <c r="D8" s="9">
+        <v>-1</v>
+      </c>
+      <c r="E8" s="9">
+        <v>-1</v>
       </c>
       <c r="F8" s="9">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>0</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0</v>
-      </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9">
-        <v>0</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9">
-        <v>0</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="9">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9">
-        <v>0</v>
-      </c>
-      <c r="T8" s="9">
-        <v>0</v>
-      </c>
-      <c r="U8" s="9">
-        <v>0</v>
-      </c>
-      <c r="V8" s="9">
-        <v>0</v>
-      </c>
-      <c r="W8" s="9">
-        <v>0</v>
-      </c>
-      <c r="X8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="64" t="s">
-        <v>318</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>790</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>0</v>
-      </c>
-      <c r="I9" s="9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="9">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9">
-        <v>0</v>
-      </c>
-      <c r="N9" s="9">
-        <v>0</v>
-      </c>
-      <c r="O9" s="9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="9">
-        <v>0</v>
-      </c>
-      <c r="S9" s="9">
-        <v>0</v>
-      </c>
-      <c r="T9" s="9">
-        <v>0</v>
-      </c>
-      <c r="U9" s="9">
-        <v>0</v>
-      </c>
-      <c r="V9" s="9">
-        <v>0</v>
-      </c>
-      <c r="W9" s="9">
-        <v>0</v>
-      </c>
-      <c r="X9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="64" t="s">
-        <v>293</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>792</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="9">
-        <v>0</v>
-      </c>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="9">
-        <v>0</v>
-      </c>
-      <c r="S10" s="9">
-        <v>0</v>
-      </c>
-      <c r="T10" s="9">
-        <v>0</v>
-      </c>
-      <c r="U10" s="9">
-        <v>0</v>
-      </c>
-      <c r="V10" s="9">
-        <v>0</v>
-      </c>
-      <c r="W10" s="9">
-        <v>0</v>
-      </c>
-      <c r="X10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="70" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>794</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>795</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9">
-        <v>0</v>
-      </c>
-      <c r="N11" s="9">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9">
-        <v>0</v>
-      </c>
-      <c r="P11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0</v>
-      </c>
-      <c r="R11" s="9">
-        <v>0</v>
-      </c>
-      <c r="S11" s="9">
-        <v>0</v>
-      </c>
-      <c r="T11" s="9">
-        <v>0</v>
-      </c>
-      <c r="U11" s="9">
-        <v>0</v>
-      </c>
-      <c r="V11" s="9">
-        <v>0</v>
-      </c>
-      <c r="W11" s="9">
-        <v>0</v>
-      </c>
-      <c r="X11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="64" t="s">
-        <v>274</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>796</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9">
-        <v>0</v>
-      </c>
-      <c r="O12" s="9">
-        <v>0</v>
-      </c>
-      <c r="P12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-      <c r="R12" s="9">
-        <v>0</v>
-      </c>
-      <c r="S12" s="9">
-        <v>0</v>
-      </c>
-      <c r="T12" s="9">
-        <v>0</v>
-      </c>
-      <c r="U12" s="9">
-        <v>0</v>
-      </c>
-      <c r="V12" s="9">
-        <v>0</v>
-      </c>
-      <c r="W12" s="9">
-        <v>0</v>
-      </c>
-      <c r="X12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="64" t="s">
-        <v>310</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>797</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="J13" s="9">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9">
-        <v>0</v>
-      </c>
-      <c r="N13" s="9">
-        <v>0</v>
-      </c>
-      <c r="O13" s="9">
-        <v>0</v>
-      </c>
-      <c r="P13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9">
-        <v>0</v>
-      </c>
-      <c r="S13" s="9">
-        <v>0</v>
-      </c>
-      <c r="T13" s="9">
-        <v>0</v>
-      </c>
-      <c r="U13" s="9">
-        <v>0</v>
-      </c>
-      <c r="V13" s="9">
-        <v>0</v>
-      </c>
-      <c r="W13" s="9">
-        <v>0</v>
-      </c>
-      <c r="X13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="64" t="s">
-        <v>379</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>799</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9">
-        <v>0</v>
-      </c>
-      <c r="P14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>0</v>
-      </c>
-      <c r="R14" s="9">
-        <v>0</v>
-      </c>
-      <c r="S14" s="9">
-        <v>0</v>
-      </c>
-      <c r="T14" s="9">
-        <v>0</v>
-      </c>
-      <c r="U14" s="9">
-        <v>0</v>
-      </c>
-      <c r="V14" s="9">
-        <v>0</v>
-      </c>
-      <c r="W14" s="9">
-        <v>0</v>
-      </c>
-      <c r="X14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="64" t="s">
-        <v>302</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="H15" s="9">
-        <v>0</v>
-      </c>
-      <c r="I15" s="9">
-        <v>0</v>
-      </c>
-      <c r="J15" s="9">
-        <v>0</v>
-      </c>
-      <c r="K15" s="9">
-        <v>0</v>
-      </c>
-      <c r="L15" s="9">
-        <v>0</v>
-      </c>
-      <c r="M15" s="9">
-        <v>0</v>
-      </c>
-      <c r="N15" s="9">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9">
-        <v>0</v>
-      </c>
-      <c r="P15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>0</v>
-      </c>
-      <c r="R15" s="9">
-        <v>0</v>
-      </c>
-      <c r="S15" s="9">
-        <v>0</v>
-      </c>
-      <c r="T15" s="9">
-        <v>0</v>
-      </c>
-      <c r="U15" s="9">
-        <v>0</v>
-      </c>
-      <c r="V15" s="9">
-        <v>0</v>
-      </c>
-      <c r="W15" s="9">
-        <v>0</v>
-      </c>
-      <c r="X15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="64" t="s">
-        <v>331</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>803</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
-        <v>0</v>
-      </c>
-      <c r="O16" s="9">
-        <v>0</v>
-      </c>
-      <c r="P16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>0</v>
-      </c>
-      <c r="R16" s="9">
-        <v>0</v>
-      </c>
-      <c r="S16" s="9">
-        <v>0</v>
-      </c>
-      <c r="T16" s="9">
-        <v>0</v>
-      </c>
-      <c r="U16" s="9">
-        <v>0</v>
-      </c>
-      <c r="V16" s="9">
-        <v>0</v>
-      </c>
-      <c r="W16" s="9">
-        <v>0</v>
-      </c>
-      <c r="X16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="64" t="s">
-        <v>286</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9">
-        <v>0</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9">
-        <v>0</v>
-      </c>
-      <c r="N17" s="9">
-        <v>0</v>
-      </c>
-      <c r="O17" s="9">
-        <v>0</v>
-      </c>
-      <c r="P17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>0</v>
-      </c>
-      <c r="R17" s="9">
-        <v>0</v>
-      </c>
-      <c r="S17" s="9">
-        <v>0</v>
-      </c>
-      <c r="T17" s="9">
-        <v>0</v>
-      </c>
-      <c r="U17" s="9">
-        <v>0</v>
-      </c>
-      <c r="V17" s="9">
-        <v>0</v>
-      </c>
-      <c r="W17" s="9">
-        <v>0</v>
-      </c>
-      <c r="X17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="64" t="s">
-        <v>336</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>805</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>799</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9">
-        <v>0</v>
-      </c>
-      <c r="O18" s="9">
-        <v>0</v>
-      </c>
-      <c r="P18" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="9">
-        <v>0</v>
-      </c>
-      <c r="R18" s="9">
-        <v>0</v>
-      </c>
-      <c r="S18" s="9">
-        <v>0</v>
-      </c>
-      <c r="T18" s="9">
-        <v>0</v>
-      </c>
-      <c r="U18" s="9">
-        <v>0</v>
-      </c>
-      <c r="V18" s="9">
-        <v>0</v>
-      </c>
-      <c r="W18" s="9">
-        <v>0</v>
-      </c>
-      <c r="X18" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="66" t="s">
-        <v>340</v>
-      </c>
-      <c r="B19" s="67" t="s">
-        <v>806</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D19" s="67" t="s">
-        <v>284</v>
-      </c>
-      <c r="E19" s="67" t="s">
-        <v>785</v>
-      </c>
-      <c r="F19" s="67" t="s">
-        <v>791</v>
-      </c>
-      <c r="G19" s="67" t="s">
-        <v>285</v>
-      </c>
-      <c r="H19" s="67" t="s">
-        <v>800</v>
-      </c>
-      <c r="I19" s="68">
-        <v>0</v>
-      </c>
-      <c r="J19" s="68">
-        <v>0</v>
-      </c>
-      <c r="K19" s="68">
-        <v>0</v>
-      </c>
-      <c r="L19" s="68">
-        <v>0</v>
-      </c>
-      <c r="M19" s="68">
-        <v>0</v>
-      </c>
-      <c r="N19" s="68">
-        <v>0</v>
-      </c>
-      <c r="O19" s="68">
-        <v>0</v>
-      </c>
-      <c r="P19" s="68">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="68">
-        <v>0</v>
-      </c>
-      <c r="R19" s="68">
-        <v>0</v>
-      </c>
-      <c r="S19" s="68">
-        <v>0</v>
-      </c>
-      <c r="T19" s="68">
-        <v>0</v>
-      </c>
-      <c r="U19" s="68">
-        <v>0</v>
-      </c>
-      <c r="V19" s="68">
-        <v>0</v>
-      </c>
-      <c r="W19" s="68">
-        <v>0</v>
-      </c>
-      <c r="X19" s="68">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="68">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="68">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="71" t="s">
-        <v>392</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>807</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D20" s="61" t="s">
-        <v>774</v>
-      </c>
-      <c r="E20" s="62">
-        <v>0</v>
-      </c>
-      <c r="F20" s="62">
-        <v>0</v>
-      </c>
-      <c r="G20" s="62">
-        <v>0</v>
-      </c>
-      <c r="H20" s="62">
-        <v>0</v>
-      </c>
-      <c r="I20" s="62">
-        <v>0</v>
-      </c>
-      <c r="J20" s="62">
-        <v>0</v>
-      </c>
-      <c r="K20" s="62">
-        <v>0</v>
-      </c>
-      <c r="L20" s="62">
-        <v>0</v>
-      </c>
-      <c r="M20" s="62">
-        <v>0</v>
-      </c>
-      <c r="N20" s="62">
-        <v>0</v>
-      </c>
-      <c r="O20" s="62">
-        <v>0</v>
-      </c>
-      <c r="P20" s="62">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="62">
-        <v>0</v>
-      </c>
-      <c r="R20" s="62">
-        <v>0</v>
-      </c>
-      <c r="S20" s="62">
-        <v>0</v>
-      </c>
-      <c r="T20" s="62">
-        <v>0</v>
-      </c>
-      <c r="U20" s="62">
-        <v>0</v>
-      </c>
-      <c r="V20" s="62">
-        <v>0</v>
-      </c>
-      <c r="W20" s="62">
-        <v>0</v>
-      </c>
-      <c r="X20" s="62">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="62">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="62">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="64" t="s">
-        <v>474</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>808</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="H21" s="9">
-        <v>0</v>
-      </c>
-      <c r="I21" s="9">
-        <v>0</v>
-      </c>
-      <c r="J21" s="9">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-      <c r="N21" s="9">
-        <v>0</v>
-      </c>
-      <c r="O21" s="9">
-        <v>0</v>
-      </c>
-      <c r="P21" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>0</v>
-      </c>
-      <c r="R21" s="9">
-        <v>0</v>
-      </c>
-      <c r="S21" s="9">
-        <v>0</v>
-      </c>
-      <c r="T21" s="9">
-        <v>0</v>
-      </c>
-      <c r="U21" s="9">
-        <v>0</v>
-      </c>
-      <c r="V21" s="9">
-        <v>0</v>
-      </c>
-      <c r="W21" s="9">
-        <v>0</v>
-      </c>
-      <c r="X21" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="64" t="s">
-        <v>478</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>809</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>784</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>786</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9">
-        <v>0</v>
-      </c>
-      <c r="N22" s="9">
-        <v>0</v>
-      </c>
-      <c r="O22" s="9">
-        <v>0</v>
-      </c>
-      <c r="P22" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="9">
-        <v>0</v>
-      </c>
-      <c r="R22" s="9">
-        <v>0</v>
-      </c>
-      <c r="S22" s="9">
-        <v>0</v>
-      </c>
-      <c r="T22" s="9">
-        <v>0</v>
-      </c>
-      <c r="U22" s="9">
-        <v>0</v>
-      </c>
-      <c r="V22" s="9">
-        <v>0</v>
-      </c>
-      <c r="W22" s="9">
-        <v>0</v>
-      </c>
-      <c r="X22" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="72" t="s">
-        <v>221</v>
-      </c>
-      <c r="B23" s="67" t="s">
-        <v>531</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>774</v>
-      </c>
-      <c r="D23" s="68">
-        <v>0</v>
-      </c>
-      <c r="E23" s="68">
-        <v>0</v>
-      </c>
-      <c r="F23" s="68">
-        <v>0</v>
-      </c>
-      <c r="G23" s="68">
-        <v>0</v>
-      </c>
-      <c r="H23" s="68">
-        <v>0</v>
-      </c>
-      <c r="I23" s="68">
-        <v>0</v>
-      </c>
-      <c r="J23" s="68">
-        <v>0</v>
-      </c>
-      <c r="K23" s="68">
-        <v>0</v>
-      </c>
-      <c r="L23" s="68">
-        <v>0</v>
-      </c>
-      <c r="M23" s="68">
-        <v>0</v>
-      </c>
-      <c r="N23" s="68">
-        <v>0</v>
-      </c>
-      <c r="O23" s="68">
-        <v>0</v>
-      </c>
-      <c r="P23" s="68">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="68">
-        <v>0</v>
-      </c>
-      <c r="R23" s="68">
-        <v>0</v>
-      </c>
-      <c r="S23" s="68">
-        <v>0</v>
-      </c>
-      <c r="T23" s="68">
-        <v>0</v>
-      </c>
-      <c r="U23" s="68">
-        <v>0</v>
-      </c>
-      <c r="V23" s="68">
-        <v>0</v>
-      </c>
-      <c r="W23" s="68">
-        <v>0</v>
-      </c>
-      <c r="X23" s="68">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="68">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="68">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32">
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-    </row>
-    <row r="25" spans="1:32">
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-    </row>
-    <row r="26" spans="1:32">
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-    </row>
-    <row r="27" spans="1:32">
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-    </row>
-    <row r="28" spans="1:32">
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-    </row>
-    <row r="29" spans="1:32">
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-    </row>
-    <row r="30" spans="1:32">
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-    </row>
-    <row r="31" spans="1:32">
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-    </row>
-    <row r="32" spans="1:32">
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-    </row>
+        <v>-1</v>
+      </c>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A9" s="55" t="s">
+        <v>644</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="68">
+        <v>27</v>
+      </c>
+      <c r="D9" s="68">
+        <v>-1</v>
+      </c>
+      <c r="E9" s="68">
+        <v>-1</v>
+      </c>
+      <c r="F9" s="68">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+    </row>
+    <row r="10" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A10" s="49" t="s">
+        <v>647</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="62">
+        <v>34</v>
+      </c>
+      <c r="D10" s="62">
+        <v>-1</v>
+      </c>
+      <c r="E10" s="62">
+        <v>-1</v>
+      </c>
+      <c r="F10" s="62">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>710</v>
+      </c>
+      <c r="H10" s="84">
+        <v>1</v>
+      </c>
+      <c r="I10" s="84">
+        <v>60</v>
+      </c>
+      <c r="J10" s="84">
+        <v>30</v>
+      </c>
+      <c r="K10" s="84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A11" s="55" t="s">
+        <v>647</v>
+      </c>
+      <c r="B11" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="68">
+        <v>27</v>
+      </c>
+      <c r="D11" s="68">
+        <v>-1</v>
+      </c>
+      <c r="E11" s="68">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="68">
+        <v>-1</v>
+      </c>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+    </row>
+    <row r="12" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A12" s="49" t="s">
+        <v>650</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="62">
+        <v>27</v>
+      </c>
+      <c r="D12" s="62">
+        <v>-1</v>
+      </c>
+      <c r="E12" s="62">
+        <v>-1</v>
+      </c>
+      <c r="F12" s="62">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>711</v>
+      </c>
+      <c r="H12" s="84">
+        <v>1</v>
+      </c>
+      <c r="I12" s="84">
+        <v>60</v>
+      </c>
+      <c r="J12" s="84">
+        <v>30</v>
+      </c>
+      <c r="K12" s="84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A13" s="56" t="s">
+        <v>650</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="9">
+        <v>24</v>
+      </c>
+      <c r="D13" s="9">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1</v>
+      </c>
+      <c r="F13" s="9">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+    </row>
+    <row r="14" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A14" s="55" t="s">
+        <v>650</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="68">
+        <v>33</v>
+      </c>
+      <c r="D14" s="68">
+        <v>-1</v>
+      </c>
+      <c r="E14" s="68">
+        <v>-1</v>
+      </c>
+      <c r="F14" s="68">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+    </row>
+    <row r="15" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A15" s="57" t="s">
+        <v>655</v>
+      </c>
+      <c r="B15" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="58">
+        <v>27</v>
+      </c>
+      <c r="D15" s="58">
+        <v>-1</v>
+      </c>
+      <c r="E15" s="58">
+        <v>-1</v>
+      </c>
+      <c r="F15" s="58">
+        <v>-1</v>
+      </c>
+      <c r="G15" s="59" t="s">
+        <v>712</v>
+      </c>
+      <c r="H15" s="85">
+        <v>1</v>
+      </c>
+      <c r="I15" s="85">
+        <v>60</v>
+      </c>
+      <c r="J15" s="85">
+        <v>30</v>
+      </c>
+      <c r="K15" s="85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="16.5" customHeight="1"/>
+    <row r="17" ht="16.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6998,392 +5271,2313 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:AF32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
-    <col min="2" max="2" width="22.875" style="43" customWidth="1"/>
-    <col min="3" max="4" width="19.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="20.125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="18.625" style="43" customWidth="1"/>
-    <col min="7" max="7" width="57.25" style="43" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="18.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" style="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="24" t="s">
-        <v>810</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>464</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="75" t="s">
-        <v>811</v>
-      </c>
-      <c r="B2" s="75" t="s">
+    <row r="1" spans="1:32">
+      <c r="A1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="17.25" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="75" t="s">
-        <v>199</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="76" t="s">
-        <v>468</v>
-      </c>
-      <c r="H2" s="43"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="B3" s="73" t="s">
-        <v>813</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="73">
-        <v>1</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>814</v>
-      </c>
-      <c r="H3" s="43"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="B4" s="73" t="s">
-        <v>816</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4" s="73">
-        <v>1</v>
-      </c>
-      <c r="G4" s="74" t="s">
-        <v>817</v>
-      </c>
-      <c r="H4" s="43"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="B5" s="73" t="s">
-        <v>819</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="F5" s="73">
-        <v>1</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>820</v>
-      </c>
-      <c r="H5" s="43"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="B6" s="73" t="s">
-        <v>822</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E6" s="1">
-        <v>-2</v>
-      </c>
-      <c r="F6" s="73">
-        <v>1</v>
-      </c>
-      <c r="G6" s="73" t="s">
-        <v>823</v>
-      </c>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="B7" s="73" t="s">
-        <v>825</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="73">
-        <v>1</v>
-      </c>
-      <c r="G7" s="74" t="s">
-        <v>826</v>
-      </c>
-      <c r="H7" s="43"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="B8" s="73" t="s">
-        <v>828</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="73">
-        <v>1</v>
-      </c>
-      <c r="G8" s="74" t="s">
-        <v>829</v>
-      </c>
-      <c r="H8" s="43"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>831</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="73">
-        <v>1</v>
-      </c>
-      <c r="G9" s="74" t="s">
-        <v>832</v>
-      </c>
-      <c r="H9" s="43"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="B10" s="73" t="s">
-        <v>834</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="73">
-        <v>1</v>
-      </c>
-      <c r="G10" s="74" t="s">
-        <v>835</v>
-      </c>
-      <c r="H10" s="43"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="B11" s="73" t="s">
-        <v>837</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="73">
-        <v>1</v>
-      </c>
-      <c r="G11" s="73" t="s">
-        <v>838</v>
-      </c>
-      <c r="H11" s="43"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="B12" s="73" t="s">
-        <v>840</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="73">
-        <v>1</v>
-      </c>
-      <c r="G12" s="73" t="s">
-        <v>841</v>
-      </c>
-      <c r="H12" s="43"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-    </row>
-    <row r="17" spans="8:9">
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-    </row>
-    <row r="18" spans="8:9">
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-    </row>
-    <row r="19" spans="8:9">
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-    </row>
-    <row r="20" spans="8:9">
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-    </row>
-    <row r="21" spans="8:9">
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-    </row>
-    <row r="22" spans="8:9">
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-    </row>
-    <row r="23" spans="8:9">
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-    </row>
-    <row r="24" spans="8:9">
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-    </row>
-    <row r="25" spans="8:9">
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-    </row>
-    <row r="26" spans="8:9">
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-    </row>
-    <row r="27" spans="8:9">
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-    </row>
-    <row r="28" spans="8:9">
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-    </row>
-    <row r="29" spans="8:9">
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-    </row>
-    <row r="30" spans="8:9">
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-    </row>
-    <row r="31" spans="8:9">
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-    </row>
-    <row r="32" spans="8:9">
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-    </row>
-    <row r="33" spans="8:9">
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-    </row>
-    <row r="34" spans="8:9">
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
+      <c r="C2" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A3" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>773</v>
+      </c>
+      <c r="C3" s="80" t="s">
+        <v>774</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>284</v>
+      </c>
+      <c r="E3" s="61" t="s">
+        <v>775</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>776</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>777</v>
+      </c>
+      <c r="H3" s="62">
+        <v>0</v>
+      </c>
+      <c r="I3" s="62">
+        <v>0</v>
+      </c>
+      <c r="J3" s="62">
+        <v>0</v>
+      </c>
+      <c r="K3" s="62">
+        <v>0</v>
+      </c>
+      <c r="L3" s="62">
+        <v>0</v>
+      </c>
+      <c r="M3" s="62">
+        <v>0</v>
+      </c>
+      <c r="N3" s="62">
+        <v>0</v>
+      </c>
+      <c r="O3" s="62">
+        <v>0</v>
+      </c>
+      <c r="P3" s="62">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="62">
+        <v>0</v>
+      </c>
+      <c r="R3" s="62">
+        <v>0</v>
+      </c>
+      <c r="S3" s="62">
+        <v>0</v>
+      </c>
+      <c r="T3" s="62">
+        <v>0</v>
+      </c>
+      <c r="U3" s="62">
+        <v>0</v>
+      </c>
+      <c r="V3" s="62">
+        <v>0</v>
+      </c>
+      <c r="W3" s="62">
+        <v>0</v>
+      </c>
+      <c r="X3" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="62">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="62">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A4" s="64" t="s">
+        <v>348</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
+      <c r="R4" s="9">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9">
+        <v>0</v>
+      </c>
+      <c r="T4" s="9">
+        <v>0</v>
+      </c>
+      <c r="U4" s="9">
+        <v>0</v>
+      </c>
+      <c r="V4" s="9">
+        <v>0</v>
+      </c>
+      <c r="W4" s="9">
+        <v>0</v>
+      </c>
+      <c r="X4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A5" s="64" t="s">
+        <v>401</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0</v>
+      </c>
+      <c r="S5" s="9">
+        <v>0</v>
+      </c>
+      <c r="T5" s="9">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9">
+        <v>0</v>
+      </c>
+      <c r="V5" s="9">
+        <v>0</v>
+      </c>
+      <c r="W5" s="9">
+        <v>0</v>
+      </c>
+      <c r="X5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A6" s="66" t="s">
+        <v>472</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>787</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D6" s="67" t="s">
+        <v>783</v>
+      </c>
+      <c r="E6" s="67" t="s">
+        <v>776</v>
+      </c>
+      <c r="F6" s="67" t="s">
+        <v>784</v>
+      </c>
+      <c r="G6" s="67" t="s">
+        <v>775</v>
+      </c>
+      <c r="H6" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="I6" s="67" t="s">
+        <v>785</v>
+      </c>
+      <c r="J6" s="67" t="s">
+        <v>777</v>
+      </c>
+      <c r="K6" s="67" t="s">
+        <v>786</v>
+      </c>
+      <c r="L6" s="68">
+        <v>0</v>
+      </c>
+      <c r="M6" s="68">
+        <v>0</v>
+      </c>
+      <c r="N6" s="68">
+        <v>0</v>
+      </c>
+      <c r="O6" s="68">
+        <v>0</v>
+      </c>
+      <c r="P6" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="68">
+        <v>0</v>
+      </c>
+      <c r="R6" s="68">
+        <v>0</v>
+      </c>
+      <c r="S6" s="68">
+        <v>0</v>
+      </c>
+      <c r="T6" s="68">
+        <v>0</v>
+      </c>
+      <c r="U6" s="68">
+        <v>0</v>
+      </c>
+      <c r="V6" s="68">
+        <v>0</v>
+      </c>
+      <c r="W6" s="68">
+        <v>0</v>
+      </c>
+      <c r="X6" s="68">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="68">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="68">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A7" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>788</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7" s="62">
+        <v>0</v>
+      </c>
+      <c r="F7" s="62">
+        <v>0</v>
+      </c>
+      <c r="G7" s="62">
+        <v>0</v>
+      </c>
+      <c r="H7" s="62">
+        <v>0</v>
+      </c>
+      <c r="I7" s="62">
+        <v>0</v>
+      </c>
+      <c r="J7" s="62">
+        <v>0</v>
+      </c>
+      <c r="K7" s="62">
+        <v>0</v>
+      </c>
+      <c r="L7" s="62">
+        <v>0</v>
+      </c>
+      <c r="M7" s="62">
+        <v>0</v>
+      </c>
+      <c r="N7" s="62">
+        <v>0</v>
+      </c>
+      <c r="O7" s="62">
+        <v>0</v>
+      </c>
+      <c r="P7" s="62">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="62">
+        <v>0</v>
+      </c>
+      <c r="R7" s="62">
+        <v>0</v>
+      </c>
+      <c r="S7" s="62">
+        <v>0</v>
+      </c>
+      <c r="T7" s="62">
+        <v>0</v>
+      </c>
+      <c r="U7" s="62">
+        <v>0</v>
+      </c>
+      <c r="V7" s="62">
+        <v>0</v>
+      </c>
+      <c r="W7" s="62">
+        <v>0</v>
+      </c>
+      <c r="X7" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="62">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A8" s="64" t="s">
+        <v>367</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9">
+        <v>0</v>
+      </c>
+      <c r="T8" s="9">
+        <v>0</v>
+      </c>
+      <c r="U8" s="9">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9">
+        <v>0</v>
+      </c>
+      <c r="W8" s="9">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A9" s="64" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>0</v>
+      </c>
+      <c r="S9" s="9">
+        <v>0</v>
+      </c>
+      <c r="T9" s="9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0</v>
+      </c>
+      <c r="W9" s="9">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A10" s="64" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
+      </c>
+      <c r="S10" s="9">
+        <v>0</v>
+      </c>
+      <c r="T10" s="9">
+        <v>0</v>
+      </c>
+      <c r="U10" s="9">
+        <v>0</v>
+      </c>
+      <c r="V10" s="9">
+        <v>0</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A11" s="70" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9">
+        <v>0</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A12" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0</v>
+      </c>
+      <c r="S12" s="9">
+        <v>0</v>
+      </c>
+      <c r="T12" s="9">
+        <v>0</v>
+      </c>
+      <c r="U12" s="9">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A13" s="64" t="s">
+        <v>310</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0</v>
+      </c>
+      <c r="S13" s="9">
+        <v>0</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A14" s="64" t="s">
+        <v>379</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9">
+        <v>0</v>
+      </c>
+      <c r="V14" s="9">
+        <v>0</v>
+      </c>
+      <c r="W14" s="9">
+        <v>0</v>
+      </c>
+      <c r="X14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A15" s="64" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9">
+        <v>0</v>
+      </c>
+      <c r="S15" s="9">
+        <v>0</v>
+      </c>
+      <c r="T15" s="9">
+        <v>0</v>
+      </c>
+      <c r="U15" s="9">
+        <v>0</v>
+      </c>
+      <c r="V15" s="9">
+        <v>0</v>
+      </c>
+      <c r="W15" s="9">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A16" s="64" t="s">
+        <v>331</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
+      </c>
+      <c r="P16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9">
+        <v>0</v>
+      </c>
+      <c r="S16" s="9">
+        <v>0</v>
+      </c>
+      <c r="T16" s="9">
+        <v>0</v>
+      </c>
+      <c r="U16" s="9">
+        <v>0</v>
+      </c>
+      <c r="V16" s="9">
+        <v>0</v>
+      </c>
+      <c r="W16" s="9">
+        <v>0</v>
+      </c>
+      <c r="X16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A17" s="64" t="s">
+        <v>286</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9">
+        <v>0</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0</v>
+      </c>
+      <c r="P17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9">
+        <v>0</v>
+      </c>
+      <c r="S17" s="9">
+        <v>0</v>
+      </c>
+      <c r="T17" s="9">
+        <v>0</v>
+      </c>
+      <c r="U17" s="9">
+        <v>0</v>
+      </c>
+      <c r="V17" s="9">
+        <v>0</v>
+      </c>
+      <c r="W17" s="9">
+        <v>0</v>
+      </c>
+      <c r="X17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A18" s="64" t="s">
+        <v>336</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+      <c r="O18" s="9">
+        <v>0</v>
+      </c>
+      <c r="P18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>0</v>
+      </c>
+      <c r="R18" s="9">
+        <v>0</v>
+      </c>
+      <c r="S18" s="9">
+        <v>0</v>
+      </c>
+      <c r="T18" s="9">
+        <v>0</v>
+      </c>
+      <c r="U18" s="9">
+        <v>0</v>
+      </c>
+      <c r="V18" s="9">
+        <v>0</v>
+      </c>
+      <c r="W18" s="9">
+        <v>0</v>
+      </c>
+      <c r="X18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A19" s="66" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>806</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D19" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="E19" s="67" t="s">
+        <v>785</v>
+      </c>
+      <c r="F19" s="67" t="s">
+        <v>791</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>285</v>
+      </c>
+      <c r="H19" s="67" t="s">
+        <v>800</v>
+      </c>
+      <c r="I19" s="68">
+        <v>0</v>
+      </c>
+      <c r="J19" s="68">
+        <v>0</v>
+      </c>
+      <c r="K19" s="68">
+        <v>0</v>
+      </c>
+      <c r="L19" s="68">
+        <v>0</v>
+      </c>
+      <c r="M19" s="68">
+        <v>0</v>
+      </c>
+      <c r="N19" s="68">
+        <v>0</v>
+      </c>
+      <c r="O19" s="68">
+        <v>0</v>
+      </c>
+      <c r="P19" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="68">
+        <v>0</v>
+      </c>
+      <c r="R19" s="68">
+        <v>0</v>
+      </c>
+      <c r="S19" s="68">
+        <v>0</v>
+      </c>
+      <c r="T19" s="68">
+        <v>0</v>
+      </c>
+      <c r="U19" s="68">
+        <v>0</v>
+      </c>
+      <c r="V19" s="68">
+        <v>0</v>
+      </c>
+      <c r="W19" s="68">
+        <v>0</v>
+      </c>
+      <c r="X19" s="68">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="68">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="68">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A20" s="71" t="s">
+        <v>392</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>807</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>774</v>
+      </c>
+      <c r="E20" s="62">
+        <v>0</v>
+      </c>
+      <c r="F20" s="62">
+        <v>0</v>
+      </c>
+      <c r="G20" s="62">
+        <v>0</v>
+      </c>
+      <c r="H20" s="62">
+        <v>0</v>
+      </c>
+      <c r="I20" s="62">
+        <v>0</v>
+      </c>
+      <c r="J20" s="62">
+        <v>0</v>
+      </c>
+      <c r="K20" s="62">
+        <v>0</v>
+      </c>
+      <c r="L20" s="62">
+        <v>0</v>
+      </c>
+      <c r="M20" s="62">
+        <v>0</v>
+      </c>
+      <c r="N20" s="62">
+        <v>0</v>
+      </c>
+      <c r="O20" s="62">
+        <v>0</v>
+      </c>
+      <c r="P20" s="62">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="62">
+        <v>0</v>
+      </c>
+      <c r="R20" s="62">
+        <v>0</v>
+      </c>
+      <c r="S20" s="62">
+        <v>0</v>
+      </c>
+      <c r="T20" s="62">
+        <v>0</v>
+      </c>
+      <c r="U20" s="62">
+        <v>0</v>
+      </c>
+      <c r="V20" s="62">
+        <v>0</v>
+      </c>
+      <c r="W20" s="62">
+        <v>0</v>
+      </c>
+      <c r="X20" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="62">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="62">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A21" s="64" t="s">
+        <v>474</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="9">
+        <v>0</v>
+      </c>
+      <c r="P21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>0</v>
+      </c>
+      <c r="R21" s="9">
+        <v>0</v>
+      </c>
+      <c r="S21" s="9">
+        <v>0</v>
+      </c>
+      <c r="T21" s="9">
+        <v>0</v>
+      </c>
+      <c r="U21" s="9">
+        <v>0</v>
+      </c>
+      <c r="V21" s="9">
+        <v>0</v>
+      </c>
+      <c r="W21" s="9">
+        <v>0</v>
+      </c>
+      <c r="X21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A22" s="64" t="s">
+        <v>478</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+      <c r="O22" s="9">
+        <v>0</v>
+      </c>
+      <c r="P22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>0</v>
+      </c>
+      <c r="R22" s="9">
+        <v>0</v>
+      </c>
+      <c r="S22" s="9">
+        <v>0</v>
+      </c>
+      <c r="T22" s="9">
+        <v>0</v>
+      </c>
+      <c r="U22" s="9">
+        <v>0</v>
+      </c>
+      <c r="V22" s="9">
+        <v>0</v>
+      </c>
+      <c r="W22" s="9">
+        <v>0</v>
+      </c>
+      <c r="X22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" ht="20.149999999999999" customHeight="1">
+      <c r="A23" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>531</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="D23" s="68">
+        <v>0</v>
+      </c>
+      <c r="E23" s="68">
+        <v>0</v>
+      </c>
+      <c r="F23" s="68">
+        <v>0</v>
+      </c>
+      <c r="G23" s="68">
+        <v>0</v>
+      </c>
+      <c r="H23" s="68">
+        <v>0</v>
+      </c>
+      <c r="I23" s="68">
+        <v>0</v>
+      </c>
+      <c r="J23" s="68">
+        <v>0</v>
+      </c>
+      <c r="K23" s="68">
+        <v>0</v>
+      </c>
+      <c r="L23" s="68">
+        <v>0</v>
+      </c>
+      <c r="M23" s="68">
+        <v>0</v>
+      </c>
+      <c r="N23" s="68">
+        <v>0</v>
+      </c>
+      <c r="O23" s="68">
+        <v>0</v>
+      </c>
+      <c r="P23" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="68">
+        <v>0</v>
+      </c>
+      <c r="R23" s="68">
+        <v>0</v>
+      </c>
+      <c r="S23" s="68">
+        <v>0</v>
+      </c>
+      <c r="T23" s="68">
+        <v>0</v>
+      </c>
+      <c r="U23" s="68">
+        <v>0</v>
+      </c>
+      <c r="V23" s="68">
+        <v>0</v>
+      </c>
+      <c r="W23" s="68">
+        <v>0</v>
+      </c>
+      <c r="X23" s="68">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="68">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="68">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32">
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+    </row>
+    <row r="25" spans="1:32">
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+    </row>
+    <row r="27" spans="1:32">
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+    </row>
+    <row r="28" spans="1:32">
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+    </row>
+    <row r="29" spans="1:32">
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+    </row>
+    <row r="30" spans="1:32">
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+    </row>
+    <row r="31" spans="1:32">
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+    </row>
+    <row r="32" spans="1:32">
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -7392,149 +7586,392 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
-    <col min="2" max="2" width="14" style="43" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="43" customWidth="1"/>
-    <col min="4" max="4" width="10.75" style="43" customWidth="1"/>
-    <col min="5" max="5" width="12" style="43" customWidth="1"/>
-    <col min="6" max="6" width="37" style="43" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="43" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" style="43" customWidth="1"/>
+    <col min="3" max="4" width="19.5" style="43" customWidth="1"/>
+    <col min="5" max="5" width="20.08203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="18.58203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="57.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="43" t="s">
-        <v>842</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>843</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>844</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>845</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>846</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>693</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>847</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="43" t="s">
-        <v>629</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>849</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>850</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>851</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>852</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>702</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>853</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="43" t="s">
-        <v>855</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>856</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>857</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>858</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>859</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>860</v>
-      </c>
-      <c r="G3" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="43" t="s">
-        <v>862</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>863</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>857</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>858</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>864</v>
-      </c>
-      <c r="F4" s="43" t="s">
-        <v>865</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>866</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="43" t="s">
-        <v>868</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>869</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>857</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>870</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>871</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>872</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H5" s="43" t="s">
-        <v>873</v>
-      </c>
+    <row r="1" spans="1:9">
+      <c r="A1" s="24" t="s">
+        <v>810</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="75" t="s">
+        <v>811</v>
+      </c>
+      <c r="B2" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="75" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="76" t="s">
+        <v>468</v>
+      </c>
+      <c r="H2" s="43"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>813</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="73">
+        <v>1</v>
+      </c>
+      <c r="G3" s="74" t="s">
+        <v>814</v>
+      </c>
+      <c r="H3" s="43"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>816</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="73">
+        <v>1</v>
+      </c>
+      <c r="G4" s="74" t="s">
+        <v>817</v>
+      </c>
+      <c r="H4" s="43"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>819</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="73">
+        <v>1</v>
+      </c>
+      <c r="G5" s="73" t="s">
+        <v>820</v>
+      </c>
+      <c r="H5" s="43"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B6" s="73" t="s">
+        <v>822</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-2</v>
+      </c>
+      <c r="F6" s="73">
+        <v>1</v>
+      </c>
+      <c r="G6" s="73" t="s">
+        <v>823</v>
+      </c>
+      <c r="H6" s="43"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B7" s="73" t="s">
+        <v>825</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="73">
+        <v>1</v>
+      </c>
+      <c r="G7" s="74" t="s">
+        <v>826</v>
+      </c>
+      <c r="H7" s="43"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B8" s="73" t="s">
+        <v>828</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="73">
+        <v>1</v>
+      </c>
+      <c r="G8" s="74" t="s">
+        <v>829</v>
+      </c>
+      <c r="H8" s="43"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>831</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="73">
+        <v>1</v>
+      </c>
+      <c r="G9" s="74" t="s">
+        <v>832</v>
+      </c>
+      <c r="H9" s="43"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B10" s="73" t="s">
+        <v>834</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="73">
+        <v>1</v>
+      </c>
+      <c r="G10" s="74" t="s">
+        <v>835</v>
+      </c>
+      <c r="H10" s="43"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B11" s="73" t="s">
+        <v>837</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="73">
+        <v>1</v>
+      </c>
+      <c r="G11" s="73" t="s">
+        <v>838</v>
+      </c>
+      <c r="H11" s="43"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B12" s="73" t="s">
+        <v>840</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="73">
+        <v>1</v>
+      </c>
+      <c r="G12" s="73" t="s">
+        <v>841</v>
+      </c>
+      <c r="H12" s="43"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+    </row>
+    <row r="17" spans="8:9">
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+    </row>
+    <row r="18" spans="8:9">
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+    </row>
+    <row r="19" spans="8:9">
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+    </row>
+    <row r="20" spans="8:9">
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+    </row>
+    <row r="21" spans="8:9">
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+    </row>
+    <row r="22" spans="8:9">
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+    </row>
+    <row r="23" spans="8:9">
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+    </row>
+    <row r="24" spans="8:9">
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+    </row>
+    <row r="25" spans="8:9">
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+    </row>
+    <row r="26" spans="8:9">
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+    </row>
+    <row r="27" spans="8:9">
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+    </row>
+    <row r="28" spans="8:9">
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+    </row>
+    <row r="29" spans="8:9">
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+    </row>
+    <row r="30" spans="8:9">
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+    </row>
+    <row r="31" spans="8:9">
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+    </row>
+    <row r="32" spans="8:9">
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+    </row>
+    <row r="33" spans="8:9">
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+    </row>
+    <row r="34" spans="8:9">
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -7543,358 +7980,148 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="43" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="20.375" style="43" customWidth="1"/>
-    <col min="4" max="4" width="12" style="43" customWidth="1"/>
-    <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="43" customWidth="1"/>
-    <col min="7" max="7" width="11" style="43" customWidth="1"/>
-    <col min="8" max="8" width="10.375" style="43" customWidth="1"/>
-    <col min="9" max="9" width="11" style="43" customWidth="1"/>
-    <col min="10" max="10" width="20.25" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
-    <col min="12" max="12" width="12.125" style="43" customWidth="1"/>
-    <col min="13" max="13" width="12.75" style="43" customWidth="1"/>
-    <col min="14" max="14" width="14.625" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="14" style="43" customWidth="1"/>
+    <col min="3" max="3" width="15.75" style="43" customWidth="1"/>
+    <col min="4" max="4" width="10.75" style="43" customWidth="1"/>
+    <col min="5" max="5" width="12" style="43" customWidth="1"/>
+    <col min="6" max="6" width="37" style="43" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="20.25" style="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
         <v>842</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>874</v>
+        <v>843</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>875</v>
+        <v>844</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>876</v>
+        <v>845</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>877</v>
+        <v>846</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>878</v>
+        <v>693</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>879</v>
+        <v>847</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>880</v>
-      </c>
-      <c r="I1" s="43" t="s">
-        <v>881</v>
-      </c>
-      <c r="J1" s="43" t="s">
-        <v>882</v>
-      </c>
-      <c r="K1" s="43" t="s">
-        <v>883</v>
-      </c>
-      <c r="L1" s="43" t="s">
-        <v>884</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>885</v>
-      </c>
-      <c r="N1" s="43" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
         <v>629</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>889</v>
+        <v>851</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>890</v>
+        <v>852</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>891</v>
+        <v>702</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>892</v>
+        <v>853</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>893</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>894</v>
-      </c>
-      <c r="J2" s="43" t="s">
-        <v>895</v>
-      </c>
-      <c r="K2" s="43" t="s">
-        <v>896</v>
-      </c>
-      <c r="L2" s="43" t="s">
-        <v>897</v>
-      </c>
-      <c r="M2" s="43" t="s">
-        <v>898</v>
-      </c>
-      <c r="N2" s="43" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
         <v>855</v>
       </c>
-      <c r="B3" s="43">
-        <v>1</v>
+      <c r="B3" s="43" t="s">
+        <v>856</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>900</v>
+        <v>857</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>901</v>
+        <v>858</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>218</v>
+        <v>859</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>218</v>
+        <v>860</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="H3" s="43">
-        <v>0</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>901</v>
-      </c>
-      <c r="J3" s="43" t="s">
+      <c r="H3" s="43" t="s">
         <v>861</v>
       </c>
-      <c r="K3" s="43">
-        <v>1</v>
-      </c>
-      <c r="L3" s="43">
-        <v>1</v>
-      </c>
-      <c r="M3" s="43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
-        <v>855</v>
-      </c>
-      <c r="B4" s="43">
-        <v>2</v>
+        <v>862</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>863</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>902</v>
+        <v>857</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>903</v>
+        <v>858</v>
       </c>
       <c r="E4" s="43" t="s">
-        <v>218</v>
+        <v>864</v>
       </c>
       <c r="F4" s="43" t="s">
-        <v>218</v>
+        <v>865</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H4" s="43">
-        <v>0</v>
-      </c>
-      <c r="I4" s="43" t="s">
-        <v>901</v>
-      </c>
-      <c r="J4" s="43" t="s">
-        <v>861</v>
-      </c>
-      <c r="K4" s="43">
-        <v>1</v>
-      </c>
-      <c r="L4" s="43">
-        <v>0.7</v>
-      </c>
-      <c r="M4" s="43" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>866</v>
+      </c>
+      <c r="H4" s="43" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
-        <v>855</v>
-      </c>
-      <c r="B5" s="43">
-        <v>3</v>
+        <v>868</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>869</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>905</v>
+        <v>857</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>906</v>
+        <v>870</v>
       </c>
       <c r="E5" s="43" t="s">
-        <v>218</v>
+        <v>871</v>
       </c>
       <c r="F5" s="43" t="s">
-        <v>218</v>
+        <v>872</v>
       </c>
       <c r="G5" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="H5" s="43">
-        <v>0</v>
-      </c>
-      <c r="I5" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="J5" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="K5" s="43">
-        <v>0</v>
-      </c>
-      <c r="L5" s="43">
-        <v>1</v>
-      </c>
-      <c r="M5" s="43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="43" t="s">
-        <v>862</v>
-      </c>
-      <c r="B6" s="43">
-        <v>1</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>907</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>908</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>909</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>910</v>
-      </c>
-      <c r="H6" s="43">
-        <v>100</v>
-      </c>
-      <c r="I6" s="43" t="s">
-        <v>901</v>
-      </c>
-      <c r="J6" s="43" t="s">
-        <v>867</v>
-      </c>
-      <c r="K6" s="43">
-        <v>1</v>
-      </c>
-      <c r="L6" s="43">
-        <v>1</v>
-      </c>
-      <c r="M6" s="43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="43" t="s">
-        <v>862</v>
-      </c>
-      <c r="B7" s="43">
-        <v>2</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>911</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>906</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="G7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H7" s="43">
-        <v>0</v>
-      </c>
-      <c r="I7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="K7" s="43">
-        <v>0</v>
-      </c>
-      <c r="L7" s="43">
-        <v>1</v>
-      </c>
-      <c r="M7" s="43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="43" t="s">
-        <v>868</v>
-      </c>
-      <c r="B8" s="43">
-        <v>1</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>912</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>913</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="H8" s="43">
-        <v>0</v>
-      </c>
-      <c r="I8" s="43" t="s">
-        <v>913</v>
-      </c>
-      <c r="J8" s="43" t="s">
-        <v>914</v>
-      </c>
-      <c r="K8" s="43">
-        <v>30</v>
-      </c>
-      <c r="L8" s="43">
-        <v>1</v>
-      </c>
-      <c r="M8" s="43" t="s">
-        <v>218</v>
+      <c r="H5" s="43" t="s">
+        <v>873</v>
       </c>
     </row>
   </sheetData>
@@ -7904,200 +8131,358 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="43" customWidth="1"/>
-    <col min="2" max="2" width="15.75" style="43" customWidth="1"/>
-    <col min="3" max="3" width="24.625" style="43" customWidth="1"/>
-    <col min="4" max="4" width="14" style="43" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="43" customWidth="1"/>
+    <col min="4" max="4" width="12" style="43" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="43" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="43" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="43" customWidth="1"/>
+    <col min="7" max="7" width="11" style="43" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="11" style="43" customWidth="1"/>
+    <col min="10" max="10" width="20.25" style="43" customWidth="1"/>
+    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
+    <col min="12" max="12" width="12.08203125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="12.75" style="43" customWidth="1"/>
+    <col min="14" max="14" width="14.58203125" style="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:14">
       <c r="A1" s="43" t="s">
-        <v>915</v>
+        <v>842</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>1</v>
+        <v>874</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>693</v>
+        <v>875</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>916</v>
+        <v>876</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>917</v>
+        <v>877</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>918</v>
+        <v>878</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>919</v>
+        <v>879</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>880</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>881</v>
+      </c>
+      <c r="J1" s="43" t="s">
+        <v>882</v>
+      </c>
+      <c r="K1" s="43" t="s">
+        <v>883</v>
+      </c>
+      <c r="L1" s="43" t="s">
+        <v>884</v>
+      </c>
+      <c r="M1" s="43" t="s">
+        <v>885</v>
+      </c>
+      <c r="N1" s="43" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="43" t="s">
-        <v>921</v>
+        <v>629</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>26</v>
+        <v>887</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>702</v>
+        <v>888</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>922</v>
+        <v>889</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>923</v>
+        <v>890</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>924</v>
+        <v>891</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>925</v>
+        <v>892</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>893</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>894</v>
+      </c>
+      <c r="J2" s="43" t="s">
+        <v>895</v>
+      </c>
+      <c r="K2" s="43" t="s">
+        <v>896</v>
+      </c>
+      <c r="L2" s="43" t="s">
+        <v>897</v>
+      </c>
+      <c r="M2" s="43" t="s">
+        <v>898</v>
+      </c>
+      <c r="N2" s="43" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="43" t="s">
-        <v>927</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>928</v>
+        <v>855</v>
+      </c>
+      <c r="B3" s="43">
+        <v>1</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>929</v>
+        <v>900</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>930</v>
+        <v>901</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>931</v>
-      </c>
-      <c r="F3" s="43">
-        <v>5</v>
+        <v>218</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>218</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>932</v>
+        <v>218</v>
       </c>
       <c r="H3" s="43">
+        <v>0</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>901</v>
+      </c>
+      <c r="J3" s="43" t="s">
+        <v>861</v>
+      </c>
+      <c r="K3" s="43">
+        <v>1</v>
+      </c>
+      <c r="L3" s="43">
+        <v>1</v>
+      </c>
+      <c r="M3" s="43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="43" t="s">
+        <v>855</v>
+      </c>
+      <c r="B4" s="43">
+        <v>2</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>902</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" s="43">
+        <v>0</v>
+      </c>
+      <c r="I4" s="43" t="s">
+        <v>901</v>
+      </c>
+      <c r="J4" s="43" t="s">
+        <v>861</v>
+      </c>
+      <c r="K4" s="43">
+        <v>1</v>
+      </c>
+      <c r="L4" s="43">
+        <v>0.7</v>
+      </c>
+      <c r="M4" s="43" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="43" t="s">
+        <v>855</v>
+      </c>
+      <c r="B5" s="43">
+        <v>3</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>905</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>906</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="H5" s="43">
+        <v>0</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="K5" s="43">
+        <v>0</v>
+      </c>
+      <c r="L5" s="43">
+        <v>1</v>
+      </c>
+      <c r="M5" s="43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="43" t="s">
+        <v>862</v>
+      </c>
+      <c r="B6" s="43">
+        <v>1</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>907</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>908</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>909</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>910</v>
+      </c>
+      <c r="H6" s="43">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="43" t="s">
-        <v>933</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>934</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>935</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>930</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>936</v>
-      </c>
-      <c r="F4" s="43">
-        <v>10</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="H4" s="43">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="43" t="s">
-        <v>937</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>938</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>939</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>930</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>940</v>
-      </c>
-      <c r="F5" s="43">
-        <v>1</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>941</v>
-      </c>
-      <c r="H5" s="43">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="43" t="s">
-        <v>942</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>943</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>944</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>945</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>946</v>
-      </c>
-      <c r="F6" s="43">
-        <v>3</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="H6" s="43">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="43" t="s">
+        <v>901</v>
+      </c>
+      <c r="J6" s="43" t="s">
+        <v>867</v>
+      </c>
+      <c r="K6" s="43">
+        <v>1</v>
+      </c>
+      <c r="L6" s="43">
+        <v>1</v>
+      </c>
+      <c r="M6" s="43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="43" t="s">
-        <v>947</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>948</v>
+        <v>862</v>
+      </c>
+      <c r="B7" s="43">
+        <v>2</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>949</v>
+        <v>911</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>950</v>
+        <v>906</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>951</v>
-      </c>
-      <c r="F7" s="43">
-        <v>1</v>
+        <v>218</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>218</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>941</v>
+        <v>218</v>
       </c>
       <c r="H7" s="43">
+        <v>0</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="J7" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="K7" s="43">
+        <v>0</v>
+      </c>
+      <c r="L7" s="43">
+        <v>1</v>
+      </c>
+      <c r="M7" s="43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="43" t="s">
+        <v>868</v>
+      </c>
+      <c r="B8" s="43">
+        <v>1</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>912</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>913</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="H8" s="43">
+        <v>0</v>
+      </c>
+      <c r="I8" s="43" t="s">
+        <v>913</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>914</v>
+      </c>
+      <c r="K8" s="43">
         <v>30</v>
+      </c>
+      <c r="L8" s="43">
+        <v>1</v>
+      </c>
+      <c r="M8" s="43" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -8107,12 +8492,215 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="11.58203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="43" customWidth="1"/>
+    <col min="3" max="3" width="24.58203125" style="43" customWidth="1"/>
+    <col min="4" max="4" width="14" style="43" customWidth="1"/>
+    <col min="5" max="5" width="15.5" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.58203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="12.25" style="43" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" style="43" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="43" t="s">
+        <v>915</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>693</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>916</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>917</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>918</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="43" t="s">
+        <v>921</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>702</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>922</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>923</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>924</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>925</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="43" t="s">
+        <v>927</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>928</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>929</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>931</v>
+      </c>
+      <c r="F3" s="43">
+        <v>5</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>932</v>
+      </c>
+      <c r="H3" s="43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="43" t="s">
+        <v>933</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>935</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>936</v>
+      </c>
+      <c r="F4" s="43">
+        <v>10</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>932</v>
+      </c>
+      <c r="H4" s="43">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="43" t="s">
+        <v>937</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>938</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>939</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>940</v>
+      </c>
+      <c r="F5" s="43">
+        <v>1</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>941</v>
+      </c>
+      <c r="H5" s="43">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="43" t="s">
+        <v>942</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>943</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>944</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>946</v>
+      </c>
+      <c r="F6" s="43">
+        <v>3</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>932</v>
+      </c>
+      <c r="H6" s="43">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="43" t="s">
+        <v>947</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>948</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>949</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>950</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>951</v>
+      </c>
+      <c r="F7" s="43">
+        <v>1</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>941</v>
+      </c>
+      <c r="H7" s="43">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="3" width="15.625" style="43" customWidth="1"/>
-    <col min="4" max="4" width="80.375" style="43" customWidth="1"/>
+    <col min="1" max="3" width="15.58203125" style="43" customWidth="1"/>
+    <col min="4" max="4" width="80.33203125" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8321,19 +8909,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="43" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="17.25" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.58203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="43" customWidth="1"/>
-    <col min="5" max="5" width="19.125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="43" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="19.08203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="13.58203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="18.08203125" style="43" customWidth="1"/>
     <col min="8" max="8" width="19.75" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.625" style="43" customWidth="1"/>
-    <col min="10" max="16" width="15.625" style="43" customWidth="1"/>
-    <col min="17" max="19" width="15.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.58203125" style="43" customWidth="1"/>
+    <col min="10" max="16" width="15.58203125" style="43" customWidth="1"/>
+    <col min="17" max="19" width="15.58203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -8708,7 +9296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.25" thickBot="1">
+    <row r="7" spans="1:20" ht="17.5" thickBot="1">
       <c r="A7" s="9" t="s">
         <v>155</v>
       </c>
@@ -9049,28 +9637,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH288"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="13.875" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="43" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="43" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="11.375" style="43" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="43" customWidth="1"/>
     <col min="6" max="6" width="5.75" style="43" customWidth="1"/>
-    <col min="7" max="7" width="9.125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="9.08203125" style="43" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="15.375" style="43" customWidth="1"/>
-    <col min="10" max="10" width="10.125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="43" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="43" customWidth="1"/>
+    <col min="10" max="10" width="10.08203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="10.58203125" style="43" customWidth="1"/>
     <col min="12" max="12" width="30.25" style="43" customWidth="1"/>
-    <col min="13" max="13" width="18.125" style="43" customWidth="1"/>
-    <col min="14" max="14" width="18.875" style="43" customWidth="1"/>
+    <col min="13" max="13" width="18.08203125" style="43" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" style="43" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="43" customWidth="1"/>
-    <col min="16" max="16" width="11.125" style="43" customWidth="1"/>
+    <col min="16" max="16" width="11.08203125" style="43" customWidth="1"/>
     <col min="17" max="17" width="19.75" style="43" customWidth="1"/>
-    <col min="18" max="18" width="44.125" style="43" customWidth="1"/>
-    <col min="19" max="19" width="99.875" style="43" customWidth="1"/>
-    <col min="20" max="20" width="99.875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="44.08203125" style="43" customWidth="1"/>
+    <col min="19" max="19" width="99.83203125" style="43" customWidth="1"/>
+    <col min="20" max="20" width="99.83203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -15206,18 +15794,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="13.375" style="43" customWidth="1"/>
-    <col min="2" max="2" width="20.125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="20.08203125" style="43" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="43" customWidth="1"/>
     <col min="4" max="4" width="12.75" style="43" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="43" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" style="43" customWidth="1"/>
     <col min="6" max="7" width="14.25" style="43" customWidth="1"/>
     <col min="8" max="8" width="11.25" style="43" customWidth="1"/>
-    <col min="9" max="9" width="12.625" style="43" customWidth="1"/>
-    <col min="10" max="10" width="17.875" style="43" customWidth="1"/>
-    <col min="11" max="11" width="36.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.58203125" style="43" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="36.58203125" style="3" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15953,12 +16541,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{691955B9-B5D3-4198-86F9-315C3F5DF400}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="23.125" customWidth="1"/>
-    <col min="3" max="3" width="26.625" customWidth="1"/>
-    <col min="4" max="4" width="42.625" customWidth="1"/>
+    <col min="2" max="2" width="23.08203125" customWidth="1"/>
+    <col min="3" max="3" width="26.58203125" customWidth="1"/>
+    <col min="4" max="4" width="42.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -16040,19 +16628,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="21.625" style="43" customWidth="1"/>
-    <col min="3" max="3" width="18.625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="21.58203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="18.58203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="13" style="43" customWidth="1"/>
     <col min="5" max="6" width="19.25" style="43" customWidth="1"/>
     <col min="7" max="7" width="14.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="14.875" style="43" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" style="43" customWidth="1"/>
     <col min="9" max="9" width="14" style="43" customWidth="1"/>
     <col min="10" max="10" width="19" style="43" customWidth="1"/>
-    <col min="11" max="11" width="11.625" style="43" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="43" customWidth="1"/>
-    <col min="13" max="13" width="44.125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.58203125" style="43" customWidth="1"/>
+    <col min="12" max="12" width="9.58203125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="44.08203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -17175,20 +17763,206 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94629EF7-5B8C-4E18-8EA0-D0E4DC9F8BA7}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.58203125" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="23" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="23" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1</v>
+      </c>
+      <c r="D3" s="13">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9">
+        <v>-1</v>
+      </c>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C4" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D4" s="13">
+        <v>5</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C5" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D5" s="13">
+        <v>3</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C6" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D6" s="13">
+        <v>10</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C7" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="13">
+        <v>4</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="D8" s="43"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="D9" s="43"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="D10" s="43"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="D11" s="43"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="D12" s="43"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="D13" s="43"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="D14" s="43"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="D15" s="43"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="D16" s="43"/>
+    </row>
+    <row r="17" spans="4:5">
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+    </row>
+    <row r="18" spans="4:5">
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+    </row>
+    <row r="19" spans="4:5">
+      <c r="E19" s="43"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AH91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="18.125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="43" customWidth="1"/>
-    <col min="4" max="4" width="17.375" style="43" customWidth="1"/>
-    <col min="5" max="5" width="34.625" style="43" customWidth="1"/>
-    <col min="6" max="6" width="11.125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="43" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="34.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="11.08203125" style="43" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="43" customWidth="1"/>
-    <col min="8" max="8" width="13.875" style="43" customWidth="1"/>
-    <col min="9" max="9" width="10.625" style="43" customWidth="1"/>
-    <col min="10" max="10" width="14.875" style="43" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="10.58203125" style="43" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" style="43" customWidth="1"/>
     <col min="11" max="11" width="34.5" style="43" customWidth="1"/>
     <col min="12" max="12" width="20" style="43" customWidth="1"/>
   </cols>
@@ -17766,6 +18540,21 @@
       <c r="Q26" s="43"/>
     </row>
     <row r="27" spans="1:17">
+      <c r="A27" s="36" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C27" s="37">
+        <v>1</v>
+      </c>
+      <c r="D27" s="37">
+        <v>0</v>
+      </c>
+      <c r="E27" s="91" t="s">
+        <v>1034</v>
+      </c>
       <c r="M27" s="43"/>
       <c r="N27" s="43"/>
       <c r="O27" s="43"/>
@@ -17773,6 +18562,21 @@
       <c r="Q27" s="43"/>
     </row>
     <row r="28" spans="1:17">
+      <c r="A28" s="36" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B28" s="90" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C28" s="37">
+        <v>1</v>
+      </c>
+      <c r="D28" s="37">
+        <v>0</v>
+      </c>
+      <c r="E28" s="92" t="s">
+        <v>1035</v>
+      </c>
       <c r="M28" s="43"/>
       <c r="N28" s="43"/>
       <c r="O28" s="43"/>
@@ -19195,19 +19999,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="16" style="43" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="43" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="16.25" style="43" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="13.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="12.08203125" style="43" customWidth="1"/>
+    <col min="7" max="7" width="13.58203125" style="43" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="43" customWidth="1"/>
-    <col min="9" max="9" width="13.875" style="43" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" style="43" customWidth="1"/>
     <col min="10" max="10" width="19" style="43" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20195,479 +20999,4 @@
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="16.25" style="43" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="43" customWidth="1"/>
-    <col min="3" max="6" width="14.625" style="43" customWidth="1"/>
-    <col min="7" max="7" width="41.5" style="43" customWidth="1"/>
-    <col min="8" max="11" width="41.5" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A1" s="24" t="s">
-        <v>619</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>689</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>690</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>691</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>692</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>693</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>694</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>695</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>696</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A2" s="45" t="s">
-        <v>628</v>
-      </c>
-      <c r="B2" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>698</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>699</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>700</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>701</v>
-      </c>
-      <c r="G2" s="45" t="s">
-        <v>702</v>
-      </c>
-      <c r="H2" s="45" t="s">
-        <v>703</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>704</v>
-      </c>
-      <c r="J2" s="45" t="s">
-        <v>705</v>
-      </c>
-      <c r="K2" s="45" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A3" s="46" t="s">
-        <v>637</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="62">
-        <v>21</v>
-      </c>
-      <c r="D3" s="62">
-        <v>-1</v>
-      </c>
-      <c r="E3" s="62">
-        <v>-1</v>
-      </c>
-      <c r="F3" s="62">
-        <v>-1</v>
-      </c>
-      <c r="G3" s="47" t="s">
-        <v>707</v>
-      </c>
-      <c r="H3" s="83">
-        <v>1</v>
-      </c>
-      <c r="I3" s="83">
-        <v>60</v>
-      </c>
-      <c r="J3" s="83">
-        <v>30</v>
-      </c>
-      <c r="K3" s="83">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A4" s="55" t="s">
-        <v>637</v>
-      </c>
-      <c r="B4" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="68">
-        <v>28</v>
-      </c>
-      <c r="D4" s="68">
-        <v>-1</v>
-      </c>
-      <c r="E4" s="68">
-        <v>-1</v>
-      </c>
-      <c r="F4" s="68">
-        <v>-1</v>
-      </c>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-    </row>
-    <row r="5" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A5" s="46" t="s">
-        <v>641</v>
-      </c>
-      <c r="B5" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="C5" s="62">
-        <v>26</v>
-      </c>
-      <c r="D5" s="62">
-        <v>-1</v>
-      </c>
-      <c r="E5" s="62">
-        <v>-1</v>
-      </c>
-      <c r="F5" s="62">
-        <v>-1</v>
-      </c>
-      <c r="G5" s="47" t="s">
-        <v>708</v>
-      </c>
-      <c r="H5" s="83">
-        <v>1</v>
-      </c>
-      <c r="I5" s="83">
-        <v>60</v>
-      </c>
-      <c r="J5" s="83">
-        <v>30</v>
-      </c>
-      <c r="K5" s="83">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A6" s="55" t="s">
-        <v>641</v>
-      </c>
-      <c r="B6" s="68" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="68">
-        <v>23</v>
-      </c>
-      <c r="D6" s="68">
-        <v>-1</v>
-      </c>
-      <c r="E6" s="68">
-        <v>-1</v>
-      </c>
-      <c r="F6" s="68">
-        <v>-1</v>
-      </c>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-    </row>
-    <row r="7" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A7" s="49" t="s">
-        <v>644</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="62">
-        <v>25</v>
-      </c>
-      <c r="D7" s="62">
-        <v>-1</v>
-      </c>
-      <c r="E7" s="62">
-        <v>-1</v>
-      </c>
-      <c r="F7" s="62">
-        <v>-1</v>
-      </c>
-      <c r="G7" s="51" t="s">
-        <v>709</v>
-      </c>
-      <c r="H7" s="84">
-        <v>1</v>
-      </c>
-      <c r="I7" s="84">
-        <v>60</v>
-      </c>
-      <c r="J7" s="84">
-        <v>30</v>
-      </c>
-      <c r="K7" s="84">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A8" s="52" t="s">
-        <v>644</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="9">
-        <v>24</v>
-      </c>
-      <c r="D8" s="9">
-        <v>-1</v>
-      </c>
-      <c r="E8" s="9">
-        <v>-1</v>
-      </c>
-      <c r="F8" s="9">
-        <v>-1</v>
-      </c>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-    </row>
-    <row r="9" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A9" s="55" t="s">
-        <v>644</v>
-      </c>
-      <c r="B9" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" s="68">
-        <v>27</v>
-      </c>
-      <c r="D9" s="68">
-        <v>-1</v>
-      </c>
-      <c r="E9" s="68">
-        <v>-1</v>
-      </c>
-      <c r="F9" s="68">
-        <v>-1</v>
-      </c>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-    </row>
-    <row r="10" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A10" s="49" t="s">
-        <v>647</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="62">
-        <v>34</v>
-      </c>
-      <c r="D10" s="62">
-        <v>-1</v>
-      </c>
-      <c r="E10" s="62">
-        <v>-1</v>
-      </c>
-      <c r="F10" s="62">
-        <v>-1</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>710</v>
-      </c>
-      <c r="H10" s="84">
-        <v>1</v>
-      </c>
-      <c r="I10" s="84">
-        <v>60</v>
-      </c>
-      <c r="J10" s="84">
-        <v>30</v>
-      </c>
-      <c r="K10" s="84">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A11" s="55" t="s">
-        <v>647</v>
-      </c>
-      <c r="B11" s="68" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="68">
-        <v>27</v>
-      </c>
-      <c r="D11" s="68">
-        <v>-1</v>
-      </c>
-      <c r="E11" s="68">
-        <v>-1</v>
-      </c>
-      <c r="F11" s="68">
-        <v>-1</v>
-      </c>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-    </row>
-    <row r="12" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A12" s="49" t="s">
-        <v>650</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="62">
-        <v>27</v>
-      </c>
-      <c r="D12" s="62">
-        <v>-1</v>
-      </c>
-      <c r="E12" s="62">
-        <v>-1</v>
-      </c>
-      <c r="F12" s="62">
-        <v>-1</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>711</v>
-      </c>
-      <c r="H12" s="84">
-        <v>1</v>
-      </c>
-      <c r="I12" s="84">
-        <v>60</v>
-      </c>
-      <c r="J12" s="84">
-        <v>30</v>
-      </c>
-      <c r="K12" s="84">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A13" s="56" t="s">
-        <v>650</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="9">
-        <v>24</v>
-      </c>
-      <c r="D13" s="9">
-        <v>-1</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-1</v>
-      </c>
-      <c r="F13" s="9">
-        <v>-1</v>
-      </c>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-    </row>
-    <row r="14" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A14" s="55" t="s">
-        <v>650</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="68">
-        <v>33</v>
-      </c>
-      <c r="D14" s="68">
-        <v>-1</v>
-      </c>
-      <c r="E14" s="68">
-        <v>-1</v>
-      </c>
-      <c r="F14" s="68">
-        <v>-1</v>
-      </c>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-    </row>
-    <row r="15" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A15" s="57" t="s">
-        <v>655</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15" s="58">
-        <v>27</v>
-      </c>
-      <c r="D15" s="58">
-        <v>-1</v>
-      </c>
-      <c r="E15" s="58">
-        <v>-1</v>
-      </c>
-      <c r="F15" s="58">
-        <v>-1</v>
-      </c>
-      <c r="G15" s="59" t="s">
-        <v>712</v>
-      </c>
-      <c r="H15" s="85">
-        <v>1</v>
-      </c>
-      <c r="I15" s="85">
-        <v>60</v>
-      </c>
-      <c r="J15" s="85">
-        <v>30</v>
-      </c>
-      <c r="K15" s="85">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="16.5" customHeight="1"/>
-    <row r="17" ht="16.5" customHeight="1"/>
-  </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0925ADE7-1F66-4F7D-B78C-8D0FFE5F1DF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7129FF7-8497-4B8A-930D-29C1B3E94B6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17540" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="1036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="1038">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -3330,6 +3330,14 @@
   </si>
   <si>
     <t>데미지 피해</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>소모성</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>expendable</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -17764,17 +17772,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94629EF7-5B8C-4E18-8EA0-D0E4DC9F8BA7}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="12.58203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.58203125" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" s="23" t="s">
         <v>1015</v>
       </c>
@@ -17785,16 +17792,25 @@
         <v>1027</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>182</v>
+        <v>1036</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>464</v>
       </c>
       <c r="F1" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="I1" s="23" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2" s="23" t="s">
         <v>1017</v>
       </c>
@@ -17805,16 +17821,25 @@
         <v>1028</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>201</v>
+        <v>1037</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="I2" s="24" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
         <v>1016</v>
       </c>
@@ -17822,17 +17847,26 @@
         <v>1022</v>
       </c>
       <c r="C3" s="9">
-        <v>1</v>
-      </c>
-      <c r="D3" s="13">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9">
         <v>0</v>
       </c>
       <c r="E3" s="9">
         <v>-1</v>
       </c>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="F3" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="G3" s="13">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>1</v>
+      </c>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="9" t="s">
         <v>1018</v>
       </c>
@@ -17840,17 +17874,26 @@
         <v>1023</v>
       </c>
       <c r="C4" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D4" s="13">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0</v>
       </c>
       <c r="E4" s="36" t="s">
         <v>1031</v>
       </c>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="G4" s="13">
+        <v>5</v>
+      </c>
+      <c r="H4" s="9">
+        <v>1</v>
+      </c>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="9" t="s">
         <v>1019</v>
       </c>
@@ -17858,17 +17901,26 @@
         <v>1024</v>
       </c>
       <c r="C5" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D5" s="13">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="G5" s="13">
+        <v>3</v>
+      </c>
+      <c r="H5" s="9">
+        <v>1</v>
+      </c>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="9" t="s">
         <v>1020</v>
       </c>
@@ -17876,17 +17928,26 @@
         <v>1025</v>
       </c>
       <c r="C6" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D6" s="13">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D6" s="9">
+        <v>1</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>1030</v>
       </c>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="G6" s="13">
+        <v>10</v>
+      </c>
+      <c r="H6" s="9">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="9" t="s">
         <v>1021</v>
       </c>
@@ -17894,53 +17955,376 @@
         <v>1026</v>
       </c>
       <c r="C7" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D7" s="13">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>330</v>
       </c>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="G7" s="13">
+        <v>4</v>
+      </c>
+      <c r="H7" s="9">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="D8" s="43"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="43"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="D9" s="43"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:13">
       <c r="D10" s="43"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:13">
       <c r="D11" s="43"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:13">
       <c r="D12" s="43"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:13">
       <c r="D13" s="43"/>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+    </row>
+    <row r="14" spans="1:13">
       <c r="D14" s="43"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+    </row>
+    <row r="15" spans="1:13">
       <c r="D15" s="43"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+    </row>
+    <row r="16" spans="1:13">
       <c r="D16" s="43"/>
-    </row>
-    <row r="17" spans="4:5">
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+    </row>
+    <row r="17" spans="4:13">
       <c r="D17" s="43"/>
       <c r="E17" s="43"/>
-    </row>
-    <row r="18" spans="4:5">
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+    </row>
+    <row r="18" spans="4:13">
       <c r="D18" s="43"/>
       <c r="E18" s="43"/>
-    </row>
-    <row r="19" spans="4:5">
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+    </row>
+    <row r="19" spans="4:13">
       <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+    </row>
+    <row r="20" spans="4:13">
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+    </row>
+    <row r="21" spans="4:13">
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+    </row>
+    <row r="22" spans="4:13">
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+    </row>
+    <row r="23" spans="4:13">
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+    </row>
+    <row r="24" spans="4:13">
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+    </row>
+    <row r="25" spans="4:13">
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+    </row>
+    <row r="26" spans="4:13">
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+    </row>
+    <row r="27" spans="4:13">
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+    </row>
+    <row r="28" spans="4:13">
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+    </row>
+    <row r="29" spans="4:13">
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="43"/>
+    </row>
+    <row r="30" spans="4:13">
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+    </row>
+    <row r="31" spans="4:13">
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+    </row>
+    <row r="32" spans="4:13">
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+    </row>
+    <row r="33" spans="5:13">
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+    </row>
+    <row r="34" spans="5:13">
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+    </row>
+    <row r="35" spans="5:13">
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+    </row>
+    <row r="36" spans="5:13">
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+    </row>
+    <row r="37" spans="5:13">
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+    </row>
+    <row r="38" spans="5:13">
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+    </row>
+    <row r="39" spans="5:13">
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+    </row>
+    <row r="40" spans="5:13">
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+    </row>
+    <row r="41" spans="5:13">
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
+      <c r="M41" s="43"/>
+    </row>
+    <row r="42" spans="5:13">
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="43"/>
+      <c r="M42" s="43"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6A0DDD-3164-4741-A820-18B669AA336E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57D1B76-BC7C-49AC-970A-EA45C55E79E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4575" yWindow="4710" windowWidth="38700" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="1076">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -3225,10 +3225,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>내용</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>그리드효과ID</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -3444,11 +3440,58 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>S_Monster_01</t>
+    <t>S_Monster_07</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>S_Monster_07</t>
+    <t>S_Monster_03</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillInfo</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬내용</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>패턴내용</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1칸 이동합니다.</t>
+  </si>
+  <si>
+    <t>1칸 이동합니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>6(±2)의 피해를 줍니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>4(±1)의 피해를 줍니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1칸 또는 2칸 이동합니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>5(±2)의 피해를 줍니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>침식을 1 부여합니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>원한을 1 부여합니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>16(±2)의 피해를 줍니다.</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -9234,7 +9277,7 @@
         <v>141</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>137</v>
@@ -9296,7 +9339,7 @@
         <v>145</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>137</v>
@@ -9358,7 +9401,7 @@
         <v>149</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>137</v>
@@ -9420,7 +9463,7 @@
         <v>152</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>137</v>
@@ -9446,8 +9489,8 @@
       <c r="J7" s="72" t="s">
         <v>217</v>
       </c>
-      <c r="K7" s="9" t="s">
-        <v>139</v>
+      <c r="K7" s="39" t="s">
+        <v>1063</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>154</v>
@@ -16667,6 +16710,7 @@
     <col min="3" max="3" width="26.625" customWidth="1"/>
     <col min="4" max="4" width="26.625" style="43" customWidth="1"/>
     <col min="5" max="5" width="42.625" customWidth="1"/>
+    <col min="6" max="6" width="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -16680,10 +16724,13 @@
         <v>1009</v>
       </c>
       <c r="D1" s="80" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E1" s="80" t="s">
-        <v>1010</v>
+        <v>1066</v>
+      </c>
+      <c r="F1" s="80" t="s">
+        <v>1065</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -16697,10 +16744,13 @@
         <v>1000</v>
       </c>
       <c r="D2" s="89" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E2" s="89" t="s">
         <v>698</v>
+      </c>
+      <c r="F2" s="89" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -16719,7 +16769,9 @@
       <c r="E3" s="80" t="s">
         <v>1002</v>
       </c>
-      <c r="F3" s="10"/>
+      <c r="F3" s="80" t="s">
+        <v>1068</v>
+      </c>
       <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7">
@@ -16738,7 +16790,9 @@
       <c r="E4" s="80" t="s">
         <v>1004</v>
       </c>
-      <c r="F4" s="10"/>
+      <c r="F4" s="80" t="s">
+        <v>1069</v>
+      </c>
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7">
@@ -16760,10 +16814,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="80" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B6" s="80" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C6" s="10">
         <v>1</v>
@@ -16772,17 +16826,19 @@
         <v>143</v>
       </c>
       <c r="E6" s="80" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F6" s="10"/>
+        <v>1049</v>
+      </c>
+      <c r="F6" s="80" t="s">
+        <v>1068</v>
+      </c>
       <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="80" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B7" s="80" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C7" s="10">
         <v>2</v>
@@ -16791,17 +16847,19 @@
         <v>144</v>
       </c>
       <c r="E7" s="80" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F7" s="10"/>
+        <v>1050</v>
+      </c>
+      <c r="F7" s="80" t="s">
+        <v>1070</v>
+      </c>
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="80" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B8" s="80" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
@@ -16810,52 +16868,58 @@
         <v>143</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F8" s="10"/>
+        <v>1051</v>
+      </c>
+      <c r="F8" s="80" t="s">
+        <v>1068</v>
+      </c>
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="80" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B9" s="80" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C9" s="10">
         <v>2</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E9" s="80" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F9" s="10"/>
+        <v>1052</v>
+      </c>
+      <c r="F9" s="80" t="s">
+        <v>1072</v>
+      </c>
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="80" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B10" s="80" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C10" s="10">
         <v>3</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E10" s="80" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F10" s="10"/>
+        <v>1053</v>
+      </c>
+      <c r="F10" s="80" t="s">
+        <v>1073</v>
+      </c>
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="80" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B11" s="80" t="s">
         <v>149</v>
@@ -16867,14 +16931,16 @@
         <v>143</v>
       </c>
       <c r="E11" s="80" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F11" s="10"/>
+        <v>1051</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>1067</v>
+      </c>
       <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="80" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B12" s="80" t="s">
         <v>149</v>
@@ -16883,17 +16949,19 @@
         <v>2</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E12" s="80" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F12" s="10"/>
+        <v>1052</v>
+      </c>
+      <c r="F12" s="80" t="s">
+        <v>1072</v>
+      </c>
       <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="80" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B13" s="80" t="s">
         <v>149</v>
@@ -16902,17 +16970,19 @@
         <v>3</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E13" s="80" t="s">
-        <v>1055</v>
-      </c>
-      <c r="F13" s="10"/>
+        <v>1054</v>
+      </c>
+      <c r="F13" s="80" t="s">
+        <v>1074</v>
+      </c>
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="80" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B14" s="80" t="s">
         <v>152</v>
@@ -16924,14 +16994,16 @@
         <v>1063</v>
       </c>
       <c r="E14" s="80" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F14" s="10"/>
+        <v>1055</v>
+      </c>
+      <c r="F14" s="80" t="s">
+        <v>1071</v>
+      </c>
       <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="80" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B15" s="80" t="s">
         <v>152</v>
@@ -16940,12 +17012,14 @@
         <v>2</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E15" s="80" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F15" s="10"/>
+        <v>1056</v>
+      </c>
+      <c r="F15" s="80" t="s">
+        <v>1075</v>
+      </c>
       <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7">
@@ -18203,16 +18277,16 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="23" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>460</v>
@@ -18227,21 +18301,21 @@
         <v>179</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="23" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>195</v>
@@ -18261,10 +18335,10 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C3" s="9">
         <v>0</v>
@@ -18288,10 +18362,10 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="9" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C4" s="9">
         <v>1</v>
@@ -18300,7 +18374,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>215</v>
@@ -18315,10 +18389,10 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="9" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C5" s="9">
         <v>1</v>
@@ -18342,10 +18416,10 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="9" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C6" s="9">
         <v>1</v>
@@ -18354,7 +18428,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>215</v>
@@ -18369,10 +18443,10 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="9" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C7" s="9">
         <v>1</v>
@@ -19345,10 +19419,10 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="36" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C27" s="37">
         <v>1</v>
@@ -19357,7 +19431,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="91" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M27" s="43"/>
       <c r="N27" s="43"/>
@@ -19367,10 +19441,10 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="36" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B28" s="90" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C28" s="37">
         <v>1</v>
@@ -19379,7 +19453,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="92" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M28" s="43"/>
       <c r="N28" s="43"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484CD6B5-8369-4F92-BE05-DC561631F938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE30CB80-14BE-472F-A07E-D8AB08D9C1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -1824,13 +1824,7 @@
     <t>주는 피해 30% 감소</t>
   </si>
   <si>
-    <t>원한</t>
-  </si>
-  <si>
     <t>Maintain</t>
-  </si>
-  <si>
-    <t>침식</t>
   </si>
   <si>
     <t>차단</t>
@@ -3543,6 +3537,14 @@
       </rPr>
       <t>칸 증가</t>
     </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>침식</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>원한</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -3955,7 +3957,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4222,6 +4224,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4617,7 +4622,7 @@
         <v>50</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C3" s="6">
         <v>106</v>
@@ -4686,7 +4691,7 @@
         <v>65</v>
       </c>
       <c r="Y3" s="87" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="115.5">
@@ -4694,7 +4699,7 @@
         <v>66</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C4" s="6">
         <v>100</v>
@@ -4763,7 +4768,7 @@
         <v>81</v>
       </c>
       <c r="Y4" s="87" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="115.5">
@@ -4771,7 +4776,7 @@
         <v>82</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C5" s="6">
         <v>94</v>
@@ -4840,7 +4845,7 @@
         <v>97</v>
       </c>
       <c r="Y5" s="87" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -5037,77 +5042,77 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" customHeight="1">
       <c r="A1" s="24" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>98</v>
       </c>
       <c r="C1" s="24" t="s">
+        <v>679</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>680</v>
+      </c>
+      <c r="E1" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="F1" s="24" t="s">
         <v>682</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="G1" s="24" t="s">
         <v>683</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="H1" s="24" t="s">
         <v>684</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="I1" s="24" t="s">
         <v>685</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="J1" s="24" t="s">
         <v>686</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="K1" s="24" t="s">
         <v>687</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>688</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.5" customHeight="1">
       <c r="A2" s="45" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B2" s="45" t="s">
         <v>115</v>
       </c>
       <c r="C2" s="45" t="s">
+        <v>688</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>689</v>
+      </c>
+      <c r="E2" s="45" t="s">
         <v>690</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="F2" s="45" t="s">
         <v>691</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="G2" s="45" t="s">
         <v>692</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="H2" s="45" t="s">
         <v>693</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="I2" s="45" t="s">
         <v>694</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="J2" s="45" t="s">
         <v>695</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="K2" s="45" t="s">
         <v>696</v>
-      </c>
-      <c r="J2" s="45" t="s">
-        <v>697</v>
-      </c>
-      <c r="K2" s="45" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.5" customHeight="1">
       <c r="A3" s="46" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B3" s="62" t="s">
         <v>132</v>
@@ -5125,7 +5130,7 @@
         <v>-1</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H3" s="83">
         <v>1</v>
@@ -5142,7 +5147,7 @@
     </row>
     <row r="4" spans="1:11" ht="16.5" customHeight="1">
       <c r="A4" s="55" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B4" s="68" t="s">
         <v>132</v>
@@ -5167,7 +5172,7 @@
     </row>
     <row r="5" spans="1:11" ht="16.5" customHeight="1">
       <c r="A5" s="46" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B5" s="50" t="s">
         <v>149</v>
@@ -5185,7 +5190,7 @@
         <v>-1</v>
       </c>
       <c r="G5" s="47" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H5" s="83">
         <v>1</v>
@@ -5202,7 +5207,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" customHeight="1">
       <c r="A6" s="55" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B6" s="68" t="s">
         <v>149</v>
@@ -5227,7 +5232,7 @@
     </row>
     <row r="7" spans="1:11" ht="16.5" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B7" s="50" t="s">
         <v>132</v>
@@ -5245,7 +5250,7 @@
         <v>-1</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H7" s="84">
         <v>1</v>
@@ -5262,7 +5267,7 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" customHeight="1">
       <c r="A8" s="52" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B8" s="39" t="s">
         <v>132</v>
@@ -5287,7 +5292,7 @@
     </row>
     <row r="9" spans="1:11" ht="16.5" customHeight="1">
       <c r="A9" s="55" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B9" s="54" t="s">
         <v>142</v>
@@ -5312,7 +5317,7 @@
     </row>
     <row r="10" spans="1:11" ht="16.5" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B10" s="50" t="s">
         <v>149</v>
@@ -5330,7 +5335,7 @@
         <v>-1</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H10" s="84">
         <v>1</v>
@@ -5347,7 +5352,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" customHeight="1">
       <c r="A11" s="55" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B11" s="68" t="s">
         <v>146</v>
@@ -5372,7 +5377,7 @@
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
       <c r="A12" s="49" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B12" s="50" t="s">
         <v>132</v>
@@ -5390,7 +5395,7 @@
         <v>-1</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H12" s="84">
         <v>1</v>
@@ -5407,7 +5412,7 @@
     </row>
     <row r="13" spans="1:11" ht="16.5" customHeight="1">
       <c r="A13" s="56" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B13" s="39" t="s">
         <v>149</v>
@@ -5432,7 +5437,7 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" customHeight="1">
       <c r="A14" s="55" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B14" s="54" t="s">
         <v>142</v>
@@ -5457,7 +5462,7 @@
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1">
       <c r="A15" s="57" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B15" s="58" t="s">
         <v>156</v>
@@ -5475,7 +5480,7 @@
         <v>-1</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H15" s="85">
         <v>1</v>
@@ -5516,94 +5521,94 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>732</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="17.25" customHeight="1">
@@ -5614,94 +5619,94 @@
         <v>26</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>740</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>742</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>743</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>750</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>751</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>752</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>754</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AC2" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AE2" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AF2" s="5" t="s">
         <v>762</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1">
@@ -5709,22 +5714,22 @@
         <v>257</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C3" s="80" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D3" s="61" t="s">
         <v>277</v>
       </c>
       <c r="E3" s="61" t="s">
+        <v>765</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>766</v>
+      </c>
+      <c r="G3" s="61" t="s">
         <v>767</v>
-      </c>
-      <c r="F3" s="61" t="s">
-        <v>768</v>
-      </c>
-      <c r="G3" s="61" t="s">
-        <v>769</v>
       </c>
       <c r="H3" s="62">
         <v>0</v>
@@ -5807,34 +5812,34 @@
         <v>341</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>277</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>767</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>768</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>769</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>771</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>266</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="L4" s="9">
         <v>0</v>
@@ -5905,46 +5910,46 @@
         <v>394</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C5" s="39" t="s">
+        <v>764</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>766</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>771</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>768</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>266</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>277</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="P5" s="9">
         <v>0</v>
@@ -6003,34 +6008,34 @@
         <v>465</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C6" s="39" t="s">
+        <v>764</v>
+      </c>
+      <c r="D6" s="67" t="s">
+        <v>773</v>
+      </c>
+      <c r="E6" s="67" t="s">
         <v>766</v>
       </c>
-      <c r="D6" s="67" t="s">
-        <v>775</v>
-      </c>
-      <c r="E6" s="67" t="s">
-        <v>768</v>
-      </c>
       <c r="F6" s="67" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="H6" s="67" t="s">
         <v>277</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="J6" s="67" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="K6" s="67" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="L6" s="68">
         <v>0</v>
@@ -6101,10 +6106,10 @@
         <v>429</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D7" s="61" t="s">
         <v>277</v>
@@ -6199,16 +6204,16 @@
         <v>360</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>277</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
@@ -6297,19 +6302,19 @@
         <v>311</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>277</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -6395,22 +6400,22 @@
         <v>286</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>277</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>783</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>785</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -6493,28 +6498,28 @@
         <v>272</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>277</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F11" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>783</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>785</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>265</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -6591,25 +6596,25 @@
         <v>267</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>277</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>266</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="I12" s="9">
         <v>0</v>
@@ -6689,28 +6694,28 @@
         <v>303</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>277</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>266</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -6787,10 +6792,10 @@
         <v>372</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>266</v>
@@ -6799,22 +6804,22 @@
         <v>278</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>277</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="L14" s="9">
         <v>0</v>
@@ -6885,22 +6890,22 @@
         <v>295</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>277</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>266</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -6983,10 +6988,10 @@
         <v>324</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>266</v>
@@ -6998,16 +7003,16 @@
         <v>277</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="K16" s="9">
         <v>0</v>
@@ -7081,16 +7086,16 @@
         <v>279</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>277</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>266</v>
@@ -7099,10 +7104,10 @@
         <v>278</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -7179,10 +7184,10 @@
         <v>329</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>266</v>
@@ -7191,25 +7196,25 @@
         <v>278</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>277</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="M18" s="9">
         <v>0</v>
@@ -7277,25 +7282,25 @@
         <v>333</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D19" s="67" t="s">
         <v>277</v>
       </c>
       <c r="E19" s="67" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F19" s="67" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G19" s="67" t="s">
         <v>278</v>
       </c>
       <c r="H19" s="67" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="I19" s="68">
         <v>0</v>
@@ -7375,13 +7380,13 @@
         <v>385</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E20" s="62">
         <v>0</v>
@@ -7473,22 +7478,22 @@
         <v>467</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C21" s="39" t="s">
+        <v>764</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>766</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>768</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>277</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -7571,34 +7576,34 @@
         <v>471</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C22" s="39" t="s">
+        <v>764</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>766</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>768</v>
-      </c>
       <c r="F22" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>277</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="L22" s="9">
         <v>0</v>
@@ -7672,7 +7677,7 @@
         <v>523</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D23" s="68">
         <v>0</v>
@@ -7828,7 +7833,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="24" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>1</v>
@@ -7851,7 +7856,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="75" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B2" s="75" t="s">
         <v>26</v>
@@ -7875,10 +7880,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B3" s="73" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>492</v>
@@ -7893,16 +7898,16 @@
         <v>1</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="H3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B4" s="73" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>492</v>
@@ -7917,16 +7922,16 @@
         <v>1</v>
       </c>
       <c r="G4" s="74" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="H4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B5" s="73" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>492</v>
@@ -7941,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="G5" s="73" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B6" s="73" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>492</v>
@@ -7965,16 +7970,16 @@
         <v>1</v>
       </c>
       <c r="G6" s="73" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="H6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B7" s="73" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>492</v>
@@ -7989,16 +7994,16 @@
         <v>1</v>
       </c>
       <c r="G7" s="74" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="H7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B8" s="73" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>492</v>
@@ -8013,16 +8018,16 @@
         <v>1</v>
       </c>
       <c r="G8" s="74" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="H8" s="43"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B9" s="73" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>492</v>
@@ -8037,16 +8042,16 @@
         <v>1</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B10" s="73" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>492</v>
@@ -8061,16 +8066,16 @@
         <v>1</v>
       </c>
       <c r="G10" s="74" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="H10" s="43"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B11" s="73" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>492</v>
@@ -8085,16 +8090,16 @@
         <v>1</v>
       </c>
       <c r="G11" s="73" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="H11" s="43"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B12" s="73" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>492</v>
@@ -8109,7 +8114,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="73" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="H12" s="43"/>
     </row>
@@ -8224,132 +8229,132 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>833</v>
+      </c>
+      <c r="C1" s="43" t="s">
         <v>834</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="D1" s="43" t="s">
         <v>835</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>836</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="F1" s="43" t="s">
+        <v>683</v>
+      </c>
+      <c r="G1" s="43" t="s">
         <v>837</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>838</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>685</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>839</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B2" s="43" t="s">
+        <v>839</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>840</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>841</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="E2" s="43" t="s">
         <v>842</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="F2" s="43" t="s">
+        <v>692</v>
+      </c>
+      <c r="G2" s="43" t="s">
         <v>843</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="H2" s="43" t="s">
         <v>844</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>694</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>845</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
+        <v>845</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>846</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>847</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="D3" s="43" t="s">
         <v>848</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="E3" s="43" t="s">
         <v>849</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="F3" s="43" t="s">
         <v>850</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>851</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>852</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>211</v>
       </c>
       <c r="H3" s="43" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
+        <v>852</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>853</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>847</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>848</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>854</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="F4" s="43" t="s">
         <v>855</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>849</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>850</v>
-      </c>
-      <c r="E4" s="43" t="s">
+      <c r="G4" s="43" t="s">
         <v>856</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="H4" s="43" t="s">
         <v>857</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>858</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
+        <v>858</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>859</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>847</v>
+      </c>
+      <c r="D5" s="43" t="s">
         <v>860</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="E5" s="43" t="s">
         <v>861</v>
       </c>
-      <c r="C5" s="43" t="s">
-        <v>849</v>
-      </c>
-      <c r="D5" s="43" t="s">
+      <c r="F5" s="43" t="s">
         <v>862</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>863</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>864</v>
       </c>
       <c r="G5" s="43" t="s">
         <v>211</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
   </sheetData>
@@ -8381,104 +8386,104 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="43" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B1" s="43" t="s">
+        <v>864</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>865</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>866</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>867</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>868</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>869</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>870</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="I1" s="43" t="s">
         <v>871</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="J1" s="43" t="s">
         <v>872</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="K1" s="43" t="s">
         <v>873</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>874</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>875</v>
       </c>
-      <c r="L1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>876</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>877</v>
-      </c>
-      <c r="N1" s="43" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="43" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B2" s="43" t="s">
+        <v>877</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>878</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>879</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="E2" s="43" t="s">
         <v>880</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="F2" s="43" t="s">
         <v>881</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="G2" s="43" t="s">
         <v>882</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="H2" s="43" t="s">
         <v>883</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="I2" s="43" t="s">
         <v>884</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="J2" s="43" t="s">
         <v>885</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="K2" s="43" t="s">
         <v>886</v>
       </c>
-      <c r="J2" s="43" t="s">
+      <c r="L2" s="43" t="s">
         <v>887</v>
       </c>
-      <c r="K2" s="43" t="s">
+      <c r="M2" s="43" t="s">
         <v>888</v>
       </c>
-      <c r="L2" s="43" t="s">
+      <c r="N2" s="43" t="s">
         <v>889</v>
-      </c>
-      <c r="M2" s="43" t="s">
-        <v>890</v>
-      </c>
-      <c r="N2" s="43" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="43" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B3" s="43">
         <v>1</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>211</v>
@@ -8493,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="43" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="J3" s="43" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="K3" s="43">
         <v>1</v>
@@ -8510,16 +8515,16 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="43" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B4" s="43">
         <v>2</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E4" s="43" t="s">
         <v>211</v>
@@ -8534,10 +8539,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="K4" s="43">
         <v>1</v>
@@ -8546,21 +8551,21 @@
         <v>0.7</v>
       </c>
       <c r="M4" s="43" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="43" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B5" s="43">
         <v>3</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E5" s="43" t="s">
         <v>211</v>
@@ -8592,34 +8597,34 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="43" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B6" s="43">
         <v>1</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E6" s="43" t="s">
         <v>211</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H6" s="43">
         <v>100</v>
       </c>
       <c r="I6" s="43" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="K6" s="43">
         <v>1</v>
@@ -8633,16 +8638,16 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="43" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B7" s="43">
         <v>2</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E7" s="43" t="s">
         <v>211</v>
@@ -8674,16 +8679,16 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="43" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B8" s="43">
         <v>1</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="E8" s="43" t="s">
         <v>211</v>
@@ -8698,10 +8703,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="J8" s="43" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="K8" s="43">
         <v>30</v>
@@ -8736,77 +8741,77 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="43" t="s">
+        <v>905</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>683</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>906</v>
+      </c>
+      <c r="E1" s="43" t="s">
         <v>907</v>
       </c>
-      <c r="B1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>685</v>
-      </c>
-      <c r="D1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>908</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>909</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>910</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>911</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D2" s="43" t="s">
+        <v>912</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>913</v>
+      </c>
+      <c r="F2" s="43" t="s">
         <v>914</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="G2" s="43" t="s">
         <v>915</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="H2" s="43" t="s">
         <v>916</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>917</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="43" t="s">
+        <v>917</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>918</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>919</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="D3" s="43" t="s">
         <v>920</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="E3" s="43" t="s">
         <v>921</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>922</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>923</v>
       </c>
       <c r="F3" s="43">
         <v>5</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="H3" s="43">
         <v>100</v>
@@ -8814,25 +8819,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="43" t="s">
+        <v>923</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>924</v>
+      </c>
+      <c r="C4" s="43" t="s">
         <v>925</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="D4" s="43" t="s">
+        <v>920</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>926</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>927</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>922</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>928</v>
       </c>
       <c r="F4" s="43">
         <v>10</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="H4" s="43">
         <v>200</v>
@@ -8840,25 +8845,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="43" t="s">
+        <v>927</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>928</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>929</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="D5" s="43" t="s">
+        <v>920</v>
+      </c>
+      <c r="E5" s="43" t="s">
         <v>930</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="F5" s="43">
+        <v>1</v>
+      </c>
+      <c r="G5" s="43" t="s">
         <v>931</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>922</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="F5" s="43">
-        <v>1</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>933</v>
       </c>
       <c r="H5" s="43">
         <v>50</v>
@@ -8866,25 +8871,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="43" t="s">
+        <v>932</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>933</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>934</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="D6" s="43" t="s">
         <v>935</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="E6" s="43" t="s">
         <v>936</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>937</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>938</v>
       </c>
       <c r="F6" s="43">
         <v>3</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="H6" s="43">
         <v>150</v>
@@ -8892,25 +8897,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="43" t="s">
+        <v>937</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>938</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>939</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="D7" s="43" t="s">
         <v>940</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="E7" s="43" t="s">
         <v>941</v>
       </c>
-      <c r="D7" s="43" t="s">
-        <v>942</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>943</v>
-      </c>
       <c r="F7" s="43">
         <v>1</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H7" s="43">
         <v>30</v>
@@ -8933,30 +8938,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="77" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B1" s="77" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="24" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8964,13 +8969,13 @@
         <v>135</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C3" s="9">
         <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8978,13 +8983,13 @@
         <v>139</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C4" s="9">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8992,13 +8997,13 @@
         <v>143</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C5" s="9">
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -9006,13 +9011,13 @@
         <v>147</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C6" s="9">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -9020,69 +9025,69 @@
         <v>150</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C7" s="9">
         <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="9" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C8" s="9">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="9" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C9" s="9">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="9" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C10" s="9">
         <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="9" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C11" s="9">
         <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -9090,41 +9095,41 @@
         <v>159</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C12" s="9">
         <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="9" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C13" s="9">
         <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C14" s="9">
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
   </sheetData>
@@ -9181,10 +9186,10 @@
         <v>105</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>106</v>
@@ -9243,7 +9248,7 @@
         <v>121</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>122</v>
@@ -9305,7 +9310,7 @@
         <v>0.05</v>
       </c>
       <c r="J3" s="86" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>136</v>
@@ -9343,7 +9348,7 @@
         <v>138</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>134</v>
@@ -9367,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="86" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="K4" s="39" t="s">
         <v>140</v>
@@ -9405,7 +9410,7 @@
         <v>142</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>134</v>
@@ -9429,7 +9434,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="86" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>140</v>
@@ -9467,7 +9472,7 @@
         <v>146</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>134</v>
@@ -9491,10 +9496,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="86" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>144</v>
@@ -9529,7 +9534,7 @@
         <v>149</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>134</v>
@@ -9556,7 +9561,7 @@
         <v>214</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>151</v>
@@ -9727,7 +9732,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="86" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>464</v>
@@ -16021,7 +16026,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.375" style="43" customWidth="1"/>
@@ -16104,7 +16109,7 @@
         <v>201</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="K2" s="23" t="s">
         <v>461</v>
@@ -16268,7 +16273,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="39" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>466</v>
@@ -16461,13 +16466,13 @@
         <v>145</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>474</v>
+        <v>253</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>479</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>212</v>
@@ -16485,10 +16490,10 @@
         <v>214</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K12" s="42" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
@@ -16537,13 +16542,13 @@
         <v>148</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>479</v>
+        <v>261</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>474</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>212</v>
@@ -16561,10 +16566,10 @@
         <v>214</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="K14" s="42" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -16612,131 +16617,243 @@
       <c r="K16" s="43"/>
       <c r="L16" s="43"/>
     </row>
-    <row r="17" spans="11:12">
+    <row r="17" spans="11:19">
       <c r="K17" s="43"/>
       <c r="L17" s="43"/>
     </row>
-    <row r="18" spans="11:12">
+    <row r="18" spans="11:19">
       <c r="K18" s="43"/>
       <c r="L18" s="43"/>
     </row>
-    <row r="19" spans="11:12">
+    <row r="19" spans="11:19">
       <c r="K19" s="43"/>
       <c r="L19" s="43"/>
-    </row>
-    <row r="20" spans="11:12">
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+    </row>
+    <row r="20" spans="11:19">
       <c r="K20" s="43"/>
       <c r="L20" s="43"/>
-    </row>
-    <row r="21" spans="11:12">
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+    </row>
+    <row r="21" spans="11:19">
       <c r="K21" s="43"/>
       <c r="L21" s="43"/>
-    </row>
-    <row r="22" spans="11:12">
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+    </row>
+    <row r="22" spans="11:19">
       <c r="K22" s="43"/>
       <c r="L22" s="43"/>
-    </row>
-    <row r="23" spans="11:12">
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+    </row>
+    <row r="23" spans="11:19">
       <c r="K23" s="43"/>
       <c r="L23" s="43"/>
-    </row>
-    <row r="24" spans="11:12">
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+    </row>
+    <row r="24" spans="11:19">
       <c r="K24" s="43"/>
       <c r="L24" s="43"/>
-    </row>
-    <row r="25" spans="11:12">
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
+    </row>
+    <row r="25" spans="11:19">
       <c r="K25" s="43"/>
       <c r="L25" s="43"/>
-    </row>
-    <row r="26" spans="11:12">
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+    </row>
+    <row r="26" spans="11:19">
       <c r="K26" s="43"/>
       <c r="L26" s="43"/>
-    </row>
-    <row r="27" spans="11:12">
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+    </row>
+    <row r="27" spans="11:19">
       <c r="K27" s="43"/>
       <c r="L27" s="43"/>
-    </row>
-    <row r="28" spans="11:12">
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+    </row>
+    <row r="28" spans="11:19">
       <c r="K28" s="43"/>
       <c r="L28" s="43"/>
-    </row>
-    <row r="29" spans="11:12">
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+    </row>
+    <row r="29" spans="11:19">
       <c r="K29" s="43"/>
       <c r="L29" s="43"/>
-    </row>
-    <row r="30" spans="11:12">
+      <c r="M29" s="43"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="43"/>
+      <c r="R29" s="43"/>
+      <c r="S29" s="43"/>
+    </row>
+    <row r="30" spans="11:19">
       <c r="K30" s="43"/>
       <c r="L30" s="43"/>
-    </row>
-    <row r="31" spans="11:12">
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+    </row>
+    <row r="31" spans="11:19">
       <c r="K31" s="43"/>
       <c r="L31" s="43"/>
-    </row>
-    <row r="32" spans="11:12">
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="43"/>
+    </row>
+    <row r="32" spans="11:19">
       <c r="K32" s="43"/>
       <c r="L32" s="43"/>
-    </row>
-    <row r="33" spans="11:12">
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="43"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="43"/>
+    </row>
+    <row r="33" spans="11:19">
       <c r="K33" s="43"/>
       <c r="L33" s="43"/>
-    </row>
-    <row r="34" spans="11:12">
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="43"/>
+      <c r="Q33" s="43"/>
+      <c r="R33" s="43"/>
+      <c r="S33" s="43"/>
+    </row>
+    <row r="34" spans="11:19">
       <c r="K34" s="43"/>
       <c r="L34" s="43"/>
-    </row>
-    <row r="35" spans="11:12">
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="43"/>
+      <c r="S34" s="43"/>
+    </row>
+    <row r="35" spans="11:19">
       <c r="K35" s="43"/>
       <c r="L35" s="43"/>
     </row>
-    <row r="36" spans="11:12">
+    <row r="36" spans="11:19">
       <c r="K36" s="43"/>
       <c r="L36" s="43"/>
     </row>
-    <row r="37" spans="11:12">
+    <row r="37" spans="11:19">
       <c r="K37" s="43"/>
       <c r="L37" s="43"/>
     </row>
-    <row r="38" spans="11:12">
+    <row r="38" spans="11:19">
       <c r="K38" s="43"/>
       <c r="L38" s="43"/>
     </row>
-    <row r="39" spans="11:12">
+    <row r="39" spans="11:19">
       <c r="K39" s="43"/>
       <c r="L39" s="43"/>
     </row>
-    <row r="40" spans="11:12">
+    <row r="40" spans="11:19">
       <c r="K40" s="43"/>
       <c r="L40" s="43"/>
     </row>
-    <row r="41" spans="11:12">
+    <row r="41" spans="11:19">
       <c r="K41" s="43"/>
       <c r="L41" s="43"/>
     </row>
-    <row r="42" spans="11:12">
+    <row r="42" spans="11:19">
       <c r="K42" s="43"/>
       <c r="L42" s="43"/>
     </row>
-    <row r="43" spans="11:12">
+    <row r="43" spans="11:19">
       <c r="K43" s="43"/>
       <c r="L43" s="43"/>
     </row>
-    <row r="44" spans="11:12">
+    <row r="44" spans="11:19">
       <c r="K44" s="43"/>
       <c r="L44" s="43"/>
     </row>
-    <row r="45" spans="11:12">
+    <row r="45" spans="11:19">
       <c r="K45" s="43"/>
       <c r="L45" s="43"/>
     </row>
-    <row r="46" spans="11:12">
+    <row r="46" spans="11:19">
       <c r="K46" s="43"/>
       <c r="L46" s="43"/>
     </row>
-    <row r="47" spans="11:12">
+    <row r="47" spans="11:19">
       <c r="K47" s="43"/>
       <c r="L47" s="43"/>
     </row>
-    <row r="48" spans="11:12">
+    <row r="48" spans="11:19">
       <c r="K48" s="43"/>
       <c r="L48" s="43"/>
     </row>
@@ -16781,47 +16898,47 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="80" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C1" s="80" t="s">
         <v>1003</v>
       </c>
-      <c r="B1" s="80" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C1" s="80" t="s">
-        <v>1005</v>
-      </c>
       <c r="D1" s="80" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E1" s="80" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="F1" s="80" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="89" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B2" s="89" t="s">
         <v>115</v>
       </c>
       <c r="C2" s="89" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="D2" s="89" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E2" s="89" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F2" s="89" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="80" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B3" s="80" t="s">
         <v>132</v>
@@ -16833,16 +16950,16 @@
         <v>136</v>
       </c>
       <c r="E3" s="80" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="F3" s="80" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="80" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B4" s="80" t="s">
         <v>132</v>
@@ -16854,16 +16971,16 @@
         <v>137</v>
       </c>
       <c r="E4" s="80" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="F4" s="80" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="80" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B5" s="80" t="s">
         <v>132</v>
@@ -16873,17 +16990,17 @@
       </c>
       <c r="D5" s="39"/>
       <c r="E5" s="80" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="80" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B6" s="80" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C6" s="10">
         <v>1</v>
@@ -16892,19 +17009,19 @@
         <v>140</v>
       </c>
       <c r="E6" s="80" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="F6" s="80" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="80" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B7" s="80" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C7" s="10">
         <v>2</v>
@@ -16913,19 +17030,19 @@
         <v>141</v>
       </c>
       <c r="E7" s="80" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="F7" s="80" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="80" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B8" s="80" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
@@ -16934,58 +17051,58 @@
         <v>140</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="F8" s="80" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="80" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B9" s="80" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C9" s="10">
         <v>2</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E9" s="80" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F9" s="80" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="80" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B10" s="80" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C10" s="10">
         <v>3</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="E10" s="80" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F10" s="80" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="80" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B11" s="80" t="s">
         <v>146</v>
@@ -16997,16 +17114,16 @@
         <v>140</v>
       </c>
       <c r="E11" s="80" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="80" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B12" s="80" t="s">
         <v>146</v>
@@ -17015,19 +17132,19 @@
         <v>2</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E12" s="80" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="80" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B13" s="80" t="s">
         <v>146</v>
@@ -17036,19 +17153,19 @@
         <v>3</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E13" s="80" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="F13" s="80" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="80" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B14" s="80" t="s">
         <v>149</v>
@@ -17057,19 +17174,19 @@
         <v>1</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E14" s="80" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F14" s="80" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="80" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B15" s="80" t="s">
         <v>149</v>
@@ -17078,13 +17195,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="E15" s="80" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="F15" s="80" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G15" s="10"/>
     </row>
@@ -17864,7 +17981,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="93" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -18343,16 +18460,16 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="23" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>457</v>
@@ -18367,21 +18484,21 @@
         <v>176</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="23" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>192</v>
@@ -18401,10 +18518,10 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C3" s="9">
         <v>0</v>
@@ -18428,10 +18545,10 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="9" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C4" s="9">
         <v>1</v>
@@ -18440,7 +18557,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>212</v>
@@ -18455,10 +18572,10 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="9" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C5" s="9">
         <v>1</v>
@@ -18482,10 +18599,10 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="9" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C6" s="9">
         <v>1</v>
@@ -18494,7 +18611,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>212</v>
@@ -18509,10 +18626,10 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="9" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C7" s="9">
         <v>1</v>
@@ -19331,19 +19448,19 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="36" t="s">
-        <v>993</v>
-      </c>
-      <c r="B20" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="B20" s="94" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C20" s="37">
+        <v>1</v>
+      </c>
+      <c r="D20" s="39" t="s">
         <v>594</v>
       </c>
-      <c r="C20" s="37">
-        <v>1</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>595</v>
-      </c>
       <c r="E20" s="88" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M20" s="43"/>
       <c r="N20" s="43"/>
@@ -19353,19 +19470,19 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="36" t="s">
-        <v>994</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>596</v>
+        <v>992</v>
+      </c>
+      <c r="B21" s="90" t="s">
+        <v>1075</v>
       </c>
       <c r="C21" s="37">
         <v>1</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E21" s="88" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M21" s="43"/>
       <c r="N21" s="43"/>
@@ -19378,7 +19495,7 @@
         <v>477</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C22" s="38">
         <v>0</v>
@@ -19387,7 +19504,7 @@
         <v>569</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="M22" s="43"/>
       <c r="N22" s="43"/>
@@ -19400,7 +19517,7 @@
         <v>401</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C23" s="38">
         <v>0</v>
@@ -19409,7 +19526,7 @@
         <v>569</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="M23" s="43"/>
       <c r="N23" s="43"/>
@@ -19419,10 +19536,10 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="36" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C24" s="38">
         <v>0</v>
@@ -19431,7 +19548,7 @@
         <v>569</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="M24" s="43"/>
       <c r="N24" s="43"/>
@@ -19441,19 +19558,19 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="36" t="s">
+        <v>602</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>603</v>
+      </c>
+      <c r="C25" s="37">
+        <v>1</v>
+      </c>
+      <c r="D25" s="37">
+        <v>0</v>
+      </c>
+      <c r="E25" s="42" t="s">
         <v>604</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>605</v>
-      </c>
-      <c r="C25" s="37">
-        <v>1</v>
-      </c>
-      <c r="D25" s="37">
-        <v>0</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>606</v>
       </c>
       <c r="M25" s="43"/>
       <c r="N25" s="43"/>
@@ -19463,19 +19580,19 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="36" t="s">
+        <v>605</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>606</v>
+      </c>
+      <c r="C26" s="37">
+        <v>1</v>
+      </c>
+      <c r="D26" s="37">
+        <v>0</v>
+      </c>
+      <c r="E26" s="42" t="s">
         <v>607</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>608</v>
-      </c>
-      <c r="C26" s="37">
-        <v>1</v>
-      </c>
-      <c r="D26" s="37">
-        <v>0</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>609</v>
       </c>
       <c r="M26" s="43"/>
       <c r="N26" s="43"/>
@@ -19485,19 +19602,19 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="36" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B27" s="36" t="s">
         <v>1021</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="C27" s="37">
+        <v>1</v>
+      </c>
+      <c r="D27" s="37">
+        <v>0</v>
+      </c>
+      <c r="E27" s="91" t="s">
         <v>1023</v>
-      </c>
-      <c r="C27" s="37">
-        <v>1</v>
-      </c>
-      <c r="D27" s="37">
-        <v>0</v>
-      </c>
-      <c r="E27" s="91" t="s">
-        <v>1025</v>
       </c>
       <c r="M27" s="43"/>
       <c r="N27" s="43"/>
@@ -19507,19 +19624,19 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="36" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B28" s="90" t="s">
         <v>1022</v>
       </c>
-      <c r="B28" s="90" t="s">
+      <c r="C28" s="37">
+        <v>1</v>
+      </c>
+      <c r="D28" s="37">
+        <v>0</v>
+      </c>
+      <c r="E28" s="92" t="s">
         <v>1024</v>
-      </c>
-      <c r="C28" s="37">
-        <v>1</v>
-      </c>
-      <c r="D28" s="37">
-        <v>0</v>
-      </c>
-      <c r="E28" s="92" t="s">
-        <v>1026</v>
       </c>
       <c r="M28" s="43"/>
       <c r="N28" s="43"/>
@@ -20961,7 +21078,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -20970,25 +21087,25 @@
         <v>172</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>615</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>617</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -20999,34 +21116,34 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>624</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>626</v>
       </c>
       <c r="K2" s="43"/>
       <c r="L2" s="43"/>
@@ -21037,25 +21154,25 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="9" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>134</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>629</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>631</v>
       </c>
       <c r="H3" s="9">
         <v>1</v>
@@ -21075,25 +21192,25 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="9" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>134</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E4" s="9">
         <v>0</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H4" s="9">
         <v>1</v>
@@ -21113,25 +21230,25 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="9" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>134</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E5" s="9">
         <v>0</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H5" s="9">
         <v>1</v>
@@ -21151,25 +21268,25 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="9" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>134</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E6" s="9">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H6" s="9">
         <v>1</v>
@@ -21189,25 +21306,25 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>158</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E7" s="9">
         <v>0</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H7" s="9">
         <v>1</v>
@@ -21227,25 +21344,25 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="9" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>158</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E8" s="9">
         <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H8" s="9">
         <v>1</v>
@@ -21265,31 +21382,31 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="9" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>166</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E9" s="9">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H9" s="9">
         <v>1</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="J9" s="39" t="s">
         <v>383</v>
@@ -21303,31 +21420,31 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="F10" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>651</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="H10" s="9">
-        <v>1</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>653</v>
       </c>
       <c r="J10" s="39" t="s">
         <v>383</v>
@@ -21341,25 +21458,25 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="9" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D11" s="9">
         <v>0</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H11" s="9">
         <v>1</v>
@@ -21377,25 +21494,25 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>658</v>
-      </c>
       <c r="F12" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H12" s="9">
         <v>1</v>
@@ -21413,25 +21530,25 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>659</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>661</v>
-      </c>
       <c r="F13" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H13" s="9">
         <v>1</v>
@@ -21449,25 +21566,25 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>665</v>
-      </c>
       <c r="F14" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H14" s="9">
         <v>1</v>
@@ -21485,25 +21602,25 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>666</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="D15" s="9">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>668</v>
-      </c>
       <c r="F15" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H15" s="9">
         <v>1</v>
@@ -21521,25 +21638,25 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>671</v>
-      </c>
       <c r="F16" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H16" s="9">
         <v>1</v>
@@ -21557,25 +21674,25 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>674</v>
-      </c>
       <c r="F17" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H17" s="9">
         <v>1</v>
@@ -21593,25 +21710,25 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>675</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>676</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>677</v>
-      </c>
       <c r="F18" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H18" s="9">
         <v>1</v>
@@ -21629,25 +21746,25 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="D19" s="9">
-        <v>0</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>680</v>
-      </c>
       <c r="F19" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H19" s="9">
         <v>1</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE30CB80-14BE-472F-A07E-D8AB08D9C1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D9C0B8-B404-4252-ADDA-A7569EC725AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="1078">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -3545,6 +3545,14 @@
   </si>
   <si>
     <t>원한</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>버프</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>디버프</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -16466,10 +16474,10 @@
         <v>145</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>478</v>
+        <v>1076</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>479</v>
@@ -16490,10 +16498,10 @@
         <v>214</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="K12" s="42" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
@@ -16542,10 +16550,10 @@
         <v>148</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>473</v>
+        <v>1077</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>474</v>
@@ -16566,10 +16574,10 @@
         <v>214</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K14" s="42" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -16804,6 +16812,11 @@
     <row r="35" spans="11:19">
       <c r="K35" s="43"/>
       <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="43"/>
+      <c r="Q35" s="43"/>
     </row>
     <row r="36" spans="11:19">
       <c r="K36" s="43"/>
@@ -19450,8 +19463,8 @@
       <c r="A20" s="36" t="s">
         <v>991</v>
       </c>
-      <c r="B20" s="94" t="s">
-        <v>1074</v>
+      <c r="B20" s="90" t="s">
+        <v>1075</v>
       </c>
       <c r="C20" s="37">
         <v>1</v>
@@ -19460,7 +19473,7 @@
         <v>594</v>
       </c>
       <c r="E20" s="88" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="M20" s="43"/>
       <c r="N20" s="43"/>
@@ -19472,8 +19485,8 @@
       <c r="A21" s="36" t="s">
         <v>992</v>
       </c>
-      <c r="B21" s="90" t="s">
-        <v>1075</v>
+      <c r="B21" s="94" t="s">
+        <v>1074</v>
       </c>
       <c r="C21" s="37">
         <v>1</v>
@@ -19482,7 +19495,7 @@
         <v>594</v>
       </c>
       <c r="E21" s="88" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M21" s="43"/>
       <c r="N21" s="43"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\RELIC\Assets\ExcelSource\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83597A4-3126-4B0C-814D-44368EE7F031}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="16860" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -25,24 +31,11 @@
     <sheet name="Item" sheetId="14" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="1071">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -1778,7 +1771,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial Unicode MS"/>
-        <charset val="129"/>
+        <family val="2"/>
       </rPr>
       <t>스킬</t>
     </r>
@@ -1787,7 +1780,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1796,7 +1789,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial Unicode MS"/>
-        <charset val="129"/>
+        <family val="2"/>
       </rPr>
       <t>범위</t>
     </r>
@@ -1805,7 +1798,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 2</t>
     </r>
@@ -1814,7 +1807,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial Unicode MS"/>
-        <charset val="129"/>
+        <family val="2"/>
       </rPr>
       <t>칸 증가</t>
     </r>
@@ -1965,9 +1958,6 @@
   </si>
   <si>
     <t>E_Heal</t>
-  </si>
-  <si>
-    <t>GR_Poisson</t>
   </si>
   <si>
     <t>독</t>
@@ -2110,6 +2100,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>수치만큼</t>
@@ -2119,7 +2110,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2128,6 +2119,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>주는</t>
@@ -2137,7 +2129,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2146,6 +2138,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>피해가 증가함</t>
@@ -2160,6 +2153,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>수치만큼</t>
@@ -2169,7 +2163,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2178,6 +2172,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>받는</t>
@@ -2187,7 +2182,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2196,6 +2191,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>피해가</t>
@@ -2205,7 +2201,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2214,6 +2210,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>증가</t>
@@ -2223,6 +2220,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>함</t>
@@ -2273,7 +2271,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">HP </t>
     </r>
@@ -2282,7 +2280,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="129"/>
+        <family val="2"/>
       </rPr>
       <t>회복</t>
     </r>
@@ -3373,19 +3371,101 @@
   </si>
   <si>
     <t>강대한 존재를 쓰러뜨린 증표다. 판매 시 100 더스티움을 얻는다.</t>
+  </si>
+  <si>
+    <t>타입</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Durability</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>내구도</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Active</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>GR_Poisson</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 위치에 GR_Poisson 스폰</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 위치로 이동</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 아군 캐릭터와 위치 변경</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번 턴 주는 피해 100%증가</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번 턴 받는 피해 50%감소</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Relic_11</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Relic_12</t>
+  </si>
+  <si>
+    <t>Relic_13</t>
+  </si>
+  <si>
+    <t>Relic_14</t>
+  </si>
+  <si>
+    <t>Relic_15</t>
+  </si>
+  <si>
+    <t>아드레날린</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>수호자의 비늘</t>
+  </si>
+  <si>
+    <t>차원의 깃털</t>
+  </si>
+  <si>
+    <t>쌍둥이의 반지</t>
+  </si>
+  <si>
+    <t>역병의 향로</t>
+  </si>
+  <si>
+    <t>유물</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Relic</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="36">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3416,228 +3496,94 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Inherit"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="129"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
-      <charset val="129"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="129"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3662,194 +3608,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="25">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -4087,251 +3847,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -4341,7 +3859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4357,14 +3875,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -4435,7 +3953,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4444,13 +3962,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4465,7 +3983,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4511,18 +4029,18 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4553,7 +4071,7 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4571,7 +4089,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4580,76 +4098,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="표준 2" xfId="49"/>
-    <cellStyle name="표준 3" xfId="50"/>
+  <cellStyles count="3">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="표준 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4844,35 +4325,35 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="12.08203125" customWidth="1"/>
     <col min="2" max="2" width="7.25" customWidth="1"/>
-    <col min="3" max="3" width="11.625" customWidth="1"/>
+    <col min="3" max="3" width="11.58203125" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="17.625" customWidth="1"/>
-    <col min="6" max="6" width="13.875" customWidth="1"/>
-    <col min="7" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="22.375" customWidth="1"/>
-    <col min="9" max="9" width="11.375" customWidth="1"/>
+    <col min="5" max="5" width="17.58203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.08203125" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="16.375" customWidth="1"/>
-    <col min="12" max="13" width="12.125" customWidth="1"/>
-    <col min="14" max="15" width="12.375" customWidth="1"/>
-    <col min="16" max="17" width="14.5" customWidth="1"/>
-    <col min="18" max="19" width="14.125" customWidth="1"/>
-    <col min="20" max="24" width="8.5" customWidth="1"/>
-    <col min="25" max="25" width="58.25" style="28" customWidth="1"/>
+    <col min="11" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="14" width="12.08203125" customWidth="1"/>
+    <col min="15" max="16" width="12.33203125" customWidth="1"/>
+    <col min="17" max="18" width="14.5" customWidth="1"/>
+    <col min="19" max="20" width="14.08203125" customWidth="1"/>
+    <col min="21" max="25" width="8.5" customWidth="1"/>
+    <col min="26" max="26" width="58.25" style="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4906,50 +4387,53 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="88" t="s">
+        <v>1069</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -4983,50 +4467,53 @@
       <c r="K2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="88" t="s">
+        <v>1070</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" ht="115.5" spans="1:25">
+    <row r="3" spans="1:26" ht="119">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
@@ -5060,50 +4547,53 @@
       <c r="K3" s="3">
         <v>1</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="55" t="s">
+        <v>1059</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="X3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="Y3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="Y3" s="87" t="s">
+      <c r="Z3" s="87" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" ht="115.5" spans="1:25">
+    <row r="4" spans="1:26" ht="102">
       <c r="A4" s="3" t="s">
         <v>68</v>
       </c>
@@ -5137,50 +4627,53 @@
       <c r="K4" s="3">
         <v>1</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="55" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="Y4" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="Y4" s="87" t="s">
+      <c r="Z4" s="87" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" ht="115.5" spans="1:25">
+    <row r="5" spans="1:26" ht="119">
       <c r="A5" s="3" t="s">
         <v>86</v>
       </c>
@@ -5214,50 +4707,53 @@
       <c r="K5" s="3">
         <v>1</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="55" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="U5" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="V5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="W5" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="W5" s="3" t="s">
+      <c r="X5" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="X5" s="3" t="s">
+      <c r="Y5" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Y5" s="87" t="s">
+      <c r="Z5" s="87" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:26">
       <c r="A6" s="66"/>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
@@ -5268,8 +4764,9 @@
       <c r="I6" s="66"/>
       <c r="J6" s="66"/>
       <c r="K6" s="66"/>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" s="66"/>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="66"/>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -5280,8 +4777,9 @@
       <c r="I7" s="66"/>
       <c r="J7" s="66"/>
       <c r="K7" s="66"/>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" s="66"/>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" s="66"/>
       <c r="B8" s="66"/>
       <c r="C8" s="66"/>
@@ -5292,8 +4790,9 @@
       <c r="I8" s="66"/>
       <c r="J8" s="66"/>
       <c r="K8" s="66"/>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" s="66"/>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" s="66"/>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
@@ -5304,8 +4803,9 @@
       <c r="I9" s="66"/>
       <c r="J9" s="66"/>
       <c r="K9" s="66"/>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" s="66"/>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="66"/>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
@@ -5316,8 +4816,9 @@
       <c r="I10" s="66"/>
       <c r="J10" s="66"/>
       <c r="K10" s="66"/>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="66"/>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -5329,8 +4830,9 @@
       <c r="I11" s="66"/>
       <c r="J11" s="66"/>
       <c r="K11" s="66"/>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" s="66"/>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="66"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>
@@ -5342,8 +4844,9 @@
       <c r="I12" s="66"/>
       <c r="J12" s="66"/>
       <c r="K12" s="66"/>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" s="66"/>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" s="66"/>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
@@ -5354,8 +4857,9 @@
       <c r="I13" s="66"/>
       <c r="J13" s="66"/>
       <c r="K13" s="66"/>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" s="66"/>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14" s="66"/>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -5364,10 +4868,9 @@
       <c r="G14" s="66"/>
       <c r="H14" s="66"/>
       <c r="I14" s="66"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" s="66"/>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="66"/>
       <c r="B15" s="66"/>
       <c r="C15" s="66"/>
@@ -5376,10 +4879,9 @@
       <c r="G15" s="66"/>
       <c r="H15" s="66"/>
       <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" s="66"/>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16" s="66"/>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
@@ -5389,10 +4891,9 @@
       <c r="G16" s="66"/>
       <c r="H16" s="66"/>
       <c r="I16" s="66"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="66"/>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" s="66"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="66"/>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
@@ -5402,10 +4903,8 @@
       <c r="G17" s="66"/>
       <c r="H17" s="66"/>
       <c r="I17" s="66"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
-    </row>
-    <row r="18" spans="1:11">
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="66"/>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
@@ -5415,10 +4914,8 @@
       <c r="G18" s="66"/>
       <c r="H18" s="66"/>
       <c r="I18" s="66"/>
-      <c r="J18" s="66"/>
-      <c r="K18" s="66"/>
-    </row>
-    <row r="19" spans="1:11">
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="66"/>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
@@ -5428,101 +4925,98 @@
       <c r="G19" s="66"/>
       <c r="H19" s="66"/>
       <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
     <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="6" width="14.625" customWidth="1"/>
+    <col min="3" max="6" width="14.58203125" customWidth="1"/>
     <col min="7" max="7" width="41.5" customWidth="1"/>
     <col min="8" max="11" width="41.5" style="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" spans="1:11" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:11">
+    </row>
+    <row r="2" spans="1:11" ht="16.5" customHeight="1">
       <c r="A2" s="29" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B2" s="29" t="s">
         <v>123</v>
       </c>
       <c r="C2" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="D2" s="29" t="s">
         <v>768</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="E2" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="F2" s="29" t="s">
         <v>770</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>771</v>
       </c>
       <c r="G2" s="29" t="s">
         <v>503</v>
       </c>
       <c r="H2" s="29" t="s">
+        <v>771</v>
+      </c>
+      <c r="I2" s="29" t="s">
         <v>772</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="J2" s="29" t="s">
         <v>773</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="K2" s="29" t="s">
         <v>774</v>
       </c>
-      <c r="K2" s="29" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:11">
+    </row>
+    <row r="3" spans="1:11" ht="16.5" customHeight="1">
       <c r="A3" s="30" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>141</v>
@@ -5540,7 +5034,7 @@
         <v>-1</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H3" s="31">
         <v>1</v>
@@ -5555,9 +5049,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:11">
+    <row r="4" spans="1:11" ht="16.5" customHeight="1">
       <c r="A4" s="32" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>141</v>
@@ -5580,9 +5074,9 @@
       <c r="J4" s="33"/>
       <c r="K4" s="33"/>
     </row>
-    <row r="5" customHeight="1" spans="1:11">
+    <row r="5" spans="1:11" ht="16.5" customHeight="1">
       <c r="A5" s="30" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>163</v>
@@ -5600,7 +5094,7 @@
         <v>-1</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H5" s="31">
         <v>1</v>
@@ -5615,9 +5109,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:11">
+    <row r="6" spans="1:11" ht="16.5" customHeight="1">
       <c r="A6" s="32" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>163</v>
@@ -5640,9 +5134,9 @@
       <c r="J6" s="33"/>
       <c r="K6" s="33"/>
     </row>
-    <row r="7" customHeight="1" spans="1:11">
+    <row r="7" spans="1:11" ht="16.5" customHeight="1">
       <c r="A7" s="35" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>141</v>
@@ -5660,7 +5154,7 @@
         <v>-1</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H7" s="36">
         <v>1</v>
@@ -5675,9 +5169,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:11">
+    <row r="8" spans="1:11" ht="16.5" customHeight="1">
       <c r="A8" s="37" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>141</v>
@@ -5700,9 +5194,9 @@
       <c r="J8" s="38"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" customHeight="1" spans="1:11">
+    <row r="9" spans="1:11" ht="16.5" customHeight="1">
       <c r="A9" s="32" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B9" s="39" t="s">
         <v>153</v>
@@ -5725,9 +5219,9 @@
       <c r="J9" s="33"/>
       <c r="K9" s="33"/>
     </row>
-    <row r="10" customHeight="1" spans="1:11">
+    <row r="10" spans="1:11" ht="16.5" customHeight="1">
       <c r="A10" s="35" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>163</v>
@@ -5745,7 +5239,7 @@
         <v>-1</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H10" s="36">
         <v>1</v>
@@ -5760,9 +5254,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:11">
+    <row r="11" spans="1:11" ht="16.5" customHeight="1">
       <c r="A11" s="32" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>159</v>
@@ -5785,9 +5279,9 @@
       <c r="J11" s="33"/>
       <c r="K11" s="33"/>
     </row>
-    <row r="12" customHeight="1" spans="1:11">
+    <row r="12" spans="1:11" ht="16.5" customHeight="1">
       <c r="A12" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>141</v>
@@ -5805,7 +5299,7 @@
         <v>-1</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H12" s="36">
         <v>1</v>
@@ -5820,9 +5314,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:11">
+    <row r="13" spans="1:11" ht="16.5" customHeight="1">
       <c r="A13" s="40" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>163</v>
@@ -5845,9 +5339,9 @@
       <c r="J13" s="38"/>
       <c r="K13" s="38"/>
     </row>
-    <row r="14" customHeight="1" spans="1:11">
+    <row r="14" spans="1:11" ht="16.5" customHeight="1">
       <c r="A14" s="32" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B14" s="39" t="s">
         <v>153</v>
@@ -5870,9 +5364,9 @@
       <c r="J14" s="33"/>
       <c r="K14" s="33"/>
     </row>
-    <row r="15" customHeight="1" spans="1:11">
+    <row r="15" spans="1:11" ht="16.5" customHeight="1">
       <c r="A15" s="41" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>173</v>
@@ -5890,7 +5384,7 @@
         <v>-1</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H15" s="43">
         <v>1</v>
@@ -5905,23 +5399,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customHeight="1"/>
-    <row r="17" customHeight="1"/>
+    <row r="16" spans="1:11" ht="16.5" customHeight="1"/>
+    <row r="17" ht="16.5" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AF23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="9.375" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="14.875" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.58203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -5932,97 +5425,97 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>782</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>783</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>784</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>785</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>786</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>787</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>788</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>790</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="10" t="s">
         <v>791</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="N1" s="10" t="s">
         <v>792</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>793</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>794</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>796</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>797</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="T1" s="10" t="s">
         <v>798</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>799</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>800</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>801</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="X1" s="10" t="s">
         <v>802</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="Y1" s="10" t="s">
         <v>803</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Z1" s="10" t="s">
         <v>804</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AA1" s="10" t="s">
         <v>805</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AB1" s="10" t="s">
         <v>806</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AC1" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AD1" s="10" t="s">
         <v>808</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AE1" s="10" t="s">
         <v>809</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AF1" s="10" t="s">
         <v>810</v>
       </c>
-      <c r="AF1" s="10" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" spans="1:32">
+    </row>
+    <row r="2" spans="1:32" ht="17.25" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>219</v>
       </c>
@@ -6030,118 +5523,118 @@
         <v>26</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>811</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>812</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>813</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>814</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>815</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>816</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>817</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>818</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>819</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>820</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>821</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>822</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>823</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>824</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="Q2" s="11" t="s">
         <v>825</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>826</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="S2" s="11" t="s">
         <v>827</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="T2" s="11" t="s">
         <v>828</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>829</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="W2" s="11" t="s">
         <v>831</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>832</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="Y2" s="11" t="s">
         <v>833</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Z2" s="11" t="s">
         <v>834</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="AA2" s="11" t="s">
         <v>835</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AB2" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="AB2" s="11" t="s">
+      <c r="AC2" s="11" t="s">
         <v>837</v>
       </c>
-      <c r="AC2" s="11" t="s">
+      <c r="AD2" s="11" t="s">
         <v>838</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AE2" s="11" t="s">
         <v>839</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AF2" s="11" t="s">
         <v>840</v>
       </c>
-      <c r="AF2" s="11" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:32">
+    </row>
+    <row r="3" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>274</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>841</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>842</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>843</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>294</v>
       </c>
       <c r="E3" s="13" t="s">
+        <v>843</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>844</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>845</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>846</v>
-      </c>
       <c r="H3" s="15">
         <v>0</v>
       </c>
@@ -6218,40 +5711,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:32">
+    <row r="4" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A4" s="16" t="s">
         <v>156</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>294</v>
       </c>
       <c r="E4" s="17" t="s">
+        <v>843</v>
+      </c>
+      <c r="F4" s="17" t="s">
         <v>844</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="G4" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>846</v>
-      </c>
       <c r="H4" s="17" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>283</v>
       </c>
       <c r="J4" s="17" t="s">
+        <v>848</v>
+      </c>
+      <c r="K4" s="17" t="s">
         <v>849</v>
       </c>
-      <c r="K4" s="17" t="s">
-        <v>850</v>
-      </c>
       <c r="L4" s="3">
         <v>0</v>
       </c>
@@ -6316,52 +5809,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:32">
+    <row r="5" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A5" s="16" t="s">
         <v>177</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>850</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>842</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>851</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>843</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>852</v>
-      </c>
       <c r="E5" s="17" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>283</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="J5" s="17" t="s">
         <v>294</v>
       </c>
       <c r="K5" s="17" t="s">
+        <v>853</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>849</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>845</v>
+      </c>
+      <c r="N5" s="17" t="s">
+        <v>848</v>
+      </c>
+      <c r="O5" s="17" t="s">
         <v>854</v>
       </c>
-      <c r="L5" s="17" t="s">
-        <v>850</v>
-      </c>
-      <c r="M5" s="17" t="s">
-        <v>846</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>849</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>855</v>
-      </c>
       <c r="P5" s="3">
         <v>0</v>
       </c>
@@ -6414,40 +5907,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:32">
+    <row r="6" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A6" s="19" t="s">
         <v>145</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C6" s="18" t="s">
+        <v>842</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>851</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>844</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>852</v>
+      </c>
+      <c r="G6" s="20" t="s">
         <v>843</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>852</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>845</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>853</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>844</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>294</v>
       </c>
       <c r="I6" s="20" t="s">
+        <v>853</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>845</v>
+      </c>
+      <c r="K6" s="20" t="s">
         <v>854</v>
       </c>
-      <c r="J6" s="20" t="s">
-        <v>846</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>855</v>
-      </c>
       <c r="L6" s="24">
         <v>0</v>
       </c>
@@ -6512,15 +6005,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:32">
+    <row r="7" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A7" s="12" t="s">
         <v>444</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>294</v>
@@ -6610,21 +6103,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:32">
+    <row r="8" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A8" s="16" t="s">
         <v>376</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>294</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -6708,24 +6201,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:32">
+    <row r="9" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>328</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>294</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -6806,27 +6299,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:32">
+    <row r="10" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A10" s="16" t="s">
         <v>303</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>294</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -6904,33 +6397,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:32">
+    <row r="11" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A11" s="21" t="s">
         <v>289</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>294</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>282</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -7002,30 +6495,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:32">
+    <row r="12" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A12" s="16" t="s">
         <v>284</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>294</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>283</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I12" s="3">
         <v>0</v>
@@ -7100,33 +6593,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:32">
+    <row r="13" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A13" s="16" t="s">
         <v>320</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>294</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>283</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J13" s="3">
         <v>0</v>
@@ -7198,15 +6691,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:32">
+    <row r="14" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A14" s="16" t="s">
         <v>388</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>283</v>
@@ -7215,23 +6708,23 @@
         <v>295</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>294</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J14" s="17" t="s">
+        <v>868</v>
+      </c>
+      <c r="K14" s="17" t="s">
         <v>869</v>
       </c>
-      <c r="K14" s="17" t="s">
-        <v>870</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -7296,27 +6789,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:32">
+    <row r="15" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A15" s="16" t="s">
         <v>312</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>294</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>283</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -7394,15 +6887,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:32">
+    <row r="16" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A16" s="16" t="s">
         <v>341</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>283</v>
@@ -7414,16 +6907,16 @@
         <v>294</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -7492,21 +6985,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:32">
+    <row r="17" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A17" s="16" t="s">
         <v>296</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>294</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>283</v>
@@ -7515,10 +7008,10 @@
         <v>295</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="J17" s="3">
         <v>0</v>
@@ -7590,15 +7083,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:32">
+    <row r="18" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A18" s="16" t="s">
         <v>346</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>283</v>
@@ -7607,26 +7100,26 @@
         <v>295</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>294</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K18" s="17" t="s">
+        <v>868</v>
+      </c>
+      <c r="L18" s="17" t="s">
         <v>869</v>
       </c>
-      <c r="L18" s="17" t="s">
-        <v>870</v>
-      </c>
       <c r="M18" s="3">
         <v>0</v>
       </c>
@@ -7688,30 +7181,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:32">
+    <row r="19" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A19" s="19" t="s">
         <v>350</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>294</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>295</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="I19" s="24">
         <v>0</v>
@@ -7786,18 +7279,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:32">
+    <row r="20" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A20" s="22" t="s">
         <v>401</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
@@ -7884,27 +7377,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:32">
+    <row r="21" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A21" s="16" t="s">
         <v>481</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>294</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H21" s="3">
         <v>0</v>
@@ -7982,40 +7475,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:32">
+    <row r="22" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A22" s="16" t="s">
         <v>485</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C22" s="18" t="s">
+        <v>842</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>851</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>852</v>
+      </c>
+      <c r="G22" s="17" t="s">
         <v>843</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>852</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>845</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>853</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>844</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>294</v>
       </c>
       <c r="I22" s="17" t="s">
+        <v>853</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>845</v>
+      </c>
+      <c r="K22" s="17" t="s">
         <v>854</v>
       </c>
-      <c r="J22" s="17" t="s">
-        <v>846</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>855</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -8080,7 +7573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:32">
+    <row r="23" spans="1:32" ht="20.149999999999999" customHeight="1">
       <c r="A23" s="23" t="s">
         <v>166</v>
       </c>
@@ -8088,7 +7581,7 @@
         <v>578</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D23" s="24">
         <v>0</v>
@@ -8179,29 +7672,28 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
     <col min="3" max="4" width="19.5" customWidth="1"/>
-    <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="6" max="6" width="18.625" customWidth="1"/>
-    <col min="7" max="7" width="57.25" customWidth="1"/>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="20.08203125" customWidth="1"/>
+    <col min="6" max="8" width="18.58203125" customWidth="1"/>
+    <col min="9" max="9" width="57.25" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -8218,16 +7710,22 @@
       <c r="F1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="88" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H1" s="88" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" s="5" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>26</v>
@@ -8244,19 +7742,25 @@
       <c r="F2" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="88" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H2" s="88" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>881</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>882</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>546</v>
@@ -8270,19 +7774,25 @@
       <c r="F3" s="7">
         <v>1</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>885</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>886</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>546</v>
@@ -8296,19 +7806,25 @@
       <c r="F4" s="7">
         <v>1</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="H4" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="7" t="s">
         <v>888</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>889</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>546</v>
@@ -8322,19 +7838,25 @@
       <c r="F5" s="7">
         <v>1</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="H5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>891</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>892</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>546</v>
@@ -8348,19 +7870,25 @@
       <c r="F6" s="7">
         <v>1</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4" t="s">
         <v>893</v>
       </c>
-      <c r="H6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>894</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>895</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>546</v>
@@ -8374,19 +7902,25 @@
       <c r="F7" s="7">
         <v>1</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="H7" t="s">
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="7" t="s">
         <v>898</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>899</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>546</v>
@@ -8400,19 +7934,25 @@
       <c r="F8" s="7">
         <v>1</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4" t="s">
         <v>900</v>
       </c>
-      <c r="H8" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>901</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>902</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>546</v>
@@ -8426,19 +7966,25 @@
       <c r="F9" s="7">
         <v>1</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="H9" t="s">
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>905</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>906</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>546</v>
@@ -8452,19 +7998,25 @@
       <c r="F10" s="7">
         <v>1</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4" t="s">
         <v>907</v>
       </c>
-      <c r="H10" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="7" t="s">
         <v>908</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>909</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>546</v>
@@ -8478,19 +8030,25 @@
       <c r="F11" s="7">
         <v>1</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4" t="s">
         <v>910</v>
       </c>
-      <c r="H11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="4" t="s">
+      <c r="B12" s="7" t="s">
         <v>911</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>912</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>546</v>
@@ -8504,81 +8062,247 @@
       <c r="F12" s="7">
         <v>1</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>913</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="G12" s="89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>269</v>
       </c>
     </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="55" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B13" s="89" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1</v>
+      </c>
+      <c r="G13" s="89" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H13" s="7">
+        <v>1</v>
+      </c>
+      <c r="I13" s="89" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="55" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B14" s="55" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7">
+        <v>1</v>
+      </c>
+      <c r="G14" s="89" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H14" s="7">
+        <v>2</v>
+      </c>
+      <c r="I14" s="89" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="55" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B15" s="55" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7">
+        <v>1</v>
+      </c>
+      <c r="G15" s="89" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H15" s="7">
+        <v>3</v>
+      </c>
+      <c r="I15" s="89" t="s">
+        <v>1055</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="55" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7">
+        <v>1</v>
+      </c>
+      <c r="G16" s="89" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H16" s="7">
+        <v>5</v>
+      </c>
+      <c r="I16" s="89" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="55" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B17" s="55" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="89" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H17" s="7">
+        <v>10</v>
+      </c>
+      <c r="I17" s="89" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="15.75" customWidth="1"/>
-    <col min="4" max="4" width="37.625" customWidth="1"/>
-    <col min="5" max="5" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="37.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.08203125" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="15.875" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
     <col min="8" max="8" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>913</v>
+      </c>
+      <c r="B1" t="s">
         <v>914</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>915</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>762</v>
+      </c>
+      <c r="E1" t="s">
         <v>916</v>
-      </c>
-      <c r="D1" t="s">
-        <v>763</v>
-      </c>
-      <c r="E1" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C2" t="s">
         <v>918</v>
-      </c>
-      <c r="C2" t="s">
-        <v>919</v>
       </c>
       <c r="D2" t="s">
         <v>503</v>
       </c>
       <c r="E2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>920</v>
+      </c>
+      <c r="B3" t="s">
+        <v>737</v>
+      </c>
+      <c r="C3" t="s">
         <v>921</v>
       </c>
-      <c r="B3" t="s">
-        <v>738</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>922</v>
-      </c>
-      <c r="D3" t="s">
-        <v>923</v>
       </c>
       <c r="E3" t="s">
         <v>229</v>
@@ -8586,166 +8310,165 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>923</v>
+      </c>
+      <c r="B4" t="s">
         <v>924</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>925</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>926</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>927</v>
-      </c>
-      <c r="E4" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
+        <v>928</v>
+      </c>
+      <c r="B5" t="s">
         <v>929</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>930</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>931</v>
-      </c>
-      <c r="D5" t="s">
-        <v>932</v>
       </c>
       <c r="E5" t="s">
         <v>229</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="9.75" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="20.25" customWidth="1"/>
-    <col min="11" max="11" width="11.625" customWidth="1"/>
-    <col min="12" max="12" width="12.125" customWidth="1"/>
+    <col min="11" max="11" width="11.58203125" customWidth="1"/>
+    <col min="12" max="12" width="12.08203125" customWidth="1"/>
     <col min="13" max="13" width="12.75" customWidth="1"/>
-    <col min="14" max="14" width="14.625" customWidth="1"/>
+    <col min="14" max="14" width="14.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B1" t="s">
+        <v>932</v>
+      </c>
+      <c r="C1" t="s">
         <v>933</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>934</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>935</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>936</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>937</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>938</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>939</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>940</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>941</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>942</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>943</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>944</v>
-      </c>
-      <c r="N1" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B2" t="s">
+        <v>945</v>
+      </c>
+      <c r="C2" t="s">
         <v>946</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>947</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>948</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>949</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>950</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>951</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>952</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>953</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>954</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>955</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>956</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>957</v>
       </c>
-      <c r="N2" t="s">
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>920</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>958</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>921</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>959</v>
-      </c>
-      <c r="D3" t="s">
-        <v>960</v>
       </c>
       <c r="E3" t="s">
         <v>229</v>
@@ -8760,10 +8483,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
+        <v>959</v>
+      </c>
+      <c r="J3" t="s">
         <v>960</v>
-      </c>
-      <c r="J3" t="s">
-        <v>961</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -8775,18 +8498,18 @@
         <v>229</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
+        <v>961</v>
+      </c>
+      <c r="D4" t="s">
         <v>962</v>
-      </c>
-      <c r="D4" t="s">
-        <v>963</v>
       </c>
       <c r="E4" t="s">
         <v>229</v>
@@ -8801,10 +8524,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
+        <v>959</v>
+      </c>
+      <c r="J4" t="s">
         <v>960</v>
-      </c>
-      <c r="J4" t="s">
-        <v>961</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -8813,21 +8536,21 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
+        <v>964</v>
+      </c>
+      <c r="D5" t="s">
         <v>965</v>
-      </c>
-      <c r="D5" t="s">
-        <v>966</v>
       </c>
       <c r="E5" t="s">
         <v>229</v>
@@ -8857,36 +8580,36 @@
         <v>229</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>966</v>
+      </c>
+      <c r="D6" t="s">
         <v>967</v>
-      </c>
-      <c r="D6" t="s">
-        <v>968</v>
       </c>
       <c r="E6" t="s">
         <v>229</v>
       </c>
       <c r="F6" t="s">
+        <v>968</v>
+      </c>
+      <c r="G6" t="s">
         <v>969</v>
-      </c>
-      <c r="G6" t="s">
-        <v>970</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="J6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -8898,18 +8621,18 @@
         <v>229</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D7" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E7" t="s">
         <v>229</v>
@@ -8939,18 +8662,18 @@
         <v>229</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>972</v>
+      </c>
+      <c r="D8" t="s">
         <v>973</v>
-      </c>
-      <c r="D8" t="s">
-        <v>974</v>
       </c>
       <c r="E8" t="s">
         <v>229</v>
@@ -8965,10 +8688,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
+        <v>973</v>
+      </c>
+      <c r="J8" t="s">
         <v>974</v>
-      </c>
-      <c r="J8" t="s">
-        <v>975</v>
       </c>
       <c r="K8">
         <v>30</v>
@@ -8981,56 +8704,55 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" customWidth="1"/>
     <col min="2" max="2" width="15.75" customWidth="1"/>
-    <col min="3" max="3" width="24.625" customWidth="1"/>
+    <col min="3" max="3" width="24.58203125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="6" max="6" width="14.58203125" customWidth="1"/>
     <col min="7" max="7" width="12.25" customWidth="1"/>
-    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>975</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>762</v>
+      </c>
+      <c r="D1" t="s">
         <v>976</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>763</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>977</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>978</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>979</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>980</v>
-      </c>
-      <c r="H1" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -9039,42 +8761,42 @@
         <v>503</v>
       </c>
       <c r="D2" t="s">
+        <v>982</v>
+      </c>
+      <c r="E2" t="s">
         <v>983</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>984</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>985</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>986</v>
-      </c>
-      <c r="H2" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
+        <v>987</v>
+      </c>
+      <c r="B3" t="s">
         <v>988</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>989</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>990</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>991</v>
-      </c>
-      <c r="E3" t="s">
-        <v>992</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H3">
         <v>100</v>
@@ -9082,25 +8804,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
+        <v>993</v>
+      </c>
+      <c r="B4" t="s">
         <v>994</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>995</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>990</v>
+      </c>
+      <c r="E4" t="s">
         <v>996</v>
-      </c>
-      <c r="D4" t="s">
-        <v>991</v>
-      </c>
-      <c r="E4" t="s">
-        <v>997</v>
       </c>
       <c r="F4">
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H4">
         <v>200</v>
@@ -9108,25 +8830,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
+        <v>997</v>
+      </c>
+      <c r="B5" t="s">
         <v>998</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>999</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>990</v>
+      </c>
+      <c r="E5" t="s">
         <v>1000</v>
       </c>
-      <c r="D5" t="s">
-        <v>991</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
         <v>1001</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1002</v>
       </c>
       <c r="H5">
         <v>50</v>
@@ -9134,25 +8856,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B6" t="s">
         <v>1003</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>1004</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>1005</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>1006</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1007</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H6">
         <v>150</v>
@@ -9160,72 +8882,71 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B7" t="s">
         <v>1008</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>1009</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>1010</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>1011</v>
       </c>
-      <c r="E7" t="s">
-        <v>1012</v>
-      </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H7">
         <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="4" width="80.375" customWidth="1"/>
+    <col min="1" max="3" width="15.58203125" customWidth="1"/>
+    <col min="4" max="4" width="80.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1014</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>1016</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -9233,13 +8954,13 @@
         <v>144</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C3" s="3">
         <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -9247,13 +8968,13 @@
         <v>150</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C4" s="3">
         <v>7</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -9261,13 +8982,13 @@
         <v>155</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C5" s="3">
         <v>12</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -9275,13 +8996,13 @@
         <v>161</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C6" s="3">
         <v>10</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -9289,69 +9010,69 @@
         <v>165</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C7" s="3">
         <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>1028</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>1029</v>
       </c>
       <c r="C8" s="3">
         <v>20</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>1031</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>1032</v>
       </c>
       <c r="C9" s="3">
         <v>25</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>1034</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1035</v>
       </c>
       <c r="C10" s="3">
         <v>25</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>1037</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>1038</v>
       </c>
       <c r="C11" s="3">
         <v>30</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -9359,67 +9080,66 @@
         <v>176</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C12" s="3">
         <v>50</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>1042</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>1043</v>
       </c>
       <c r="C13" s="3">
         <v>60</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>1045</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>1046</v>
       </c>
       <c r="C14" s="3">
         <v>100</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" customWidth="1"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
-    <col min="3" max="3" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="9.58203125" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
-    <col min="5" max="5" width="19.125" customWidth="1"/>
-    <col min="6" max="6" width="13.625" customWidth="1"/>
-    <col min="7" max="7" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="19.08203125" customWidth="1"/>
+    <col min="6" max="6" width="13.58203125" customWidth="1"/>
+    <col min="7" max="7" width="18.08203125" customWidth="1"/>
     <col min="8" max="8" width="19.75" customWidth="1"/>
-    <col min="9" max="9" width="13.625" customWidth="1"/>
-    <col min="10" max="16" width="15.625" customWidth="1"/>
-    <col min="17" max="19" width="15.625" style="28" customWidth="1"/>
+    <col min="9" max="9" width="13.58203125" customWidth="1"/>
+    <col min="10" max="16" width="15.58203125" customWidth="1"/>
+    <col min="17" max="19" width="15.58203125" style="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -9794,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="17.25" spans="1:20">
+    <row r="7" spans="1:20">
       <c r="A7" s="3" t="s">
         <v>163</v>
       </c>
@@ -10086,12 +9806,12 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
     </row>
-    <row r="15" spans="17:19">
+    <row r="15" spans="1:20">
       <c r="Q15"/>
       <c r="R15"/>
       <c r="S15"/>
     </row>
-    <row r="16" spans="17:19">
+    <row r="16" spans="1:20">
       <c r="Q16"/>
       <c r="R16"/>
       <c r="S16"/>
@@ -10127,36 +9847,35 @@
       <c r="S22"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T60"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="13.875" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
     <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="11.375" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
     <col min="6" max="6" width="5.75" customWidth="1"/>
-    <col min="7" max="7" width="9.125" customWidth="1"/>
+    <col min="7" max="7" width="9.08203125" customWidth="1"/>
     <col min="8" max="8" width="21.25" customWidth="1"/>
-    <col min="9" max="9" width="15.375" customWidth="1"/>
-    <col min="10" max="10" width="10.125" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.08203125" customWidth="1"/>
+    <col min="11" max="11" width="10.58203125" customWidth="1"/>
     <col min="12" max="12" width="30.25" customWidth="1"/>
-    <col min="13" max="13" width="18.125" customWidth="1"/>
-    <col min="14" max="14" width="18.875" customWidth="1"/>
+    <col min="13" max="13" width="18.08203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
     <col min="15" max="15" width="10.75" customWidth="1"/>
-    <col min="16" max="16" width="11.125" customWidth="1"/>
+    <col min="16" max="16" width="11.08203125" customWidth="1"/>
     <col min="17" max="17" width="19.75" customWidth="1"/>
-    <col min="18" max="18" width="44.125" customWidth="1"/>
-    <col min="19" max="19" width="99.875" customWidth="1"/>
+    <col min="18" max="18" width="44.08203125" customWidth="1"/>
+    <col min="19" max="19" width="99.83203125" customWidth="1"/>
     <col min="20" max="20" width="17.75" style="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10284,7 +10003,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" spans="1:20">
+    <row r="3" spans="1:20" ht="18" customHeight="1">
       <c r="A3" s="58" t="s">
         <v>223</v>
       </c>
@@ -10346,7 +10065,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" spans="1:20">
+    <row r="4" spans="1:20" ht="18" customHeight="1">
       <c r="A4" s="58" t="s">
         <v>234</v>
       </c>
@@ -10408,7 +10127,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:20">
+    <row r="5" spans="1:20" ht="18" customHeight="1">
       <c r="A5" s="58" t="s">
         <v>54</v>
       </c>
@@ -10470,7 +10189,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" spans="1:20">
+    <row r="6" spans="1:20" ht="18" customHeight="1">
       <c r="A6" s="58" t="s">
         <v>55</v>
       </c>
@@ -10532,7 +10251,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:20">
+    <row r="7" spans="1:20" ht="18" customHeight="1">
       <c r="A7" s="58" t="s">
         <v>72</v>
       </c>
@@ -10594,7 +10313,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:20">
+    <row r="8" spans="1:20" ht="18" customHeight="1">
       <c r="A8" s="58" t="s">
         <v>73</v>
       </c>
@@ -10656,7 +10375,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:20">
+    <row r="9" spans="1:20" ht="18" customHeight="1">
       <c r="A9" s="58" t="s">
         <v>90</v>
       </c>
@@ -10718,7 +10437,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" spans="1:20">
+    <row r="10" spans="1:20" ht="18" customHeight="1">
       <c r="A10" s="58" t="s">
         <v>91</v>
       </c>
@@ -10780,7 +10499,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:20">
+    <row r="11" spans="1:20" ht="18" customHeight="1">
       <c r="A11" s="58" t="s">
         <v>56</v>
       </c>
@@ -10842,7 +10561,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" spans="1:20">
+    <row r="12" spans="1:20" ht="18" customHeight="1">
       <c r="A12" s="58" t="s">
         <v>57</v>
       </c>
@@ -10904,7 +10623,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:20">
+    <row r="13" spans="1:20" ht="18" customHeight="1">
       <c r="A13" s="58" t="s">
         <v>74</v>
       </c>
@@ -10966,7 +10685,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" spans="1:20">
+    <row r="14" spans="1:20" ht="18" customHeight="1">
       <c r="A14" s="58" t="s">
         <v>75</v>
       </c>
@@ -11028,7 +10747,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="1:20">
+    <row r="15" spans="1:20" ht="18" customHeight="1">
       <c r="A15" s="58" t="s">
         <v>92</v>
       </c>
@@ -11090,7 +10809,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" spans="1:20">
+    <row r="16" spans="1:20" ht="18" customHeight="1">
       <c r="A16" s="58" t="s">
         <v>93</v>
       </c>
@@ -11152,7 +10871,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:20">
+    <row r="17" spans="1:20" ht="18" customHeight="1">
       <c r="A17" s="58" t="s">
         <v>58</v>
       </c>
@@ -11214,7 +10933,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1" spans="1:20">
+    <row r="18" spans="1:20" ht="18" customHeight="1">
       <c r="A18" s="58" t="s">
         <v>316</v>
       </c>
@@ -11276,7 +10995,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1" spans="1:20">
+    <row r="19" spans="1:20" ht="18" customHeight="1">
       <c r="A19" s="58" t="s">
         <v>59</v>
       </c>
@@ -11338,7 +11057,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1" spans="1:20">
+    <row r="20" spans="1:20" ht="18" customHeight="1">
       <c r="A20" s="58" t="s">
         <v>323</v>
       </c>
@@ -11400,7 +11119,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" spans="1:20">
+    <row r="21" spans="1:20" ht="18" customHeight="1">
       <c r="A21" s="58" t="s">
         <v>76</v>
       </c>
@@ -11462,7 +11181,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" spans="1:20">
+    <row r="22" spans="1:20" ht="18" customHeight="1">
       <c r="A22" s="58" t="s">
         <v>331</v>
       </c>
@@ -11524,7 +11243,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" spans="1:20">
+    <row r="23" spans="1:20" ht="18" customHeight="1">
       <c r="A23" s="58" t="s">
         <v>77</v>
       </c>
@@ -11586,7 +11305,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" spans="1:20">
+    <row r="24" spans="1:20" ht="18" customHeight="1">
       <c r="A24" s="58" t="s">
         <v>336</v>
       </c>
@@ -11648,7 +11367,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:20">
+    <row r="25" spans="1:20" ht="18" customHeight="1">
       <c r="A25" s="58" t="s">
         <v>94</v>
       </c>
@@ -11710,7 +11429,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1" spans="1:20">
+    <row r="26" spans="1:20" ht="18" customHeight="1">
       <c r="A26" s="58" t="s">
         <v>344</v>
       </c>
@@ -11772,7 +11491,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1" spans="1:20">
+    <row r="27" spans="1:20" ht="18" customHeight="1">
       <c r="A27" s="58" t="s">
         <v>95</v>
       </c>
@@ -11834,7 +11553,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1" spans="1:20">
+    <row r="28" spans="1:20" ht="18" customHeight="1">
       <c r="A28" s="58" t="s">
         <v>353</v>
       </c>
@@ -11896,7 +11615,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" spans="1:20">
+    <row r="29" spans="1:20" ht="18" customHeight="1">
       <c r="A29" s="58" t="s">
         <v>60</v>
       </c>
@@ -11958,7 +11677,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1" spans="1:20">
+    <row r="30" spans="1:20" ht="18" customHeight="1">
       <c r="A30" s="58" t="s">
         <v>361</v>
       </c>
@@ -12020,7 +11739,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1" spans="1:20">
+    <row r="31" spans="1:20" ht="18" customHeight="1">
       <c r="A31" s="58" t="s">
         <v>61</v>
       </c>
@@ -12082,7 +11801,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1" spans="1:20">
+    <row r="32" spans="1:20" ht="18" customHeight="1">
       <c r="A32" s="58" t="s">
         <v>367</v>
       </c>
@@ -12144,7 +11863,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1" spans="1:20">
+    <row r="33" spans="1:20" ht="18" customHeight="1">
       <c r="A33" s="58" t="s">
         <v>78</v>
       </c>
@@ -12206,7 +11925,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1" spans="1:20">
+    <row r="34" spans="1:20" ht="18" customHeight="1">
       <c r="A34" s="58" t="s">
         <v>372</v>
       </c>
@@ -12268,7 +11987,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1" spans="1:20">
+    <row r="35" spans="1:20" ht="18" customHeight="1">
       <c r="A35" s="58" t="s">
         <v>79</v>
       </c>
@@ -12330,7 +12049,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1" spans="1:20">
+    <row r="36" spans="1:20" ht="18" customHeight="1">
       <c r="A36" s="58" t="s">
         <v>379</v>
       </c>
@@ -12392,7 +12111,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1" spans="1:20">
+    <row r="37" spans="1:20" ht="18" customHeight="1">
       <c r="A37" s="58" t="s">
         <v>96</v>
       </c>
@@ -12454,7 +12173,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1" spans="1:20">
+    <row r="38" spans="1:20" ht="18" customHeight="1">
       <c r="A38" s="58" t="s">
         <v>386</v>
       </c>
@@ -12516,7 +12235,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1" spans="1:20">
+    <row r="39" spans="1:20" ht="18" customHeight="1">
       <c r="A39" s="58" t="s">
         <v>97</v>
       </c>
@@ -12578,7 +12297,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1" spans="1:20">
+    <row r="40" spans="1:20" ht="18" customHeight="1">
       <c r="A40" s="58" t="s">
         <v>394</v>
       </c>
@@ -12640,7 +12359,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1" spans="1:20">
+    <row r="41" spans="1:20" ht="18" customHeight="1">
       <c r="A41" s="76" t="s">
         <v>397</v>
       </c>
@@ -12702,7 +12421,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1" spans="1:20">
+    <row r="42" spans="1:20" ht="18" customHeight="1">
       <c r="A42" s="58" t="s">
         <v>405</v>
       </c>
@@ -12764,7 +12483,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1" spans="1:20">
+    <row r="43" spans="1:20" ht="18" customHeight="1">
       <c r="A43" s="58" t="s">
         <v>408</v>
       </c>
@@ -12826,7 +12545,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1" spans="1:20">
+    <row r="44" spans="1:20" ht="18" customHeight="1">
       <c r="A44" s="58" t="s">
         <v>411</v>
       </c>
@@ -12888,7 +12607,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1" spans="1:20">
+    <row r="45" spans="1:20" ht="18" customHeight="1">
       <c r="A45" s="58" t="s">
         <v>414</v>
       </c>
@@ -12950,7 +12669,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1" spans="1:20">
+    <row r="46" spans="1:20" ht="18" customHeight="1">
       <c r="A46" s="58" t="s">
         <v>419</v>
       </c>
@@ -13012,7 +12731,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1" spans="1:20">
+    <row r="47" spans="1:20" ht="18" customHeight="1">
       <c r="A47" s="58" t="s">
         <v>422</v>
       </c>
@@ -13074,7 +12793,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1" spans="1:20">
+    <row r="48" spans="1:20" ht="18" customHeight="1">
       <c r="A48" s="58" t="s">
         <v>426</v>
       </c>
@@ -13136,7 +12855,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1" spans="1:20">
+    <row r="49" spans="1:20" ht="18" customHeight="1">
       <c r="A49" s="58" t="s">
         <v>429</v>
       </c>
@@ -13198,7 +12917,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1" spans="1:20">
+    <row r="50" spans="1:20" ht="18" customHeight="1">
       <c r="A50" s="58" t="s">
         <v>433</v>
       </c>
@@ -13260,7 +12979,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1" spans="1:20">
+    <row r="51" spans="1:20" ht="18" customHeight="1">
       <c r="A51" s="58" t="s">
         <v>436</v>
       </c>
@@ -13322,7 +13041,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1" spans="1:20">
+    <row r="52" spans="1:20" ht="18" customHeight="1">
       <c r="A52" s="58" t="s">
         <v>439</v>
       </c>
@@ -13384,7 +13103,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1" spans="1:20">
+    <row r="53" spans="1:20" ht="18" customHeight="1">
       <c r="A53" s="58" t="s">
         <v>442</v>
       </c>
@@ -13446,7 +13165,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1" spans="1:20">
+    <row r="54" spans="1:20" ht="18" customHeight="1">
       <c r="A54" s="58" t="s">
         <v>447</v>
       </c>
@@ -13508,7 +13227,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1" spans="1:20">
+    <row r="55" spans="1:20" ht="18" customHeight="1">
       <c r="A55" s="58" t="s">
         <v>450</v>
       </c>
@@ -13570,7 +13289,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1" spans="1:20">
+    <row r="56" spans="1:20" ht="18" customHeight="1">
       <c r="A56" s="58" t="s">
         <v>455</v>
       </c>
@@ -13632,7 +13351,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1" spans="1:20">
+    <row r="57" spans="1:20" ht="18" customHeight="1">
       <c r="A57" s="58" t="s">
         <v>458</v>
       </c>
@@ -13694,7 +13413,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1" spans="1:20">
+    <row r="58" spans="1:20" ht="18" customHeight="1">
       <c r="A58" s="58" t="s">
         <v>462</v>
       </c>
@@ -13756,7 +13475,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1" spans="1:20">
+    <row r="59" spans="1:20" ht="18" customHeight="1">
       <c r="A59" s="58" t="s">
         <v>465</v>
       </c>
@@ -13818,7 +13537,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1" spans="1:20">
+    <row r="60" spans="1:20" ht="18" customHeight="1">
       <c r="A60" s="58" t="s">
         <v>468</v>
       </c>
@@ -13881,27 +13600,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="13.375" customWidth="1"/>
-    <col min="2" max="2" width="20.125" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.08203125" customWidth="1"/>
     <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="4" max="4" width="12.75" customWidth="1"/>
-    <col min="5" max="5" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
     <col min="6" max="7" width="14.25" customWidth="1"/>
     <col min="8" max="8" width="11.25" customWidth="1"/>
-    <col min="9" max="9" width="12.625" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-    <col min="11" max="11" width="36.625" style="28" customWidth="1"/>
+    <col min="9" max="9" width="12.58203125" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" customWidth="1"/>
+    <col min="11" max="11" width="36.58203125" style="28" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14475,7 +14193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="11:12">
+    <row r="16" spans="1:12">
       <c r="K16"/>
       <c r="L16"/>
     </row>
@@ -14628,26 +14346,24 @@
       <c r="L53"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="23.125" customWidth="1"/>
-    <col min="3" max="3" width="26.625" customWidth="1"/>
-    <col min="4" max="4" width="26.625" customWidth="1"/>
-    <col min="5" max="5" width="42.625" customWidth="1"/>
+    <col min="2" max="2" width="23.08203125" customWidth="1"/>
+    <col min="3" max="4" width="26.58203125" customWidth="1"/>
+    <col min="5" max="5" width="42.58203125" customWidth="1"/>
     <col min="6" max="6" width="57" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="14" t="s">
         <v>496</v>
       </c>
@@ -14667,7 +14383,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="65" t="s">
         <v>501</v>
       </c>
@@ -15056,28 +14772,27 @@
       <c r="G26" s="66"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="21.625" customWidth="1"/>
-    <col min="3" max="3" width="18.625" customWidth="1"/>
+    <col min="2" max="2" width="21.58203125" customWidth="1"/>
+    <col min="3" max="3" width="18.58203125" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="6" width="19.25" customWidth="1"/>
     <col min="7" max="7" width="14.25" customWidth="1"/>
-    <col min="8" max="8" width="14.875" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="11.625" customWidth="1"/>
-    <col min="12" max="12" width="9.625" customWidth="1"/>
-    <col min="13" max="13" width="44.125" style="28" customWidth="1"/>
+    <col min="11" max="11" width="11.58203125" customWidth="1"/>
+    <col min="12" max="12" width="9.58203125" customWidth="1"/>
+    <col min="13" max="13" width="44.08203125" style="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -16187,28 +15902,27 @@
         <v>606</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1" spans="2:2">
+    <row r="28" spans="1:13" ht="17.25" customHeight="1">
       <c r="B28" s="60"/>
     </row>
-    <row r="29" ht="17.25" customHeight="1" spans="2:2">
+    <row r="29" spans="1:13" ht="17.25" customHeight="1">
       <c r="B29" s="61"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="12.625" customWidth="1"/>
-    <col min="3" max="3" width="7.625" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.58203125" customWidth="1"/>
     <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="6" width="15.125" customWidth="1"/>
+    <col min="5" max="6" width="15.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -16378,11 +16092,11 @@
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="90" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>623</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>624</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -16405,27 +16119,26 @@
       <c r="I7" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="18.125" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="3" width="9.375" customWidth="1"/>
-    <col min="4" max="4" width="17.375" customWidth="1"/>
-    <col min="5" max="5" width="34.625" customWidth="1"/>
-    <col min="6" max="6" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="34.58203125" customWidth="1"/>
+    <col min="6" max="6" width="11.08203125" customWidth="1"/>
     <col min="7" max="7" width="15.25" customWidth="1"/>
-    <col min="8" max="8" width="13.875" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
-    <col min="10" max="10" width="14.875" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.58203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
     <col min="11" max="11" width="34.5" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
@@ -16438,10 +16151,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>201</v>
@@ -16449,16 +16162,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>629</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>220</v>
@@ -16466,7 +16179,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="44" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B3" s="44" t="s">
         <v>2</v>
@@ -16478,12 +16191,12 @@
         <v>0</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="47" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B4" s="47" t="s">
         <v>3</v>
@@ -16495,24 +16208,24 @@
         <v>0</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="44" t="s">
+        <v>633</v>
+      </c>
+      <c r="B5" s="44" t="s">
         <v>634</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="C5" s="45">
+        <v>1</v>
+      </c>
+      <c r="D5" s="45">
+        <v>0</v>
+      </c>
+      <c r="E5" s="46" t="s">
         <v>635</v>
-      </c>
-      <c r="C5" s="45">
-        <v>1</v>
-      </c>
-      <c r="D5" s="45">
-        <v>0</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -16520,16 +16233,16 @@
         <v>307</v>
       </c>
       <c r="B6" s="44" t="s">
+        <v>636</v>
+      </c>
+      <c r="C6" s="45">
+        <v>1</v>
+      </c>
+      <c r="D6" s="45">
+        <v>0</v>
+      </c>
+      <c r="E6" s="46" t="s">
         <v>637</v>
-      </c>
-      <c r="C6" s="45">
-        <v>1</v>
-      </c>
-      <c r="D6" s="45">
-        <v>0</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -16537,16 +16250,16 @@
         <v>288</v>
       </c>
       <c r="B7" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C7" s="45">
+        <v>1</v>
+      </c>
+      <c r="D7" s="45">
+        <v>0</v>
+      </c>
+      <c r="E7" s="46" t="s">
         <v>639</v>
-      </c>
-      <c r="C7" s="45">
-        <v>1</v>
-      </c>
-      <c r="D7" s="45">
-        <v>0</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -16554,16 +16267,16 @@
         <v>349</v>
       </c>
       <c r="B8" s="44" t="s">
+        <v>640</v>
+      </c>
+      <c r="C8" s="45">
+        <v>1</v>
+      </c>
+      <c r="D8" s="49" t="s">
         <v>641</v>
       </c>
-      <c r="C8" s="45">
-        <v>1</v>
-      </c>
-      <c r="D8" s="49" t="s">
+      <c r="E8" s="46" t="s">
         <v>642</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -16571,16 +16284,16 @@
         <v>391</v>
       </c>
       <c r="B9" s="44" t="s">
+        <v>643</v>
+      </c>
+      <c r="C9" s="45">
+        <v>1</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E9" s="46" t="s">
         <v>644</v>
-      </c>
-      <c r="C9" s="45">
-        <v>1</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -16588,16 +16301,16 @@
         <v>340</v>
       </c>
       <c r="B10" s="44" t="s">
+        <v>645</v>
+      </c>
+      <c r="C10" s="45">
+        <v>1</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E10" s="46" t="s">
         <v>646</v>
-      </c>
-      <c r="C10" s="45">
-        <v>1</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -16605,16 +16318,16 @@
         <v>245</v>
       </c>
       <c r="B11" s="44" t="s">
+        <v>647</v>
+      </c>
+      <c r="C11" s="45">
+        <v>1</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E11" s="46" t="s">
         <v>648</v>
-      </c>
-      <c r="C11" s="45">
-        <v>1</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E11" s="46" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -16622,16 +16335,16 @@
         <v>240</v>
       </c>
       <c r="B12" s="44" t="s">
+        <v>649</v>
+      </c>
+      <c r="C12" s="45">
+        <v>1</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E12" s="46" t="s">
         <v>650</v>
-      </c>
-      <c r="C12" s="45">
-        <v>1</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -16639,16 +16352,16 @@
         <v>250</v>
       </c>
       <c r="B13" s="44" t="s">
+        <v>651</v>
+      </c>
+      <c r="C13" s="49">
+        <v>0</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E13" s="46" t="s">
         <v>652</v>
-      </c>
-      <c r="C13" s="49">
-        <v>0</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E13" s="46" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -16656,16 +16369,16 @@
         <v>400</v>
       </c>
       <c r="B14" s="44" t="s">
+        <v>653</v>
+      </c>
+      <c r="C14" s="49">
+        <v>0</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E14" s="46" t="s">
         <v>654</v>
-      </c>
-      <c r="C14" s="49">
-        <v>0</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -16673,16 +16386,16 @@
         <v>259</v>
       </c>
       <c r="B15" s="44" t="s">
+        <v>655</v>
+      </c>
+      <c r="C15" s="49">
+        <v>0</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E15" s="46" t="s">
         <v>656</v>
-      </c>
-      <c r="C15" s="49">
-        <v>0</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E15" s="46" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -16690,16 +16403,16 @@
         <v>264</v>
       </c>
       <c r="B16" s="44" t="s">
+        <v>657</v>
+      </c>
+      <c r="C16" s="49">
+        <v>0</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E16" s="46" t="s">
         <v>658</v>
-      </c>
-      <c r="C16" s="49">
-        <v>0</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E16" s="46" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -16707,16 +16420,16 @@
         <v>255</v>
       </c>
       <c r="B17" s="44" t="s">
+        <v>659</v>
+      </c>
+      <c r="C17" s="49">
+        <v>0</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E17" s="46" t="s">
         <v>660</v>
-      </c>
-      <c r="C17" s="49">
-        <v>0</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E17" s="46" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -16724,16 +16437,16 @@
         <v>301</v>
       </c>
       <c r="B18" s="44" t="s">
+        <v>661</v>
+      </c>
+      <c r="C18" s="45">
+        <v>1</v>
+      </c>
+      <c r="D18" s="50" t="s">
         <v>662</v>
       </c>
-      <c r="C18" s="45">
-        <v>1</v>
-      </c>
-      <c r="D18" s="50" t="s">
+      <c r="E18" s="46" t="s">
         <v>663</v>
-      </c>
-      <c r="E18" s="46" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -16741,16 +16454,16 @@
         <v>383</v>
       </c>
       <c r="B19" s="44" t="s">
+        <v>664</v>
+      </c>
+      <c r="C19" s="45">
+        <v>1</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>662</v>
+      </c>
+      <c r="E19" s="46" t="s">
         <v>665</v>
-      </c>
-      <c r="C19" s="45">
-        <v>1</v>
-      </c>
-      <c r="D19" s="50" t="s">
-        <v>663</v>
-      </c>
-      <c r="E19" s="46" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -16758,16 +16471,16 @@
         <v>488</v>
       </c>
       <c r="B20" s="51" t="s">
+        <v>666</v>
+      </c>
+      <c r="C20" s="45">
+        <v>1</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>667</v>
       </c>
-      <c r="C20" s="45">
-        <v>1</v>
-      </c>
-      <c r="D20" s="18" t="s">
+      <c r="E20" s="52" t="s">
         <v>668</v>
-      </c>
-      <c r="E20" s="52" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -16775,16 +16488,16 @@
         <v>493</v>
       </c>
       <c r="B21" s="53" t="s">
+        <v>669</v>
+      </c>
+      <c r="C21" s="45">
+        <v>1</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>667</v>
+      </c>
+      <c r="E21" s="52" t="s">
         <v>670</v>
-      </c>
-      <c r="C21" s="45">
-        <v>1</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>668</v>
-      </c>
-      <c r="E21" s="52" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -16792,16 +16505,16 @@
         <v>491</v>
       </c>
       <c r="B22" s="44" t="s">
+        <v>671</v>
+      </c>
+      <c r="C22" s="49">
+        <v>0</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E22" s="46" t="s">
         <v>672</v>
-      </c>
-      <c r="C22" s="49">
-        <v>0</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E22" s="46" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -16815,61 +16528,61 @@
         <v>0</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="44" t="s">
+        <v>674</v>
+      </c>
+      <c r="B24" s="44" t="s">
         <v>675</v>
       </c>
-      <c r="B24" s="44" t="s">
+      <c r="C24" s="49">
+        <v>0</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="E24" s="46" t="s">
         <v>676</v>
-      </c>
-      <c r="C24" s="49">
-        <v>0</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E24" s="46" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="44" t="s">
+        <v>677</v>
+      </c>
+      <c r="B25" s="44" t="s">
         <v>678</v>
       </c>
-      <c r="B25" s="44" t="s">
+      <c r="C25" s="45">
+        <v>1</v>
+      </c>
+      <c r="D25" s="45">
+        <v>0</v>
+      </c>
+      <c r="E25" s="46" t="s">
         <v>679</v>
-      </c>
-      <c r="C25" s="45">
-        <v>1</v>
-      </c>
-      <c r="D25" s="45">
-        <v>0</v>
-      </c>
-      <c r="E25" s="46" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="44" t="s">
+        <v>680</v>
+      </c>
+      <c r="B26" s="44" t="s">
         <v>681</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="C26" s="45">
+        <v>1</v>
+      </c>
+      <c r="D26" s="45">
+        <v>0</v>
+      </c>
+      <c r="E26" s="46" t="s">
         <v>682</v>
-      </c>
-      <c r="C26" s="45">
-        <v>1</v>
-      </c>
-      <c r="D26" s="45">
-        <v>0</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -16877,16 +16590,16 @@
         <v>622</v>
       </c>
       <c r="B27" s="44" t="s">
+        <v>683</v>
+      </c>
+      <c r="C27" s="45">
+        <v>1</v>
+      </c>
+      <c r="D27" s="45">
+        <v>0</v>
+      </c>
+      <c r="E27" s="54" t="s">
         <v>684</v>
-      </c>
-      <c r="C27" s="45">
-        <v>1</v>
-      </c>
-      <c r="D27" s="45">
-        <v>0</v>
-      </c>
-      <c r="E27" s="54" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -16894,44 +16607,43 @@
         <v>617</v>
       </c>
       <c r="B28" s="51" t="s">
+        <v>685</v>
+      </c>
+      <c r="C28" s="45">
+        <v>1</v>
+      </c>
+      <c r="D28" s="45">
+        <v>0</v>
+      </c>
+      <c r="E28" s="55" t="s">
         <v>686</v>
       </c>
-      <c r="C28" s="45">
-        <v>1</v>
-      </c>
-      <c r="D28" s="45">
-        <v>0</v>
-      </c>
-      <c r="E28" s="55" t="s">
-        <v>687</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.25" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="6" max="6" width="12.08203125" customWidth="1"/>
+    <col min="7" max="7" width="13.58203125" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>1</v>
@@ -16940,80 +16652,80 @@
         <v>190</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>689</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>690</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>691</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>692</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>694</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>697</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>698</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>699</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>700</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>701</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>703</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>705</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>706</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H3" s="3">
         <v>1</v>
@@ -17027,25 +16739,25 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
@@ -17059,25 +16771,25 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>712</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>713</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H5" s="3">
         <v>1</v>
@@ -17091,25 +16803,25 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>715</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>716</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H6" s="3">
         <v>1</v>
@@ -17123,25 +16835,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>718</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>719</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>175</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H7" s="3">
         <v>1</v>
@@ -17155,25 +16867,25 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>721</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>722</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>175</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H8" s="3">
         <v>1</v>
@@ -17187,31 +16899,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>723</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>724</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>184</v>
       </c>
       <c r="D9" s="18" t="s">
+        <v>724</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>725</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>726</v>
       </c>
       <c r="J9" s="18" t="s">
         <v>399</v>
@@ -17219,31 +16931,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>730</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>731</v>
       </c>
       <c r="J10" s="18" t="s">
         <v>399</v>
@@ -17251,25 +16963,25 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>733</v>
-      </c>
       <c r="C11" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>730</v>
-      </c>
       <c r="F11" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H11" s="3">
         <v>1</v>
@@ -17281,25 +16993,25 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>736</v>
-      </c>
       <c r="F12" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H12" s="3">
         <v>1</v>
@@ -17311,25 +17023,25 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>739</v>
-      </c>
       <c r="F13" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H13" s="3">
         <v>1</v>
@@ -17341,25 +17053,25 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>743</v>
-      </c>
       <c r="F14" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H14" s="3">
         <v>1</v>
@@ -17371,25 +17083,25 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>746</v>
-      </c>
       <c r="F15" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H15" s="3">
         <v>1</v>
@@ -17401,25 +17113,25 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>749</v>
-      </c>
       <c r="F16" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H16" s="3">
         <v>1</v>
@@ -17431,25 +17143,25 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>752</v>
-      </c>
       <c r="F17" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H17" s="3">
         <v>1</v>
@@ -17461,25 +17173,25 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>755</v>
-      </c>
       <c r="F18" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="H18" s="3">
         <v>1</v>
@@ -17491,26 +17203,26 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>758</v>
-      </c>
       <c r="F19" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>709</v>
-      </c>
       <c r="H19" s="3">
         <v>1</v>
       </c>
@@ -17520,7 +17232,7 @@
       <c r="J19" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D625FD-89CC-44E6-B045-207334920C28}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A9658E-E059-4837-83BD-345348F2F6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="16860" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -31,11 +31,16 @@
     <sheet name="Item" sheetId="14" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="1383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3134" uniqueCount="1393">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -7084,6 +7089,463 @@
   </si>
   <si>
     <t>Mon_02</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>분열</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭발</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_Split</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_Explode</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피해횟수에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수치가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t>.  0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되었을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>블롭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마리로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분열한다.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수치가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수치가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자폭을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시전하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ari"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사망한다.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintain</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decrease</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어도</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -7091,7 +7553,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -7248,6 +7710,26 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="ari"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="ari"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -7722,7 +8204,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -8166,6 +8648,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8174,9 +8665,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -8631,14 +9119,14 @@
       <c r="W3" s="123" t="s">
         <v>1247</v>
       </c>
-      <c r="X3" s="153" t="s">
+      <c r="X3" s="156" t="s">
         <v>1248</v>
       </c>
-      <c r="Y3" s="154"/>
-      <c r="Z3" s="154"/>
-      <c r="AA3" s="154"/>
-      <c r="AB3" s="154"/>
-      <c r="AC3" s="155"/>
+      <c r="Y3" s="157"/>
+      <c r="Z3" s="157"/>
+      <c r="AA3" s="157"/>
+      <c r="AB3" s="157"/>
+      <c r="AC3" s="158"/>
     </row>
     <row r="4" spans="1:29" ht="76.5" customHeight="1" thickBot="1">
       <c r="A4" s="124" t="s">
@@ -8710,14 +9198,14 @@
       <c r="W4" s="125" t="s">
         <v>1253</v>
       </c>
-      <c r="X4" s="153" t="s">
+      <c r="X4" s="156" t="s">
         <v>1254</v>
       </c>
-      <c r="Y4" s="154"/>
-      <c r="Z4" s="154"/>
-      <c r="AA4" s="154"/>
-      <c r="AB4" s="154"/>
-      <c r="AC4" s="155"/>
+      <c r="Y4" s="157"/>
+      <c r="Z4" s="157"/>
+      <c r="AA4" s="157"/>
+      <c r="AB4" s="157"/>
+      <c r="AC4" s="158"/>
     </row>
     <row r="5" spans="1:29" ht="76.5" customHeight="1" thickBot="1">
       <c r="A5" s="124" t="s">
@@ -8789,14 +9277,14 @@
       <c r="W5" s="125" t="s">
         <v>1259</v>
       </c>
-      <c r="X5" s="153" t="s">
+      <c r="X5" s="156" t="s">
         <v>1260</v>
       </c>
-      <c r="Y5" s="154"/>
-      <c r="Z5" s="154"/>
-      <c r="AA5" s="154"/>
-      <c r="AB5" s="154"/>
-      <c r="AC5" s="155"/>
+      <c r="Y5" s="157"/>
+      <c r="Z5" s="157"/>
+      <c r="AA5" s="157"/>
+      <c r="AB5" s="157"/>
+      <c r="AC5" s="158"/>
     </row>
     <row r="6" spans="1:29" ht="76.5" customHeight="1" thickBot="1">
       <c r="A6" s="124" t="s">
@@ -8868,14 +9356,14 @@
       <c r="W6" s="125" t="s">
         <v>1266</v>
       </c>
-      <c r="X6" s="153" t="s">
+      <c r="X6" s="156" t="s">
         <v>1267</v>
       </c>
-      <c r="Y6" s="154"/>
-      <c r="Z6" s="154"/>
-      <c r="AA6" s="154"/>
-      <c r="AB6" s="154"/>
-      <c r="AC6" s="155"/>
+      <c r="Y6" s="157"/>
+      <c r="Z6" s="157"/>
+      <c r="AA6" s="157"/>
+      <c r="AB6" s="157"/>
+      <c r="AC6" s="158"/>
     </row>
     <row r="7" spans="1:29" ht="76.5" customHeight="1" thickBot="1">
       <c r="A7" s="124" t="s">
@@ -8947,14 +9435,14 @@
       <c r="W7" s="125" t="s">
         <v>1272</v>
       </c>
-      <c r="X7" s="153" t="s">
+      <c r="X7" s="156" t="s">
         <v>1273</v>
       </c>
-      <c r="Y7" s="154"/>
-      <c r="Z7" s="154"/>
-      <c r="AA7" s="154"/>
-      <c r="AB7" s="154"/>
-      <c r="AC7" s="155"/>
+      <c r="Y7" s="157"/>
+      <c r="Z7" s="157"/>
+      <c r="AA7" s="157"/>
+      <c r="AB7" s="157"/>
+      <c r="AC7" s="158"/>
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="45"/>
@@ -9216,7 +9704,7 @@
       <c r="A4" s="21" t="s">
         <v>494</v>
       </c>
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="153" t="s">
         <v>1382</v>
       </c>
       <c r="C4" s="16">
@@ -16033,7 +16521,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -16050,7 +16538,7 @@
     <col min="20" max="20" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>94</v>
       </c>
@@ -16063,56 +16551,59 @@
       <c r="D1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="57" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
         <v>113</v>
       </c>
@@ -16125,56 +16616,59 @@
       <c r="D2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="57" t="s">
+        <v>1392</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:21">
       <c r="A3" s="3" t="s">
         <v>131</v>
       </c>
@@ -16185,35 +16679,35 @@
         <v>133</v>
       </c>
       <c r="D3" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E3" s="55">
+        <v>0</v>
+      </c>
+      <c r="F3" s="55">
         <v>8</v>
       </c>
-      <c r="F3" s="55">
+      <c r="G3" s="55">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H3" s="55">
-        <v>0.3</v>
-      </c>
       <c r="I3" s="55">
+        <v>0.2</v>
+      </c>
+      <c r="J3" s="55">
         <v>0.1</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="K3" s="59" t="s">
         <v>1369</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
       <c r="N3" s="3">
         <v>0</v>
       </c>
@@ -16235,8 +16729,11 @@
       <c r="T3" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="U3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="3" t="s">
         <v>138</v>
       </c>
@@ -16247,35 +16744,35 @@
         <v>133</v>
       </c>
       <c r="D4" s="3">
+        <v>15</v>
+      </c>
+      <c r="E4" s="55">
+        <v>0</v>
+      </c>
+      <c r="F4" s="55">
+        <v>5</v>
+      </c>
+      <c r="G4" s="55">
         <v>10</v>
       </c>
-      <c r="E4" s="55">
-        <v>5</v>
-      </c>
-      <c r="F4" s="55">
-        <v>10</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H4" s="55">
-        <v>0.2</v>
-      </c>
       <c r="I4" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="J4" s="55">
         <v>0.05</v>
       </c>
-      <c r="J4" s="59" t="s">
+      <c r="K4" s="59" t="s">
         <v>1370</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="M4" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="M4" s="3">
-        <v>0</v>
-      </c>
       <c r="N4" s="3">
         <v>0</v>
       </c>
@@ -16297,8 +16794,11 @@
       <c r="T4" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="U4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="3" t="s">
         <v>143</v>
       </c>
@@ -16309,38 +16809,38 @@
         <v>133</v>
       </c>
       <c r="D5" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="55">
+        <v>0</v>
+      </c>
+      <c r="F5" s="55">
         <v>12</v>
       </c>
-      <c r="F5" s="55">
+      <c r="G5" s="55">
         <v>18</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H5" s="55">
-        <v>0.2</v>
-      </c>
       <c r="I5" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="55">
         <v>0.05</v>
       </c>
-      <c r="J5" s="59" t="s">
+      <c r="K5" s="59" t="s">
         <v>1369</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="N5" s="3">
-        <v>0</v>
-      </c>
       <c r="O5" s="3">
         <v>0</v>
       </c>
@@ -16359,8 +16859,11 @@
       <c r="T5" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="U5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="3" t="s">
         <v>149</v>
       </c>
@@ -16374,35 +16877,35 @@
         <v>20</v>
       </c>
       <c r="E6" s="55">
+        <v>0</v>
+      </c>
+      <c r="F6" s="55">
         <v>12</v>
       </c>
-      <c r="F6" s="55">
+      <c r="G6" s="55">
         <v>18</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H6" s="55">
-        <v>0.2</v>
-      </c>
       <c r="I6" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="J6" s="55">
         <v>0.05</v>
       </c>
-      <c r="J6" s="59" t="s">
+      <c r="K6" s="59" t="s">
         <v>1369</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="N6" s="3">
-        <v>0</v>
-      </c>
       <c r="O6" s="3">
         <v>0</v>
       </c>
@@ -16421,8 +16924,11 @@
       <c r="T6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="U6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="3" t="s">
         <v>153</v>
       </c>
@@ -16436,32 +16942,32 @@
         <v>35</v>
       </c>
       <c r="E7" s="55">
+        <v>0</v>
+      </c>
+      <c r="F7" s="55">
         <v>18</v>
       </c>
-      <c r="F7" s="55">
+      <c r="G7" s="55">
         <v>25</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="55">
-        <v>0.2</v>
-      </c>
       <c r="I7" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="J7" s="55">
         <v>0.05</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="K7" s="59" t="s">
         <v>1370</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
       <c r="N7" s="3">
         <v>0</v>
       </c>
@@ -16483,8 +16989,11 @@
       <c r="T7" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="U7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="59" t="s">
         <v>1380</v>
       </c>
@@ -16495,35 +17004,35 @@
         <v>133</v>
       </c>
       <c r="D8" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E8" s="3">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3">
         <v>15</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="H8" s="55">
-        <v>0.2</v>
-      </c>
       <c r="I8" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="J8" s="55">
         <v>0.05</v>
       </c>
-      <c r="J8" s="59" t="s">
+      <c r="K8" s="59" t="s">
         <v>1371</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>1374</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -16545,8 +17054,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="3" t="s">
         <v>159</v>
       </c>
@@ -16560,11 +17072,9 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="56"/>
+      <c r="H9" s="3"/>
       <c r="I9" s="56"/>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
+      <c r="J9" s="56"/>
       <c r="K9" s="3">
         <v>0</v>
       </c>
@@ -16595,8 +17105,11 @@
       <c r="T9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:20">
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="3" t="s">
         <v>160</v>
       </c>
@@ -16610,11 +17123,9 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="56"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="56"/>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
+      <c r="J10" s="56"/>
       <c r="K10" s="3">
         <v>0</v>
       </c>
@@ -16645,8 +17156,11 @@
       <c r="T10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="3" t="s">
         <v>161</v>
       </c>
@@ -16660,11 +17174,9 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="56"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="56"/>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
+      <c r="J11" s="56"/>
       <c r="K11" s="3">
         <v>0</v>
       </c>
@@ -16695,8 +17207,11 @@
       <c r="T11" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="15" t="s">
         <v>162</v>
       </c>
@@ -16709,12 +17224,10 @@
       <c r="D12" s="3"/>
       <c r="E12" s="55"/>
       <c r="F12" s="55"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="3"/>
       <c r="I12" s="55"/>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
+      <c r="J12" s="55"/>
       <c r="K12" s="3">
         <v>0</v>
       </c>
@@ -16745,8 +17258,11 @@
       <c r="T12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="3" t="s">
         <v>170</v>
       </c>
@@ -16762,9 +17278,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
+      <c r="J13" s="3"/>
       <c r="K13" s="3">
         <v>0</v>
       </c>
@@ -16795,8 +17309,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="3" t="s">
         <v>171</v>
       </c>
@@ -16810,22 +17327,22 @@
         <v>142</v>
       </c>
       <c r="E14" s="55">
+        <v>0</v>
+      </c>
+      <c r="F14" s="55">
         <v>36</v>
       </c>
-      <c r="F14" s="55">
+      <c r="G14" s="55">
         <v>48</v>
       </c>
-      <c r="G14" s="59" t="s">
+      <c r="H14" s="59" t="s">
         <v>1381</v>
       </c>
-      <c r="H14" s="55">
+      <c r="I14" s="55">
         <v>0.7</v>
       </c>
-      <c r="I14" s="55">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="55">
+        <v>1</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -16857,47 +17374,26 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="Q15"/>
       <c r="R15"/>
       <c r="S15"/>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:21">
       <c r="Q16"/>
       <c r="R16"/>
       <c r="S16"/>
     </row>
-    <row r="17" spans="17:19">
-      <c r="Q17"/>
-      <c r="R17"/>
-      <c r="S17"/>
-    </row>
-    <row r="18" spans="17:19">
-      <c r="Q18"/>
-      <c r="R18"/>
-      <c r="S18"/>
-    </row>
-    <row r="19" spans="17:19">
-      <c r="Q19"/>
-      <c r="R19"/>
-      <c r="S19"/>
-    </row>
-    <row r="20" spans="17:19">
-      <c r="Q20"/>
-      <c r="R20"/>
-      <c r="S20"/>
-    </row>
-    <row r="21" spans="17:19">
-      <c r="Q21"/>
-      <c r="R21"/>
-      <c r="S21"/>
-    </row>
-    <row r="22" spans="17:19">
-      <c r="Q22"/>
-      <c r="R22"/>
-      <c r="S22"/>
-    </row>
+    <row r="17" customFormat="1"/>
+    <row r="18" customFormat="1"/>
+    <row r="19" customFormat="1"/>
+    <row r="20" customFormat="1"/>
+    <row r="21" customFormat="1"/>
+    <row r="22" customFormat="1"/>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25989,7 +26485,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.125" style="91" customWidth="1"/>
@@ -26421,6 +26917,34 @@
       </c>
       <c r="D30" s="89" t="s">
         <v>1164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="85" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B31" s="154" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C31" s="59" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D31" s="155" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="85" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B32" s="154" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C32" s="59" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D32" s="155" t="s">
+        <v>1388</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydjh1\Desktop\지원사업\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07899D19-798A-42FE-8733-495135095D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A357E1FC-592E-4A93-9A6C-5EFF3D54B1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -6571,12 +6571,6 @@
     <t>Rune_70</t>
   </si>
   <si>
-    <t>이네스, 상냥한 집행자
-밝은 얼굴로 아군을 보살핍니다.
-다정하게 아군을 감싸지만, 그들을 위협하는 존재 앞에서는 웃음마저 차갑게 식어갑니다.
-아군에게 이로운 효과가 부여되면 턴 종료 시 신앙을 1 획득합니다.</t>
-  </si>
-  <si>
     <t>Rune_71</t>
   </si>
   <si>
@@ -7605,6 +7599,10 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
+    <t>Rune_60</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -7613,7 +7611,242 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">"더 강한 놈, 더 열렬한 전투! 내가 쓰러트리지 못할 적은 없다."
+      <t xml:space="preserve">"흔들리는 검 끝은 죽음을 부를 뿐."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>침착하고 냉철한 검사입니다.
+모든 전투 기술을 끊임없이 배우고 검술의 극의에 닿고자 합니다.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슬롯에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>행동하면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기세를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>획득합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">"더 강한 놈, 더 열렬한 전투!"
 호전적이고 거침없이 돌격하는 전사입니다.
 전투를 통해 자신의 한계를 시험하고 강함을 증명하고자 합니다.
 </t>
@@ -7821,10 +8054,6 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>Rune_60</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -7833,7 +8062,9 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">"흔들리는 검 끝은 죽음을 부를 뿐."
+      <t xml:space="preserve">"니아, 제발 내 곁에서 떨어지지 마!"
+겁이 많고 소심한 소환사입니다.
+자신의 나약함을 극복하고자 소환수와 함께 전투를 진행합니다.
 </t>
     </r>
     <r>
@@ -7854,8 +8085,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>침착하고 냉철한 검사입니다.
-모든 전투 기술을 끊임없이 배우고 검술의 극의에 닿고자 합니다.</t>
+      <t>한</t>
     </r>
     <r>
       <rPr>
@@ -7864,8 +8094,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -7875,7 +8104,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>한</t>
+      <t>턴에</t>
     </r>
     <r>
       <rPr>
@@ -7894,7 +8123,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>슬롯에서</t>
+      <t>코스트를</t>
     </r>
     <r>
       <rPr>
@@ -7903,7 +8132,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 3</t>
+      <t xml:space="preserve"> 8 </t>
     </r>
     <r>
       <rPr>
@@ -7913,7 +8142,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>회</t>
+      <t>이상</t>
     </r>
     <r>
       <rPr>
@@ -7932,7 +8161,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>이상</t>
+      <t>소모하면</t>
     </r>
     <r>
       <rPr>
@@ -7951,7 +8180,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>행동하면</t>
+      <t>턴</t>
     </r>
     <r>
       <rPr>
@@ -7970,7 +8199,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>턴</t>
+      <t>종료</t>
     </r>
     <r>
       <rPr>
@@ -7989,7 +8218,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>종료</t>
+      <t>시</t>
     </r>
     <r>
       <rPr>
@@ -8008,7 +8237,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>시</t>
+      <t>에테르를</t>
     </r>
     <r>
       <rPr>
@@ -8017,7 +8246,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> 1 </t>
     </r>
     <r>
       <rPr>
@@ -8027,7 +8256,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>기세를</t>
+      <t>획득합니다</t>
     </r>
     <r>
       <rPr>
@@ -8036,8 +8265,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 1 </t>
-    </r>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8046,7 +8278,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>획득합니다</t>
+      <t>이네스</t>
     </r>
     <r>
       <rPr>
@@ -8055,11 +8287,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve">, </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8068,14 +8297,14 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>"너무 무서워…</t>
+      <t>상냥한</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="3"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8087,10 +8316,8 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">그러니까 니아, 제발 내 곁에서 떠어지지 마!"
-겁이 많고 소심한 소환사입니다.
-자신의 나약함을 극복하고자 소환수와 함께 전투를 진행합니다.
-</t>
+      <t>집행자
+밝은</t>
     </r>
     <r>
       <rPr>
@@ -8099,8 +8326,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -8110,7 +8336,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>한</t>
+      <t>얼굴로</t>
     </r>
     <r>
       <rPr>
@@ -8129,7 +8355,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>턴에</t>
+      <t>아군을</t>
     </r>
     <r>
       <rPr>
@@ -8148,7 +8374,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>코스트를</t>
+      <t>보살핍니다</t>
     </r>
     <r>
       <rPr>
@@ -8157,7 +8383,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 8 </t>
+      <t xml:space="preserve">.
+</t>
     </r>
     <r>
       <rPr>
@@ -8167,7 +8394,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>이상</t>
+      <t>다정하게</t>
     </r>
     <r>
       <rPr>
@@ -8186,7 +8413,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>소모하면</t>
+      <t>아군을</t>
     </r>
     <r>
       <rPr>
@@ -8205,7 +8432,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>턴</t>
+      <t>감싸지만</t>
     </r>
     <r>
       <rPr>
@@ -8214,7 +8441,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -8224,7 +8451,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>종료</t>
+      <t>그들을</t>
     </r>
     <r>
       <rPr>
@@ -8243,7 +8470,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>시</t>
+      <t>위협하는</t>
     </r>
     <r>
       <rPr>
@@ -8262,7 +8489,236 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>에테르를</t>
+      <t>존재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞에서는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>웃음마저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차갑게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>식어갑니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아군에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이로운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>효과가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부여되면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신앙을</t>
     </r>
     <r>
       <rPr>
@@ -8299,7 +8755,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -8491,12 +8947,6 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="10"/>
@@ -9416,7 +9866,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9425,7 +9875,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9760,7 +10210,7 @@
         <v>30</v>
       </c>
       <c r="H2" s="55" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>31</v>
@@ -9834,7 +10284,7 @@
         <v>49</v>
       </c>
       <c r="H3" s="57" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="I3" s="119">
         <v>1</v>
@@ -9881,8 +10331,8 @@
       <c r="W3" s="116" t="s">
         <v>1236</v>
       </c>
-      <c r="X3" s="154" t="s">
-        <v>1408</v>
+      <c r="X3" s="151" t="s">
+        <v>1409</v>
       </c>
       <c r="Y3" s="152"/>
       <c r="Z3" s="152"/>
@@ -9913,7 +10363,7 @@
         <v>64</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="I4" s="120">
         <v>1</v>
@@ -9958,10 +10408,10 @@
         <v>1240</v>
       </c>
       <c r="W4" s="118" t="s">
-        <v>1409</v>
-      </c>
-      <c r="X4" s="154" t="s">
-        <v>1410</v>
+        <v>1407</v>
+      </c>
+      <c r="X4" s="151" t="s">
+        <v>1408</v>
       </c>
       <c r="Y4" s="152"/>
       <c r="Z4" s="152"/>
@@ -9992,7 +10442,7 @@
         <v>80</v>
       </c>
       <c r="H5" s="57" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="I5" s="120">
         <v>1</v>
@@ -10039,8 +10489,8 @@
       <c r="W5" s="118" t="s">
         <v>1246</v>
       </c>
-      <c r="X5" s="154" t="s">
-        <v>1411</v>
+      <c r="X5" s="151" t="s">
+        <v>1410</v>
       </c>
       <c r="Y5" s="152"/>
       <c r="Z5" s="152"/>
@@ -10071,7 +10521,7 @@
         <v>1230</v>
       </c>
       <c r="H6" s="119" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="I6" s="120">
         <v>1</v>
@@ -10119,7 +10569,7 @@
         <v>1252</v>
       </c>
       <c r="X6" s="151" t="s">
-        <v>1253</v>
+        <v>1411</v>
       </c>
       <c r="Y6" s="152"/>
       <c r="Z6" s="152"/>
@@ -10150,7 +10600,7 @@
         <v>1231</v>
       </c>
       <c r="H7" s="120" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="I7" s="120">
         <v>2</v>
@@ -10183,22 +10633,22 @@
         <v>884</v>
       </c>
       <c r="S7" s="118" t="s">
+        <v>1253</v>
+      </c>
+      <c r="T7" s="118" t="s">
         <v>1254</v>
       </c>
-      <c r="T7" s="118" t="s">
+      <c r="U7" s="118" t="s">
         <v>1255</v>
       </c>
-      <c r="U7" s="118" t="s">
+      <c r="V7" s="118" t="s">
         <v>1256</v>
       </c>
-      <c r="V7" s="118" t="s">
+      <c r="W7" s="118" t="s">
         <v>1257</v>
       </c>
-      <c r="W7" s="118" t="s">
+      <c r="X7" s="154" t="s">
         <v>1258</v>
-      </c>
-      <c r="X7" s="151" t="s">
-        <v>1259</v>
       </c>
       <c r="Y7" s="152"/>
       <c r="Z7" s="152"/>
@@ -10359,7 +10809,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" customHeight="1">
       <c r="A1" s="55" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>94</v>
@@ -10432,7 +10882,7 @@
         <v>486</v>
       </c>
       <c r="B3" s="141" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C3" s="13">
         <v>26</v>
@@ -10447,7 +10897,7 @@
         <v>-1</v>
       </c>
       <c r="G3" s="139" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H3" s="20">
         <v>1</v>
@@ -10467,7 +10917,7 @@
         <v>486</v>
       </c>
       <c r="B4" s="142" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C4" s="16">
         <v>28</v>
@@ -10492,7 +10942,7 @@
         <v>490</v>
       </c>
       <c r="B5" s="141" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C5" s="13">
         <v>21</v>
@@ -10507,7 +10957,7 @@
         <v>-1</v>
       </c>
       <c r="G5" s="139" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H5" s="20">
         <v>1</v>
@@ -10567,7 +11017,7 @@
         <v>-1</v>
       </c>
       <c r="G7" s="140" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H7" s="25">
         <v>1</v>
@@ -10587,7 +11037,7 @@
         <v>493</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C8" s="3">
         <v>24</v>
@@ -10612,7 +11062,7 @@
         <v>496</v>
       </c>
       <c r="B9" s="141" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C9" s="13">
         <v>30</v>
@@ -10627,7 +11077,7 @@
         <v>-1</v>
       </c>
       <c r="G9" s="140" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H9" s="25">
         <v>1</v>
@@ -10669,10 +11119,10 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" customHeight="1">
       <c r="A11" s="145" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B11" s="141" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C11" s="13">
         <v>25</v>
@@ -10687,7 +11137,7 @@
         <v>-1</v>
       </c>
       <c r="G11" s="140" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H11" s="25">
         <v>1</v>
@@ -10707,7 +11157,7 @@
         <v>499</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C12" s="3">
         <v>34</v>
@@ -10732,7 +11182,7 @@
         <v>499</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C13" s="3">
         <v>22</v>
@@ -10754,10 +11204,10 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" customHeight="1">
       <c r="A14" s="145" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B14" s="141" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C14" s="13">
         <v>20</v>
@@ -10772,7 +11222,7 @@
         <v>-1</v>
       </c>
       <c r="G14" s="140" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H14" s="25">
         <v>1</v>
@@ -10789,7 +11239,7 @@
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>153</v>
@@ -10814,7 +11264,7 @@
     </row>
     <row r="16" spans="1:11" ht="16.5" customHeight="1" thickBot="1">
       <c r="A16" s="147" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B16" s="28" t="s">
         <v>143</v>
@@ -10839,7 +11289,7 @@
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" thickBot="1">
       <c r="A17" s="148" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B17" s="30" t="s">
         <v>162</v>
@@ -11352,7 +11802,7 @@
     </row>
     <row r="5" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="59" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B5" s="59" t="s">
         <v>624</v>
@@ -13018,7 +13468,7 @@
     </row>
     <row r="22" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="59" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B22" s="59" t="s">
         <v>651</v>
@@ -13116,25 +13566,25 @@
     </row>
     <row r="23" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="59" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>616</v>
       </c>
       <c r="D23" s="75" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E23" s="75" t="s">
         <v>1302</v>
       </c>
-      <c r="E23" s="75" t="s">
+      <c r="F23" s="75" t="s">
         <v>1303</v>
       </c>
-      <c r="F23" s="75" t="s">
+      <c r="G23" s="75" t="s">
         <v>1304</v>
-      </c>
-      <c r="G23" s="75" t="s">
-        <v>1305</v>
       </c>
       <c r="H23" s="43">
         <v>0</v>
@@ -13214,22 +13664,22 @@
     </row>
     <row r="24" spans="1:32">
       <c r="A24" s="59" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B24" s="75" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>616</v>
       </c>
       <c r="D24" s="75" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="E24" s="75" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F24" s="75" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G24" s="43">
         <v>0</v>
@@ -13312,85 +13762,85 @@
     </row>
     <row r="25" spans="1:32">
       <c r="A25" s="59" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B25" s="59" t="s">
         <v>1328</v>
-      </c>
-      <c r="B25" s="59" t="s">
-        <v>1329</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>616</v>
       </c>
       <c r="D25" s="59" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E25" s="59" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F25" s="59" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G25" s="59" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H25" s="59" t="s">
+        <v>1335</v>
+      </c>
+      <c r="I25" s="59" t="s">
         <v>1331</v>
       </c>
-      <c r="E25" s="59" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F25" s="59" t="s">
-        <v>1334</v>
-      </c>
-      <c r="G25" s="59" t="s">
-        <v>1335</v>
-      </c>
-      <c r="H25" s="59" t="s">
+      <c r="J25" s="59" t="s">
         <v>1336</v>
       </c>
-      <c r="I25" s="59" t="s">
-        <v>1332</v>
-      </c>
-      <c r="J25" s="59" t="s">
+      <c r="K25" s="59" t="s">
         <v>1337</v>
       </c>
-      <c r="K25" s="59" t="s">
+      <c r="L25" s="59" t="s">
         <v>1338</v>
       </c>
-      <c r="L25" s="59" t="s">
+      <c r="M25" s="59" t="s">
         <v>1339</v>
       </c>
-      <c r="M25" s="59" t="s">
+      <c r="N25" s="59" t="s">
         <v>1340</v>
       </c>
-      <c r="N25" s="59" t="s">
+      <c r="O25" s="59" t="s">
         <v>1341</v>
       </c>
-      <c r="O25" s="59" t="s">
+      <c r="P25" s="59" t="s">
         <v>1342</v>
       </c>
-      <c r="P25" s="59" t="s">
+      <c r="Q25" s="59" t="s">
         <v>1343</v>
       </c>
-      <c r="Q25" s="59" t="s">
+      <c r="R25" s="59" t="s">
         <v>1344</v>
       </c>
-      <c r="R25" s="59" t="s">
+      <c r="S25" s="59" t="s">
         <v>1345</v>
       </c>
-      <c r="S25" s="59" t="s">
+      <c r="T25" s="59" t="s">
         <v>1346</v>
       </c>
-      <c r="T25" s="59" t="s">
+      <c r="U25" s="59" t="s">
         <v>1347</v>
       </c>
-      <c r="U25" s="59" t="s">
+      <c r="V25" s="59" t="s">
         <v>1348</v>
       </c>
-      <c r="V25" s="59" t="s">
+      <c r="W25" s="59" t="s">
+        <v>1329</v>
+      </c>
+      <c r="X25" s="59" t="s">
         <v>1349</v>
       </c>
-      <c r="W25" s="59" t="s">
-        <v>1330</v>
-      </c>
-      <c r="X25" s="59" t="s">
+      <c r="Y25" s="59" t="s">
         <v>1350</v>
       </c>
-      <c r="Y25" s="59" t="s">
+      <c r="Z25" s="59" t="s">
         <v>1351</v>
       </c>
-      <c r="Z25" s="59" t="s">
+      <c r="AA25" s="59" t="s">
         <v>1352</v>
-      </c>
-      <c r="AA25" s="59" t="s">
-        <v>1353</v>
       </c>
       <c r="AB25" s="59">
         <v>0</v>
@@ -13508,13 +13958,13 @@
     </row>
     <row r="27" spans="1:32">
       <c r="A27" s="59" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B27" s="75" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C27" s="75" t="s">
         <v>1273</v>
-      </c>
-      <c r="C27" s="75" t="s">
-        <v>1274</v>
       </c>
       <c r="D27" s="43">
         <v>0</v>
@@ -13606,13 +14056,13 @@
     </row>
     <row r="28" spans="1:32">
       <c r="A28" s="59" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B28" s="75" t="s">
         <v>993</v>
       </c>
       <c r="C28" s="75" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D28" s="43">
         <v>0</v>
@@ -13704,7 +14154,7 @@
     </row>
     <row r="29" spans="1:32">
       <c r="A29" s="59" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B29" s="59" t="s">
         <v>615</v>
@@ -13802,7 +14252,7 @@
     </row>
     <row r="30" spans="1:32">
       <c r="A30" s="59" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B30" s="59" t="s">
         <v>620</v>
@@ -13900,7 +14350,7 @@
     </row>
     <row r="31" spans="1:32">
       <c r="A31" s="59" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B31" s="59" t="s">
         <v>624</v>
@@ -13998,7 +14448,7 @@
     </row>
     <row r="32" spans="1:32">
       <c r="A32" s="59" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B32" s="59" t="s">
         <v>629</v>
@@ -14096,7 +14546,7 @@
     </row>
     <row r="33" spans="1:32">
       <c r="A33" s="59" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B33" s="59" t="s">
         <v>630</v>
@@ -14194,7 +14644,7 @@
     </row>
     <row r="34" spans="1:32">
       <c r="A34" s="59" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B34" s="59" t="s">
         <v>631</v>
@@ -14292,7 +14742,7 @@
     </row>
     <row r="35" spans="1:32">
       <c r="A35" s="59" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B35" s="59" t="s">
         <v>632</v>
@@ -14390,7 +14840,7 @@
     </row>
     <row r="36" spans="1:32">
       <c r="A36" s="59" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B36" s="59" t="s">
         <v>634</v>
@@ -14488,7 +14938,7 @@
     </row>
     <row r="37" spans="1:32">
       <c r="A37" s="59" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B37" s="59" t="s">
         <v>636</v>
@@ -14586,7 +15036,7 @@
     </row>
     <row r="38" spans="1:32">
       <c r="A38" s="59" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B38" s="59" t="s">
         <v>638</v>
@@ -14684,7 +15134,7 @@
     </row>
     <row r="39" spans="1:32">
       <c r="A39" s="59" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B39" s="59" t="s">
         <v>639</v>
@@ -14782,7 +15232,7 @@
     </row>
     <row r="40" spans="1:32">
       <c r="A40" s="59" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B40" s="59" t="s">
         <v>640</v>
@@ -14880,7 +15330,7 @@
     </row>
     <row r="41" spans="1:32">
       <c r="A41" s="59" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B41" s="59" t="s">
         <v>644</v>
@@ -14978,7 +15428,7 @@
     </row>
     <row r="42" spans="1:32">
       <c r="A42" s="59" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B42" s="59" t="s">
         <v>645</v>
@@ -15076,7 +15526,7 @@
     </row>
     <row r="43" spans="1:32">
       <c r="A43" s="59" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B43" s="59" t="s">
         <v>646</v>
@@ -15174,7 +15624,7 @@
     </row>
     <row r="44" spans="1:32">
       <c r="A44" s="59" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B44" s="59" t="s">
         <v>647</v>
@@ -15272,7 +15722,7 @@
     </row>
     <row r="45" spans="1:32">
       <c r="A45" s="59" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B45" s="59" t="s">
         <v>648</v>
@@ -15370,7 +15820,7 @@
     </row>
     <row r="46" spans="1:32">
       <c r="A46" s="59" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B46" s="59" t="s">
         <v>649</v>
@@ -15468,7 +15918,7 @@
     </row>
     <row r="47" spans="1:32">
       <c r="A47" s="59" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B47" s="59" t="s">
         <v>650</v>
@@ -15566,7 +16016,7 @@
     </row>
     <row r="48" spans="1:32">
       <c r="A48" s="59" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B48" s="59" t="s">
         <v>651</v>
@@ -15664,25 +16114,25 @@
     </row>
     <row r="49" spans="1:32">
       <c r="A49" s="59" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B49" s="59" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>616</v>
       </c>
       <c r="D49" s="75" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E49" s="75" t="s">
         <v>1302</v>
       </c>
-      <c r="E49" s="75" t="s">
+      <c r="F49" s="75" t="s">
         <v>1303</v>
       </c>
-      <c r="F49" s="75" t="s">
+      <c r="G49" s="75" t="s">
         <v>1304</v>
-      </c>
-      <c r="G49" s="75" t="s">
-        <v>1305</v>
       </c>
       <c r="H49" s="43">
         <v>0</v>
@@ -15762,22 +16212,22 @@
     </row>
     <row r="50" spans="1:32">
       <c r="A50" s="59" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B50" s="75" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>616</v>
       </c>
       <c r="D50" s="75" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="E50" s="75" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F50" s="75" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G50" s="43">
         <v>0</v>
@@ -15860,85 +16310,85 @@
     </row>
     <row r="51" spans="1:32">
       <c r="A51" s="59" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B51" s="59" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>616</v>
       </c>
       <c r="D51" s="59" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E51" s="59" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F51" s="59" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G51" s="59" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H51" s="59" t="s">
+        <v>1335</v>
+      </c>
+      <c r="I51" s="59" t="s">
         <v>1331</v>
       </c>
-      <c r="E51" s="59" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F51" s="59" t="s">
-        <v>1334</v>
-      </c>
-      <c r="G51" s="59" t="s">
-        <v>1335</v>
-      </c>
-      <c r="H51" s="59" t="s">
+      <c r="J51" s="59" t="s">
         <v>1336</v>
       </c>
-      <c r="I51" s="59" t="s">
-        <v>1332</v>
-      </c>
-      <c r="J51" s="59" t="s">
+      <c r="K51" s="59" t="s">
         <v>1337</v>
       </c>
-      <c r="K51" s="59" t="s">
+      <c r="L51" s="59" t="s">
         <v>1338</v>
       </c>
-      <c r="L51" s="59" t="s">
+      <c r="M51" s="59" t="s">
         <v>1339</v>
       </c>
-      <c r="M51" s="59" t="s">
+      <c r="N51" s="59" t="s">
         <v>1340</v>
       </c>
-      <c r="N51" s="59" t="s">
+      <c r="O51" s="59" t="s">
         <v>1341</v>
       </c>
-      <c r="O51" s="59" t="s">
+      <c r="P51" s="59" t="s">
         <v>1342</v>
       </c>
-      <c r="P51" s="59" t="s">
+      <c r="Q51" s="59" t="s">
         <v>1343</v>
       </c>
-      <c r="Q51" s="59" t="s">
+      <c r="R51" s="59" t="s">
         <v>1344</v>
       </c>
-      <c r="R51" s="59" t="s">
+      <c r="S51" s="59" t="s">
         <v>1345</v>
       </c>
-      <c r="S51" s="59" t="s">
+      <c r="T51" s="59" t="s">
         <v>1346</v>
       </c>
-      <c r="T51" s="59" t="s">
+      <c r="U51" s="59" t="s">
         <v>1347</v>
       </c>
-      <c r="U51" s="59" t="s">
+      <c r="V51" s="59" t="s">
         <v>1348</v>
       </c>
-      <c r="V51" s="59" t="s">
+      <c r="W51" s="59" t="s">
+        <v>1329</v>
+      </c>
+      <c r="X51" s="59" t="s">
         <v>1349</v>
       </c>
-      <c r="W51" s="59" t="s">
-        <v>1330</v>
-      </c>
-      <c r="X51" s="59" t="s">
+      <c r="Y51" s="59" t="s">
         <v>1350</v>
       </c>
-      <c r="Y51" s="59" t="s">
+      <c r="Z51" s="59" t="s">
         <v>1351</v>
       </c>
-      <c r="Z51" s="59" t="s">
+      <c r="AA51" s="59" t="s">
         <v>1352</v>
-      </c>
-      <c r="AA51" s="59" t="s">
-        <v>1353</v>
       </c>
       <c r="AB51" s="59">
         <v>0</v>
@@ -17442,7 +17892,7 @@
         <v>96</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>97</v>
@@ -17507,7 +17957,7 @@
         <v>96</v>
       </c>
       <c r="E2" s="55" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>115</v>
@@ -17590,7 +18040,7 @@
         <v>0.1</v>
       </c>
       <c r="K3" s="57" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>136</v>
@@ -17655,7 +18105,7 @@
         <v>0.02</v>
       </c>
       <c r="K4" s="57" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>141</v>
@@ -17720,7 +18170,7 @@
         <v>0.02</v>
       </c>
       <c r="K5" s="57" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>157</v>
@@ -17785,7 +18235,7 @@
         <v>0.02</v>
       </c>
       <c r="K6" s="57" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>157</v>
@@ -17850,7 +18300,7 @@
         <v>0.02</v>
       </c>
       <c r="K7" s="57" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>157</v>
@@ -17885,10 +18335,10 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="57" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C8" s="52" t="s">
         <v>133</v>
@@ -17915,13 +18365,13 @@
         <v>0.05</v>
       </c>
       <c r="K8" s="57" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>136</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -18208,7 +18658,7 @@
         <v>171</v>
       </c>
       <c r="B14" s="138" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C14" s="52" t="s">
         <v>172</v>
@@ -18226,7 +18676,7 @@
         <v>48</v>
       </c>
       <c r="H14" s="57" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="I14" s="53">
         <v>0.7</v>
@@ -18353,7 +18803,7 @@
         <v>182</v>
       </c>
       <c r="M1" s="61" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="N1" s="61" t="s">
         <v>184</v>
@@ -18376,7 +18826,7 @@
         <v>190</v>
       </c>
       <c r="B2" s="61" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C2" s="61" t="s">
         <v>191</v>
@@ -18385,7 +18835,7 @@
         <v>203</v>
       </c>
       <c r="E2" s="61" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="F2" s="61" t="s">
         <v>192</v>
@@ -18397,7 +18847,7 @@
         <v>194</v>
       </c>
       <c r="I2" s="61" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="J2" s="61" t="s">
         <v>196</v>
@@ -18409,22 +18859,22 @@
         <v>198</v>
       </c>
       <c r="M2" s="61" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="N2" s="61" t="s">
         <v>199</v>
       </c>
       <c r="O2" s="61" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="P2" s="61" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q2" s="61" t="s">
         <v>202</v>
       </c>
       <c r="R2" s="61" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="3" spans="1:18" s="67" customFormat="1" ht="18" customHeight="1" thickTop="1" thickBot="1">
@@ -18527,7 +18977,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="123" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="P4" s="124" t="s">
         <v>156</v>
@@ -18586,7 +19036,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q5" s="58">
         <v>0</v>
@@ -18642,7 +19092,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q6" s="58">
         <v>0</v>
@@ -18698,7 +19148,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q7" s="58">
         <v>0</v>
@@ -18754,7 +19204,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q8" s="58">
         <v>0</v>
@@ -18810,7 +19260,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q9" s="58">
         <v>0</v>
@@ -18866,7 +19316,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q10" s="58">
         <v>0</v>
@@ -18922,7 +19372,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q11" s="58">
         <v>0</v>
@@ -18978,7 +19428,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q12" s="58">
         <v>0</v>
@@ -19034,7 +19484,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q13" s="58">
         <v>0</v>
@@ -19090,7 +19540,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="126" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q14" s="91">
         <v>0</v>
@@ -19143,7 +19593,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="123" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="P15" s="124" t="s">
         <v>156</v>
@@ -19184,7 +19634,7 @@
         <v>226</v>
       </c>
       <c r="J16" s="58" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="K16" s="58" t="s">
         <v>1213</v>
@@ -19296,10 +19746,10 @@
         <v>1197</v>
       </c>
       <c r="J18" s="58" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="K18" s="58" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="L18" s="58" t="s">
         <v>228</v>
@@ -19426,7 +19876,7 @@
         <v>222</v>
       </c>
       <c r="P20" s="124" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="Q20" s="78" t="s">
         <v>1035</v>
@@ -19482,7 +19932,7 @@
         <v>222</v>
       </c>
       <c r="P21" s="124" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="Q21" s="78" t="s">
         <v>1084</v>
@@ -19803,7 +20253,7 @@
         <v>1212</v>
       </c>
       <c r="K27" s="58" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="L27" s="58">
         <v>1</v>
@@ -19859,7 +20309,7 @@
         <v>1212</v>
       </c>
       <c r="K28" s="99" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="L28" s="98">
         <v>1</v>
@@ -20042,7 +20492,7 @@
         <v>222</v>
       </c>
       <c r="P31" s="124" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="Q31" s="78" t="s">
         <v>1093</v>
@@ -20098,7 +20548,7 @@
         <v>222</v>
       </c>
       <c r="P32" s="128" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="Q32" s="100" t="s">
         <v>1094</v>
@@ -20490,7 +20940,7 @@
         <v>212</v>
       </c>
       <c r="P39" s="124" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="Q39" s="78" t="s">
         <v>1097</v>
@@ -20546,7 +20996,7 @@
         <v>212</v>
       </c>
       <c r="P40" s="129" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="Q40" s="100" t="s">
         <v>1097</v>
@@ -20938,7 +21388,7 @@
         <v>222</v>
       </c>
       <c r="P47" s="124" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="Q47" s="78" t="s">
         <v>1034</v>
@@ -20994,7 +21444,7 @@
         <v>222</v>
       </c>
       <c r="P48" s="128" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="Q48" s="100" t="s">
         <v>1102</v>
@@ -21162,7 +21612,7 @@
         <v>222</v>
       </c>
       <c r="P51" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q51" s="78" t="s">
         <v>1104</v>
@@ -21218,7 +21668,7 @@
         <v>222</v>
       </c>
       <c r="P52" s="128" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q52" s="100" t="s">
         <v>1104</v>
@@ -21274,7 +21724,7 @@
         <v>222</v>
       </c>
       <c r="P53" s="124" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="Q53" s="78" t="s">
         <v>1105</v>
@@ -21330,7 +21780,7 @@
         <v>222</v>
       </c>
       <c r="P54" s="128" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="Q54" s="100" t="s">
         <v>1105</v>
@@ -21386,7 +21836,7 @@
         <v>212</v>
       </c>
       <c r="P55" s="124" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="Q55" s="78" t="s">
         <v>1106</v>
@@ -21442,7 +21892,7 @@
         <v>212</v>
       </c>
       <c r="P56" s="128" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="Q56" s="100" t="s">
         <v>1106</v>
@@ -21498,7 +21948,7 @@
         <v>222</v>
       </c>
       <c r="P57" s="124" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="Q57" s="78" t="s">
         <v>1107</v>
@@ -21554,7 +22004,7 @@
         <v>222</v>
       </c>
       <c r="P58" s="129" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="Q58" s="100" t="s">
         <v>1107</v>
@@ -21610,7 +22060,7 @@
         <v>222</v>
       </c>
       <c r="P59" s="124" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="Q59" s="78" t="s">
         <v>1108</v>
@@ -21666,7 +22116,7 @@
         <v>222</v>
       </c>
       <c r="P60" s="128" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="Q60" s="100" t="s">
         <v>1098</v>
@@ -21834,7 +22284,7 @@
         <v>222</v>
       </c>
       <c r="P63" s="124" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q63" s="78" t="s">
         <v>1110</v>
@@ -21890,7 +22340,7 @@
         <v>222</v>
       </c>
       <c r="P64" s="131" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q64" s="109" t="s">
         <v>1110</v>
@@ -24461,7 +24911,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="57" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B3" s="45" t="s">
         <v>205</v>
@@ -24499,7 +24949,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="57" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B4" s="46" t="s">
         <v>205</v>
@@ -24599,7 +25049,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="49" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>225</v>
@@ -24701,10 +25151,10 @@
         <v>226</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -24955,7 +25405,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="57" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B16" s="46" t="s">
         <v>306</v>
@@ -24979,7 +25429,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="49" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>225</v>
@@ -25354,10 +25804,10 @@
         <v>148</v>
       </c>
       <c r="E10" s="75" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F10" s="75" t="s">
         <v>1406</v>
-      </c>
-      <c r="F10" s="75" t="s">
-        <v>1407</v>
       </c>
       <c r="G10" s="43"/>
     </row>
@@ -25417,10 +25867,10 @@
         <v>152</v>
       </c>
       <c r="E13" s="75" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F13" s="75" t="s">
         <v>1404</v>
-      </c>
-      <c r="F13" s="75" t="s">
-        <v>1405</v>
       </c>
       <c r="G13" s="43"/>
     </row>
@@ -25673,7 +26123,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="57" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B3" s="38" t="s">
         <v>367</v>
@@ -26403,7 +26853,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="57" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B23" s="38">
         <v>71</v>
@@ -26426,7 +26876,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="57" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B24" s="38">
         <v>72</v>
@@ -26449,7 +26899,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="57" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B25" s="38">
         <v>73</v>
@@ -26472,7 +26922,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="57" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B26" s="38">
         <v>74</v>
@@ -26495,7 +26945,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="57" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B27" s="38">
         <v>75</v>
@@ -26518,7 +26968,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.25" customHeight="1">
       <c r="A28" s="57" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B28" s="38" t="s">
         <v>399</v>
@@ -27177,7 +27627,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="149" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B1" s="35" t="s">
         <v>1</v>
@@ -27201,13 +27651,13 @@
         <v>182</v>
       </c>
       <c r="I1" s="149" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J1" s="149" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="K1" s="149" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -27236,10 +27686,10 @@
         <v>198</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J2" s="55" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>202</v>
@@ -27247,7 +27697,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="57" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>429</v>
@@ -27274,7 +27724,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="57" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="K3" s="3"/>
     </row>
@@ -27292,7 +27742,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="F4" s="36" t="s">
         <v>211</v>
@@ -27307,7 +27757,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="57" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="K4" s="3"/>
     </row>
@@ -27340,7 +27790,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="57" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -27373,7 +27823,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="57" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="K6" s="3"/>
     </row>
@@ -27406,16 +27856,16 @@
         <v>0</v>
       </c>
       <c r="J7" s="57" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="57" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -27424,7 +27874,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="F8" s="36" t="s">
         <v>211</v>
@@ -27439,7 +27889,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="57" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="K8" s="3"/>
     </row>
@@ -27542,7 +27992,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="80" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>448</v>
@@ -27890,30 +28340,30 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="80" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B31" s="143" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D31" s="144" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="80" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="B32" s="143" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="C32" s="57" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D32" s="144" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
   </sheetData>
@@ -28010,7 +28460,7 @@
         <v>485</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>486</v>
@@ -28135,13 +28585,13 @@
         <v>497</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -28173,7 +28623,7 @@
         <v>163</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -28205,7 +28655,7 @@
         <v>163</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -28237,7 +28687,7 @@
         <v>172</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -28532,7 +28982,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="3" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>535</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydjh1\Desktop\지원사업\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A357E1FC-592E-4A93-9A6C-5EFF3D54B1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DA1EE5-6C64-4580-9F9D-835B56FB84A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -7611,8 +7611,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">"흔들리는 검 끝은 죽음을 부를 뿐."
-</t>
+      <t>이네스</t>
     </r>
     <r>
       <rPr>
@@ -7621,8 +7620,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -7632,8 +7630,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>침착하고 냉철한 검사입니다.
-모든 전투 기술을 끊임없이 배우고 검술의 극의에 닿고자 합니다.</t>
+      <t>상냥한</t>
     </r>
     <r>
       <rPr>
@@ -7642,8 +7639,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -7653,7 +7649,8 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>한</t>
+      <t>집행자
+밝은</t>
     </r>
     <r>
       <rPr>
@@ -7672,7 +7669,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>슬롯에서</t>
+      <t>얼굴로</t>
     </r>
     <r>
       <rPr>
@@ -7681,7 +7678,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 3</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -7691,7 +7688,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>회</t>
+      <t>아군을</t>
     </r>
     <r>
       <rPr>
@@ -7710,7 +7707,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>이상</t>
+      <t>보살핍니다</t>
     </r>
     <r>
       <rPr>
@@ -7719,7 +7716,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">.
+</t>
     </r>
     <r>
       <rPr>
@@ -7729,7 +7727,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>행동하면</t>
+      <t>다정하게</t>
     </r>
     <r>
       <rPr>
@@ -7748,7 +7746,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>턴</t>
+      <t>아군을</t>
     </r>
     <r>
       <rPr>
@@ -7767,7 +7765,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>종료</t>
+      <t>감싸지만</t>
     </r>
     <r>
       <rPr>
@@ -7776,7 +7774,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -7786,7 +7784,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>시</t>
+      <t>그들을</t>
     </r>
     <r>
       <rPr>
@@ -7805,7 +7803,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>기세를</t>
+      <t>위협하는</t>
     </r>
     <r>
       <rPr>
@@ -7814,7 +7812,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 1 </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -7824,7 +7822,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>획득합니다</t>
+      <t>존재</t>
     </r>
     <r>
       <rPr>
@@ -7833,11 +7831,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve"> </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -7846,10 +7841,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">"더 강한 놈, 더 열렬한 전투!"
-호전적이고 거침없이 돌격하는 전사입니다.
-전투를 통해 자신의 한계를 시험하고 강함을 증명하고자 합니다.
-</t>
+      <t>앞에서는</t>
     </r>
     <r>
       <rPr>
@@ -7858,8 +7850,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -7869,7 +7860,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>자신</t>
+      <t>웃음마저</t>
     </r>
     <r>
       <rPr>
@@ -7888,7 +7879,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>또는</t>
+      <t>차갑게</t>
     </r>
     <r>
       <rPr>
@@ -7907,7 +7898,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>아군이</t>
+      <t>식어갑니다</t>
     </r>
     <r>
       <rPr>
@@ -7916,7 +7907,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">.
+</t>
     </r>
     <r>
       <rPr>
@@ -7926,7 +7918,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>피해를</t>
+      <t>아군에게</t>
     </r>
     <r>
       <rPr>
@@ -7945,7 +7937,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>받으면</t>
+      <t>이로운</t>
     </r>
     <r>
       <rPr>
@@ -7964,7 +7956,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>턴</t>
+      <t>효과가</t>
     </r>
     <r>
       <rPr>
@@ -7983,7 +7975,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>종료</t>
+      <t>부여되면</t>
     </r>
     <r>
       <rPr>
@@ -8002,7 +7994,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>시</t>
+      <t>턴</t>
     </r>
     <r>
       <rPr>
@@ -8021,7 +8013,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>분노를</t>
+      <t>종료</t>
     </r>
     <r>
       <rPr>
@@ -8030,7 +8022,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 1 </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -8040,7 +8032,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>획득합니다</t>
+      <t>시</t>
     </r>
     <r>
       <rPr>
@@ -8049,11 +8041,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve"> </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8062,10 +8051,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">"니아, 제발 내 곁에서 떨어지지 마!"
-겁이 많고 소심한 소환사입니다.
-자신의 나약함을 극복하고자 소환수와 함께 전투를 진행합니다.
-</t>
+      <t>신앙을</t>
     </r>
     <r>
       <rPr>
@@ -8074,8 +8060,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t xml:space="preserve"> 1 </t>
     </r>
     <r>
       <rPr>
@@ -8085,7 +8070,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>한</t>
+      <t>획득합니다</t>
     </r>
     <r>
       <rPr>
@@ -8094,8 +8079,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8104,7 +8092,10 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>턴에</t>
+      <t xml:space="preserve">"더 강한 놈, 더 열렬한 전투!"
+호전적이고 거침없이 돌격하는 탐사자입니다.
+전투를 통해 자신의 한계를 시험하고 강함을 증명하고자 합니다.
+</t>
     </r>
     <r>
       <rPr>
@@ -8113,7 +8104,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -8123,7 +8115,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>코스트를</t>
+      <t>자신</t>
     </r>
     <r>
       <rPr>
@@ -8132,7 +8124,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 8 </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -8142,7 +8134,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>이상</t>
+      <t>또는</t>
     </r>
     <r>
       <rPr>
@@ -8161,7 +8153,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>소모하면</t>
+      <t>아군이</t>
     </r>
     <r>
       <rPr>
@@ -8180,7 +8172,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>턴</t>
+      <t>피해를</t>
     </r>
     <r>
       <rPr>
@@ -8199,7 +8191,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>종료</t>
+      <t>받으면</t>
     </r>
     <r>
       <rPr>
@@ -8218,7 +8210,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>시</t>
+      <t>턴</t>
     </r>
     <r>
       <rPr>
@@ -8237,7 +8229,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>에테르를</t>
+      <t>종료</t>
     </r>
     <r>
       <rPr>
@@ -8246,7 +8238,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 1 </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -8256,7 +8248,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>획득합니다</t>
+      <t>시</t>
     </r>
     <r>
       <rPr>
@@ -8265,11 +8257,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve"> </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8278,7 +8267,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>이네스</t>
+      <t>분노를</t>
     </r>
     <r>
       <rPr>
@@ -8287,7 +8276,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> 1 </t>
     </r>
     <r>
       <rPr>
@@ -8297,7 +8286,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>상냥한</t>
+      <t>획득합니다</t>
     </r>
     <r>
       <rPr>
@@ -8306,8 +8295,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8316,8 +8308,8 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>집행자
-밝은</t>
+      <t xml:space="preserve">"흔들리는 검 끝은 죽음을 부를 뿐."
+</t>
     </r>
     <r>
       <rPr>
@@ -8326,7 +8318,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -8336,7 +8329,8 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>얼굴로</t>
+      <t>침착하고 냉철한 탐사자입니다.
+모든 전투 기술을 끊임없이 배우고 검술의 극의에 닿고자 합니다.</t>
     </r>
     <r>
       <rPr>
@@ -8345,7 +8339,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -8355,7 +8350,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>아군을</t>
+      <t>한</t>
     </r>
     <r>
       <rPr>
@@ -8374,7 +8369,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>보살핍니다</t>
+      <t>슬롯에서</t>
     </r>
     <r>
       <rPr>
@@ -8383,8 +8378,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">.
-</t>
+      <t xml:space="preserve"> 3</t>
     </r>
     <r>
       <rPr>
@@ -8394,7 +8388,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>다정하게</t>
+      <t>회</t>
     </r>
     <r>
       <rPr>
@@ -8413,7 +8407,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>아군을</t>
+      <t>이상</t>
     </r>
     <r>
       <rPr>
@@ -8432,7 +8426,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>감싸지만</t>
+      <t>행동하면</t>
     </r>
     <r>
       <rPr>
@@ -8441,7 +8435,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -8451,7 +8445,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>그들을</t>
+      <t>턴</t>
     </r>
     <r>
       <rPr>
@@ -8470,7 +8464,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>위협하는</t>
+      <t>종료</t>
     </r>
     <r>
       <rPr>
@@ -8489,7 +8483,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>존재</t>
+      <t>시</t>
     </r>
     <r>
       <rPr>
@@ -8508,7 +8502,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>앞에서는</t>
+      <t>기세를</t>
     </r>
     <r>
       <rPr>
@@ -8517,7 +8511,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> 1 </t>
     </r>
     <r>
       <rPr>
@@ -8527,7 +8521,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>웃음마저</t>
+      <t>획득합니다</t>
     </r>
     <r>
       <rPr>
@@ -8536,8 +8530,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8546,7 +8543,10 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>차갑게</t>
+      <t xml:space="preserve">"니아, 제발 내 곁에서 떨어지지 마!"
+겁이 많고 소심한 탐사자입니다.
+자신의 나약함을 극복하고자 소환수와 함께 전투를 진행합니다.
+</t>
     </r>
     <r>
       <rPr>
@@ -8555,7 +8555,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -8565,7 +8566,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>식어갑니다</t>
+      <t>한</t>
     </r>
     <r>
       <rPr>
@@ -8574,8 +8575,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">.
-</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -8585,7 +8585,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>아군에게</t>
+      <t>턴에</t>
     </r>
     <r>
       <rPr>
@@ -8604,7 +8604,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>이로운</t>
+      <t>코스트를</t>
     </r>
     <r>
       <rPr>
@@ -8613,7 +8613,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> 8 </t>
     </r>
     <r>
       <rPr>
@@ -8623,7 +8623,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>효과가</t>
+      <t>이상</t>
     </r>
     <r>
       <rPr>
@@ -8642,7 +8642,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>부여되면</t>
+      <t>소모하면</t>
     </r>
     <r>
       <rPr>
@@ -8718,7 +8718,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>신앙을</t>
+      <t>에테르를</t>
     </r>
     <r>
       <rPr>
@@ -10411,7 +10411,7 @@
         <v>1407</v>
       </c>
       <c r="X4" s="151" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="Y4" s="152"/>
       <c r="Z4" s="152"/>
@@ -10490,7 +10490,7 @@
         <v>1246</v>
       </c>
       <c r="X5" s="151" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="Y5" s="152"/>
       <c r="Z5" s="152"/>
@@ -10569,7 +10569,7 @@
         <v>1252</v>
       </c>
       <c r="X6" s="151" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="Y6" s="152"/>
       <c r="Z6" s="152"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A10BC7B-0D03-4B13-AB57-4A6180FAD6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27B75EC-9E25-43B9-87D1-D4EDCAF37CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -1742,9 +1742,6 @@
     <t>CoreEpicChance</t>
   </si>
   <si>
-    <t>Elise*1</t>
-  </si>
-  <si>
     <t>범위1</t>
   </si>
   <si>
@@ -8844,6 +8841,10 @@
       </rPr>
       <t>.</t>
     </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elise*1</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -10360,7 +10361,7 @@
         <v>30</v>
       </c>
       <c r="H2" s="53" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>31</v>
@@ -10434,7 +10435,7 @@
         <v>49</v>
       </c>
       <c r="H3" s="55" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="I3" s="117">
         <v>1</v>
@@ -10467,22 +10468,22 @@
         <v>57</v>
       </c>
       <c r="S3" s="114" t="s">
+        <v>1227</v>
+      </c>
+      <c r="T3" s="114" t="s">
         <v>1228</v>
       </c>
-      <c r="T3" s="114" t="s">
+      <c r="U3" s="114" t="s">
         <v>1229</v>
       </c>
-      <c r="U3" s="114" t="s">
+      <c r="V3" s="114" t="s">
         <v>1230</v>
       </c>
-      <c r="V3" s="114" t="s">
+      <c r="W3" s="114" t="s">
         <v>1231</v>
       </c>
-      <c r="W3" s="114" t="s">
-        <v>1232</v>
-      </c>
       <c r="X3" s="158" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="Y3" s="159"/>
       <c r="Z3" s="159"/>
@@ -10513,7 +10514,7 @@
         <v>64</v>
       </c>
       <c r="H4" s="55" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="I4" s="118">
         <v>1</v>
@@ -10546,22 +10547,22 @@
         <v>72</v>
       </c>
       <c r="S4" s="116" t="s">
+        <v>1232</v>
+      </c>
+      <c r="T4" s="116" t="s">
         <v>1233</v>
       </c>
-      <c r="T4" s="116" t="s">
+      <c r="U4" s="116" t="s">
         <v>1234</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="V4" s="116" t="s">
         <v>1235</v>
       </c>
-      <c r="V4" s="116" t="s">
-        <v>1236</v>
-      </c>
       <c r="W4" s="116" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="X4" s="158" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="Y4" s="159"/>
       <c r="Z4" s="159"/>
@@ -10592,7 +10593,7 @@
         <v>80</v>
       </c>
       <c r="H5" s="55" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="I5" s="118">
         <v>1</v>
@@ -10625,22 +10626,22 @@
         <v>88</v>
       </c>
       <c r="S5" s="116" t="s">
+        <v>1237</v>
+      </c>
+      <c r="T5" s="116" t="s">
         <v>1238</v>
       </c>
-      <c r="T5" s="116" t="s">
+      <c r="U5" s="116" t="s">
         <v>1239</v>
       </c>
-      <c r="U5" s="116" t="s">
+      <c r="V5" s="116" t="s">
         <v>1240</v>
       </c>
-      <c r="V5" s="116" t="s">
+      <c r="W5" s="116" t="s">
         <v>1241</v>
       </c>
-      <c r="W5" s="116" t="s">
-        <v>1242</v>
-      </c>
       <c r="X5" s="158" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="Y5" s="159"/>
       <c r="Z5" s="159"/>
@@ -10650,10 +10651,10 @@
     </row>
     <row r="6" spans="1:29" ht="76.5" customHeight="1" thickBot="1">
       <c r="A6" s="115" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B6" s="116" t="s">
         <v>1222</v>
-      </c>
-      <c r="B6" s="116" t="s">
-        <v>1223</v>
       </c>
       <c r="C6" s="118">
         <v>100</v>
@@ -10668,10 +10669,10 @@
         <v>3</v>
       </c>
       <c r="G6" s="116" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H6" s="117" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="I6" s="118">
         <v>1</v>
@@ -10680,46 +10681,46 @@
         <v>1</v>
       </c>
       <c r="K6" s="118" t="s">
+        <v>838</v>
+      </c>
+      <c r="L6" s="116" t="s">
         <v>839</v>
       </c>
-      <c r="L6" s="116" t="s">
-        <v>840</v>
-      </c>
       <c r="M6" s="116" t="s">
+        <v>849</v>
+      </c>
+      <c r="N6" s="116" t="s">
         <v>850</v>
       </c>
-      <c r="N6" s="116" t="s">
-        <v>851</v>
-      </c>
       <c r="O6" s="116" t="s">
+        <v>1242</v>
+      </c>
+      <c r="P6" s="116" t="s">
+        <v>867</v>
+      </c>
+      <c r="Q6" s="116" t="s">
+        <v>873</v>
+      </c>
+      <c r="R6" s="116" t="s">
+        <v>875</v>
+      </c>
+      <c r="S6" s="116" t="s">
         <v>1243</v>
       </c>
-      <c r="P6" s="116" t="s">
-        <v>868</v>
-      </c>
-      <c r="Q6" s="116" t="s">
-        <v>874</v>
-      </c>
-      <c r="R6" s="116" t="s">
-        <v>876</v>
-      </c>
-      <c r="S6" s="116" t="s">
+      <c r="T6" s="116" t="s">
         <v>1244</v>
       </c>
-      <c r="T6" s="116" t="s">
+      <c r="U6" s="116" t="s">
         <v>1245</v>
       </c>
-      <c r="U6" s="116" t="s">
+      <c r="V6" s="116" t="s">
         <v>1246</v>
       </c>
-      <c r="V6" s="116" t="s">
+      <c r="W6" s="116" t="s">
         <v>1247</v>
       </c>
-      <c r="W6" s="116" t="s">
-        <v>1248</v>
-      </c>
       <c r="X6" s="158" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="Y6" s="159"/>
       <c r="Z6" s="159"/>
@@ -10729,10 +10730,10 @@
     </row>
     <row r="7" spans="1:29" ht="76.5" customHeight="1" thickBot="1">
       <c r="A7" s="115" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B7" s="116" t="s">
         <v>1224</v>
-      </c>
-      <c r="B7" s="116" t="s">
-        <v>1225</v>
       </c>
       <c r="C7" s="118">
         <v>90</v>
@@ -10747,10 +10748,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="116" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H7" s="118" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="I7" s="118">
         <v>2</v>
@@ -10759,46 +10760,46 @@
         <v>2</v>
       </c>
       <c r="K7" s="118" t="s">
+        <v>840</v>
+      </c>
+      <c r="L7" s="116" t="s">
         <v>841</v>
       </c>
-      <c r="L7" s="116" t="s">
-        <v>842</v>
-      </c>
       <c r="M7" s="116" t="s">
+        <v>851</v>
+      </c>
+      <c r="N7" s="116" t="s">
         <v>852</v>
       </c>
-      <c r="N7" s="116" t="s">
-        <v>853</v>
-      </c>
       <c r="O7" s="116" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="P7" s="116" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="Q7" s="116" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="R7" s="116" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="S7" s="116" t="s">
+        <v>1248</v>
+      </c>
+      <c r="T7" s="116" t="s">
         <v>1249</v>
       </c>
-      <c r="T7" s="116" t="s">
+      <c r="U7" s="116" t="s">
         <v>1250</v>
       </c>
-      <c r="U7" s="116" t="s">
+      <c r="V7" s="116" t="s">
         <v>1251</v>
       </c>
-      <c r="V7" s="116" t="s">
+      <c r="W7" s="116" t="s">
         <v>1252</v>
       </c>
-      <c r="W7" s="116" t="s">
+      <c r="X7" s="161" t="s">
         <v>1253</v>
-      </c>
-      <c r="X7" s="161" t="s">
-        <v>1254</v>
       </c>
       <c r="Y7" s="159"/>
       <c r="Z7" s="159"/>
@@ -10959,7 +10960,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" customHeight="1">
       <c r="A1" s="53" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>94</v>
@@ -11032,7 +11033,7 @@
         <v>484</v>
       </c>
       <c r="B3" s="139" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C3" s="13">
         <v>21</v>
@@ -11047,7 +11048,7 @@
         <v>-1</v>
       </c>
       <c r="G3" s="137" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H3" s="20">
         <v>1</v>
@@ -11067,7 +11068,7 @@
         <v>484</v>
       </c>
       <c r="B4" s="140" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C4" s="16">
         <v>23</v>
@@ -11092,7 +11093,7 @@
         <v>488</v>
       </c>
       <c r="B5" s="139" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C5" s="13">
         <v>27</v>
@@ -11107,7 +11108,7 @@
         <v>-1</v>
       </c>
       <c r="G5" s="137" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H5" s="20">
         <v>1</v>
@@ -11167,7 +11168,7 @@
         <v>-1</v>
       </c>
       <c r="G7" s="138" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H7" s="25">
         <v>1</v>
@@ -11187,7 +11188,7 @@
         <v>491</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C8" s="3">
         <v>23</v>
@@ -11212,7 +11213,7 @@
         <v>494</v>
       </c>
       <c r="B9" s="139" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C9" s="13">
         <v>25</v>
@@ -11227,7 +11228,7 @@
         <v>-1</v>
       </c>
       <c r="G9" s="138" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H9" s="25">
         <v>1</v>
@@ -11269,10 +11270,10 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" customHeight="1">
       <c r="A11" s="143" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B11" s="139" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C11" s="13">
         <v>26</v>
@@ -11287,7 +11288,7 @@
         <v>-1</v>
       </c>
       <c r="G11" s="138" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H11" s="25">
         <v>1</v>
@@ -11307,7 +11308,7 @@
         <v>497</v>
       </c>
       <c r="B12" s="151" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C12" s="152">
         <v>23</v>
@@ -11329,10 +11330,10 @@
     </row>
     <row r="13" spans="1:11" ht="16.5" customHeight="1" thickBot="1">
       <c r="A13" s="144" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="B13" s="154" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C13" s="28">
         <v>22</v>
@@ -11347,7 +11348,7 @@
         <v>-1</v>
       </c>
       <c r="G13" s="155" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H13" s="156">
         <v>1</v>
@@ -11364,10 +11365,10 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" customHeight="1" thickBot="1">
       <c r="A14" s="144" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="B14" s="154" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C14" s="28">
         <v>27</v>
@@ -11381,8 +11382,8 @@
       <c r="F14" s="28">
         <v>-1</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>552</v>
+      <c r="G14" s="155" t="s">
+        <v>1429</v>
       </c>
       <c r="H14" s="29">
         <v>1</v>
@@ -11494,94 +11495,94 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="N1" s="10" t="s">
         <v>563</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>564</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>566</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="T1" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="X1" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="Y1" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Z1" s="10" t="s">
         <v>575</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AA1" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AB1" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AC1" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AD1" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AE1" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AF1" s="10" t="s">
         <v>581</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="17.25" customHeight="1">
@@ -11592,94 +11593,94 @@
         <v>25</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>592</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="Q2" s="11" t="s">
         <v>596</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="S2" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="T2" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>601</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="W2" s="11" t="s">
         <v>602</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="Y2" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Z2" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="AA2" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AB2" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="AB2" s="11" t="s">
+      <c r="AC2" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="AC2" s="11" t="s">
+      <c r="AD2" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AE2" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AF2" s="11" t="s">
         <v>611</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1">
@@ -11687,22 +11688,22 @@
         <v>222</v>
       </c>
       <c r="B3" s="57" t="s">
+        <v>612</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>613</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>614</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E3" s="57" t="s">
+        <v>614</v>
+      </c>
+      <c r="F3" s="57" t="s">
         <v>615</v>
       </c>
-      <c r="F3" s="57" t="s">
+      <c r="G3" s="57" t="s">
         <v>616</v>
-      </c>
-      <c r="G3" s="57" t="s">
-        <v>617</v>
       </c>
       <c r="H3" s="41">
         <v>0</v>
@@ -11785,34 +11786,34 @@
         <v>146</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D4" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E4" s="57" t="s">
+        <v>614</v>
+      </c>
+      <c r="F4" s="57" t="s">
         <v>615</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="G4" s="57" t="s">
         <v>616</v>
       </c>
-      <c r="G4" s="57" t="s">
-        <v>617</v>
-      </c>
       <c r="H4" s="57" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I4" s="57" t="s">
         <v>227</v>
       </c>
       <c r="J4" s="57" t="s">
+        <v>619</v>
+      </c>
+      <c r="K4" s="57" t="s">
         <v>620</v>
-      </c>
-      <c r="K4" s="57" t="s">
-        <v>621</v>
       </c>
       <c r="L4" s="41">
         <v>0</v>
@@ -11880,49 +11881,49 @@
     </row>
     <row r="5" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="57" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>621</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D5" s="57" t="s">
         <v>622</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>614</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>623</v>
-      </c>
       <c r="E5" s="57" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G5" s="57" t="s">
         <v>227</v>
       </c>
       <c r="H5" s="57" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I5" s="57" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J5" s="57" t="s">
         <v>231</v>
       </c>
       <c r="K5" s="57" t="s">
+        <v>624</v>
+      </c>
+      <c r="L5" s="57" t="s">
+        <v>620</v>
+      </c>
+      <c r="M5" s="57" t="s">
+        <v>616</v>
+      </c>
+      <c r="N5" s="57" t="s">
+        <v>619</v>
+      </c>
+      <c r="O5" s="57" t="s">
         <v>625</v>
-      </c>
-      <c r="L5" s="57" t="s">
-        <v>621</v>
-      </c>
-      <c r="M5" s="57" t="s">
-        <v>617</v>
-      </c>
-      <c r="N5" s="57" t="s">
-        <v>620</v>
-      </c>
-      <c r="O5" s="57" t="s">
-        <v>626</v>
       </c>
       <c r="P5" s="41">
         <v>0</v>
@@ -11981,34 +11982,34 @@
         <v>135</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>622</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>615</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>623</v>
+      </c>
+      <c r="G6" s="57" t="s">
         <v>614</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>623</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>616</v>
-      </c>
-      <c r="F6" s="57" t="s">
-        <v>624</v>
-      </c>
-      <c r="G6" s="57" t="s">
-        <v>615</v>
       </c>
       <c r="H6" s="57" t="s">
         <v>231</v>
       </c>
       <c r="I6" s="57" t="s">
+        <v>624</v>
+      </c>
+      <c r="J6" s="57" t="s">
+        <v>616</v>
+      </c>
+      <c r="K6" s="57" t="s">
         <v>625</v>
-      </c>
-      <c r="J6" s="57" t="s">
-        <v>617</v>
-      </c>
-      <c r="K6" s="57" t="s">
-        <v>626</v>
       </c>
       <c r="L6" s="41">
         <v>0</v>
@@ -12079,10 +12080,10 @@
         <v>285</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D7" s="57" t="s">
         <v>231</v>
@@ -12177,16 +12178,16 @@
         <v>257</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E8" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F8" s="41">
         <v>0</v>
@@ -12275,19 +12276,19 @@
         <v>243</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E9" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G9" s="41">
         <v>0</v>
@@ -12373,22 +12374,22 @@
         <v>235</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D10" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E10" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G10" s="57" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H10" s="41">
         <v>0</v>
@@ -12471,28 +12472,28 @@
         <v>230</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D11" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H11" s="57" t="s">
         <v>226</v>
       </c>
       <c r="I11" s="57" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J11" s="41">
         <v>0</v>
@@ -12569,25 +12570,25 @@
         <v>228</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D12" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E12" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F12" s="57" t="s">
         <v>227</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H12" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I12" s="41">
         <v>0</v>
@@ -12667,28 +12668,28 @@
         <v>241</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D13" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E13" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F13" s="57" t="s">
         <v>227</v>
       </c>
       <c r="G13" s="57" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H13" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I13" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J13" s="41">
         <v>0</v>
@@ -12765,10 +12766,10 @@
         <v>262</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D14" s="57" t="s">
         <v>227</v>
@@ -12777,22 +12778,22 @@
         <v>232</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G14" s="57" t="s">
         <v>231</v>
       </c>
       <c r="H14" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I14" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J14" s="57" t="s">
+        <v>639</v>
+      </c>
+      <c r="K14" s="57" t="s">
         <v>640</v>
-      </c>
-      <c r="K14" s="57" t="s">
-        <v>641</v>
       </c>
       <c r="L14" s="41">
         <v>0</v>
@@ -12863,22 +12864,22 @@
         <v>238</v>
       </c>
       <c r="B15" s="57" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D15" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E15" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F15" s="57" t="s">
         <v>227</v>
       </c>
       <c r="G15" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H15" s="41">
         <v>0</v>
@@ -12961,10 +12962,10 @@
         <v>246</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D16" s="57" t="s">
         <v>227</v>
@@ -12976,16 +12977,16 @@
         <v>231</v>
       </c>
       <c r="G16" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H16" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="I16" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J16" s="57" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K16" s="41">
         <v>0</v>
@@ -13059,16 +13060,16 @@
         <v>233</v>
       </c>
       <c r="B17" s="57" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D17" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F17" s="57" t="s">
         <v>227</v>
@@ -13077,10 +13078,10 @@
         <v>232</v>
       </c>
       <c r="H17" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I17" s="57" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J17" s="41">
         <v>0</v>
@@ -13157,10 +13158,10 @@
         <v>248</v>
       </c>
       <c r="B18" s="57" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D18" s="57" t="s">
         <v>227</v>
@@ -13169,25 +13170,25 @@
         <v>232</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G18" s="57" t="s">
         <v>231</v>
       </c>
       <c r="H18" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I18" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="J18" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K18" s="57" t="s">
+        <v>639</v>
+      </c>
+      <c r="L18" s="57" t="s">
         <v>640</v>
-      </c>
-      <c r="L18" s="57" t="s">
-        <v>641</v>
       </c>
       <c r="M18" s="41">
         <v>0</v>
@@ -13255,25 +13256,25 @@
         <v>250</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D19" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E19" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F19" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G19" s="57" t="s">
         <v>232</v>
       </c>
       <c r="H19" s="57" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I19" s="41">
         <v>0</v>
@@ -13353,10 +13354,10 @@
         <v>268</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D20" s="41">
         <v>0</v>
@@ -13451,22 +13452,22 @@
         <v>306</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D21" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E21" s="57" t="s">
         <v>231</v>
       </c>
       <c r="F21" s="57" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G21" s="57" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H21" s="41">
         <v>0</v>
@@ -13546,37 +13547,37 @@
     </row>
     <row r="22" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="57" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B22" s="57" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D22" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E22" s="57" t="s">
+        <v>614</v>
+      </c>
+      <c r="F22" s="57" t="s">
         <v>615</v>
       </c>
-      <c r="F22" s="57" t="s">
+      <c r="G22" s="57" t="s">
         <v>616</v>
       </c>
-      <c r="G22" s="57" t="s">
-        <v>617</v>
-      </c>
       <c r="H22" s="57" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I22" s="57" t="s">
         <v>227</v>
       </c>
       <c r="J22" s="57" t="s">
+        <v>619</v>
+      </c>
+      <c r="K22" s="57" t="s">
         <v>620</v>
-      </c>
-      <c r="K22" s="57" t="s">
-        <v>621</v>
       </c>
       <c r="L22" s="41">
         <v>0</v>
@@ -13644,25 +13645,25 @@
     </row>
     <row r="23" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="57" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D23" s="73" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E23" s="73" t="s">
         <v>1297</v>
       </c>
-      <c r="E23" s="73" t="s">
+      <c r="F23" s="73" t="s">
         <v>1298</v>
       </c>
-      <c r="F23" s="73" t="s">
+      <c r="G23" s="73" t="s">
         <v>1299</v>
-      </c>
-      <c r="G23" s="73" t="s">
-        <v>1300</v>
       </c>
       <c r="H23" s="41">
         <v>0</v>
@@ -13742,22 +13743,22 @@
     </row>
     <row r="24" spans="1:32">
       <c r="A24" s="57" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B24" s="73" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D24" s="73" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E24" s="73" t="s">
         <v>1296</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>614</v>
-      </c>
-      <c r="D24" s="73" t="s">
-        <v>1304</v>
-      </c>
-      <c r="E24" s="73" t="s">
-        <v>1297</v>
-      </c>
       <c r="F24" s="73" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="G24" s="41">
         <v>0</v>
@@ -13840,85 +13841,85 @@
     </row>
     <row r="25" spans="1:32">
       <c r="A25" s="57" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B25" s="57" t="s">
         <v>1323</v>
       </c>
-      <c r="B25" s="57" t="s">
+      <c r="C25" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D25" s="57" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E25" s="57" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F25" s="57" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G25" s="57" t="s">
+        <v>1329</v>
+      </c>
+      <c r="H25" s="57" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I25" s="57" t="s">
+        <v>1326</v>
+      </c>
+      <c r="J25" s="57" t="s">
+        <v>1331</v>
+      </c>
+      <c r="K25" s="57" t="s">
+        <v>1332</v>
+      </c>
+      <c r="L25" s="57" t="s">
+        <v>1333</v>
+      </c>
+      <c r="M25" s="57" t="s">
+        <v>1334</v>
+      </c>
+      <c r="N25" s="57" t="s">
+        <v>1335</v>
+      </c>
+      <c r="O25" s="57" t="s">
+        <v>1336</v>
+      </c>
+      <c r="P25" s="57" t="s">
+        <v>1337</v>
+      </c>
+      <c r="Q25" s="57" t="s">
+        <v>1338</v>
+      </c>
+      <c r="R25" s="57" t="s">
+        <v>1339</v>
+      </c>
+      <c r="S25" s="57" t="s">
+        <v>1340</v>
+      </c>
+      <c r="T25" s="57" t="s">
+        <v>1341</v>
+      </c>
+      <c r="U25" s="57" t="s">
+        <v>1342</v>
+      </c>
+      <c r="V25" s="57" t="s">
+        <v>1343</v>
+      </c>
+      <c r="W25" s="57" t="s">
         <v>1324</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>614</v>
-      </c>
-      <c r="D25" s="57" t="s">
-        <v>1326</v>
-      </c>
-      <c r="E25" s="57" t="s">
-        <v>1328</v>
-      </c>
-      <c r="F25" s="57" t="s">
-        <v>1329</v>
-      </c>
-      <c r="G25" s="57" t="s">
-        <v>1330</v>
-      </c>
-      <c r="H25" s="57" t="s">
-        <v>1331</v>
-      </c>
-      <c r="I25" s="57" t="s">
-        <v>1327</v>
-      </c>
-      <c r="J25" s="57" t="s">
-        <v>1332</v>
-      </c>
-      <c r="K25" s="57" t="s">
-        <v>1333</v>
-      </c>
-      <c r="L25" s="57" t="s">
-        <v>1334</v>
-      </c>
-      <c r="M25" s="57" t="s">
-        <v>1335</v>
-      </c>
-      <c r="N25" s="57" t="s">
-        <v>1336</v>
-      </c>
-      <c r="O25" s="57" t="s">
-        <v>1337</v>
-      </c>
-      <c r="P25" s="57" t="s">
-        <v>1338</v>
-      </c>
-      <c r="Q25" s="57" t="s">
-        <v>1339</v>
-      </c>
-      <c r="R25" s="57" t="s">
-        <v>1340</v>
-      </c>
-      <c r="S25" s="57" t="s">
-        <v>1341</v>
-      </c>
-      <c r="T25" s="57" t="s">
-        <v>1342</v>
-      </c>
-      <c r="U25" s="57" t="s">
-        <v>1343</v>
-      </c>
-      <c r="V25" s="57" t="s">
+      <c r="X25" s="57" t="s">
         <v>1344</v>
       </c>
-      <c r="W25" s="57" t="s">
-        <v>1325</v>
-      </c>
-      <c r="X25" s="57" t="s">
+      <c r="Y25" s="57" t="s">
         <v>1345</v>
       </c>
-      <c r="Y25" s="57" t="s">
+      <c r="Z25" s="57" t="s">
         <v>1346</v>
       </c>
-      <c r="Z25" s="57" t="s">
+      <c r="AA25" s="57" t="s">
         <v>1347</v>
-      </c>
-      <c r="AA25" s="57" t="s">
-        <v>1348</v>
       </c>
       <c r="AB25" s="57">
         <v>0</v>
@@ -13944,7 +13945,7 @@
         <v>399</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D26" s="41">
         <v>0</v>
@@ -14036,13 +14037,13 @@
     </row>
     <row r="27" spans="1:32">
       <c r="A27" s="57" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B27" s="73" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C27" s="73" t="s">
         <v>1268</v>
-      </c>
-      <c r="C27" s="73" t="s">
-        <v>1269</v>
       </c>
       <c r="D27" s="41">
         <v>0</v>
@@ -14134,13 +14135,13 @@
     </row>
     <row r="28" spans="1:32">
       <c r="A28" s="57" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B28" s="73" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C28" s="73" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D28" s="41">
         <v>0</v>
@@ -14232,25 +14233,25 @@
     </row>
     <row r="29" spans="1:32">
       <c r="A29" s="57" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B29" s="57" t="s">
+        <v>612</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>613</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>614</v>
       </c>
       <c r="D29" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E29" s="57" t="s">
+        <v>614</v>
+      </c>
+      <c r="F29" s="57" t="s">
         <v>615</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="G29" s="57" t="s">
         <v>616</v>
-      </c>
-      <c r="G29" s="57" t="s">
-        <v>617</v>
       </c>
       <c r="H29" s="41">
         <v>0</v>
@@ -14330,37 +14331,37 @@
     </row>
     <row r="30" spans="1:32">
       <c r="A30" s="57" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B30" s="57" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D30" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E30" s="57" t="s">
+        <v>614</v>
+      </c>
+      <c r="F30" s="57" t="s">
         <v>615</v>
       </c>
-      <c r="F30" s="57" t="s">
+      <c r="G30" s="57" t="s">
         <v>616</v>
       </c>
-      <c r="G30" s="57" t="s">
-        <v>617</v>
-      </c>
       <c r="H30" s="57" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I30" s="57" t="s">
         <v>227</v>
       </c>
       <c r="J30" s="57" t="s">
+        <v>619</v>
+      </c>
+      <c r="K30" s="57" t="s">
         <v>620</v>
-      </c>
-      <c r="K30" s="57" t="s">
-        <v>621</v>
       </c>
       <c r="L30" s="41">
         <v>0</v>
@@ -14428,49 +14429,49 @@
     </row>
     <row r="31" spans="1:32">
       <c r="A31" s="57" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B31" s="57" t="s">
+        <v>621</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D31" s="57" t="s">
         <v>622</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>614</v>
-      </c>
-      <c r="D31" s="57" t="s">
-        <v>623</v>
-      </c>
       <c r="E31" s="57" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F31" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G31" s="57" t="s">
         <v>227</v>
       </c>
       <c r="H31" s="57" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I31" s="57" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J31" s="57" t="s">
         <v>231</v>
       </c>
       <c r="K31" s="57" t="s">
+        <v>624</v>
+      </c>
+      <c r="L31" s="57" t="s">
+        <v>620</v>
+      </c>
+      <c r="M31" s="57" t="s">
+        <v>616</v>
+      </c>
+      <c r="N31" s="57" t="s">
+        <v>619</v>
+      </c>
+      <c r="O31" s="57" t="s">
         <v>625</v>
-      </c>
-      <c r="L31" s="57" t="s">
-        <v>621</v>
-      </c>
-      <c r="M31" s="57" t="s">
-        <v>617</v>
-      </c>
-      <c r="N31" s="57" t="s">
-        <v>620</v>
-      </c>
-      <c r="O31" s="57" t="s">
-        <v>626</v>
       </c>
       <c r="P31" s="41">
         <v>0</v>
@@ -14526,37 +14527,37 @@
     </row>
     <row r="32" spans="1:32">
       <c r="A32" s="57" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B32" s="57" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D32" s="57" t="s">
+        <v>622</v>
+      </c>
+      <c r="E32" s="57" t="s">
+        <v>615</v>
+      </c>
+      <c r="F32" s="57" t="s">
+        <v>623</v>
+      </c>
+      <c r="G32" s="57" t="s">
         <v>614</v>
-      </c>
-      <c r="D32" s="57" t="s">
-        <v>623</v>
-      </c>
-      <c r="E32" s="57" t="s">
-        <v>616</v>
-      </c>
-      <c r="F32" s="57" t="s">
-        <v>624</v>
-      </c>
-      <c r="G32" s="57" t="s">
-        <v>615</v>
       </c>
       <c r="H32" s="57" t="s">
         <v>231</v>
       </c>
       <c r="I32" s="57" t="s">
+        <v>624</v>
+      </c>
+      <c r="J32" s="57" t="s">
+        <v>616</v>
+      </c>
+      <c r="K32" s="57" t="s">
         <v>625</v>
-      </c>
-      <c r="J32" s="57" t="s">
-        <v>617</v>
-      </c>
-      <c r="K32" s="57" t="s">
-        <v>626</v>
       </c>
       <c r="L32" s="41">
         <v>0</v>
@@ -14624,13 +14625,13 @@
     </row>
     <row r="33" spans="1:32">
       <c r="A33" s="57" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B33" s="57" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D33" s="57" t="s">
         <v>231</v>
@@ -14722,19 +14723,19 @@
     </row>
     <row r="34" spans="1:32">
       <c r="A34" s="57" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B34" s="57" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D34" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E34" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F34" s="41">
         <v>0</v>
@@ -14820,22 +14821,22 @@
     </row>
     <row r="35" spans="1:32">
       <c r="A35" s="57" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B35" s="57" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D35" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E35" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F35" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G35" s="41">
         <v>0</v>
@@ -14918,25 +14919,25 @@
     </row>
     <row r="36" spans="1:32">
       <c r="A36" s="57" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B36" s="57" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D36" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E36" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F36" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G36" s="57" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H36" s="41">
         <v>0</v>
@@ -15016,31 +15017,31 @@
     </row>
     <row r="37" spans="1:32">
       <c r="A37" s="57" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B37" s="57" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D37" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E37" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F37" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G37" s="57" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H37" s="57" t="s">
         <v>226</v>
       </c>
       <c r="I37" s="57" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J37" s="41">
         <v>0</v>
@@ -15114,28 +15115,28 @@
     </row>
     <row r="38" spans="1:32">
       <c r="A38" s="57" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B38" s="57" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D38" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E38" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F38" s="57" t="s">
         <v>227</v>
       </c>
       <c r="G38" s="57" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H38" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I38" s="41">
         <v>0</v>
@@ -15212,31 +15213,31 @@
     </row>
     <row r="39" spans="1:32">
       <c r="A39" s="57" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B39" s="57" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D39" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E39" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F39" s="57" t="s">
         <v>227</v>
       </c>
       <c r="G39" s="57" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H39" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I39" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J39" s="41">
         <v>0</v>
@@ -15310,13 +15311,13 @@
     </row>
     <row r="40" spans="1:32">
       <c r="A40" s="57" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B40" s="57" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D40" s="57" t="s">
         <v>227</v>
@@ -15325,22 +15326,22 @@
         <v>232</v>
       </c>
       <c r="F40" s="57" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G40" s="57" t="s">
         <v>231</v>
       </c>
       <c r="H40" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I40" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J40" s="57" t="s">
+        <v>639</v>
+      </c>
+      <c r="K40" s="57" t="s">
         <v>640</v>
-      </c>
-      <c r="K40" s="57" t="s">
-        <v>641</v>
       </c>
       <c r="L40" s="41">
         <v>0</v>
@@ -15408,25 +15409,25 @@
     </row>
     <row r="41" spans="1:32">
       <c r="A41" s="57" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B41" s="57" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D41" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E41" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F41" s="57" t="s">
         <v>227</v>
       </c>
       <c r="G41" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H41" s="41">
         <v>0</v>
@@ -15506,13 +15507,13 @@
     </row>
     <row r="42" spans="1:32">
       <c r="A42" s="57" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B42" s="57" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D42" s="57" t="s">
         <v>227</v>
@@ -15524,16 +15525,16 @@
         <v>231</v>
       </c>
       <c r="G42" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H42" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="I42" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J42" s="57" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K42" s="41">
         <v>0</v>
@@ -15604,19 +15605,19 @@
     </row>
     <row r="43" spans="1:32">
       <c r="A43" s="57" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B43" s="57" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D43" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E43" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F43" s="57" t="s">
         <v>227</v>
@@ -15625,10 +15626,10 @@
         <v>232</v>
       </c>
       <c r="H43" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I43" s="57" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J43" s="41">
         <v>0</v>
@@ -15702,13 +15703,13 @@
     </row>
     <row r="44" spans="1:32">
       <c r="A44" s="57" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B44" s="57" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D44" s="57" t="s">
         <v>227</v>
@@ -15717,25 +15718,25 @@
         <v>232</v>
       </c>
       <c r="F44" s="57" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G44" s="57" t="s">
         <v>231</v>
       </c>
       <c r="H44" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I44" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="J44" s="57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K44" s="57" t="s">
+        <v>639</v>
+      </c>
+      <c r="L44" s="57" t="s">
         <v>640</v>
-      </c>
-      <c r="L44" s="57" t="s">
-        <v>641</v>
       </c>
       <c r="M44" s="41">
         <v>0</v>
@@ -15800,28 +15801,28 @@
     </row>
     <row r="45" spans="1:32">
       <c r="A45" s="57" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B45" s="57" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D45" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E45" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F45" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G45" s="57" t="s">
         <v>232</v>
       </c>
       <c r="H45" s="57" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I45" s="41">
         <v>0</v>
@@ -15898,16 +15899,16 @@
     </row>
     <row r="46" spans="1:32">
       <c r="A46" s="57" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B46" s="57" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D46" s="57" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E46" s="41">
         <v>0</v>
@@ -15996,25 +15997,25 @@
     </row>
     <row r="47" spans="1:32">
       <c r="A47" s="57" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B47" s="57" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D47" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E47" s="57" t="s">
         <v>231</v>
       </c>
       <c r="F47" s="57" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G47" s="57" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H47" s="41">
         <v>0</v>
@@ -16094,37 +16095,37 @@
     </row>
     <row r="48" spans="1:32">
       <c r="A48" s="57" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B48" s="57" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D48" s="57" t="s">
         <v>231</v>
       </c>
       <c r="E48" s="57" t="s">
+        <v>614</v>
+      </c>
+      <c r="F48" s="57" t="s">
         <v>615</v>
       </c>
-      <c r="F48" s="57" t="s">
+      <c r="G48" s="57" t="s">
         <v>616</v>
       </c>
-      <c r="G48" s="57" t="s">
-        <v>617</v>
-      </c>
       <c r="H48" s="57" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I48" s="57" t="s">
         <v>227</v>
       </c>
       <c r="J48" s="57" t="s">
+        <v>619</v>
+      </c>
+      <c r="K48" s="57" t="s">
         <v>620</v>
-      </c>
-      <c r="K48" s="57" t="s">
-        <v>621</v>
       </c>
       <c r="L48" s="41">
         <v>0</v>
@@ -16192,25 +16193,25 @@
     </row>
     <row r="49" spans="1:32">
       <c r="A49" s="57" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B49" s="57" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D49" s="73" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E49" s="73" t="s">
         <v>1297</v>
       </c>
-      <c r="E49" s="73" t="s">
+      <c r="F49" s="73" t="s">
         <v>1298</v>
       </c>
-      <c r="F49" s="73" t="s">
+      <c r="G49" s="73" t="s">
         <v>1299</v>
-      </c>
-      <c r="G49" s="73" t="s">
-        <v>1300</v>
       </c>
       <c r="H49" s="41">
         <v>0</v>
@@ -16290,22 +16291,22 @@
     </row>
     <row r="50" spans="1:32">
       <c r="A50" s="57" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B50" s="73" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D50" s="73" t="s">
         <v>1303</v>
       </c>
-      <c r="B50" s="73" t="s">
+      <c r="E50" s="73" t="s">
         <v>1296</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>614</v>
-      </c>
-      <c r="D50" s="73" t="s">
-        <v>1304</v>
-      </c>
-      <c r="E50" s="73" t="s">
-        <v>1297</v>
-      </c>
       <c r="F50" s="73" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="G50" s="41">
         <v>0</v>
@@ -16388,85 +16389,85 @@
     </row>
     <row r="51" spans="1:32">
       <c r="A51" s="57" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B51" s="57" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D51" s="57" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E51" s="57" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F51" s="57" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G51" s="57" t="s">
+        <v>1329</v>
+      </c>
+      <c r="H51" s="57" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I51" s="57" t="s">
+        <v>1326</v>
+      </c>
+      <c r="J51" s="57" t="s">
+        <v>1331</v>
+      </c>
+      <c r="K51" s="57" t="s">
+        <v>1332</v>
+      </c>
+      <c r="L51" s="57" t="s">
+        <v>1333</v>
+      </c>
+      <c r="M51" s="57" t="s">
+        <v>1334</v>
+      </c>
+      <c r="N51" s="57" t="s">
+        <v>1335</v>
+      </c>
+      <c r="O51" s="57" t="s">
+        <v>1336</v>
+      </c>
+      <c r="P51" s="57" t="s">
+        <v>1337</v>
+      </c>
+      <c r="Q51" s="57" t="s">
+        <v>1338</v>
+      </c>
+      <c r="R51" s="57" t="s">
+        <v>1339</v>
+      </c>
+      <c r="S51" s="57" t="s">
+        <v>1340</v>
+      </c>
+      <c r="T51" s="57" t="s">
+        <v>1341</v>
+      </c>
+      <c r="U51" s="57" t="s">
+        <v>1342</v>
+      </c>
+      <c r="V51" s="57" t="s">
+        <v>1343</v>
+      </c>
+      <c r="W51" s="57" t="s">
         <v>1324</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>614</v>
-      </c>
-      <c r="D51" s="57" t="s">
-        <v>1326</v>
-      </c>
-      <c r="E51" s="57" t="s">
-        <v>1328</v>
-      </c>
-      <c r="F51" s="57" t="s">
-        <v>1329</v>
-      </c>
-      <c r="G51" s="57" t="s">
-        <v>1330</v>
-      </c>
-      <c r="H51" s="57" t="s">
-        <v>1331</v>
-      </c>
-      <c r="I51" s="57" t="s">
-        <v>1327</v>
-      </c>
-      <c r="J51" s="57" t="s">
-        <v>1332</v>
-      </c>
-      <c r="K51" s="57" t="s">
-        <v>1333</v>
-      </c>
-      <c r="L51" s="57" t="s">
-        <v>1334</v>
-      </c>
-      <c r="M51" s="57" t="s">
-        <v>1335</v>
-      </c>
-      <c r="N51" s="57" t="s">
-        <v>1336</v>
-      </c>
-      <c r="O51" s="57" t="s">
-        <v>1337</v>
-      </c>
-      <c r="P51" s="57" t="s">
-        <v>1338</v>
-      </c>
-      <c r="Q51" s="57" t="s">
-        <v>1339</v>
-      </c>
-      <c r="R51" s="57" t="s">
-        <v>1340</v>
-      </c>
-      <c r="S51" s="57" t="s">
-        <v>1341</v>
-      </c>
-      <c r="T51" s="57" t="s">
-        <v>1342</v>
-      </c>
-      <c r="U51" s="57" t="s">
-        <v>1343</v>
-      </c>
-      <c r="V51" s="57" t="s">
+      <c r="X51" s="57" t="s">
         <v>1344</v>
       </c>
-      <c r="W51" s="57" t="s">
-        <v>1325</v>
-      </c>
-      <c r="X51" s="57" t="s">
+      <c r="Y51" s="57" t="s">
         <v>1345</v>
       </c>
-      <c r="Y51" s="57" t="s">
+      <c r="Z51" s="57" t="s">
         <v>1346</v>
       </c>
-      <c r="Z51" s="57" t="s">
+      <c r="AA51" s="57" t="s">
         <v>1347</v>
-      </c>
-      <c r="AA51" s="57" t="s">
-        <v>1348</v>
       </c>
       <c r="AB51" s="57">
         <v>0</v>
@@ -16506,7 +16507,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -16524,10 +16525,10 @@
         <v>181</v>
       </c>
       <c r="G1" s="53" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1" s="53" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>299</v>
@@ -16538,7 +16539,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>25</v>
@@ -16556,10 +16557,10 @@
         <v>197</v>
       </c>
       <c r="G2" s="53" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2" s="53" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>302</v>
@@ -16570,10 +16571,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>652</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>653</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>367</v>
@@ -16588,24 +16589,24 @@
         <v>1</v>
       </c>
       <c r="G3" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H3" s="7">
         <v>0</v>
       </c>
       <c r="I3" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>654</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>656</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>657</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>367</v>
@@ -16620,13 +16621,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H4" s="7">
         <v>0</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>511</v>
@@ -16634,10 +16635,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>659</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>660</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>367</v>
@@ -16652,13 +16653,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H5" s="7">
         <v>0</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>133</v>
@@ -16666,10 +16667,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>662</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>663</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>367</v>
@@ -16684,13 +16685,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H6" s="7">
         <v>0</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>133</v>
@@ -16698,10 +16699,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>665</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>666</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>367</v>
@@ -16716,24 +16717,24 @@
         <v>1</v>
       </c>
       <c r="G7" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H7" s="7">
         <v>0</v>
       </c>
       <c r="I7" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>667</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>669</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>670</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>367</v>
@@ -16748,24 +16749,24 @@
         <v>1</v>
       </c>
       <c r="G8" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H8" s="7">
         <v>0</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>672</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>673</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>367</v>
@@ -16780,24 +16781,24 @@
         <v>1</v>
       </c>
       <c r="G9" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H9" s="7">
         <v>0</v>
       </c>
       <c r="I9" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>674</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>676</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>677</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>367</v>
@@ -16812,24 +16813,24 @@
         <v>1</v>
       </c>
       <c r="G10" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H10" s="7">
         <v>0</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>679</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>680</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>367</v>
@@ -16844,13 +16845,13 @@
         <v>1</v>
       </c>
       <c r="G11" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H11" s="7">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>219</v>
@@ -16858,10 +16859,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>682</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>683</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>367</v>
@@ -16876,13 +16877,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="54" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H12" s="7">
         <v>0</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>219</v>
@@ -16890,10 +16891,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="32" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>367</v>
@@ -16908,24 +16909,24 @@
         <v>1</v>
       </c>
       <c r="G13" s="54" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H13" s="7">
         <v>1</v>
       </c>
       <c r="I13" s="54" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="32" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>367</v>
@@ -16940,24 +16941,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="54" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H14" s="7">
         <v>2</v>
       </c>
       <c r="I14" s="54" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="32" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>367</v>
@@ -16972,24 +16973,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="54" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H15" s="7">
         <v>3</v>
       </c>
       <c r="I15" s="54" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="32" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>367</v>
@@ -17004,24 +17005,24 @@
         <v>1</v>
       </c>
       <c r="G16" s="54" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H16" s="7">
         <v>5</v>
       </c>
       <c r="I16" s="54" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="32" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>367</v>
@@ -17036,13 +17037,13 @@
         <v>1</v>
       </c>
       <c r="G17" s="54" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
       </c>
       <c r="I17" s="54" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>219</v>
@@ -17072,19 +17073,19 @@
   <sh